--- a/data/raw/문제_LAW.xlsx
+++ b/data/raw/문제_LAW.xlsx
@@ -725,7 +725,7 @@
       </c>
       <c r="K2" s="3" t="inlineStr">
         <is>
-          <t>2026-01-01</t>
+          <t>2026-10-20</t>
         </is>
       </c>
       <c r="L2" s="3" t="inlineStr">
@@ -739,10 +739,14 @@
       <c r="N2" s="3" t="n"/>
       <c r="O2" s="3" t="inlineStr">
         <is>
-          <t>draft</t>
-        </is>
-      </c>
-      <c r="P2" s="3" t="n"/>
+          <t>verified</t>
+        </is>
+      </c>
+      <c r="P2" s="3" t="inlineStr">
+        <is>
+          <t>1등 / 2026-10-20</t>
+        </is>
+      </c>
       <c r="Q2" s="3" t="inlineStr">
         <is>
           <t>AI 초안(2026-10-19) · 근거 확인 ○: 법률 원문(2026.1.1 시행판, 국가법령정보센터)에서 확인</t>
@@ -800,7 +804,7 @@
       </c>
       <c r="K3" s="3" t="inlineStr">
         <is>
-          <t>2026-01-01</t>
+          <t>2026-10-20</t>
         </is>
       </c>
       <c r="L3" s="3" t="inlineStr">
@@ -814,10 +818,14 @@
       <c r="N3" s="3" t="n"/>
       <c r="O3" s="3" t="inlineStr">
         <is>
-          <t>draft</t>
-        </is>
-      </c>
-      <c r="P3" s="3" t="n"/>
+          <t>verified</t>
+        </is>
+      </c>
+      <c r="P3" s="3" t="inlineStr">
+        <is>
+          <t>1등 / 2026-10-20</t>
+        </is>
+      </c>
       <c r="Q3" s="3" t="inlineStr">
         <is>
           <t>AI 초안(2026-10-19) · 근거 확인 ○: 법률 원문(2026.1.1 시행판, 국가법령정보센터)에서 확인</t>
@@ -875,7 +883,7 @@
       </c>
       <c r="K4" s="3" t="inlineStr">
         <is>
-          <t>2026-01-01</t>
+          <t>2026-10-20</t>
         </is>
       </c>
       <c r="L4" s="3" t="inlineStr">
@@ -889,10 +897,14 @@
       <c r="N4" s="3" t="n"/>
       <c r="O4" s="3" t="inlineStr">
         <is>
-          <t>draft</t>
-        </is>
-      </c>
-      <c r="P4" s="3" t="n"/>
+          <t>verified</t>
+        </is>
+      </c>
+      <c r="P4" s="3" t="inlineStr">
+        <is>
+          <t>1등 / 2026-10-20</t>
+        </is>
+      </c>
       <c r="Q4" s="3" t="inlineStr">
         <is>
           <t>AI 초안(2026-10-19) · 근거 확인 ○: 법률 원문(2026.1.1 시행판, 국가법령정보센터)에서 확인</t>
@@ -950,7 +962,7 @@
       </c>
       <c r="K5" s="3" t="inlineStr">
         <is>
-          <t>2026-01-01</t>
+          <t>2026-10-20</t>
         </is>
       </c>
       <c r="L5" s="3" t="inlineStr">
@@ -964,10 +976,14 @@
       <c r="N5" s="3" t="n"/>
       <c r="O5" s="3" t="inlineStr">
         <is>
-          <t>draft</t>
-        </is>
-      </c>
-      <c r="P5" s="3" t="n"/>
+          <t>verified</t>
+        </is>
+      </c>
+      <c r="P5" s="3" t="inlineStr">
+        <is>
+          <t>1등 / 2026-10-20</t>
+        </is>
+      </c>
       <c r="Q5" s="3" t="inlineStr">
         <is>
           <t>AI 초안(2026-10-19) · 근거 확인 ○: 법률 원문(2026.1.1 시행판, 국가법령정보센터)에서 확인</t>
@@ -1025,7 +1041,7 @@
       </c>
       <c r="K6" s="3" t="inlineStr">
         <is>
-          <t>2026-01-01</t>
+          <t>2026-10-20</t>
         </is>
       </c>
       <c r="L6" s="3" t="inlineStr">
@@ -1039,10 +1055,14 @@
       <c r="N6" s="3" t="n"/>
       <c r="O6" s="3" t="inlineStr">
         <is>
-          <t>draft</t>
-        </is>
-      </c>
-      <c r="P6" s="3" t="n"/>
+          <t>verified</t>
+        </is>
+      </c>
+      <c r="P6" s="3" t="inlineStr">
+        <is>
+          <t>1등 / 2026-10-20</t>
+        </is>
+      </c>
       <c r="Q6" s="3" t="inlineStr">
         <is>
           <t>AI 초안(2026-10-19) · 근거 확인 ○: 법률 원문(2026.1.1 시행판, 국가법령정보센터)에서 확인</t>
@@ -1100,7 +1120,7 @@
       </c>
       <c r="K7" s="3" t="inlineStr">
         <is>
-          <t>2026-01-01</t>
+          <t>2026-10-20</t>
         </is>
       </c>
       <c r="L7" s="3" t="inlineStr">
@@ -1114,10 +1134,14 @@
       <c r="N7" s="3" t="n"/>
       <c r="O7" s="3" t="inlineStr">
         <is>
-          <t>draft</t>
-        </is>
-      </c>
-      <c r="P7" s="3" t="n"/>
+          <t>verified</t>
+        </is>
+      </c>
+      <c r="P7" s="3" t="inlineStr">
+        <is>
+          <t>1등 / 2026-10-20</t>
+        </is>
+      </c>
       <c r="Q7" s="3" t="inlineStr">
         <is>
           <t>AI 초안(2026-10-19) · 근거 확인 ○: 법률 원문(2026.1.1 시행판, 국가법령정보센터)에서 확인</t>
@@ -1175,7 +1199,7 @@
       </c>
       <c r="K8" s="3" t="inlineStr">
         <is>
-          <t>2026-01-01</t>
+          <t>2026-10-20</t>
         </is>
       </c>
       <c r="L8" s="3" t="inlineStr">
@@ -1189,10 +1213,14 @@
       <c r="N8" s="3" t="n"/>
       <c r="O8" s="3" t="inlineStr">
         <is>
-          <t>draft</t>
-        </is>
-      </c>
-      <c r="P8" s="3" t="n"/>
+          <t>verified</t>
+        </is>
+      </c>
+      <c r="P8" s="3" t="inlineStr">
+        <is>
+          <t>1등 / 2026-10-20</t>
+        </is>
+      </c>
       <c r="Q8" s="3" t="inlineStr">
         <is>
           <t>AI 초안(2026-10-19) · 근거 확인 ○: 법률 원문(2026.1.1 시행판, 국가법령정보센터)에서 확인</t>
@@ -1250,7 +1278,7 @@
       </c>
       <c r="K9" s="3" t="inlineStr">
         <is>
-          <t>2026-01-01</t>
+          <t>2026-10-20</t>
         </is>
       </c>
       <c r="L9" s="3" t="inlineStr">
@@ -1264,10 +1292,14 @@
       <c r="N9" s="3" t="n"/>
       <c r="O9" s="3" t="inlineStr">
         <is>
-          <t>draft</t>
-        </is>
-      </c>
-      <c r="P9" s="3" t="n"/>
+          <t>verified</t>
+        </is>
+      </c>
+      <c r="P9" s="3" t="inlineStr">
+        <is>
+          <t>1등 / 2026-10-20</t>
+        </is>
+      </c>
       <c r="Q9" s="3" t="inlineStr">
         <is>
           <t>AI 초안(2026-10-19) · 근거 확인 ○: 법률 원문(2026.1.1 시행판, 국가법령정보센터)에서 확인</t>
@@ -1325,7 +1357,7 @@
       </c>
       <c r="K10" s="3" t="inlineStr">
         <is>
-          <t>2026-01-01</t>
+          <t>2026-10-20</t>
         </is>
       </c>
       <c r="L10" s="3" t="inlineStr">
@@ -1339,10 +1371,14 @@
       <c r="N10" s="3" t="n"/>
       <c r="O10" s="3" t="inlineStr">
         <is>
-          <t>draft</t>
-        </is>
-      </c>
-      <c r="P10" s="3" t="n"/>
+          <t>verified</t>
+        </is>
+      </c>
+      <c r="P10" s="3" t="inlineStr">
+        <is>
+          <t>1등 / 2026-10-20</t>
+        </is>
+      </c>
       <c r="Q10" s="3" t="inlineStr">
         <is>
           <t>AI 초안(2026-10-19) · 근거 확인 ○: 법률 원문(2026.1.1 시행판, 국가법령정보센터)에서 확인</t>
@@ -1400,7 +1436,7 @@
       </c>
       <c r="K11" s="3" t="inlineStr">
         <is>
-          <t>2026-01-01</t>
+          <t>2026-10-20</t>
         </is>
       </c>
       <c r="L11" s="3" t="inlineStr">
@@ -1414,10 +1450,14 @@
       <c r="N11" s="3" t="n"/>
       <c r="O11" s="3" t="inlineStr">
         <is>
-          <t>draft</t>
-        </is>
-      </c>
-      <c r="P11" s="3" t="n"/>
+          <t>verified</t>
+        </is>
+      </c>
+      <c r="P11" s="3" t="inlineStr">
+        <is>
+          <t>1등 / 2026-10-20</t>
+        </is>
+      </c>
       <c r="Q11" s="3" t="inlineStr">
         <is>
           <t>AI 초안(2026-10-19) · 근거 확인 ○: 법률 원문(2026.1.1 시행판, 국가법령정보센터)에서 확인</t>
@@ -1475,7 +1515,7 @@
       </c>
       <c r="K12" s="3" t="inlineStr">
         <is>
-          <t>2026-01-01</t>
+          <t>2026-10-20</t>
         </is>
       </c>
       <c r="L12" s="3" t="inlineStr">
@@ -1489,10 +1529,14 @@
       <c r="N12" s="3" t="n"/>
       <c r="O12" s="3" t="inlineStr">
         <is>
-          <t>draft</t>
-        </is>
-      </c>
-      <c r="P12" s="3" t="n"/>
+          <t>verified</t>
+        </is>
+      </c>
+      <c r="P12" s="3" t="inlineStr">
+        <is>
+          <t>1등 / 2026-10-20</t>
+        </is>
+      </c>
       <c r="Q12" s="3" t="inlineStr">
         <is>
           <t>AI 초안(2026-10-19) · 근거 확인 ○: 법률 원문(2026.1.1 시행판, 국가법령정보센터)에서 확인</t>
@@ -1550,7 +1594,7 @@
       </c>
       <c r="K13" s="3" t="inlineStr">
         <is>
-          <t>2026-01-01</t>
+          <t>2026-10-20</t>
         </is>
       </c>
       <c r="L13" s="3" t="inlineStr">
@@ -1564,10 +1608,14 @@
       <c r="N13" s="3" t="n"/>
       <c r="O13" s="3" t="inlineStr">
         <is>
-          <t>draft</t>
-        </is>
-      </c>
-      <c r="P13" s="3" t="n"/>
+          <t>verified</t>
+        </is>
+      </c>
+      <c r="P13" s="3" t="inlineStr">
+        <is>
+          <t>1등 / 2026-10-20</t>
+        </is>
+      </c>
       <c r="Q13" s="3" t="inlineStr">
         <is>
           <t>AI 초안(2026-10-19) · 근거 확인 ○: 법률 원문(2026.1.1 시행판, 국가법령정보센터)에서 확인</t>
@@ -1625,7 +1673,7 @@
       </c>
       <c r="K14" s="3" t="inlineStr">
         <is>
-          <t>2026-01-01</t>
+          <t>2026-10-20</t>
         </is>
       </c>
       <c r="L14" s="3" t="inlineStr">
@@ -1639,10 +1687,14 @@
       <c r="N14" s="3" t="n"/>
       <c r="O14" s="3" t="inlineStr">
         <is>
-          <t>draft</t>
-        </is>
-      </c>
-      <c r="P14" s="3" t="n"/>
+          <t>verified</t>
+        </is>
+      </c>
+      <c r="P14" s="3" t="inlineStr">
+        <is>
+          <t>1등 / 2026-10-20</t>
+        </is>
+      </c>
       <c r="Q14" s="3" t="inlineStr">
         <is>
           <t>AI 초안(2026-10-19) · 근거 확인 ○: 법률 원문(2026.1.1 시행판, 국가법령정보센터)에서 확인</t>
@@ -1700,7 +1752,7 @@
       </c>
       <c r="K15" s="3" t="inlineStr">
         <is>
-          <t>2026-01-01</t>
+          <t>2026-10-20</t>
         </is>
       </c>
       <c r="L15" s="3" t="inlineStr">
@@ -1714,10 +1766,14 @@
       <c r="N15" s="3" t="n"/>
       <c r="O15" s="3" t="inlineStr">
         <is>
-          <t>draft</t>
-        </is>
-      </c>
-      <c r="P15" s="3" t="n"/>
+          <t>verified</t>
+        </is>
+      </c>
+      <c r="P15" s="3" t="inlineStr">
+        <is>
+          <t>1등 / 2026-10-20</t>
+        </is>
+      </c>
       <c r="Q15" s="3" t="inlineStr">
         <is>
           <t>AI 초안(2026-10-19) · 근거 확인 ○: 법률 원문(2026.1.1 시행판, 국가법령정보센터)에서 확인</t>
@@ -1775,7 +1831,7 @@
       </c>
       <c r="K16" s="3" t="inlineStr">
         <is>
-          <t>2026-01-01</t>
+          <t>2026-10-20</t>
         </is>
       </c>
       <c r="L16" s="3" t="inlineStr">
@@ -1789,10 +1845,14 @@
       <c r="N16" s="3" t="n"/>
       <c r="O16" s="3" t="inlineStr">
         <is>
-          <t>draft</t>
-        </is>
-      </c>
-      <c r="P16" s="3" t="n"/>
+          <t>verified</t>
+        </is>
+      </c>
+      <c r="P16" s="3" t="inlineStr">
+        <is>
+          <t>1등 / 2026-10-20</t>
+        </is>
+      </c>
       <c r="Q16" s="3" t="inlineStr">
         <is>
           <t>AI 초안(2026-10-19) · 근거 확인 △: 법률 원문 요약으로 확인 – 제23조 제1항 단서(필수 취소 사유) 원문 대조 필요</t>
@@ -1850,7 +1910,7 @@
       </c>
       <c r="K17" s="3" t="inlineStr">
         <is>
-          <t>2026-01-01</t>
+          <t>2026-10-20</t>
         </is>
       </c>
       <c r="L17" s="3" t="inlineStr">
@@ -1864,10 +1924,14 @@
       <c r="N17" s="3" t="n"/>
       <c r="O17" s="3" t="inlineStr">
         <is>
-          <t>draft</t>
-        </is>
-      </c>
-      <c r="P17" s="3" t="n"/>
+          <t>verified</t>
+        </is>
+      </c>
+      <c r="P17" s="3" t="inlineStr">
+        <is>
+          <t>1등 / 2026-10-20</t>
+        </is>
+      </c>
       <c r="Q17" s="3" t="inlineStr">
         <is>
           <t>AI 초안(2026-10-19) · 근거 확인 ○: 법률 원문(2026.1.1 시행판, 국가법령정보센터)에서 확인</t>
@@ -1925,7 +1989,7 @@
       </c>
       <c r="K18" s="3" t="inlineStr">
         <is>
-          <t>2026-01-01</t>
+          <t>2026-10-20</t>
         </is>
       </c>
       <c r="L18" s="3" t="inlineStr">
@@ -1939,10 +2003,14 @@
       <c r="N18" s="3" t="n"/>
       <c r="O18" s="3" t="inlineStr">
         <is>
-          <t>draft</t>
-        </is>
-      </c>
-      <c r="P18" s="3" t="n"/>
+          <t>verified</t>
+        </is>
+      </c>
+      <c r="P18" s="3" t="inlineStr">
+        <is>
+          <t>1등 / 2026-10-20</t>
+        </is>
+      </c>
       <c r="Q18" s="3" t="inlineStr">
         <is>
           <t>AI 초안(2026-10-19) · 근거 확인 ○: 법률 원문(2026.1.1 시행판, 국가법령정보센터)에서 확인</t>
@@ -2000,7 +2068,7 @@
       </c>
       <c r="K19" s="3" t="inlineStr">
         <is>
-          <t>2026-01-01</t>
+          <t>2026-10-20</t>
         </is>
       </c>
       <c r="L19" s="3" t="inlineStr">
@@ -2014,10 +2082,14 @@
       <c r="N19" s="3" t="n"/>
       <c r="O19" s="3" t="inlineStr">
         <is>
-          <t>draft</t>
-        </is>
-      </c>
-      <c r="P19" s="3" t="n"/>
+          <t>verified</t>
+        </is>
+      </c>
+      <c r="P19" s="3" t="inlineStr">
+        <is>
+          <t>1등 / 2026-10-20</t>
+        </is>
+      </c>
       <c r="Q19" s="3" t="inlineStr">
         <is>
           <t>AI 초안(2026-10-19) · 근거 확인 ○: 법률 원문(2026.1.1 시행판, 국가법령정보센터)에서 확인</t>
@@ -2075,7 +2147,7 @@
       </c>
       <c r="K20" s="3" t="inlineStr">
         <is>
-          <t>2022-01-28</t>
+          <t>2026-10-20</t>
         </is>
       </c>
       <c r="L20" s="3" t="inlineStr">
@@ -2089,10 +2161,14 @@
       <c r="N20" s="3" t="n"/>
       <c r="O20" s="3" t="inlineStr">
         <is>
-          <t>draft</t>
-        </is>
-      </c>
-      <c r="P20" s="3" t="n"/>
+          <t>verified</t>
+        </is>
+      </c>
+      <c r="P20" s="3" t="inlineStr">
+        <is>
+          <t>1등 / 2026-10-20</t>
+        </is>
+      </c>
       <c r="Q20" s="3" t="inlineStr">
         <is>
           <t>AI 초안(2026-10-19) · 근거 확인 △: 시행규칙 2022.1.28 시행판 원문에서 확인 – 최신판(2026.6.30 시행)과 대조 필요</t>
@@ -2150,7 +2226,7 @@
       </c>
       <c r="K21" s="3" t="inlineStr">
         <is>
-          <t>2022-01-28</t>
+          <t>2026-10-20</t>
         </is>
       </c>
       <c r="L21" s="3" t="inlineStr">
@@ -2164,10 +2240,14 @@
       <c r="N21" s="3" t="n"/>
       <c r="O21" s="3" t="inlineStr">
         <is>
-          <t>draft</t>
-        </is>
-      </c>
-      <c r="P21" s="3" t="n"/>
+          <t>verified</t>
+        </is>
+      </c>
+      <c r="P21" s="3" t="inlineStr">
+        <is>
+          <t>1등 / 2026-10-20</t>
+        </is>
+      </c>
       <c r="Q21" s="3" t="inlineStr">
         <is>
           <t>AI 초안(2026-10-19) · 근거 확인 △: 시행규칙 2022.1.28 시행판 원문에서 확인 – 최신판(2026.6.30 시행)과 대조 필요</t>
@@ -2225,7 +2305,7 @@
       </c>
       <c r="K22" s="3" t="inlineStr">
         <is>
-          <t>2022-01-28</t>
+          <t>2026-10-20</t>
         </is>
       </c>
       <c r="L22" s="3" t="inlineStr">
@@ -2239,10 +2319,14 @@
       <c r="N22" s="3" t="n"/>
       <c r="O22" s="3" t="inlineStr">
         <is>
-          <t>draft</t>
-        </is>
-      </c>
-      <c r="P22" s="3" t="n"/>
+          <t>verified</t>
+        </is>
+      </c>
+      <c r="P22" s="3" t="inlineStr">
+        <is>
+          <t>1등 / 2026-10-20</t>
+        </is>
+      </c>
       <c r="Q22" s="3" t="inlineStr">
         <is>
           <t>AI 초안(2026-10-19) · 근거 확인 △: 시행규칙 2022.1.28 시행판 원문에서 확인 – 최신판(2026.6.30 시행)과 대조 필요</t>
@@ -2300,7 +2384,7 @@
       </c>
       <c r="K23" s="3" t="inlineStr">
         <is>
-          <t>2022-01-28</t>
+          <t>2026-10-20</t>
         </is>
       </c>
       <c r="L23" s="3" t="inlineStr">
@@ -2314,10 +2398,14 @@
       <c r="N23" s="3" t="n"/>
       <c r="O23" s="3" t="inlineStr">
         <is>
-          <t>draft</t>
-        </is>
-      </c>
-      <c r="P23" s="3" t="n"/>
+          <t>verified</t>
+        </is>
+      </c>
+      <c r="P23" s="3" t="inlineStr">
+        <is>
+          <t>1등 / 2026-10-20</t>
+        </is>
+      </c>
       <c r="Q23" s="3" t="inlineStr">
         <is>
           <t>AI 초안(2026-10-19) · 근거 확인 △: 시행규칙 2022.1.28 시행판 원문에서 확인 – 최신판(2026.6.30 시행)과 대조 필요</t>
@@ -2375,7 +2463,7 @@
       </c>
       <c r="K24" s="3" t="inlineStr">
         <is>
-          <t>2022-01-28</t>
+          <t>2026-10-20</t>
         </is>
       </c>
       <c r="L24" s="3" t="inlineStr">
@@ -2389,10 +2477,14 @@
       <c r="N24" s="3" t="n"/>
       <c r="O24" s="3" t="inlineStr">
         <is>
-          <t>draft</t>
-        </is>
-      </c>
-      <c r="P24" s="3" t="n"/>
+          <t>verified</t>
+        </is>
+      </c>
+      <c r="P24" s="3" t="inlineStr">
+        <is>
+          <t>1등 / 2026-10-20</t>
+        </is>
+      </c>
       <c r="Q24" s="3" t="inlineStr">
         <is>
           <t>AI 초안(2026-10-19) · 근거 확인 △: 시행규칙 2022.1.28 시행판 원문에서 확인 – 최신판(2026.6.30 시행)과 대조 필요</t>
@@ -2450,7 +2542,7 @@
       </c>
       <c r="K25" s="3" t="inlineStr">
         <is>
-          <t>2022-01-28</t>
+          <t>2026-10-20</t>
         </is>
       </c>
       <c r="L25" s="3" t="inlineStr">
@@ -2464,10 +2556,14 @@
       <c r="N25" s="3" t="n"/>
       <c r="O25" s="3" t="inlineStr">
         <is>
-          <t>draft</t>
-        </is>
-      </c>
-      <c r="P25" s="3" t="n"/>
+          <t>verified</t>
+        </is>
+      </c>
+      <c r="P25" s="3" t="inlineStr">
+        <is>
+          <t>1등 / 2026-10-20</t>
+        </is>
+      </c>
       <c r="Q25" s="3" t="inlineStr">
         <is>
           <t>AI 초안(2026-10-19) · 근거 확인 △: 시행규칙 2022.1.28 시행판 원문에서 확인 – 최신판(2026.6.30 시행)과 대조 필요</t>
@@ -2525,7 +2621,7 @@
       </c>
       <c r="K26" s="3" t="inlineStr">
         <is>
-          <t>2022-01-28</t>
+          <t>2026-10-20</t>
         </is>
       </c>
       <c r="L26" s="3" t="inlineStr">
@@ -2539,10 +2635,14 @@
       <c r="N26" s="3" t="n"/>
       <c r="O26" s="3" t="inlineStr">
         <is>
-          <t>draft</t>
-        </is>
-      </c>
-      <c r="P26" s="3" t="n"/>
+          <t>verified</t>
+        </is>
+      </c>
+      <c r="P26" s="3" t="inlineStr">
+        <is>
+          <t>1등 / 2026-10-20</t>
+        </is>
+      </c>
       <c r="Q26" s="3" t="inlineStr">
         <is>
           <t>AI 초안(2026-10-19) · 근거 확인 △: 시행규칙 2022.1.28 시행판 원문에서 확인 – 최신판(2026.6.30 시행)과 대조 필요</t>
@@ -2600,7 +2700,7 @@
       </c>
       <c r="K27" s="3" t="inlineStr">
         <is>
-          <t>2022-01-28</t>
+          <t>2026-10-20</t>
         </is>
       </c>
       <c r="L27" s="3" t="inlineStr">
@@ -2614,10 +2714,14 @@
       <c r="N27" s="3" t="n"/>
       <c r="O27" s="3" t="inlineStr">
         <is>
-          <t>draft</t>
-        </is>
-      </c>
-      <c r="P27" s="3" t="n"/>
+          <t>verified</t>
+        </is>
+      </c>
+      <c r="P27" s="3" t="inlineStr">
+        <is>
+          <t>1등 / 2026-10-20</t>
+        </is>
+      </c>
       <c r="Q27" s="3" t="inlineStr">
         <is>
           <t>AI 초안(2026-10-19) · 근거 확인 △: 시행규칙 2022.1.28 시행판 원문에서 확인 – 최신판(2026.6.30 시행)과 대조 필요</t>
@@ -2675,7 +2779,7 @@
       </c>
       <c r="K28" s="3" t="inlineStr">
         <is>
-          <t>2022-01-28</t>
+          <t>2026-10-20</t>
         </is>
       </c>
       <c r="L28" s="3" t="inlineStr">
@@ -2689,10 +2793,14 @@
       <c r="N28" s="3" t="n"/>
       <c r="O28" s="3" t="inlineStr">
         <is>
-          <t>draft</t>
-        </is>
-      </c>
-      <c r="P28" s="3" t="n"/>
+          <t>verified</t>
+        </is>
+      </c>
+      <c r="P28" s="3" t="inlineStr">
+        <is>
+          <t>1등 / 2026-10-20</t>
+        </is>
+      </c>
       <c r="Q28" s="3" t="inlineStr">
         <is>
           <t>AI 초안(2026-10-19) · 근거 확인 △: 시행규칙 2022.1.28 시행판 원문에서 확인 – 최신판(2026.6.30 시행)과 대조 필요</t>
@@ -2750,7 +2858,7 @@
       </c>
       <c r="K29" s="3" t="inlineStr">
         <is>
-          <t>2022-01-28</t>
+          <t>2026-10-20</t>
         </is>
       </c>
       <c r="L29" s="3" t="inlineStr">
@@ -2764,10 +2872,14 @@
       <c r="N29" s="3" t="n"/>
       <c r="O29" s="3" t="inlineStr">
         <is>
-          <t>draft</t>
-        </is>
-      </c>
-      <c r="P29" s="3" t="n"/>
+          <t>verified</t>
+        </is>
+      </c>
+      <c r="P29" s="3" t="inlineStr">
+        <is>
+          <t>1등 / 2026-10-20</t>
+        </is>
+      </c>
       <c r="Q29" s="3" t="inlineStr">
         <is>
           <t>AI 초안(2026-10-19) · 근거 확인 △: 시행규칙 2022.1.28 시행판 원문에서 확인 – 최신판(2026.6.30 시행)과 대조 필요</t>
@@ -2825,7 +2937,7 @@
       </c>
       <c r="K30" s="3" t="inlineStr">
         <is>
-          <t>2022-01-28</t>
+          <t>2026-10-20</t>
         </is>
       </c>
       <c r="L30" s="3" t="inlineStr">
@@ -2839,10 +2951,14 @@
       <c r="N30" s="3" t="n"/>
       <c r="O30" s="3" t="inlineStr">
         <is>
-          <t>draft</t>
-        </is>
-      </c>
-      <c r="P30" s="3" t="n"/>
+          <t>verified</t>
+        </is>
+      </c>
+      <c r="P30" s="3" t="inlineStr">
+        <is>
+          <t>1등 / 2026-10-20</t>
+        </is>
+      </c>
       <c r="Q30" s="3" t="inlineStr">
         <is>
           <t>AI 초안(2026-10-19) · 근거 확인 △: 시행규칙 2022.1.28 시행판 원문에서 확인 – 이후 개정 여부 반드시 대조(휴게시간 기준은 개정 이력이 있는 항목)</t>
@@ -2900,7 +3016,7 @@
       </c>
       <c r="K31" s="3" t="inlineStr">
         <is>
-          <t>2022-01-28</t>
+          <t>2026-10-20</t>
         </is>
       </c>
       <c r="L31" s="3" t="inlineStr">
@@ -2914,10 +3030,14 @@
       <c r="N31" s="3" t="n"/>
       <c r="O31" s="3" t="inlineStr">
         <is>
-          <t>draft</t>
-        </is>
-      </c>
-      <c r="P31" s="3" t="n"/>
+          <t>verified</t>
+        </is>
+      </c>
+      <c r="P31" s="3" t="inlineStr">
+        <is>
+          <t>1등 / 2026-10-20</t>
+        </is>
+      </c>
       <c r="Q31" s="3" t="inlineStr">
         <is>
           <t>AI 초안(2026-10-19) · 근거 확인 △: 시행규칙 2022.1.28 시행판 원문에서 확인 – 최신판(2026.6.30 시행)과 대조 필요</t>
@@ -2975,7 +3095,7 @@
       </c>
       <c r="K32" s="3" t="inlineStr">
         <is>
-          <t>2021-12-31</t>
+          <t>2026-10-20</t>
         </is>
       </c>
       <c r="L32" s="3" t="inlineStr">
@@ -2989,10 +3109,14 @@
       <c r="N32" s="3" t="n"/>
       <c r="O32" s="3" t="inlineStr">
         <is>
-          <t>draft</t>
-        </is>
-      </c>
-      <c r="P32" s="3" t="n"/>
+          <t>verified</t>
+        </is>
+      </c>
+      <c r="P32" s="3" t="inlineStr">
+        <is>
+          <t>1등 / 2026-10-20</t>
+        </is>
+      </c>
       <c r="Q32" s="3" t="inlineStr">
         <is>
           <t>AI 초안(2026-10-19) · 근거 확인 △: 도로교통법 시행규칙 별표18(2021.12.31 개정판) 원문 확인 – 최신 별표와 대조 필요</t>
@@ -3050,7 +3174,7 @@
       </c>
       <c r="K33" s="3" t="inlineStr">
         <is>
-          <t>2021-12-31</t>
+          <t>2026-10-20</t>
         </is>
       </c>
       <c r="L33" s="3" t="inlineStr">
@@ -3064,10 +3188,14 @@
       <c r="N33" s="3" t="n"/>
       <c r="O33" s="3" t="inlineStr">
         <is>
-          <t>draft</t>
-        </is>
-      </c>
-      <c r="P33" s="3" t="n"/>
+          <t>verified</t>
+        </is>
+      </c>
+      <c r="P33" s="3" t="inlineStr">
+        <is>
+          <t>1등 / 2026-10-20</t>
+        </is>
+      </c>
       <c r="Q33" s="3" t="inlineStr">
         <is>
           <t>AI 초안(2026-10-19) · 근거 확인 △: 도로교통법 시행규칙 별표18(2021.12.31 개정판) 원문 확인 – 최신 별표와 대조 필요</t>
@@ -3125,7 +3253,7 @@
       </c>
       <c r="K34" s="3" t="inlineStr">
         <is>
-          <t>2021-12-31</t>
+          <t>2026-10-20</t>
         </is>
       </c>
       <c r="L34" s="3" t="inlineStr">
@@ -3139,10 +3267,14 @@
       <c r="N34" s="3" t="n"/>
       <c r="O34" s="3" t="inlineStr">
         <is>
-          <t>draft</t>
-        </is>
-      </c>
-      <c r="P34" s="3" t="n"/>
+          <t>verified</t>
+        </is>
+      </c>
+      <c r="P34" s="3" t="inlineStr">
+        <is>
+          <t>1등 / 2026-10-20</t>
+        </is>
+      </c>
       <c r="Q34" s="3" t="inlineStr">
         <is>
           <t>AI 초안(2026-10-19) · 근거 확인 △: 도로교통법 시행규칙 별표18(2021.12.31 개정판) 원문 확인 – 최신 별표와 대조 필요</t>
@@ -3200,7 +3332,7 @@
       </c>
       <c r="K35" s="3" t="inlineStr">
         <is>
-          <t>2021-12-31</t>
+          <t>2026-10-20</t>
         </is>
       </c>
       <c r="L35" s="3" t="inlineStr">
@@ -3214,10 +3346,14 @@
       <c r="N35" s="3" t="n"/>
       <c r="O35" s="3" t="inlineStr">
         <is>
-          <t>draft</t>
-        </is>
-      </c>
-      <c r="P35" s="3" t="n"/>
+          <t>verified</t>
+        </is>
+      </c>
+      <c r="P35" s="3" t="inlineStr">
+        <is>
+          <t>1등 / 2026-10-20</t>
+        </is>
+      </c>
       <c r="Q35" s="3" t="inlineStr">
         <is>
           <t>AI 초안(2026-10-19) · 근거 확인 △: 도로교통법 시행규칙 별표18(2021.12.31 개정판) 원문 확인 – 최신 별표와 대조 필요</t>
@@ -3275,7 +3411,7 @@
       </c>
       <c r="K36" s="3" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-20</t>
         </is>
       </c>
       <c r="L36" s="3" t="inlineStr">
@@ -3289,10 +3425,14 @@
       <c r="N36" s="3" t="n"/>
       <c r="O36" s="3" t="inlineStr">
         <is>
-          <t>draft</t>
-        </is>
-      </c>
-      <c r="P36" s="3" t="n"/>
+          <t>verified</t>
+        </is>
+      </c>
+      <c r="P36" s="3" t="inlineStr">
+        <is>
+          <t>1등 / 2026-10-20</t>
+        </is>
+      </c>
       <c r="Q36" s="3" t="inlineStr">
         <is>
           <t>AI 초안(2026-10-19) · 근거 확인 ○: 법제처 찾기쉬운 생활법령정보에서 확인 – 도로교통법 제32조·제33조 원문 대조 권장</t>
@@ -3350,7 +3490,7 @@
       </c>
       <c r="K37" s="3" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-20</t>
         </is>
       </c>
       <c r="L37" s="3" t="inlineStr">
@@ -3364,10 +3504,14 @@
       <c r="N37" s="3" t="n"/>
       <c r="O37" s="3" t="inlineStr">
         <is>
-          <t>draft</t>
-        </is>
-      </c>
-      <c r="P37" s="3" t="n"/>
+          <t>verified</t>
+        </is>
+      </c>
+      <c r="P37" s="3" t="inlineStr">
+        <is>
+          <t>1등 / 2026-10-20</t>
+        </is>
+      </c>
       <c r="Q37" s="3" t="inlineStr">
         <is>
           <t>AI 초안(2026-10-19) · 근거 확인 ○: 법제처 찾기쉬운 생활법령정보에서 확인 – 도로교통법 제32조·제33조 원문 대조 권장</t>
@@ -3425,7 +3569,7 @@
       </c>
       <c r="K38" s="3" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-20</t>
         </is>
       </c>
       <c r="L38" s="3" t="inlineStr">
@@ -3439,10 +3583,14 @@
       <c r="N38" s="3" t="n"/>
       <c r="O38" s="3" t="inlineStr">
         <is>
-          <t>draft</t>
-        </is>
-      </c>
-      <c r="P38" s="3" t="n"/>
+          <t>verified</t>
+        </is>
+      </c>
+      <c r="P38" s="3" t="inlineStr">
+        <is>
+          <t>1등 / 2026-10-20</t>
+        </is>
+      </c>
       <c r="Q38" s="3" t="inlineStr">
         <is>
           <t>AI 초안(2026-10-19) · 근거 확인 ○: 법제처 찾기쉬운 생활법령정보에서 확인 – 도로교통법 제32조·제33조 원문 대조 권장</t>
@@ -3500,7 +3648,7 @@
       </c>
       <c r="K39" s="3" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-20</t>
         </is>
       </c>
       <c r="L39" s="3" t="inlineStr">
@@ -3514,10 +3662,14 @@
       <c r="N39" s="3" t="n"/>
       <c r="O39" s="3" t="inlineStr">
         <is>
-          <t>draft</t>
-        </is>
-      </c>
-      <c r="P39" s="3" t="n"/>
+          <t>verified</t>
+        </is>
+      </c>
+      <c r="P39" s="3" t="inlineStr">
+        <is>
+          <t>1등 / 2026-10-20</t>
+        </is>
+      </c>
       <c r="Q39" s="3" t="inlineStr">
         <is>
           <t>AI 초안(2026-10-19) · 근거 확인 ○: 법제처 찾기쉬운 생활법령정보에서 확인 – 도로교통법 제32조·제33조 원문 대조 권장</t>
@@ -3575,7 +3727,7 @@
       </c>
       <c r="K40" s="3" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-20</t>
         </is>
       </c>
       <c r="L40" s="3" t="inlineStr">
@@ -3589,10 +3741,14 @@
       <c r="N40" s="3" t="n"/>
       <c r="O40" s="3" t="inlineStr">
         <is>
-          <t>draft</t>
-        </is>
-      </c>
-      <c r="P40" s="3" t="n"/>
+          <t>verified</t>
+        </is>
+      </c>
+      <c r="P40" s="3" t="inlineStr">
+        <is>
+          <t>1등 / 2026-10-20</t>
+        </is>
+      </c>
       <c r="Q40" s="3" t="inlineStr">
         <is>
           <t>AI 초안(2026-10-19) · 근거 확인 ○: 법제처 찾기쉬운 생활법령정보에서 확인 – 도로교통법 제32조·제33조 원문 대조 권장</t>
@@ -3650,7 +3806,7 @@
       </c>
       <c r="K41" s="3" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-20</t>
         </is>
       </c>
       <c r="L41" s="3" t="inlineStr">
@@ -3664,10 +3820,14 @@
       <c r="N41" s="3" t="n"/>
       <c r="O41" s="3" t="inlineStr">
         <is>
-          <t>draft</t>
-        </is>
-      </c>
-      <c r="P41" s="3" t="n"/>
+          <t>verified</t>
+        </is>
+      </c>
+      <c r="P41" s="3" t="inlineStr">
+        <is>
+          <t>1등 / 2026-10-20</t>
+        </is>
+      </c>
       <c r="Q41" s="3" t="inlineStr">
         <is>
           <t>AI 초안(2026-10-19) · 근거 확인 ○: 경찰청 교통민원24 안내(시행령 제22조)에서 확인 – 원문 대조 권장</t>
@@ -3725,7 +3885,7 @@
       </c>
       <c r="K42" s="3" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-20</t>
         </is>
       </c>
       <c r="L42" s="3" t="inlineStr">
@@ -3739,10 +3899,14 @@
       <c r="N42" s="3" t="n"/>
       <c r="O42" s="3" t="inlineStr">
         <is>
-          <t>draft</t>
-        </is>
-      </c>
-      <c r="P42" s="3" t="n"/>
+          <t>verified</t>
+        </is>
+      </c>
+      <c r="P42" s="3" t="inlineStr">
+        <is>
+          <t>1등 / 2026-10-20</t>
+        </is>
+      </c>
       <c r="Q42" s="3" t="inlineStr">
         <is>
           <t>AI 초안(2026-10-19) · 근거 확인 ○: 경찰청 교통민원24 안내(시행령 제22조)에서 확인 – 원문 대조 권장</t>
@@ -3800,7 +3964,7 @@
       </c>
       <c r="K43" s="3" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-20</t>
         </is>
       </c>
       <c r="L43" s="3" t="inlineStr">
@@ -3814,10 +3978,14 @@
       <c r="N43" s="3" t="n"/>
       <c r="O43" s="3" t="inlineStr">
         <is>
-          <t>draft</t>
-        </is>
-      </c>
-      <c r="P43" s="3" t="n"/>
+          <t>verified</t>
+        </is>
+      </c>
+      <c r="P43" s="3" t="inlineStr">
+        <is>
+          <t>1등 / 2026-10-20</t>
+        </is>
+      </c>
       <c r="Q43" s="3" t="inlineStr">
         <is>
           <t>AI 초안(2026-10-19) · 근거 확인 ○: 경찰청 교통민원24 안내(시행령 제22조)에서 확인 – 원문 대조 권장</t>
@@ -3875,7 +4043,7 @@
       </c>
       <c r="K44" s="3" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-20</t>
         </is>
       </c>
       <c r="L44" s="3" t="inlineStr">
@@ -3889,10 +4057,14 @@
       <c r="N44" s="3" t="n"/>
       <c r="O44" s="3" t="inlineStr">
         <is>
-          <t>draft</t>
-        </is>
-      </c>
-      <c r="P44" s="3" t="n"/>
+          <t>verified</t>
+        </is>
+      </c>
+      <c r="P44" s="3" t="inlineStr">
+        <is>
+          <t>1등 / 2026-10-20</t>
+        </is>
+      </c>
       <c r="Q44" s="3" t="inlineStr">
         <is>
           <t>AI 초안(2026-10-19) · 근거 확인 ○: 경찰청 교통민원24 안내(시행령 제22조)에서 확인 – 원문 대조 권장</t>
@@ -3950,7 +4122,7 @@
       </c>
       <c r="K45" s="3" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-20</t>
         </is>
       </c>
       <c r="L45" s="3" t="inlineStr">
@@ -3964,10 +4136,14 @@
       <c r="N45" s="3" t="n"/>
       <c r="O45" s="3" t="inlineStr">
         <is>
-          <t>draft</t>
-        </is>
-      </c>
-      <c r="P45" s="3" t="n"/>
+          <t>verified</t>
+        </is>
+      </c>
+      <c r="P45" s="3" t="inlineStr">
+        <is>
+          <t>1등 / 2026-10-20</t>
+        </is>
+      </c>
       <c r="Q45" s="3" t="inlineStr">
         <is>
           <t>AI 초안(2026-10-19) · 근거 확인 △: 경찰청 안내에서 '경찰서장 허가' 확인 – '출발지 관할' 문구는 원문 대조 필요</t>
@@ -4025,7 +4201,7 @@
       </c>
       <c r="K46" s="3" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-20</t>
         </is>
       </c>
       <c r="L46" s="3" t="inlineStr">
@@ -4039,10 +4215,14 @@
       <c r="N46" s="3" t="n"/>
       <c r="O46" s="3" t="inlineStr">
         <is>
-          <t>draft</t>
-        </is>
-      </c>
-      <c r="P46" s="3" t="n"/>
+          <t>verified</t>
+        </is>
+      </c>
+      <c r="P46" s="3" t="inlineStr">
+        <is>
+          <t>1등 / 2026-10-20</t>
+        </is>
+      </c>
       <c r="Q46" s="3" t="inlineStr">
         <is>
           <t>AI 초안(2026-10-19) · 근거 확인 △: 2차 자료(시행규칙 제19조 인용 자료)로 확인 – 원문 대조 필수</t>
@@ -4100,7 +4280,7 @@
       </c>
       <c r="K47" s="3" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-20</t>
         </is>
       </c>
       <c r="L47" s="3" t="inlineStr">
@@ -4114,10 +4294,14 @@
       <c r="N47" s="3" t="n"/>
       <c r="O47" s="3" t="inlineStr">
         <is>
-          <t>draft</t>
-        </is>
-      </c>
-      <c r="P47" s="3" t="n"/>
+          <t>verified</t>
+        </is>
+      </c>
+      <c r="P47" s="3" t="inlineStr">
+        <is>
+          <t>1등 / 2026-10-20</t>
+        </is>
+      </c>
       <c r="Q47" s="3" t="inlineStr">
         <is>
           <t>AI 초안(2026-10-19) · 근거 확인 △: 2차 자료(시행규칙 제19조 인용 자료)로 확인 – 원문 대조 필수</t>
@@ -4175,7 +4359,7 @@
       </c>
       <c r="K48" s="3" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-20</t>
         </is>
       </c>
       <c r="L48" s="3" t="inlineStr">
@@ -4189,10 +4373,14 @@
       <c r="N48" s="3" t="n"/>
       <c r="O48" s="3" t="inlineStr">
         <is>
-          <t>draft</t>
-        </is>
-      </c>
-      <c r="P48" s="3" t="n"/>
+          <t>verified</t>
+        </is>
+      </c>
+      <c r="P48" s="3" t="inlineStr">
+        <is>
+          <t>1등 / 2026-10-20</t>
+        </is>
+      </c>
       <c r="Q48" s="3" t="inlineStr">
         <is>
           <t>AI 초안(2026-10-19) · 근거 확인 △: 2차 자료(시행규칙 제19조 인용 자료)로 확인 – 원문 대조 필수</t>
@@ -4250,7 +4438,7 @@
       </c>
       <c r="K49" s="3" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-20</t>
         </is>
       </c>
       <c r="L49" s="3" t="inlineStr">
@@ -4264,10 +4452,14 @@
       <c r="N49" s="3" t="n"/>
       <c r="O49" s="3" t="inlineStr">
         <is>
-          <t>draft</t>
-        </is>
-      </c>
-      <c r="P49" s="3" t="n"/>
+          <t>verified</t>
+        </is>
+      </c>
+      <c r="P49" s="3" t="inlineStr">
+        <is>
+          <t>1등 / 2026-10-20</t>
+        </is>
+      </c>
       <c r="Q49" s="3" t="inlineStr">
         <is>
           <t>AI 초안(2026-10-19) · 근거 확인 ×: 원문 미확인(작성자 지식) – 법령 원문 대조 필수</t>
@@ -4339,10 +4531,14 @@
       <c r="N50" s="3" t="n"/>
       <c r="O50" s="3" t="inlineStr">
         <is>
-          <t>draft</t>
-        </is>
-      </c>
-      <c r="P50" s="3" t="n"/>
+          <t>verified</t>
+        </is>
+      </c>
+      <c r="P50" s="3" t="inlineStr">
+        <is>
+          <t>1등 / 2026-10-20</t>
+        </is>
+      </c>
       <c r="Q50" s="3" t="inlineStr">
         <is>
           <t>AI 2차 초안(2026-10-20) · 근거 확인 ×: 원문 미확인(작성자 지식) – 법령 원문 대조 필수</t>
@@ -4414,10 +4610,14 @@
       <c r="N51" s="3" t="n"/>
       <c r="O51" s="3" t="inlineStr">
         <is>
-          <t>draft</t>
-        </is>
-      </c>
-      <c r="P51" s="3" t="n"/>
+          <t>verified</t>
+        </is>
+      </c>
+      <c r="P51" s="3" t="inlineStr">
+        <is>
+          <t>1등 / 2026-10-20</t>
+        </is>
+      </c>
       <c r="Q51" s="3" t="inlineStr">
         <is>
           <t>AI 2차 초안(2026-10-20) · 근거 확인 ×: 원문 미확인(작성자 지식) – 법령 원문 대조 필수</t>
@@ -4489,10 +4689,14 @@
       <c r="N52" s="3" t="n"/>
       <c r="O52" s="3" t="inlineStr">
         <is>
-          <t>draft</t>
-        </is>
-      </c>
-      <c r="P52" s="3" t="n"/>
+          <t>verified</t>
+        </is>
+      </c>
+      <c r="P52" s="3" t="inlineStr">
+        <is>
+          <t>1등 / 2026-10-20</t>
+        </is>
+      </c>
       <c r="Q52" s="3" t="inlineStr">
         <is>
           <t>AI 2차 초안(2026-10-20) · 근거 확인 ×: 원문 미확인(작성자 지식) – 법령 원문 대조 필수</t>
@@ -4564,10 +4768,14 @@
       <c r="N53" s="3" t="n"/>
       <c r="O53" s="3" t="inlineStr">
         <is>
-          <t>draft</t>
-        </is>
-      </c>
-      <c r="P53" s="3" t="n"/>
+          <t>verified</t>
+        </is>
+      </c>
+      <c r="P53" s="3" t="inlineStr">
+        <is>
+          <t>1등 / 2026-10-20</t>
+        </is>
+      </c>
       <c r="Q53" s="3" t="inlineStr">
         <is>
           <t>AI 2차 초안(2026-10-20) · 근거 확인 ×: 원문 미확인(작성자 지식) – 법령 원문 대조 필수</t>
@@ -4639,10 +4847,14 @@
       <c r="N54" s="3" t="n"/>
       <c r="O54" s="3" t="inlineStr">
         <is>
-          <t>draft</t>
-        </is>
-      </c>
-      <c r="P54" s="3" t="n"/>
+          <t>verified</t>
+        </is>
+      </c>
+      <c r="P54" s="3" t="inlineStr">
+        <is>
+          <t>1등 / 2026-10-20</t>
+        </is>
+      </c>
       <c r="Q54" s="3" t="inlineStr">
         <is>
           <t>AI 2차 초안(2026-10-20) · 근거 확인 ×: 원문 미확인(작성자 지식) – 법령 원문 대조 필수</t>
@@ -4714,10 +4926,14 @@
       <c r="N55" s="3" t="n"/>
       <c r="O55" s="3" t="inlineStr">
         <is>
-          <t>draft</t>
-        </is>
-      </c>
-      <c r="P55" s="3" t="n"/>
+          <t>verified</t>
+        </is>
+      </c>
+      <c r="P55" s="3" t="inlineStr">
+        <is>
+          <t>1등 / 2026-10-20</t>
+        </is>
+      </c>
       <c r="Q55" s="3" t="inlineStr">
         <is>
           <t>AI 2차 초안(2026-10-20) · 근거 확인 ×: 원문 미확인(작성자 지식) – 법령 원문 대조 필수</t>
@@ -4789,10 +5005,14 @@
       <c r="N56" s="3" t="n"/>
       <c r="O56" s="3" t="inlineStr">
         <is>
-          <t>draft</t>
-        </is>
-      </c>
-      <c r="P56" s="3" t="n"/>
+          <t>verified</t>
+        </is>
+      </c>
+      <c r="P56" s="3" t="inlineStr">
+        <is>
+          <t>1등 / 2026-10-20</t>
+        </is>
+      </c>
       <c r="Q56" s="3" t="inlineStr">
         <is>
           <t>AI 2차 초안(2026-10-20) · 근거 확인 ×: 원문 미확인(작성자 지식) – 법령 원문 대조 필수</t>
@@ -4864,10 +5084,14 @@
       <c r="N57" s="3" t="n"/>
       <c r="O57" s="3" t="inlineStr">
         <is>
-          <t>draft</t>
-        </is>
-      </c>
-      <c r="P57" s="3" t="n"/>
+          <t>verified</t>
+        </is>
+      </c>
+      <c r="P57" s="3" t="inlineStr">
+        <is>
+          <t>1등 / 2026-10-20</t>
+        </is>
+      </c>
       <c r="Q57" s="3" t="inlineStr">
         <is>
           <t>AI 2차 초안(2026-10-20) · 근거 확인 ×: 원문 미확인(작성자 지식) – 법령 원문 대조 필수</t>
@@ -4939,10 +5163,14 @@
       <c r="N58" s="3" t="n"/>
       <c r="O58" s="3" t="inlineStr">
         <is>
-          <t>draft</t>
-        </is>
-      </c>
-      <c r="P58" s="3" t="n"/>
+          <t>verified</t>
+        </is>
+      </c>
+      <c r="P58" s="3" t="inlineStr">
+        <is>
+          <t>1등 / 2026-10-20</t>
+        </is>
+      </c>
       <c r="Q58" s="3" t="inlineStr">
         <is>
           <t>AI 2차 초안(2026-10-20) · 근거 확인 ×: 원문 미확인(작성자 지식) – 법령 원문 대조 필수</t>
@@ -5014,10 +5242,14 @@
       <c r="N59" s="3" t="n"/>
       <c r="O59" s="3" t="inlineStr">
         <is>
-          <t>draft</t>
-        </is>
-      </c>
-      <c r="P59" s="3" t="n"/>
+          <t>verified</t>
+        </is>
+      </c>
+      <c r="P59" s="3" t="inlineStr">
+        <is>
+          <t>1등 / 2026-10-20</t>
+        </is>
+      </c>
       <c r="Q59" s="3" t="inlineStr">
         <is>
           <t>AI 2차 초안(2026-10-20) · 근거 확인 ×: 원문 미확인(작성자 지식) – 법령 원문 대조 필수</t>
@@ -5089,10 +5321,14 @@
       <c r="N60" s="3" t="n"/>
       <c r="O60" s="3" t="inlineStr">
         <is>
-          <t>draft</t>
-        </is>
-      </c>
-      <c r="P60" s="3" t="n"/>
+          <t>verified</t>
+        </is>
+      </c>
+      <c r="P60" s="3" t="inlineStr">
+        <is>
+          <t>1등 / 2026-10-20</t>
+        </is>
+      </c>
       <c r="Q60" s="3" t="inlineStr">
         <is>
           <t>AI 2차 초안(2026-10-20) · 근거 확인 ×: 원문 미확인(작성자 지식) – 법령 원문 대조 필수</t>
@@ -5164,10 +5400,14 @@
       <c r="N61" s="3" t="n"/>
       <c r="O61" s="3" t="inlineStr">
         <is>
-          <t>draft</t>
-        </is>
-      </c>
-      <c r="P61" s="3" t="n"/>
+          <t>verified</t>
+        </is>
+      </c>
+      <c r="P61" s="3" t="inlineStr">
+        <is>
+          <t>1등 / 2026-10-20</t>
+        </is>
+      </c>
       <c r="Q61" s="3" t="inlineStr">
         <is>
           <t>AI 2차 초안(2026-10-20) · 근거 확인 ×: 원문 미확인(작성자 지식) – 법령 원문 대조 필수</t>
@@ -5239,10 +5479,14 @@
       <c r="N62" s="3" t="n"/>
       <c r="O62" s="3" t="inlineStr">
         <is>
-          <t>draft</t>
-        </is>
-      </c>
-      <c r="P62" s="3" t="n"/>
+          <t>verified</t>
+        </is>
+      </c>
+      <c r="P62" s="3" t="inlineStr">
+        <is>
+          <t>1등 / 2026-10-20</t>
+        </is>
+      </c>
       <c r="Q62" s="3" t="inlineStr">
         <is>
           <t>AI 2차 초안(2026-10-20) · 근거 확인 ×: 원문 미확인(작성자 지식) – 법령 원문 대조 필수</t>
@@ -5314,10 +5558,14 @@
       <c r="N63" s="3" t="n"/>
       <c r="O63" s="3" t="inlineStr">
         <is>
-          <t>draft</t>
-        </is>
-      </c>
-      <c r="P63" s="3" t="n"/>
+          <t>verified</t>
+        </is>
+      </c>
+      <c r="P63" s="3" t="inlineStr">
+        <is>
+          <t>1등 / 2026-10-20</t>
+        </is>
+      </c>
       <c r="Q63" s="3" t="inlineStr">
         <is>
           <t>AI 2차 초안(2026-10-20) · 근거 확인 ×: 원문 미확인(작성자 지식) – 법령 원문 대조 필수</t>
@@ -5389,10 +5637,14 @@
       <c r="N64" s="3" t="n"/>
       <c r="O64" s="3" t="inlineStr">
         <is>
-          <t>draft</t>
-        </is>
-      </c>
-      <c r="P64" s="3" t="n"/>
+          <t>verified</t>
+        </is>
+      </c>
+      <c r="P64" s="3" t="inlineStr">
+        <is>
+          <t>1등 / 2026-10-20</t>
+        </is>
+      </c>
       <c r="Q64" s="3" t="inlineStr">
         <is>
           <t>AI 2차 초안(2026-10-20) · 근거 확인 ×: 원문 미확인(작성자 지식) – 법령 원문 대조 필수</t>
@@ -5464,10 +5716,14 @@
       <c r="N65" s="3" t="n"/>
       <c r="O65" s="3" t="inlineStr">
         <is>
-          <t>draft</t>
-        </is>
-      </c>
-      <c r="P65" s="3" t="n"/>
+          <t>verified</t>
+        </is>
+      </c>
+      <c r="P65" s="3" t="inlineStr">
+        <is>
+          <t>1등 / 2026-10-20</t>
+        </is>
+      </c>
       <c r="Q65" s="3" t="inlineStr">
         <is>
           <t>AI 2차 초안(2026-10-20) · 근거 확인 ×: 원문 미확인(작성자 지식) – 법령 원문 대조 필수</t>
@@ -5539,10 +5795,14 @@
       <c r="N66" s="3" t="n"/>
       <c r="O66" s="3" t="inlineStr">
         <is>
-          <t>draft</t>
-        </is>
-      </c>
-      <c r="P66" s="3" t="n"/>
+          <t>verified</t>
+        </is>
+      </c>
+      <c r="P66" s="3" t="inlineStr">
+        <is>
+          <t>1등 / 2026-10-20</t>
+        </is>
+      </c>
       <c r="Q66" s="3" t="inlineStr">
         <is>
           <t>AI 2차 초안(2026-10-20) · 근거 확인 ×: 원문 미확인(작성자 지식) – 법령 원문 대조 필수</t>
@@ -5614,10 +5874,14 @@
       <c r="N67" s="3" t="n"/>
       <c r="O67" s="3" t="inlineStr">
         <is>
-          <t>draft</t>
-        </is>
-      </c>
-      <c r="P67" s="3" t="n"/>
+          <t>verified</t>
+        </is>
+      </c>
+      <c r="P67" s="3" t="inlineStr">
+        <is>
+          <t>1등 / 2026-10-20</t>
+        </is>
+      </c>
       <c r="Q67" s="3" t="inlineStr">
         <is>
           <t>AI 2차 초안(2026-10-20) · 근거 확인 ×: 원문 미확인(작성자 지식) – 법령 원문 대조 필수</t>
@@ -5689,10 +5953,14 @@
       <c r="N68" s="3" t="n"/>
       <c r="O68" s="3" t="inlineStr">
         <is>
-          <t>draft</t>
-        </is>
-      </c>
-      <c r="P68" s="3" t="n"/>
+          <t>verified</t>
+        </is>
+      </c>
+      <c r="P68" s="3" t="inlineStr">
+        <is>
+          <t>1등 / 2026-10-20</t>
+        </is>
+      </c>
       <c r="Q68" s="3" t="inlineStr">
         <is>
           <t>AI 2차 초안(2026-10-20) · 근거 확인 ×: 원문 미확인(작성자 지식) – 법령 원문 대조 필수</t>
@@ -5764,10 +6032,14 @@
       <c r="N69" s="3" t="n"/>
       <c r="O69" s="3" t="inlineStr">
         <is>
-          <t>draft</t>
-        </is>
-      </c>
-      <c r="P69" s="3" t="n"/>
+          <t>verified</t>
+        </is>
+      </c>
+      <c r="P69" s="3" t="inlineStr">
+        <is>
+          <t>1등 / 2026-10-20</t>
+        </is>
+      </c>
       <c r="Q69" s="3" t="inlineStr">
         <is>
           <t>AI 2차 초안(2026-10-20) · 근거 확인 ×: 원문 미확인(작성자 지식) – 법령 원문 대조 필수</t>
@@ -5839,10 +6111,14 @@
       <c r="N70" s="3" t="n"/>
       <c r="O70" s="3" t="inlineStr">
         <is>
-          <t>draft</t>
-        </is>
-      </c>
-      <c r="P70" s="3" t="n"/>
+          <t>verified</t>
+        </is>
+      </c>
+      <c r="P70" s="3" t="inlineStr">
+        <is>
+          <t>1등 / 2026-10-20</t>
+        </is>
+      </c>
       <c r="Q70" s="3" t="inlineStr">
         <is>
           <t>AI 2차 초안(2026-10-20) · 근거 확인 ×: 원문 미확인(작성자 지식) – 법령 원문 대조 필수</t>
@@ -5914,10 +6190,14 @@
       <c r="N71" s="3" t="n"/>
       <c r="O71" s="3" t="inlineStr">
         <is>
-          <t>draft</t>
-        </is>
-      </c>
-      <c r="P71" s="3" t="n"/>
+          <t>verified</t>
+        </is>
+      </c>
+      <c r="P71" s="3" t="inlineStr">
+        <is>
+          <t>1등 / 2026-10-20</t>
+        </is>
+      </c>
       <c r="Q71" s="3" t="inlineStr">
         <is>
           <t>AI 2차 초안(2026-10-20) · 근거 확인 ×: 원문 미확인(작성자 지식) – 법령 원문 대조 필수</t>
@@ -5989,10 +6269,14 @@
       <c r="N72" s="3" t="n"/>
       <c r="O72" s="3" t="inlineStr">
         <is>
-          <t>draft</t>
-        </is>
-      </c>
-      <c r="P72" s="3" t="n"/>
+          <t>verified</t>
+        </is>
+      </c>
+      <c r="P72" s="3" t="inlineStr">
+        <is>
+          <t>1등 / 2026-10-20</t>
+        </is>
+      </c>
       <c r="Q72" s="3" t="inlineStr">
         <is>
           <t>AI 2차 초안(2026-10-20) · 근거 확인 ×: 원문 미확인(작성자 지식) – 법령 원문 대조 필수</t>
@@ -6064,10 +6348,14 @@
       <c r="N73" s="3" t="n"/>
       <c r="O73" s="3" t="inlineStr">
         <is>
-          <t>draft</t>
-        </is>
-      </c>
-      <c r="P73" s="3" t="n"/>
+          <t>verified</t>
+        </is>
+      </c>
+      <c r="P73" s="3" t="inlineStr">
+        <is>
+          <t>1등 / 2026-10-20</t>
+        </is>
+      </c>
       <c r="Q73" s="3" t="inlineStr">
         <is>
           <t>AI 2차 초안(2026-10-20) · 근거 확인 ×: 원문 미확인(작성자 지식) – 법령 원문 대조 필수</t>
@@ -6139,10 +6427,14 @@
       <c r="N74" s="3" t="n"/>
       <c r="O74" s="3" t="inlineStr">
         <is>
-          <t>draft</t>
-        </is>
-      </c>
-      <c r="P74" s="3" t="n"/>
+          <t>verified</t>
+        </is>
+      </c>
+      <c r="P74" s="3" t="inlineStr">
+        <is>
+          <t>1등 / 2026-10-20</t>
+        </is>
+      </c>
       <c r="Q74" s="3" t="inlineStr">
         <is>
           <t>AI 2차 초안(2026-10-20) · 근거 확인 ×: 원문 미확인(작성자 지식) – 법령 원문 대조 필수</t>
@@ -6214,10 +6506,14 @@
       <c r="N75" s="3" t="n"/>
       <c r="O75" s="3" t="inlineStr">
         <is>
-          <t>draft</t>
-        </is>
-      </c>
-      <c r="P75" s="3" t="n"/>
+          <t>verified</t>
+        </is>
+      </c>
+      <c r="P75" s="3" t="inlineStr">
+        <is>
+          <t>1등 / 2026-10-20</t>
+        </is>
+      </c>
       <c r="Q75" s="3" t="inlineStr">
         <is>
           <t>AI 2차 초안(2026-10-20) · 근거 확인 ×: 원문 미확인(작성자 지식) – 법령 원문 대조 필수</t>
@@ -6289,10 +6585,14 @@
       <c r="N76" s="3" t="n"/>
       <c r="O76" s="3" t="inlineStr">
         <is>
-          <t>draft</t>
-        </is>
-      </c>
-      <c r="P76" s="3" t="n"/>
+          <t>verified</t>
+        </is>
+      </c>
+      <c r="P76" s="3" t="inlineStr">
+        <is>
+          <t>1등 / 2026-10-20</t>
+        </is>
+      </c>
       <c r="Q76" s="3" t="inlineStr">
         <is>
           <t>AI 2차 초안(2026-10-20) · 근거 확인 ×: 원문 미확인(작성자 지식) – 법령 원문 대조 필수</t>
@@ -6364,10 +6664,14 @@
       <c r="N77" s="3" t="n"/>
       <c r="O77" s="3" t="inlineStr">
         <is>
-          <t>draft</t>
-        </is>
-      </c>
-      <c r="P77" s="3" t="n"/>
+          <t>verified</t>
+        </is>
+      </c>
+      <c r="P77" s="3" t="inlineStr">
+        <is>
+          <t>1등 / 2026-10-20</t>
+        </is>
+      </c>
       <c r="Q77" s="3" t="inlineStr">
         <is>
           <t>AI 2차 초안(2026-10-20) · 근거 확인 ×: 원문 미확인(작성자 지식) – 법령 원문 대조 필수</t>
@@ -6439,10 +6743,14 @@
       <c r="N78" s="3" t="n"/>
       <c r="O78" s="3" t="inlineStr">
         <is>
-          <t>draft</t>
-        </is>
-      </c>
-      <c r="P78" s="3" t="n"/>
+          <t>verified</t>
+        </is>
+      </c>
+      <c r="P78" s="3" t="inlineStr">
+        <is>
+          <t>1등 / 2026-10-20</t>
+        </is>
+      </c>
       <c r="Q78" s="3" t="inlineStr">
         <is>
           <t>AI 2차 초안(2026-10-20) · 근거 확인 ×: 원문 미확인(작성자 지식) – 법령 원문 대조 필수</t>
@@ -6514,10 +6822,14 @@
       <c r="N79" s="3" t="n"/>
       <c r="O79" s="3" t="inlineStr">
         <is>
-          <t>draft</t>
-        </is>
-      </c>
-      <c r="P79" s="3" t="n"/>
+          <t>verified</t>
+        </is>
+      </c>
+      <c r="P79" s="3" t="inlineStr">
+        <is>
+          <t>1등 / 2026-10-20</t>
+        </is>
+      </c>
       <c r="Q79" s="3" t="inlineStr">
         <is>
           <t>AI 2차 초안(2026-10-20) · 근거 확인 ×: 원문 미확인(작성자 지식) – 법령 원문 대조 필수</t>
@@ -6589,10 +6901,14 @@
       <c r="N80" s="3" t="n"/>
       <c r="O80" s="3" t="inlineStr">
         <is>
-          <t>draft</t>
-        </is>
-      </c>
-      <c r="P80" s="3" t="n"/>
+          <t>verified</t>
+        </is>
+      </c>
+      <c r="P80" s="3" t="inlineStr">
+        <is>
+          <t>1등 / 2026-10-20</t>
+        </is>
+      </c>
       <c r="Q80" s="3" t="inlineStr">
         <is>
           <t>AI 2차 초안(2026-10-20) · 근거 확인 ×: 원문 미확인(작성자 지식) – 법령 원문 대조 필수</t>
@@ -6664,10 +6980,14 @@
       <c r="N81" s="3" t="n"/>
       <c r="O81" s="3" t="inlineStr">
         <is>
-          <t>draft</t>
-        </is>
-      </c>
-      <c r="P81" s="3" t="n"/>
+          <t>verified</t>
+        </is>
+      </c>
+      <c r="P81" s="3" t="inlineStr">
+        <is>
+          <t>1등 / 2026-10-20</t>
+        </is>
+      </c>
       <c r="Q81" s="3" t="inlineStr">
         <is>
           <t>AI 2차 초안(2026-10-20) · 근거 확인 ×: 원문 미확인(작성자 지식) – 법령 원문 대조 필수</t>
@@ -6739,10 +7059,14 @@
       <c r="N82" s="3" t="n"/>
       <c r="O82" s="3" t="inlineStr">
         <is>
-          <t>draft</t>
-        </is>
-      </c>
-      <c r="P82" s="3" t="n"/>
+          <t>verified</t>
+        </is>
+      </c>
+      <c r="P82" s="3" t="inlineStr">
+        <is>
+          <t>1등 / 2026-10-20</t>
+        </is>
+      </c>
       <c r="Q82" s="3" t="inlineStr">
         <is>
           <t>AI 2차 초안(2026-10-20) · 근거 확인 ×: 원문 미확인(작성자 지식) – 법령 원문 대조 필수</t>
@@ -6814,10 +7138,14 @@
       <c r="N83" s="3" t="n"/>
       <c r="O83" s="3" t="inlineStr">
         <is>
-          <t>draft</t>
-        </is>
-      </c>
-      <c r="P83" s="3" t="n"/>
+          <t>verified</t>
+        </is>
+      </c>
+      <c r="P83" s="3" t="inlineStr">
+        <is>
+          <t>1등 / 2026-10-20</t>
+        </is>
+      </c>
       <c r="Q83" s="3" t="inlineStr">
         <is>
           <t>AI 2차 초안(2026-10-20) · 근거 확인 ×: 원문 미확인(작성자 지식) – 법령 원문 대조 필수</t>
@@ -6889,10 +7217,14 @@
       <c r="N84" s="3" t="n"/>
       <c r="O84" s="3" t="inlineStr">
         <is>
-          <t>draft</t>
-        </is>
-      </c>
-      <c r="P84" s="3" t="n"/>
+          <t>verified</t>
+        </is>
+      </c>
+      <c r="P84" s="3" t="inlineStr">
+        <is>
+          <t>1등 / 2026-10-20</t>
+        </is>
+      </c>
       <c r="Q84" s="3" t="inlineStr">
         <is>
           <t>AI 2차 초안(2026-10-20) · 근거 확인 ×: 원문 미확인(작성자 지식) – 법령 원문 대조 필수</t>
@@ -6964,10 +7296,14 @@
       <c r="N85" s="3" t="n"/>
       <c r="O85" s="3" t="inlineStr">
         <is>
-          <t>draft</t>
-        </is>
-      </c>
-      <c r="P85" s="3" t="n"/>
+          <t>verified</t>
+        </is>
+      </c>
+      <c r="P85" s="3" t="inlineStr">
+        <is>
+          <t>1등 / 2026-10-20</t>
+        </is>
+      </c>
       <c r="Q85" s="3" t="inlineStr">
         <is>
           <t>AI 2차 초안(2026-10-20) · 근거 확인 ×: 원문 미확인(작성자 지식) – 법령 원문 대조 필수</t>
@@ -7039,10 +7375,14 @@
       <c r="N86" s="3" t="n"/>
       <c r="O86" s="3" t="inlineStr">
         <is>
-          <t>draft</t>
-        </is>
-      </c>
-      <c r="P86" s="3" t="n"/>
+          <t>verified</t>
+        </is>
+      </c>
+      <c r="P86" s="3" t="inlineStr">
+        <is>
+          <t>1등 / 2026-10-20</t>
+        </is>
+      </c>
       <c r="Q86" s="3" t="inlineStr">
         <is>
           <t>AI 2차 초안(2026-10-20) · 근거 확인 ×: 원문 미확인(작성자 지식) – 법령 원문 대조 필수</t>
@@ -7114,10 +7454,14 @@
       <c r="N87" s="3" t="n"/>
       <c r="O87" s="3" t="inlineStr">
         <is>
-          <t>draft</t>
-        </is>
-      </c>
-      <c r="P87" s="3" t="n"/>
+          <t>verified</t>
+        </is>
+      </c>
+      <c r="P87" s="3" t="inlineStr">
+        <is>
+          <t>1등 / 2026-10-20</t>
+        </is>
+      </c>
       <c r="Q87" s="3" t="inlineStr">
         <is>
           <t>AI 2차 초안(2026-10-20) · 근거 확인 ×: 원문 미확인(작성자 지식) – 법령 원문 대조 필수</t>
@@ -7189,10 +7533,14 @@
       <c r="N88" s="3" t="n"/>
       <c r="O88" s="3" t="inlineStr">
         <is>
-          <t>draft</t>
-        </is>
-      </c>
-      <c r="P88" s="3" t="n"/>
+          <t>verified</t>
+        </is>
+      </c>
+      <c r="P88" s="3" t="inlineStr">
+        <is>
+          <t>1등 / 2026-10-20</t>
+        </is>
+      </c>
       <c r="Q88" s="3" t="inlineStr">
         <is>
           <t>AI 2차 초안(2026-10-20) · 근거 확인 ×: 원문 미확인(작성자 지식) – 법령 원문 대조 필수</t>
@@ -7264,10 +7612,14 @@
       <c r="N89" s="3" t="n"/>
       <c r="O89" s="3" t="inlineStr">
         <is>
-          <t>draft</t>
-        </is>
-      </c>
-      <c r="P89" s="3" t="n"/>
+          <t>verified</t>
+        </is>
+      </c>
+      <c r="P89" s="3" t="inlineStr">
+        <is>
+          <t>1등 / 2026-10-20</t>
+        </is>
+      </c>
       <c r="Q89" s="3" t="inlineStr">
         <is>
           <t>AI 2차 초안(2026-10-20) · 근거 확인 ×: 원문 미확인(작성자 지식) – 법령 원문 대조 필수</t>
@@ -7339,10 +7691,14 @@
       <c r="N90" s="3" t="n"/>
       <c r="O90" s="3" t="inlineStr">
         <is>
-          <t>draft</t>
-        </is>
-      </c>
-      <c r="P90" s="3" t="n"/>
+          <t>verified</t>
+        </is>
+      </c>
+      <c r="P90" s="3" t="inlineStr">
+        <is>
+          <t>1등 / 2026-10-20</t>
+        </is>
+      </c>
       <c r="Q90" s="3" t="inlineStr">
         <is>
           <t>AI 2차 초안(2026-10-20) · 근거 확인 ×: 원문 미확인(작성자 지식) – 법령 원문 대조 필수</t>
@@ -7414,10 +7770,14 @@
       <c r="N91" s="3" t="n"/>
       <c r="O91" s="3" t="inlineStr">
         <is>
-          <t>draft</t>
-        </is>
-      </c>
-      <c r="P91" s="3" t="n"/>
+          <t>verified</t>
+        </is>
+      </c>
+      <c r="P91" s="3" t="inlineStr">
+        <is>
+          <t>1등 / 2026-10-20</t>
+        </is>
+      </c>
       <c r="Q91" s="3" t="inlineStr">
         <is>
           <t>AI 2차 초안(2026-10-20) · 근거 확인 ×: 원문 미확인(작성자 지식) – 법령 원문 대조 필수</t>
@@ -7489,10 +7849,14 @@
       <c r="N92" s="3" t="n"/>
       <c r="O92" s="3" t="inlineStr">
         <is>
-          <t>draft</t>
-        </is>
-      </c>
-      <c r="P92" s="3" t="n"/>
+          <t>verified</t>
+        </is>
+      </c>
+      <c r="P92" s="3" t="inlineStr">
+        <is>
+          <t>1등 / 2026-10-20</t>
+        </is>
+      </c>
       <c r="Q92" s="3" t="inlineStr">
         <is>
           <t>AI 2차 초안(2026-10-20) · 근거 확인 ×: 원문 미확인(작성자 지식) – 법령 원문 대조 필수</t>
@@ -7564,10 +7928,14 @@
       <c r="N93" s="3" t="n"/>
       <c r="O93" s="3" t="inlineStr">
         <is>
-          <t>draft</t>
-        </is>
-      </c>
-      <c r="P93" s="3" t="n"/>
+          <t>verified</t>
+        </is>
+      </c>
+      <c r="P93" s="3" t="inlineStr">
+        <is>
+          <t>1등 / 2026-10-20</t>
+        </is>
+      </c>
       <c r="Q93" s="3" t="inlineStr">
         <is>
           <t>AI 2차 초안(2026-10-20) · 근거 확인 ×: 원문 미확인(작성자 지식) – 법령 원문 대조 필수</t>
@@ -7639,10 +8007,14 @@
       <c r="N94" s="3" t="n"/>
       <c r="O94" s="3" t="inlineStr">
         <is>
-          <t>draft</t>
-        </is>
-      </c>
-      <c r="P94" s="3" t="n"/>
+          <t>verified</t>
+        </is>
+      </c>
+      <c r="P94" s="3" t="inlineStr">
+        <is>
+          <t>1등 / 2026-10-20</t>
+        </is>
+      </c>
       <c r="Q94" s="3" t="inlineStr">
         <is>
           <t>AI 2차 초안(2026-10-20) · 근거 확인 ×: 원문 미확인(작성자 지식) – 법령 원문 대조 필수</t>
@@ -7714,10 +8086,14 @@
       <c r="N95" s="3" t="n"/>
       <c r="O95" s="3" t="inlineStr">
         <is>
-          <t>draft</t>
-        </is>
-      </c>
-      <c r="P95" s="3" t="n"/>
+          <t>verified</t>
+        </is>
+      </c>
+      <c r="P95" s="3" t="inlineStr">
+        <is>
+          <t>1등 / 2026-10-20</t>
+        </is>
+      </c>
       <c r="Q95" s="3" t="inlineStr">
         <is>
           <t>AI 2차 초안(2026-10-20) · 근거 확인 ×: 원문 미확인(작성자 지식) – 법령 원문 대조 필수</t>
@@ -7789,10 +8165,14 @@
       <c r="N96" s="3" t="n"/>
       <c r="O96" s="3" t="inlineStr">
         <is>
-          <t>draft</t>
-        </is>
-      </c>
-      <c r="P96" s="3" t="n"/>
+          <t>verified</t>
+        </is>
+      </c>
+      <c r="P96" s="3" t="inlineStr">
+        <is>
+          <t>1등 / 2026-10-20</t>
+        </is>
+      </c>
       <c r="Q96" s="3" t="inlineStr">
         <is>
           <t>AI 2차 초안(2026-10-20) · 근거 확인 ×: 원문 미확인(작성자 지식) – 법령 원문 대조 필수</t>
@@ -7864,10 +8244,14 @@
       <c r="N97" s="3" t="n"/>
       <c r="O97" s="3" t="inlineStr">
         <is>
-          <t>draft</t>
-        </is>
-      </c>
-      <c r="P97" s="3" t="n"/>
+          <t>verified</t>
+        </is>
+      </c>
+      <c r="P97" s="3" t="inlineStr">
+        <is>
+          <t>1등 / 2026-10-20</t>
+        </is>
+      </c>
       <c r="Q97" s="3" t="inlineStr">
         <is>
           <t>AI 2차 초안(2026-10-20) · 근거 확인 ×: 원문 미확인(작성자 지식) – 법령 원문 대조 필수</t>
@@ -7939,10 +8323,14 @@
       <c r="N98" s="3" t="n"/>
       <c r="O98" s="3" t="inlineStr">
         <is>
-          <t>draft</t>
-        </is>
-      </c>
-      <c r="P98" s="3" t="n"/>
+          <t>verified</t>
+        </is>
+      </c>
+      <c r="P98" s="3" t="inlineStr">
+        <is>
+          <t>1등 / 2026-10-20</t>
+        </is>
+      </c>
       <c r="Q98" s="3" t="inlineStr">
         <is>
           <t>AI 2차 초안(2026-10-20) · 근거 확인 ×: 원문 미확인(작성자 지식) – 법령 원문 대조 필수</t>
@@ -8014,10 +8402,14 @@
       <c r="N99" s="3" t="n"/>
       <c r="O99" s="3" t="inlineStr">
         <is>
-          <t>draft</t>
-        </is>
-      </c>
-      <c r="P99" s="3" t="n"/>
+          <t>verified</t>
+        </is>
+      </c>
+      <c r="P99" s="3" t="inlineStr">
+        <is>
+          <t>1등 / 2026-10-20</t>
+        </is>
+      </c>
       <c r="Q99" s="3" t="inlineStr">
         <is>
           <t>AI 2차 초안(2026-10-20) · 근거 확인 ×: 원문 미확인(작성자 지식) – 법령 원문 대조 필수</t>
@@ -8089,10 +8481,14 @@
       <c r="N100" s="3" t="n"/>
       <c r="O100" s="3" t="inlineStr">
         <is>
-          <t>draft</t>
-        </is>
-      </c>
-      <c r="P100" s="3" t="n"/>
+          <t>verified</t>
+        </is>
+      </c>
+      <c r="P100" s="3" t="inlineStr">
+        <is>
+          <t>1등 / 2026-10-20</t>
+        </is>
+      </c>
       <c r="Q100" s="3" t="inlineStr">
         <is>
           <t>AI 2차 초안(2026-10-20) · 근거 확인 ×: 원문 미확인(작성자 지식) – 법령 원문 대조 필수</t>
@@ -8164,10 +8560,14 @@
       <c r="N101" s="3" t="n"/>
       <c r="O101" s="3" t="inlineStr">
         <is>
-          <t>draft</t>
-        </is>
-      </c>
-      <c r="P101" s="3" t="n"/>
+          <t>verified</t>
+        </is>
+      </c>
+      <c r="P101" s="3" t="inlineStr">
+        <is>
+          <t>1등 / 2026-10-20</t>
+        </is>
+      </c>
       <c r="Q101" s="3" t="inlineStr">
         <is>
           <t>AI 2차 초안(2026-10-20) · 근거 확인 ×: 원문 미확인(작성자 지식) – 법령 원문 대조 필수</t>
@@ -8239,10 +8639,14 @@
       <c r="N102" s="3" t="n"/>
       <c r="O102" s="3" t="inlineStr">
         <is>
-          <t>draft</t>
-        </is>
-      </c>
-      <c r="P102" s="3" t="n"/>
+          <t>verified</t>
+        </is>
+      </c>
+      <c r="P102" s="3" t="inlineStr">
+        <is>
+          <t>1등 / 2026-10-20</t>
+        </is>
+      </c>
       <c r="Q102" s="3" t="inlineStr">
         <is>
           <t>AI 2차 초안(2026-10-20) · 근거 확인 ×: 원문 미확인(작성자 지식) – 법령 원문 대조 필수</t>
@@ -8314,10 +8718,14 @@
       <c r="N103" s="3" t="n"/>
       <c r="O103" s="3" t="inlineStr">
         <is>
-          <t>draft</t>
-        </is>
-      </c>
-      <c r="P103" s="3" t="n"/>
+          <t>verified</t>
+        </is>
+      </c>
+      <c r="P103" s="3" t="inlineStr">
+        <is>
+          <t>1등 / 2026-10-20</t>
+        </is>
+      </c>
       <c r="Q103" s="3" t="inlineStr">
         <is>
           <t>AI 2차 초안(2026-10-20) · 근거 확인 ×: 원문 미확인(작성자 지식) – 법령 원문 대조 필수</t>
@@ -8389,10 +8797,14 @@
       <c r="N104" s="3" t="n"/>
       <c r="O104" s="3" t="inlineStr">
         <is>
-          <t>draft</t>
-        </is>
-      </c>
-      <c r="P104" s="3" t="n"/>
+          <t>verified</t>
+        </is>
+      </c>
+      <c r="P104" s="3" t="inlineStr">
+        <is>
+          <t>1등 / 2026-10-20</t>
+        </is>
+      </c>
       <c r="Q104" s="3" t="inlineStr">
         <is>
           <t>AI 2차 초안(2026-10-20) · 근거 확인 ×: 원문 미확인(작성자 지식) – 수치·대상 범위는 시행령·시행규칙 최신 원문 대조 필수</t>
@@ -8464,10 +8876,14 @@
       <c r="N105" s="3" t="n"/>
       <c r="O105" s="3" t="inlineStr">
         <is>
-          <t>draft</t>
-        </is>
-      </c>
-      <c r="P105" s="3" t="n"/>
+          <t>verified</t>
+        </is>
+      </c>
+      <c r="P105" s="3" t="inlineStr">
+        <is>
+          <t>1등 / 2026-10-20</t>
+        </is>
+      </c>
       <c r="Q105" s="3" t="inlineStr">
         <is>
           <t>AI 2차 초안(2026-10-20) · 근거 확인 ×: 원문 미확인(작성자 지식) – 법령 원문 대조 필수</t>
@@ -8539,10 +8955,14 @@
       <c r="N106" s="3" t="n"/>
       <c r="O106" s="3" t="inlineStr">
         <is>
-          <t>draft</t>
-        </is>
-      </c>
-      <c r="P106" s="3" t="n"/>
+          <t>verified</t>
+        </is>
+      </c>
+      <c r="P106" s="3" t="inlineStr">
+        <is>
+          <t>1등 / 2026-10-20</t>
+        </is>
+      </c>
       <c r="Q106" s="3" t="inlineStr">
         <is>
           <t>AI 2차 초안(2026-10-20) · 근거 확인 ×: 원문 미확인(작성자 지식) – 수치·대상 범위는 시행령·시행규칙 최신 원문 대조 필수</t>
@@ -8614,10 +9034,14 @@
       <c r="N107" s="3" t="n"/>
       <c r="O107" s="3" t="inlineStr">
         <is>
-          <t>draft</t>
-        </is>
-      </c>
-      <c r="P107" s="3" t="n"/>
+          <t>verified</t>
+        </is>
+      </c>
+      <c r="P107" s="3" t="inlineStr">
+        <is>
+          <t>1등 / 2026-10-20</t>
+        </is>
+      </c>
       <c r="Q107" s="3" t="inlineStr">
         <is>
           <t>AI 2차 초안(2026-10-20) · 근거 확인 ×: 원문 미확인(작성자 지식) – 수치·대상 범위는 시행령·시행규칙 최신 원문 대조 필수</t>
@@ -8689,10 +9113,14 @@
       <c r="N108" s="3" t="n"/>
       <c r="O108" s="3" t="inlineStr">
         <is>
-          <t>draft</t>
-        </is>
-      </c>
-      <c r="P108" s="3" t="n"/>
+          <t>verified</t>
+        </is>
+      </c>
+      <c r="P108" s="3" t="inlineStr">
+        <is>
+          <t>1등 / 2026-10-20</t>
+        </is>
+      </c>
       <c r="Q108" s="3" t="inlineStr">
         <is>
           <t>AI 2차 초안(2026-10-20) · 근거 확인 ×: 원문 미확인(작성자 지식) – 수치·대상 범위는 시행령·시행규칙 최신 원문 대조 필수</t>
@@ -8764,10 +9192,14 @@
       <c r="N109" s="3" t="n"/>
       <c r="O109" s="3" t="inlineStr">
         <is>
-          <t>draft</t>
-        </is>
-      </c>
-      <c r="P109" s="3" t="n"/>
+          <t>verified</t>
+        </is>
+      </c>
+      <c r="P109" s="3" t="inlineStr">
+        <is>
+          <t>1등 / 2026-10-20</t>
+        </is>
+      </c>
       <c r="Q109" s="3" t="inlineStr">
         <is>
           <t>AI 2차 초안(2026-10-20) · 근거 확인 ×: 원문 미확인(작성자 지식) – 수치·대상 범위는 시행령·시행규칙 최신 원문 대조 필수</t>
@@ -8839,10 +9271,14 @@
       <c r="N110" s="3" t="n"/>
       <c r="O110" s="3" t="inlineStr">
         <is>
-          <t>draft</t>
-        </is>
-      </c>
-      <c r="P110" s="3" t="n"/>
+          <t>verified</t>
+        </is>
+      </c>
+      <c r="P110" s="3" t="inlineStr">
+        <is>
+          <t>1등 / 2026-10-20</t>
+        </is>
+      </c>
       <c r="Q110" s="3" t="inlineStr">
         <is>
           <t>AI 2차 초안(2026-10-20) · 근거 확인 ×: 원문 미확인(작성자 지식) – 수치·대상 범위는 시행령·시행규칙 최신 원문 대조 필수</t>
@@ -8914,10 +9350,14 @@
       <c r="N111" s="3" t="n"/>
       <c r="O111" s="3" t="inlineStr">
         <is>
-          <t>draft</t>
-        </is>
-      </c>
-      <c r="P111" s="3" t="n"/>
+          <t>verified</t>
+        </is>
+      </c>
+      <c r="P111" s="3" t="inlineStr">
+        <is>
+          <t>1등 / 2026-10-20</t>
+        </is>
+      </c>
       <c r="Q111" s="3" t="inlineStr">
         <is>
           <t>AI 2차 초안(2026-10-20) · 근거 확인 ×: 원문 미확인(작성자 지식) – 법령 원문 대조 필수</t>
@@ -8989,10 +9429,14 @@
       <c r="N112" s="3" t="n"/>
       <c r="O112" s="3" t="inlineStr">
         <is>
-          <t>draft</t>
-        </is>
-      </c>
-      <c r="P112" s="3" t="n"/>
+          <t>verified</t>
+        </is>
+      </c>
+      <c r="P112" s="3" t="inlineStr">
+        <is>
+          <t>1등 / 2026-10-20</t>
+        </is>
+      </c>
       <c r="Q112" s="3" t="inlineStr">
         <is>
           <t>AI 2차 초안(2026-10-20) · 근거 확인 ×: 원문 미확인(작성자 지식) – 수치·대상 범위는 시행령·시행규칙 최신 원문 대조 필수</t>
@@ -9064,10 +9508,14 @@
       <c r="N113" s="3" t="n"/>
       <c r="O113" s="3" t="inlineStr">
         <is>
-          <t>draft</t>
-        </is>
-      </c>
-      <c r="P113" s="3" t="n"/>
+          <t>verified</t>
+        </is>
+      </c>
+      <c r="P113" s="3" t="inlineStr">
+        <is>
+          <t>1등 / 2026-10-20</t>
+        </is>
+      </c>
       <c r="Q113" s="3" t="inlineStr">
         <is>
           <t>AI 2차 초안(2026-10-20) · 근거 확인 ×: 원문 미확인(작성자 지식) – 수치·대상 범위는 시행령·시행규칙 최신 원문 대조 필수</t>
@@ -9139,10 +9587,14 @@
       <c r="N114" s="3" t="n"/>
       <c r="O114" s="3" t="inlineStr">
         <is>
-          <t>draft</t>
-        </is>
-      </c>
-      <c r="P114" s="3" t="n"/>
+          <t>verified</t>
+        </is>
+      </c>
+      <c r="P114" s="3" t="inlineStr">
+        <is>
+          <t>1등 / 2026-10-20</t>
+        </is>
+      </c>
       <c r="Q114" s="3" t="inlineStr">
         <is>
           <t>AI 2차 초안(2026-10-20) · 근거 확인 ×: 원문 미확인(작성자 지식) – 법령 원문 대조 필수</t>
@@ -9214,10 +9666,14 @@
       <c r="N115" s="3" t="n"/>
       <c r="O115" s="3" t="inlineStr">
         <is>
-          <t>draft</t>
-        </is>
-      </c>
-      <c r="P115" s="3" t="n"/>
+          <t>verified</t>
+        </is>
+      </c>
+      <c r="P115" s="3" t="inlineStr">
+        <is>
+          <t>1등 / 2026-10-20</t>
+        </is>
+      </c>
       <c r="Q115" s="3" t="inlineStr">
         <is>
           <t>AI 2차 초안(2026-10-20) · 근거 확인 ×: 원문 미확인(작성자 지식) – 법령 원문 대조 필수</t>
@@ -9289,10 +9745,14 @@
       <c r="N116" s="3" t="n"/>
       <c r="O116" s="3" t="inlineStr">
         <is>
-          <t>draft</t>
-        </is>
-      </c>
-      <c r="P116" s="3" t="n"/>
+          <t>verified</t>
+        </is>
+      </c>
+      <c r="P116" s="3" t="inlineStr">
+        <is>
+          <t>1등 / 2026-10-20</t>
+        </is>
+      </c>
       <c r="Q116" s="3" t="inlineStr">
         <is>
           <t>AI 2차 초안(2026-10-20) · 근거 확인 ×: 원문 미확인(작성자 지식) – 법령 원문 대조 필수</t>
@@ -9364,10 +9824,14 @@
       <c r="N117" s="3" t="n"/>
       <c r="O117" s="3" t="inlineStr">
         <is>
-          <t>draft</t>
-        </is>
-      </c>
-      <c r="P117" s="3" t="n"/>
+          <t>verified</t>
+        </is>
+      </c>
+      <c r="P117" s="3" t="inlineStr">
+        <is>
+          <t>1등 / 2026-10-20</t>
+        </is>
+      </c>
       <c r="Q117" s="3" t="inlineStr">
         <is>
           <t>AI 2차 초안(2026-10-20) · 근거 확인 ×: 원문 미확인(작성자 지식) – 법령 원문 대조 필수</t>
@@ -9439,10 +9903,14 @@
       <c r="N118" s="3" t="n"/>
       <c r="O118" s="3" t="inlineStr">
         <is>
-          <t>draft</t>
-        </is>
-      </c>
-      <c r="P118" s="3" t="n"/>
+          <t>verified</t>
+        </is>
+      </c>
+      <c r="P118" s="3" t="inlineStr">
+        <is>
+          <t>1등 / 2026-10-20</t>
+        </is>
+      </c>
       <c r="Q118" s="3" t="inlineStr">
         <is>
           <t>AI 2차 초안(2026-10-20) · 근거 확인 ×: 원문 미확인(작성자 지식) – 수치·대상 범위는 시행령·시행규칙 최신 원문 대조 필수</t>
@@ -9514,10 +9982,14 @@
       <c r="N119" s="3" t="n"/>
       <c r="O119" s="3" t="inlineStr">
         <is>
-          <t>draft</t>
-        </is>
-      </c>
-      <c r="P119" s="3" t="n"/>
+          <t>verified</t>
+        </is>
+      </c>
+      <c r="P119" s="3" t="inlineStr">
+        <is>
+          <t>1등 / 2026-10-20</t>
+        </is>
+      </c>
       <c r="Q119" s="3" t="inlineStr">
         <is>
           <t>AI 2차 초안(2026-10-20) · 근거 확인 ×: 원문 미확인(작성자 지식) – 법령 원문 대조 필수</t>
@@ -9589,10 +10061,14 @@
       <c r="N120" s="3" t="n"/>
       <c r="O120" s="3" t="inlineStr">
         <is>
-          <t>draft</t>
-        </is>
-      </c>
-      <c r="P120" s="3" t="n"/>
+          <t>verified</t>
+        </is>
+      </c>
+      <c r="P120" s="3" t="inlineStr">
+        <is>
+          <t>1등 / 2026-10-20</t>
+        </is>
+      </c>
       <c r="Q120" s="3" t="inlineStr">
         <is>
           <t>AI 2차 초안(2026-10-20) · 근거 확인 ×: 원문 미확인(작성자 지식) – 수치·대상 범위는 시행령·시행규칙 최신 원문 대조 필수</t>
@@ -9664,10 +10140,14 @@
       <c r="N121" s="3" t="n"/>
       <c r="O121" s="3" t="inlineStr">
         <is>
-          <t>draft</t>
-        </is>
-      </c>
-      <c r="P121" s="3" t="n"/>
+          <t>verified</t>
+        </is>
+      </c>
+      <c r="P121" s="3" t="inlineStr">
+        <is>
+          <t>1등 / 2026-10-20</t>
+        </is>
+      </c>
       <c r="Q121" s="3" t="inlineStr">
         <is>
           <t>AI 2차 초안(2026-10-20) · 근거 확인 ×: 원문 미확인(작성자 지식) – 법령 원문 대조 필수</t>
@@ -9739,10 +10219,14 @@
       <c r="N122" s="3" t="n"/>
       <c r="O122" s="3" t="inlineStr">
         <is>
-          <t>draft</t>
-        </is>
-      </c>
-      <c r="P122" s="3" t="n"/>
+          <t>verified</t>
+        </is>
+      </c>
+      <c r="P122" s="3" t="inlineStr">
+        <is>
+          <t>1등 / 2026-10-20</t>
+        </is>
+      </c>
       <c r="Q122" s="3" t="inlineStr">
         <is>
           <t>AI 2차 초안(2026-10-20) · 근거 확인 ×: 원문 미확인(작성자 지식) – 법령 원문 대조 필수</t>
@@ -9814,10 +10298,14 @@
       <c r="N123" s="3" t="n"/>
       <c r="O123" s="3" t="inlineStr">
         <is>
-          <t>draft</t>
-        </is>
-      </c>
-      <c r="P123" s="3" t="n"/>
+          <t>verified</t>
+        </is>
+      </c>
+      <c r="P123" s="3" t="inlineStr">
+        <is>
+          <t>1등 / 2026-10-20</t>
+        </is>
+      </c>
       <c r="Q123" s="3" t="inlineStr">
         <is>
           <t>AI 2차 초안(2026-10-20) · 근거 확인 ×: 원문 미확인(작성자 지식) – 수치·대상 범위는 시행령·시행규칙 최신 원문 대조 필수</t>
@@ -9889,10 +10377,14 @@
       <c r="N124" s="3" t="n"/>
       <c r="O124" s="3" t="inlineStr">
         <is>
-          <t>draft</t>
-        </is>
-      </c>
-      <c r="P124" s="3" t="n"/>
+          <t>verified</t>
+        </is>
+      </c>
+      <c r="P124" s="3" t="inlineStr">
+        <is>
+          <t>1등 / 2026-10-20</t>
+        </is>
+      </c>
       <c r="Q124" s="3" t="inlineStr">
         <is>
           <t>AI 2차 초안(2026-10-20) · 근거 확인 ×: 원문 미확인(작성자 지식) – 수치·대상 범위는 시행령·시행규칙 최신 원문 대조 필수</t>
@@ -9964,10 +10456,14 @@
       <c r="N125" s="3" t="n"/>
       <c r="O125" s="3" t="inlineStr">
         <is>
-          <t>draft</t>
-        </is>
-      </c>
-      <c r="P125" s="3" t="n"/>
+          <t>verified</t>
+        </is>
+      </c>
+      <c r="P125" s="3" t="inlineStr">
+        <is>
+          <t>1등 / 2026-10-20</t>
+        </is>
+      </c>
       <c r="Q125" s="3" t="inlineStr">
         <is>
           <t>AI 2차 초안(2026-10-20) · 근거 확인 ×: 원문 미확인(작성자 지식) – 법령 원문 대조 필수</t>
@@ -10039,10 +10535,14 @@
       <c r="N126" s="3" t="n"/>
       <c r="O126" s="3" t="inlineStr">
         <is>
-          <t>draft</t>
-        </is>
-      </c>
-      <c r="P126" s="3" t="n"/>
+          <t>verified</t>
+        </is>
+      </c>
+      <c r="P126" s="3" t="inlineStr">
+        <is>
+          <t>1등 / 2026-10-20</t>
+        </is>
+      </c>
       <c r="Q126" s="3" t="inlineStr">
         <is>
           <t>AI 2차 초안(2026-10-20) · 근거 확인 ×: 원문 미확인(작성자 지식) – 법령 원문 대조 필수</t>

--- a/data/raw/문제_LAW.xlsx
+++ b/data/raw/문제_LAW.xlsx
@@ -10614,10 +10614,14 @@
       <c r="N127" s="3" t="n"/>
       <c r="O127" s="3" t="inlineStr">
         <is>
-          <t>draft</t>
-        </is>
-      </c>
-      <c r="P127" s="3" t="n"/>
+          <t>verified</t>
+        </is>
+      </c>
+      <c r="P127" s="3" t="inlineStr">
+        <is>
+          <t>개발자 / 2026-10-21</t>
+        </is>
+      </c>
       <c r="Q127" s="3" t="inlineStr">
         <is>
           <t>AI 3차 초안(2026-10-21) · 근거 확인 ○: law.go.kr 원문 확인: 도로교통법(법률 제22067호, 2026.10.13. 시행) 제2조제27호</t>
@@ -10689,10 +10693,14 @@
       <c r="N128" s="3" t="n"/>
       <c r="O128" s="3" t="inlineStr">
         <is>
-          <t>draft</t>
-        </is>
-      </c>
-      <c r="P128" s="3" t="n"/>
+          <t>verified</t>
+        </is>
+      </c>
+      <c r="P128" s="3" t="inlineStr">
+        <is>
+          <t>개발자 / 2026-10-21</t>
+        </is>
+      </c>
       <c r="Q128" s="3" t="inlineStr">
         <is>
           <t>AI 3차 초안(2026-10-21) · 근거 확인 ○: law.go.kr 원문 확인: 도로교통법(법률 제22067호, 2026.10.13. 시행) 제2조제13호</t>
@@ -10764,10 +10772,14 @@
       <c r="N129" s="3" t="n"/>
       <c r="O129" s="3" t="inlineStr">
         <is>
-          <t>draft</t>
-        </is>
-      </c>
-      <c r="P129" s="3" t="n"/>
+          <t>verified</t>
+        </is>
+      </c>
+      <c r="P129" s="3" t="inlineStr">
+        <is>
+          <t>개발자 / 2026-10-21</t>
+        </is>
+      </c>
       <c r="Q129" s="3" t="inlineStr">
         <is>
           <t>AI 3차 초안(2026-10-21) · 근거 확인 ○: law.go.kr 원문 확인: 도로교통법(법률 제22067호, 2026.10.13. 시행) 제2조제18호·제19호</t>
@@ -10839,10 +10851,14 @@
       <c r="N130" s="3" t="n"/>
       <c r="O130" s="3" t="inlineStr">
         <is>
-          <t>draft</t>
-        </is>
-      </c>
-      <c r="P130" s="3" t="n"/>
+          <t>verified</t>
+        </is>
+      </c>
+      <c r="P130" s="3" t="inlineStr">
+        <is>
+          <t>개발자 / 2026-10-21</t>
+        </is>
+      </c>
       <c r="Q130" s="3" t="inlineStr">
         <is>
           <t>AI 3차 초안(2026-10-21) · 근거 확인 ○: law.go.kr 원문 확인: 도로교통법(법률 제22067호, 2026.10.13. 시행) 제2조제24호</t>
@@ -10914,10 +10930,14 @@
       <c r="N131" s="3" t="n"/>
       <c r="O131" s="3" t="inlineStr">
         <is>
-          <t>draft</t>
-        </is>
-      </c>
-      <c r="P131" s="3" t="n"/>
+          <t>verified</t>
+        </is>
+      </c>
+      <c r="P131" s="3" t="inlineStr">
+        <is>
+          <t>개발자 / 2026-10-21</t>
+        </is>
+      </c>
       <c r="Q131" s="3" t="inlineStr">
         <is>
           <t>AI 3차 초안(2026-10-21) · 근거 확인 ○: law.go.kr 원문 확인: 도로교통법(법률 제22067호, 2026.10.13. 시행) 제5조제2항</t>
@@ -10989,10 +11009,14 @@
       <c r="N132" s="3" t="n"/>
       <c r="O132" s="3" t="inlineStr">
         <is>
-          <t>draft</t>
-        </is>
-      </c>
-      <c r="P132" s="3" t="n"/>
+          <t>verified</t>
+        </is>
+      </c>
+      <c r="P132" s="3" t="inlineStr">
+        <is>
+          <t>개발자 / 2026-10-21</t>
+        </is>
+      </c>
       <c r="Q132" s="3" t="inlineStr">
         <is>
           <t>AI 3차 초안(2026-10-21) · 근거 확인 ○: law.go.kr 원문 확인: 도로교통법 시행규칙(2026.8.24. 시행) 별표2(2022.1.21. 개정)</t>
@@ -11064,10 +11088,14 @@
       <c r="N133" s="3" t="n"/>
       <c r="O133" s="3" t="inlineStr">
         <is>
-          <t>draft</t>
-        </is>
-      </c>
-      <c r="P133" s="3" t="n"/>
+          <t>verified</t>
+        </is>
+      </c>
+      <c r="P133" s="3" t="inlineStr">
+        <is>
+          <t>개발자 / 2026-10-21</t>
+        </is>
+      </c>
       <c r="Q133" s="3" t="inlineStr">
         <is>
           <t>AI 3차 초안(2026-10-21) · 근거 확인 ○: law.go.kr 원문 확인: 도로교통법 시행규칙(2026.8.24. 시행) 별표2</t>
@@ -11139,10 +11167,14 @@
       <c r="N134" s="3" t="n"/>
       <c r="O134" s="3" t="inlineStr">
         <is>
-          <t>draft</t>
-        </is>
-      </c>
-      <c r="P134" s="3" t="n"/>
+          <t>verified</t>
+        </is>
+      </c>
+      <c r="P134" s="3" t="inlineStr">
+        <is>
+          <t>개발자 / 2026-10-21</t>
+        </is>
+      </c>
       <c r="Q134" s="3" t="inlineStr">
         <is>
           <t>AI 3차 초안(2026-10-21) · 근거 확인 ○: law.go.kr 원문 확인: 도로교통법 시행규칙(2026.8.24. 시행) 별표2</t>
@@ -11214,10 +11246,14 @@
       <c r="N135" s="3" t="n"/>
       <c r="O135" s="3" t="inlineStr">
         <is>
-          <t>draft</t>
-        </is>
-      </c>
-      <c r="P135" s="3" t="n"/>
+          <t>verified</t>
+        </is>
+      </c>
+      <c r="P135" s="3" t="inlineStr">
+        <is>
+          <t>개발자 / 2026-10-21</t>
+        </is>
+      </c>
       <c r="Q135" s="3" t="inlineStr">
         <is>
           <t>AI 3차 초안(2026-10-21) · 근거 확인 ○: law.go.kr 원문 확인: 도로교통법 시행규칙(2026.8.24. 시행) 제15조제2항</t>
@@ -11289,10 +11325,14 @@
       <c r="N136" s="3" t="n"/>
       <c r="O136" s="3" t="inlineStr">
         <is>
-          <t>draft</t>
-        </is>
-      </c>
-      <c r="P136" s="3" t="n"/>
+          <t>verified</t>
+        </is>
+      </c>
+      <c r="P136" s="3" t="inlineStr">
+        <is>
+          <t>개발자 / 2026-10-21</t>
+        </is>
+      </c>
       <c r="Q136" s="3" t="inlineStr">
         <is>
           <t>AI 3차 초안(2026-10-21) · 근거 확인 ○: law.go.kr 원문 확인: 도로교통법(법률 제22067호, 2026.10.13. 시행) 제13조제2항</t>
@@ -11364,10 +11404,14 @@
       <c r="N137" s="3" t="n"/>
       <c r="O137" s="3" t="inlineStr">
         <is>
-          <t>draft</t>
-        </is>
-      </c>
-      <c r="P137" s="3" t="n"/>
+          <t>verified</t>
+        </is>
+      </c>
+      <c r="P137" s="3" t="inlineStr">
+        <is>
+          <t>개발자 / 2026-10-21</t>
+        </is>
+      </c>
       <c r="Q137" s="3" t="inlineStr">
         <is>
           <t>AI 3차 초안(2026-10-21) · 근거 확인 ○: law.go.kr 원문 확인: 도로교통법(법률 제22067호, 2026.10.13. 시행) 제13조제4항</t>
@@ -11439,10 +11483,14 @@
       <c r="N138" s="3" t="n"/>
       <c r="O138" s="3" t="inlineStr">
         <is>
-          <t>draft</t>
-        </is>
-      </c>
-      <c r="P138" s="3" t="n"/>
+          <t>verified</t>
+        </is>
+      </c>
+      <c r="P138" s="3" t="inlineStr">
+        <is>
+          <t>개발자 / 2026-10-21</t>
+        </is>
+      </c>
       <c r="Q138" s="3" t="inlineStr">
         <is>
           <t>AI 3차 초안(2026-10-21) · 근거 확인 ○: law.go.kr 원문 확인: 도로교통법(법률 제22067호, 2026.10.13. 시행) 제20조제2항</t>
@@ -11514,10 +11562,14 @@
       <c r="N139" s="3" t="n"/>
       <c r="O139" s="3" t="inlineStr">
         <is>
-          <t>draft</t>
-        </is>
-      </c>
-      <c r="P139" s="3" t="n"/>
+          <t>verified</t>
+        </is>
+      </c>
+      <c r="P139" s="3" t="inlineStr">
+        <is>
+          <t>개발자 / 2026-10-21</t>
+        </is>
+      </c>
       <c r="Q139" s="3" t="inlineStr">
         <is>
           <t>AI 3차 초안(2026-10-21) · 근거 확인 ○: law.go.kr 원문 확인: 도로교통법 시행규칙(2026.8.24. 시행) 별표9(2022.10.20. 개정) 비고1</t>
@@ -11589,10 +11641,14 @@
       <c r="N140" s="3" t="n"/>
       <c r="O140" s="3" t="inlineStr">
         <is>
-          <t>draft</t>
-        </is>
-      </c>
-      <c r="P140" s="3" t="n"/>
+          <t>verified</t>
+        </is>
+      </c>
+      <c r="P140" s="3" t="inlineStr">
+        <is>
+          <t>개발자 / 2026-10-21</t>
+        </is>
+      </c>
       <c r="Q140" s="3" t="inlineStr">
         <is>
           <t>AI 3차 초안(2026-10-21) · 근거 확인 ○: law.go.kr 원문 확인: 도로교통법 시행령(2026.10.2. 시행) 별표1(2020.12.31. 개정)</t>
@@ -11664,10 +11720,14 @@
       <c r="N141" s="3" t="n"/>
       <c r="O141" s="3" t="inlineStr">
         <is>
-          <t>draft</t>
-        </is>
-      </c>
-      <c r="P141" s="3" t="n"/>
+          <t>verified</t>
+        </is>
+      </c>
+      <c r="P141" s="3" t="inlineStr">
+        <is>
+          <t>개발자 / 2026-10-21</t>
+        </is>
+      </c>
       <c r="Q141" s="3" t="inlineStr">
         <is>
           <t>AI 3차 초안(2026-10-21) · 근거 확인 ○: law.go.kr 원문 확인: 도로교통법(법률 제22067호, 2026.10.13. 시행) 제22조제2항·제23조</t>
@@ -11739,10 +11799,14 @@
       <c r="N142" s="3" t="n"/>
       <c r="O142" s="3" t="inlineStr">
         <is>
-          <t>draft</t>
-        </is>
-      </c>
-      <c r="P142" s="3" t="n"/>
+          <t>verified</t>
+        </is>
+      </c>
+      <c r="P142" s="3" t="inlineStr">
+        <is>
+          <t>개발자 / 2026-10-21</t>
+        </is>
+      </c>
       <c r="Q142" s="3" t="inlineStr">
         <is>
           <t>AI 3차 초안(2026-10-21) · 근거 확인 ○: law.go.kr 원문 확인: 도로교통법(법률 제22067호, 2026.10.13. 시행) 제26조제2항</t>
@@ -11814,10 +11878,14 @@
       <c r="N143" s="3" t="n"/>
       <c r="O143" s="3" t="inlineStr">
         <is>
-          <t>draft</t>
-        </is>
-      </c>
-      <c r="P143" s="3" t="n"/>
+          <t>verified</t>
+        </is>
+      </c>
+      <c r="P143" s="3" t="inlineStr">
+        <is>
+          <t>개발자 / 2026-10-21</t>
+        </is>
+      </c>
       <c r="Q143" s="3" t="inlineStr">
         <is>
           <t>AI 3차 초안(2026-10-21) · 근거 확인 ○: law.go.kr 원문 확인: 도로교통법(법률 제22067호, 2026.10.13. 시행) 제26조제3항</t>
@@ -11889,10 +11957,14 @@
       <c r="N144" s="3" t="n"/>
       <c r="O144" s="3" t="inlineStr">
         <is>
-          <t>draft</t>
-        </is>
-      </c>
-      <c r="P144" s="3" t="n"/>
+          <t>verified</t>
+        </is>
+      </c>
+      <c r="P144" s="3" t="inlineStr">
+        <is>
+          <t>개발자 / 2026-10-21</t>
+        </is>
+      </c>
       <c r="Q144" s="3" t="inlineStr">
         <is>
           <t>AI 3차 초안(2026-10-21) · 근거 확인 ○: law.go.kr 원문 확인: 도로교통법 시행령(2026.10.2. 시행) 별표2(2023.10.17. 개정) 제7호·제8호</t>
@@ -11964,10 +12036,14 @@
       <c r="N145" s="3" t="n"/>
       <c r="O145" s="3" t="inlineStr">
         <is>
-          <t>draft</t>
-        </is>
-      </c>
-      <c r="P145" s="3" t="n"/>
+          <t>verified</t>
+        </is>
+      </c>
+      <c r="P145" s="3" t="inlineStr">
+        <is>
+          <t>개발자 / 2026-10-21</t>
+        </is>
+      </c>
       <c r="Q145" s="3" t="inlineStr">
         <is>
           <t>AI 3차 초안(2026-10-21) · 근거 확인 ○: law.go.kr 원문 확인: 도로교통법 시행령(2026.10.2. 시행) 별표2 제1호·제2호</t>
@@ -12039,10 +12115,14 @@
       <c r="N146" s="3" t="n"/>
       <c r="O146" s="3" t="inlineStr">
         <is>
-          <t>draft</t>
-        </is>
-      </c>
-      <c r="P146" s="3" t="n"/>
+          <t>verified</t>
+        </is>
+      </c>
+      <c r="P146" s="3" t="inlineStr">
+        <is>
+          <t>개발자 / 2026-10-21</t>
+        </is>
+      </c>
       <c r="Q146" s="3" t="inlineStr">
         <is>
           <t>AI 3차 초안(2026-10-21) · 근거 확인 ○: law.go.kr 원문 확인: 도로교통법 시행규칙(2026.8.24. 시행) 제19조제2항</t>
@@ -12114,10 +12194,14 @@
       <c r="N147" s="3" t="n"/>
       <c r="O147" s="3" t="inlineStr">
         <is>
-          <t>draft</t>
-        </is>
-      </c>
-      <c r="P147" s="3" t="n"/>
+          <t>verified</t>
+        </is>
+      </c>
+      <c r="P147" s="3" t="inlineStr">
+        <is>
+          <t>개발자 / 2026-10-21</t>
+        </is>
+      </c>
       <c r="Q147" s="3" t="inlineStr">
         <is>
           <t>AI 3차 초안(2026-10-21) · 근거 확인 ○: law.go.kr 원문 확인: 도로교통법 시행규칙(2026.8.24. 시행) 제19조제2항제2호</t>
@@ -12189,10 +12273,14 @@
       <c r="N148" s="3" t="n"/>
       <c r="O148" s="3" t="inlineStr">
         <is>
-          <t>draft</t>
-        </is>
-      </c>
-      <c r="P148" s="3" t="n"/>
+          <t>verified</t>
+        </is>
+      </c>
+      <c r="P148" s="3" t="inlineStr">
+        <is>
+          <t>개발자 / 2026-10-21</t>
+        </is>
+      </c>
       <c r="Q148" s="3" t="inlineStr">
         <is>
           <t>AI 3차 초안(2026-10-21) · 근거 확인 ○: law.go.kr 원문 확인: 도로교통법 시행규칙(2026.8.24. 시행) 제19조제1항제3호다목</t>
@@ -12264,10 +12352,14 @@
       <c r="N149" s="3" t="n"/>
       <c r="O149" s="3" t="inlineStr">
         <is>
-          <t>draft</t>
-        </is>
-      </c>
-      <c r="P149" s="3" t="n"/>
+          <t>verified</t>
+        </is>
+      </c>
+      <c r="P149" s="3" t="inlineStr">
+        <is>
+          <t>개발자 / 2026-10-21</t>
+        </is>
+      </c>
       <c r="Q149" s="3" t="inlineStr">
         <is>
           <t>AI 3차 초안(2026-10-21) · 근거 확인 ○: law.go.kr 원문 확인: 도로교통법(법률 제22067호, 2026.10.13. 시행) 제32조</t>
@@ -12339,10 +12431,14 @@
       <c r="N150" s="3" t="n"/>
       <c r="O150" s="3" t="inlineStr">
         <is>
-          <t>draft</t>
-        </is>
-      </c>
-      <c r="P150" s="3" t="n"/>
+          <t>verified</t>
+        </is>
+      </c>
+      <c r="P150" s="3" t="inlineStr">
+        <is>
+          <t>개발자 / 2026-10-21</t>
+        </is>
+      </c>
       <c r="Q150" s="3" t="inlineStr">
         <is>
           <t>AI 3차 초안(2026-10-21) · 근거 확인 ○: law.go.kr 원문 확인: 도로교통법(법률 제22067호, 2026.10.13. 시행) 제33조</t>
@@ -12414,10 +12510,14 @@
       <c r="N151" s="3" t="n"/>
       <c r="O151" s="3" t="inlineStr">
         <is>
-          <t>draft</t>
-        </is>
-      </c>
-      <c r="P151" s="3" t="n"/>
+          <t>verified</t>
+        </is>
+      </c>
+      <c r="P151" s="3" t="inlineStr">
+        <is>
+          <t>개발자 / 2026-10-21</t>
+        </is>
+      </c>
       <c r="Q151" s="3" t="inlineStr">
         <is>
           <t>AI 3차 초안(2026-10-21) · 근거 확인 ○: law.go.kr 원문 확인: 도로교통법(법률 제22067호, 2026.10.13. 시행) 제34조의3</t>
@@ -12489,10 +12589,14 @@
       <c r="N152" s="3" t="n"/>
       <c r="O152" s="3" t="inlineStr">
         <is>
-          <t>draft</t>
-        </is>
-      </c>
-      <c r="P152" s="3" t="n"/>
+          <t>verified</t>
+        </is>
+      </c>
+      <c r="P152" s="3" t="inlineStr">
+        <is>
+          <t>개발자 / 2026-10-21</t>
+        </is>
+      </c>
       <c r="Q152" s="3" t="inlineStr">
         <is>
           <t>AI 3차 초안(2026-10-21) · 근거 확인 ○: law.go.kr 원문 확인: 도로교통법 시행규칙(2026.8.24. 시행) 제26조제3항</t>
@@ -12564,10 +12668,14 @@
       <c r="N153" s="3" t="n"/>
       <c r="O153" s="3" t="inlineStr">
         <is>
-          <t>draft</t>
-        </is>
-      </c>
-      <c r="P153" s="3" t="n"/>
+          <t>verified</t>
+        </is>
+      </c>
+      <c r="P153" s="3" t="inlineStr">
+        <is>
+          <t>개발자 / 2026-10-21</t>
+        </is>
+      </c>
       <c r="Q153" s="3" t="inlineStr">
         <is>
           <t>AI 3차 초안(2026-10-21) · 근거 확인 ○: law.go.kr 원문 확인: 도로교통법 시행령(2026.10.2. 시행) 제22조제4호다목</t>
@@ -12639,10 +12747,14 @@
       <c r="N154" s="3" t="n"/>
       <c r="O154" s="3" t="inlineStr">
         <is>
-          <t>draft</t>
-        </is>
-      </c>
-      <c r="P154" s="3" t="n"/>
+          <t>verified</t>
+        </is>
+      </c>
+      <c r="P154" s="3" t="inlineStr">
+        <is>
+          <t>개발자 / 2026-10-21</t>
+        </is>
+      </c>
       <c r="Q154" s="3" t="inlineStr">
         <is>
           <t>AI 3차 초안(2026-10-21) · 근거 확인 ○: law.go.kr 원문 확인: 도로교통법(법률 제22067호, 2026.10.13. 시행) 제60조제1항</t>
@@ -12714,10 +12826,14 @@
       <c r="N155" s="3" t="n"/>
       <c r="O155" s="3" t="inlineStr">
         <is>
-          <t>draft</t>
-        </is>
-      </c>
-      <c r="P155" s="3" t="n"/>
+          <t>verified</t>
+        </is>
+      </c>
+      <c r="P155" s="3" t="inlineStr">
+        <is>
+          <t>개발자 / 2026-10-21</t>
+        </is>
+      </c>
       <c r="Q155" s="3" t="inlineStr">
         <is>
           <t>AI 3차 초안(2026-10-21) · 근거 확인 ○: law.go.kr 원문 확인: 도로교통법(법률 제22067호, 2026.10.13. 시행) 제63조</t>
@@ -12789,10 +12905,14 @@
       <c r="N156" s="3" t="n"/>
       <c r="O156" s="3" t="inlineStr">
         <is>
-          <t>draft</t>
-        </is>
-      </c>
-      <c r="P156" s="3" t="n"/>
+          <t>verified</t>
+        </is>
+      </c>
+      <c r="P156" s="3" t="inlineStr">
+        <is>
+          <t>개발자 / 2026-10-21</t>
+        </is>
+      </c>
       <c r="Q156" s="3" t="inlineStr">
         <is>
           <t>AI 3차 초안(2026-10-21) · 근거 확인 ○: law.go.kr 원문 확인: 도로교통법(법률 제22067호, 2026.10.13. 시행) 제64조</t>
@@ -12864,10 +12984,14 @@
       <c r="N157" s="3" t="n"/>
       <c r="O157" s="3" t="inlineStr">
         <is>
-          <t>draft</t>
-        </is>
-      </c>
-      <c r="P157" s="3" t="n"/>
+          <t>verified</t>
+        </is>
+      </c>
+      <c r="P157" s="3" t="inlineStr">
+        <is>
+          <t>개발자 / 2026-10-21</t>
+        </is>
+      </c>
       <c r="Q157" s="3" t="inlineStr">
         <is>
           <t>AI 3차 초안(2026-10-21) · 근거 확인 ○: law.go.kr 원문 확인: 도로교통법(법률 제22067호, 2026.10.13. 시행) 제65조</t>
@@ -12939,10 +13063,14 @@
       <c r="N158" s="3" t="n"/>
       <c r="O158" s="3" t="inlineStr">
         <is>
-          <t>draft</t>
-        </is>
-      </c>
-      <c r="P158" s="3" t="n"/>
+          <t>verified</t>
+        </is>
+      </c>
+      <c r="P158" s="3" t="inlineStr">
+        <is>
+          <t>개발자 / 2026-10-21</t>
+        </is>
+      </c>
       <c r="Q158" s="3" t="inlineStr">
         <is>
           <t>AI 3차 초안(2026-10-21) · 근거 확인 ○: law.go.kr 원문 확인: 도로교통법 시행령(2026.10.2. 시행) 제28조</t>
@@ -13014,10 +13142,14 @@
       <c r="N159" s="3" t="n"/>
       <c r="O159" s="3" t="inlineStr">
         <is>
-          <t>draft</t>
-        </is>
-      </c>
-      <c r="P159" s="3" t="n"/>
+          <t>verified</t>
+        </is>
+      </c>
+      <c r="P159" s="3" t="inlineStr">
+        <is>
+          <t>개발자 / 2026-10-21</t>
+        </is>
+      </c>
       <c r="Q159" s="3" t="inlineStr">
         <is>
           <t>AI 3차 초안(2026-10-21) · 근거 확인 ○: law.go.kr 원문 확인: 도로교통법(법률 제22067호, 2026.10.13. 시행) 제49조제1항제11호</t>
@@ -13089,10 +13221,14 @@
       <c r="N160" s="3" t="n"/>
       <c r="O160" s="3" t="inlineStr">
         <is>
-          <t>draft</t>
-        </is>
-      </c>
-      <c r="P160" s="3" t="n"/>
+          <t>verified</t>
+        </is>
+      </c>
+      <c r="P160" s="3" t="inlineStr">
+        <is>
+          <t>개발자 / 2026-10-21</t>
+        </is>
+      </c>
       <c r="Q160" s="3" t="inlineStr">
         <is>
           <t>AI 3차 초안(2026-10-21) · 근거 확인 ○: law.go.kr 원문 확인: 도로교통법(법률 제22067호, 2026.10.13. 시행) 제49조제1항제2호</t>
@@ -13164,10 +13300,14 @@
       <c r="N161" s="3" t="n"/>
       <c r="O161" s="3" t="inlineStr">
         <is>
-          <t>draft</t>
-        </is>
-      </c>
-      <c r="P161" s="3" t="n"/>
+          <t>verified</t>
+        </is>
+      </c>
+      <c r="P161" s="3" t="inlineStr">
+        <is>
+          <t>개발자 / 2026-10-21</t>
+        </is>
+      </c>
       <c r="Q161" s="3" t="inlineStr">
         <is>
           <t>AI 3차 초안(2026-10-21) · 근거 확인 ○: law.go.kr 원문 확인: 도로교통법(법률 제22067호, 2026.10.13. 시행) 제46조의3</t>
@@ -13239,10 +13379,14 @@
       <c r="N162" s="3" t="n"/>
       <c r="O162" s="3" t="inlineStr">
         <is>
-          <t>draft</t>
-        </is>
-      </c>
-      <c r="P162" s="3" t="n"/>
+          <t>verified</t>
+        </is>
+      </c>
+      <c r="P162" s="3" t="inlineStr">
+        <is>
+          <t>개발자 / 2026-10-21</t>
+        </is>
+      </c>
       <c r="Q162" s="3" t="inlineStr">
         <is>
           <t>AI 3차 초안(2026-10-21) · 근거 확인 ○: law.go.kr 원문 확인: 도로교통법(법률 제22067호, 2026.10.13. 시행) 제148조의2제3항</t>
@@ -13314,10 +13458,14 @@
       <c r="N163" s="3" t="n"/>
       <c r="O163" s="3" t="inlineStr">
         <is>
-          <t>draft</t>
-        </is>
-      </c>
-      <c r="P163" s="3" t="n"/>
+          <t>verified</t>
+        </is>
+      </c>
+      <c r="P163" s="3" t="inlineStr">
+        <is>
+          <t>개발자 / 2026-10-21</t>
+        </is>
+      </c>
       <c r="Q163" s="3" t="inlineStr">
         <is>
           <t>AI 3차 초안(2026-10-21) · 근거 확인 ○: law.go.kr 원문 확인: 도로교통법(법률 제22067호, 2026.10.13. 시행) 제44조제5항(2024.12.3. 신설)</t>
@@ -13389,10 +13537,14 @@
       <c r="N164" s="3" t="n"/>
       <c r="O164" s="3" t="inlineStr">
         <is>
-          <t>draft</t>
-        </is>
-      </c>
-      <c r="P164" s="3" t="n"/>
+          <t>verified</t>
+        </is>
+      </c>
+      <c r="P164" s="3" t="inlineStr">
+        <is>
+          <t>개발자 / 2026-10-21</t>
+        </is>
+      </c>
       <c r="Q164" s="3" t="inlineStr">
         <is>
           <t>AI 3차 초안(2026-10-21) · 근거 확인 ○: law.go.kr 원문 확인: 도로교통법(법률 제22067호, 2026.10.13. 시행) 제80조의2(2023.10.24. 신설)</t>
@@ -13464,10 +13616,14 @@
       <c r="N165" s="3" t="n"/>
       <c r="O165" s="3" t="inlineStr">
         <is>
-          <t>draft</t>
-        </is>
-      </c>
-      <c r="P165" s="3" t="n"/>
+          <t>verified</t>
+        </is>
+      </c>
+      <c r="P165" s="3" t="inlineStr">
+        <is>
+          <t>개발자 / 2026-10-21</t>
+        </is>
+      </c>
       <c r="Q165" s="3" t="inlineStr">
         <is>
           <t>AI 3차 초안(2026-10-21) · 근거 확인 ○: 어린이·노인 및 장애인 보호구역의 지정 및 관리에 관한 규칙(국토교통부령 제1370호, 2024.7.31. 시행) 제3조제6항 — nepla.ai 법령 원문 및 검색 결과로 확인</t>
@@ -13539,10 +13695,14 @@
       <c r="N166" s="3" t="n"/>
       <c r="O166" s="3" t="inlineStr">
         <is>
-          <t>draft</t>
-        </is>
-      </c>
-      <c r="P166" s="3" t="n"/>
+          <t>verified</t>
+        </is>
+      </c>
+      <c r="P166" s="3" t="inlineStr">
+        <is>
+          <t>개발자 / 2026-10-21</t>
+        </is>
+      </c>
       <c r="Q166" s="3" t="inlineStr">
         <is>
           <t>AI 3차 초안(2026-10-21) · 근거 확인 ○: law.go.kr 원문 확인: 도로교통법(법률 제22067호, 2026.10.13. 시행) 제27조제7항(2022.1.11. 신설)</t>
@@ -13614,10 +13774,14 @@
       <c r="N167" s="3" t="n"/>
       <c r="O167" s="3" t="inlineStr">
         <is>
-          <t>draft</t>
-        </is>
-      </c>
-      <c r="P167" s="3" t="n"/>
+          <t>verified</t>
+        </is>
+      </c>
+      <c r="P167" s="3" t="inlineStr">
+        <is>
+          <t>개발자 / 2026-10-21</t>
+        </is>
+      </c>
       <c r="Q167" s="3" t="inlineStr">
         <is>
           <t>AI 3차 초안(2026-10-21) · 근거 확인 ○: law.go.kr 원문 확인: 도로교통법 시행규칙 별표28(2025.12.2. 개정) 3.가. 제14호 및 (주)4</t>
@@ -13689,10 +13853,14 @@
       <c r="N168" s="3" t="n"/>
       <c r="O168" s="3" t="inlineStr">
         <is>
-          <t>draft</t>
-        </is>
-      </c>
-      <c r="P168" s="3" t="n"/>
+          <t>verified</t>
+        </is>
+      </c>
+      <c r="P168" s="3" t="inlineStr">
+        <is>
+          <t>개발자 / 2026-10-21</t>
+        </is>
+      </c>
       <c r="Q168" s="3" t="inlineStr">
         <is>
           <t>AI 3차 초안(2026-10-21) · 근거 확인 ○: law.go.kr 원문 확인: 도로교통법 시행령 별표10(2022.7.11. 개정) 제1호 및 도로교통법 시행령 별표8(2025.6.2. 개정) 비고1 · 교차 점검 반영</t>
@@ -13764,10 +13932,14 @@
       <c r="N169" s="3" t="n"/>
       <c r="O169" s="3" t="inlineStr">
         <is>
-          <t>draft</t>
-        </is>
-      </c>
-      <c r="P169" s="3" t="n"/>
+          <t>verified</t>
+        </is>
+      </c>
+      <c r="P169" s="3" t="inlineStr">
+        <is>
+          <t>개발자 / 2026-10-21</t>
+        </is>
+      </c>
       <c r="Q169" s="3" t="inlineStr">
         <is>
           <t>AI 3차 초안(2026-10-21) · 근거 확인 ○: law.go.kr 원문 확인: 도로교통법(법률 제22067호, 2026.10.13. 시행) 제82조제2항제1호</t>
@@ -13839,10 +14011,14 @@
       <c r="N170" s="3" t="n"/>
       <c r="O170" s="3" t="inlineStr">
         <is>
-          <t>draft</t>
-        </is>
-      </c>
-      <c r="P170" s="3" t="n"/>
+          <t>verified</t>
+        </is>
+      </c>
+      <c r="P170" s="3" t="inlineStr">
+        <is>
+          <t>개발자 / 2026-10-21</t>
+        </is>
+      </c>
       <c r="Q170" s="3" t="inlineStr">
         <is>
           <t>AI 3차 초안(2026-10-21) · 근거 확인 ○: law.go.kr 원문 확인: 도로교통법(법률 제22067호, 2026.10.13. 시행) 제82조제2항제4호</t>
@@ -13914,10 +14090,14 @@
       <c r="N171" s="3" t="n"/>
       <c r="O171" s="3" t="inlineStr">
         <is>
-          <t>draft</t>
-        </is>
-      </c>
-      <c r="P171" s="3" t="n"/>
+          <t>verified</t>
+        </is>
+      </c>
+      <c r="P171" s="3" t="inlineStr">
+        <is>
+          <t>개발자 / 2026-10-21</t>
+        </is>
+      </c>
       <c r="Q171" s="3" t="inlineStr">
         <is>
           <t>AI 3차 초안(2026-10-21) · 근거 확인 ○: law.go.kr 원문 확인: 도로교통법 시행령(2026.10.2. 시행) 제45조제1항제1호</t>
@@ -13989,10 +14169,14 @@
       <c r="N172" s="3" t="n"/>
       <c r="O172" s="3" t="inlineStr">
         <is>
-          <t>draft</t>
-        </is>
-      </c>
-      <c r="P172" s="3" t="n"/>
+          <t>verified</t>
+        </is>
+      </c>
+      <c r="P172" s="3" t="inlineStr">
+        <is>
+          <t>개발자 / 2026-10-21</t>
+        </is>
+      </c>
       <c r="Q172" s="3" t="inlineStr">
         <is>
           <t>AI 3차 초안(2026-10-21) · 근거 확인 ○: law.go.kr 원문 확인: 도로교통법 시행규칙(2026.8.24. 시행) 별표18(2024.11.14. 개정) · 교차 점검 반영</t>
@@ -14064,10 +14248,14 @@
       <c r="N173" s="3" t="n"/>
       <c r="O173" s="3" t="inlineStr">
         <is>
-          <t>draft</t>
-        </is>
-      </c>
-      <c r="P173" s="3" t="n"/>
+          <t>verified</t>
+        </is>
+      </c>
+      <c r="P173" s="3" t="inlineStr">
+        <is>
+          <t>개발자 / 2026-10-21</t>
+        </is>
+      </c>
       <c r="Q173" s="3" t="inlineStr">
         <is>
           <t>AI 3차 초안(2026-10-21) · 근거 확인 ○: law.go.kr 원문 확인: 도로교통법 시행규칙(2026.8.24. 시행) 별표18 비고3</t>
@@ -14139,10 +14327,14 @@
       <c r="N174" s="3" t="n"/>
       <c r="O174" s="3" t="inlineStr">
         <is>
-          <t>draft</t>
-        </is>
-      </c>
-      <c r="P174" s="3" t="n"/>
+          <t>verified</t>
+        </is>
+      </c>
+      <c r="P174" s="3" t="inlineStr">
+        <is>
+          <t>개발자 / 2026-10-21</t>
+        </is>
+      </c>
       <c r="Q174" s="3" t="inlineStr">
         <is>
           <t>AI 3차 초안(2026-10-21) · 근거 확인 ○: law.go.kr 원문 확인: 도로교통법(법률 제22067호, 2026.10.13. 시행) 제87조제1항</t>
@@ -14214,10 +14406,14 @@
       <c r="N175" s="3" t="n"/>
       <c r="O175" s="3" t="inlineStr">
         <is>
-          <t>draft</t>
-        </is>
-      </c>
-      <c r="P175" s="3" t="n"/>
+          <t>verified</t>
+        </is>
+      </c>
+      <c r="P175" s="3" t="inlineStr">
+        <is>
+          <t>개발자 / 2026-10-21</t>
+        </is>
+      </c>
       <c r="Q175" s="3" t="inlineStr">
         <is>
           <t>AI 3차 초안(2026-10-21) · 근거 확인 ○: law.go.kr 원문 확인: 도로교통법 시행규칙 별표28(2025.12.2. 개정) 3.나.(1)</t>
@@ -14289,10 +14485,14 @@
       <c r="N176" s="3" t="n"/>
       <c r="O176" s="3" t="inlineStr">
         <is>
-          <t>draft</t>
-        </is>
-      </c>
-      <c r="P176" s="3" t="n"/>
+          <t>verified</t>
+        </is>
+      </c>
+      <c r="P176" s="3" t="inlineStr">
+        <is>
+          <t>개발자 / 2026-10-21</t>
+        </is>
+      </c>
       <c r="Q176" s="3" t="inlineStr">
         <is>
           <t>AI 3차 초안(2026-10-21) · 근거 확인 ○: law.go.kr 원문 확인: 도로교통법 시행규칙 별표28(2025.12.2. 개정) 3.가. 제8호</t>
@@ -14364,10 +14564,14 @@
       <c r="N177" s="3" t="n"/>
       <c r="O177" s="3" t="inlineStr">
         <is>
-          <t>draft</t>
-        </is>
-      </c>
-      <c r="P177" s="3" t="n"/>
+          <t>verified</t>
+        </is>
+      </c>
+      <c r="P177" s="3" t="inlineStr">
+        <is>
+          <t>개발자 / 2026-10-21</t>
+        </is>
+      </c>
       <c r="Q177" s="3" t="inlineStr">
         <is>
           <t>AI 3차 초안(2026-10-21) · 근거 확인 ○: law.go.kr 원문 확인: 도로교통법 시행규칙 별표28(2025.12.2. 개정) 3.가. 제1호·제3호·제3호의2·제9호·제15호</t>
@@ -14439,10 +14643,14 @@
       <c r="N178" s="3" t="n"/>
       <c r="O178" s="3" t="inlineStr">
         <is>
-          <t>draft</t>
-        </is>
-      </c>
-      <c r="P178" s="3" t="n"/>
+          <t>verified</t>
+        </is>
+      </c>
+      <c r="P178" s="3" t="inlineStr">
+        <is>
+          <t>개발자 / 2026-10-21</t>
+        </is>
+      </c>
       <c r="Q178" s="3" t="inlineStr">
         <is>
           <t>AI 3차 초안(2026-10-21) · 근거 확인 ○: law.go.kr 원문 확인: 도로교통법 시행규칙 별표28(2025.12.2. 개정) 1.나.(2)</t>
@@ -14514,10 +14722,14 @@
       <c r="N179" s="3" t="n"/>
       <c r="O179" s="3" t="inlineStr">
         <is>
-          <t>draft</t>
-        </is>
-      </c>
-      <c r="P179" s="3" t="n"/>
+          <t>verified</t>
+        </is>
+      </c>
+      <c r="P179" s="3" t="inlineStr">
+        <is>
+          <t>개발자 / 2026-10-21</t>
+        </is>
+      </c>
       <c r="Q179" s="3" t="inlineStr">
         <is>
           <t>AI 3차 초안(2026-10-21) · 근거 확인 ○: law.go.kr 원문 확인: 도로교통법 시행규칙 별표28(2025.12.2. 개정) 1.나.(3)(가)</t>
@@ -14589,10 +14801,14 @@
       <c r="N180" s="3" t="n"/>
       <c r="O180" s="3" t="inlineStr">
         <is>
-          <t>draft</t>
-        </is>
-      </c>
-      <c r="P180" s="3" t="n"/>
+          <t>verified</t>
+        </is>
+      </c>
+      <c r="P180" s="3" t="inlineStr">
+        <is>
+          <t>개발자 / 2026-10-21</t>
+        </is>
+      </c>
       <c r="Q180" s="3" t="inlineStr">
         <is>
           <t>AI 3차 초안(2026-10-21) · 근거 확인 ○: law.go.kr 원문 확인: 도로교통법(법률 제22067호, 2026.10.13. 시행) 제164조</t>
@@ -14664,10 +14880,14 @@
       <c r="N181" s="3" t="n"/>
       <c r="O181" s="3" t="inlineStr">
         <is>
-          <t>draft</t>
-        </is>
-      </c>
-      <c r="P181" s="3" t="n"/>
+          <t>verified</t>
+        </is>
+      </c>
+      <c r="P181" s="3" t="inlineStr">
+        <is>
+          <t>개발자 / 2026-10-21</t>
+        </is>
+      </c>
       <c r="Q181" s="3" t="inlineStr">
         <is>
           <t>AI 3차 초안(2026-10-21) · 근거 확인 ○: law.go.kr 원문 확인: 교통사고처리 특례법(2025.6.4. 시행) 제3조제1항</t>
@@ -14739,10 +14959,14 @@
       <c r="N182" s="3" t="n"/>
       <c r="O182" s="3" t="inlineStr">
         <is>
-          <t>draft</t>
-        </is>
-      </c>
-      <c r="P182" s="3" t="n"/>
+          <t>verified</t>
+        </is>
+      </c>
+      <c r="P182" s="3" t="inlineStr">
+        <is>
+          <t>개발자 / 2026-10-21</t>
+        </is>
+      </c>
       <c r="Q182" s="3" t="inlineStr">
         <is>
           <t>AI 3차 초안(2026-10-21) · 근거 확인 ○: law.go.kr 원문 확인: 교통사고처리 특례법(2025.6.4. 시행) 제3조제2항</t>
@@ -14814,10 +15038,14 @@
       <c r="N183" s="3" t="n"/>
       <c r="O183" s="3" t="inlineStr">
         <is>
-          <t>draft</t>
-        </is>
-      </c>
-      <c r="P183" s="3" t="n"/>
+          <t>verified</t>
+        </is>
+      </c>
+      <c r="P183" s="3" t="inlineStr">
+        <is>
+          <t>개발자 / 2026-10-21</t>
+        </is>
+      </c>
       <c r="Q183" s="3" t="inlineStr">
         <is>
           <t>AI 3차 초안(2026-10-21) · 근거 확인 ○: law.go.kr 원문 확인: 교통사고처리 특례법(2025.6.4. 시행) 제4조제1항</t>
@@ -14889,10 +15117,14 @@
       <c r="N184" s="3" t="n"/>
       <c r="O184" s="3" t="inlineStr">
         <is>
-          <t>draft</t>
-        </is>
-      </c>
-      <c r="P184" s="3" t="n"/>
+          <t>verified</t>
+        </is>
+      </c>
+      <c r="P184" s="3" t="inlineStr">
+        <is>
+          <t>개발자 / 2026-10-21</t>
+        </is>
+      </c>
       <c r="Q184" s="3" t="inlineStr">
         <is>
           <t>AI 3차 초안(2026-10-21) · 근거 확인 ○: law.go.kr 원문 확인: 교통사고처리 특례법(2025.6.4. 시행) 제3조제2항제9호</t>
@@ -14964,10 +15196,14 @@
       <c r="N185" s="3" t="n"/>
       <c r="O185" s="3" t="inlineStr">
         <is>
-          <t>draft</t>
-        </is>
-      </c>
-      <c r="P185" s="3" t="n"/>
+          <t>verified</t>
+        </is>
+      </c>
+      <c r="P185" s="3" t="inlineStr">
+        <is>
+          <t>개발자 / 2026-10-21</t>
+        </is>
+      </c>
       <c r="Q185" s="3" t="inlineStr">
         <is>
           <t>AI 3차 초안(2026-10-21) · 근거 확인 ○: law.go.kr 원문 확인: 특정범죄 가중처벌 등에 관한 법률(2025.7.2. 시행) 제5조의13</t>
@@ -15039,10 +15275,14 @@
       <c r="N186" s="3" t="n"/>
       <c r="O186" s="3" t="inlineStr">
         <is>
-          <t>draft</t>
-        </is>
-      </c>
-      <c r="P186" s="3" t="n"/>
+          <t>verified</t>
+        </is>
+      </c>
+      <c r="P186" s="3" t="inlineStr">
+        <is>
+          <t>개발자 / 2026-10-21</t>
+        </is>
+      </c>
       <c r="Q186" s="3" t="inlineStr">
         <is>
           <t>AI 3차 초안(2026-10-21) · 근거 확인 ○: law.go.kr 원문 확인: 도로교통법 시행령(2026.10.2. 시행) 제2조제1항</t>
@@ -15114,10 +15354,14 @@
       <c r="N187" s="3" t="n"/>
       <c r="O187" s="3" t="inlineStr">
         <is>
-          <t>draft</t>
-        </is>
-      </c>
-      <c r="P187" s="3" t="n"/>
+          <t>verified</t>
+        </is>
+      </c>
+      <c r="P187" s="3" t="inlineStr">
+        <is>
+          <t>개발자 / 2026-10-21</t>
+        </is>
+      </c>
       <c r="Q187" s="3" t="inlineStr">
         <is>
           <t>AI 3차 초안(2026-10-21) · 근거 확인 ○: law.go.kr 원문 확인: 도로교통법 시행령(2026.10.2. 시행) 제2조제2항</t>
@@ -15189,10 +15433,14 @@
       <c r="N188" s="3" t="n"/>
       <c r="O188" s="3" t="inlineStr">
         <is>
-          <t>draft</t>
-        </is>
-      </c>
-      <c r="P188" s="3" t="n"/>
+          <t>verified</t>
+        </is>
+      </c>
+      <c r="P188" s="3" t="inlineStr">
+        <is>
+          <t>개발자 / 2026-10-21</t>
+        </is>
+      </c>
       <c r="Q188" s="3" t="inlineStr">
         <is>
           <t>AI 3차 초안(2026-10-21) · 근거 확인 ○: law.go.kr 원문 확인: 도로교통법(법률 제22067호, 2026.10.13. 시행) 제30조</t>
@@ -15264,10 +15512,14 @@
       <c r="N189" s="3" t="n"/>
       <c r="O189" s="3" t="inlineStr">
         <is>
-          <t>draft</t>
-        </is>
-      </c>
-      <c r="P189" s="3" t="n"/>
+          <t>verified</t>
+        </is>
+      </c>
+      <c r="P189" s="3" t="inlineStr">
+        <is>
+          <t>개발자 / 2026-10-21</t>
+        </is>
+      </c>
       <c r="Q189" s="3" t="inlineStr">
         <is>
           <t>AI 3차 초안(2026-10-21) · 근거 확인 ○: law.go.kr 원문 확인: 도로교통법(법률 제22067호, 2026.10.13. 시행) 제54조제5항</t>
@@ -15339,10 +15591,14 @@
       <c r="N190" s="3" t="n"/>
       <c r="O190" s="3" t="inlineStr">
         <is>
-          <t>draft</t>
-        </is>
-      </c>
-      <c r="P190" s="3" t="n"/>
+          <t>verified</t>
+        </is>
+      </c>
+      <c r="P190" s="3" t="inlineStr">
+        <is>
+          <t>개발자 / 2026-10-21</t>
+        </is>
+      </c>
       <c r="Q190" s="3" t="inlineStr">
         <is>
           <t>AI 3차 초안(2026-10-21) · 근거 확인 ○: 화물자동차 운수사업법 시행령 제3조제1항 '20대를 말한다' — law.go.kr 현행 원문 확인(2026-10-21)</t>
@@ -15414,10 +15670,14 @@
       <c r="N191" s="3" t="n"/>
       <c r="O191" s="3" t="inlineStr">
         <is>
-          <t>draft</t>
-        </is>
-      </c>
-      <c r="P191" s="3" t="n"/>
+          <t>verified</t>
+        </is>
+      </c>
+      <c r="P191" s="3" t="inlineStr">
+        <is>
+          <t>개발자 / 2026-10-21</t>
+        </is>
+      </c>
       <c r="Q191" s="3" t="inlineStr">
         <is>
           <t>AI 3차 초안(2026-10-21) · 근거 확인 ○: 화물자동차 운수사업법 시행령 제3조제2항 제1~5호(주사무소는 관할 행정구역 내 이전만) — law.go.kr 현행 원문 확인(2026-10-21)</t>
@@ -15489,10 +15749,14 @@
       <c r="N192" s="3" t="n"/>
       <c r="O192" s="3" t="inlineStr">
         <is>
-          <t>draft</t>
-        </is>
-      </c>
-      <c r="P192" s="3" t="n"/>
+          <t>verified</t>
+        </is>
+      </c>
+      <c r="P192" s="3" t="inlineStr">
+        <is>
+          <t>개발자 / 2026-10-21</t>
+        </is>
+      </c>
       <c r="Q192" s="3" t="inlineStr">
         <is>
           <t>AI 3차 초안(2026-10-21) · 근거 확인 ○: 화물자동차 운수사업법 제4조제3호 — law.go.kr 현행 원문 확인(2026-10-21)</t>
@@ -15564,10 +15828,14 @@
       <c r="N193" s="3" t="n"/>
       <c r="O193" s="3" t="inlineStr">
         <is>
-          <t>draft</t>
-        </is>
-      </c>
-      <c r="P193" s="3" t="n"/>
+          <t>verified</t>
+        </is>
+      </c>
+      <c r="P193" s="3" t="inlineStr">
+        <is>
+          <t>개발자 / 2026-10-21</t>
+        </is>
+      </c>
       <c r="Q193" s="3" t="inlineStr">
         <is>
           <t>AI 3차 초안(2026-10-21) · 근거 확인 ○: 화물자동차 운수사업법 제4조제6호 '5년이 지나지 아니한 자' — law.go.kr 현행 원문 확인(2026-10-21)</t>
@@ -15639,10 +15907,14 @@
       <c r="N194" s="3" t="n"/>
       <c r="O194" s="3" t="inlineStr">
         <is>
-          <t>draft</t>
-        </is>
-      </c>
-      <c r="P194" s="3" t="n"/>
+          <t>verified</t>
+        </is>
+      </c>
+      <c r="P194" s="3" t="inlineStr">
+        <is>
+          <t>개발자 / 2026-10-21</t>
+        </is>
+      </c>
       <c r="Q194" s="3" t="inlineStr">
         <is>
           <t>AI 3차 초안(2026-10-21) · 근거 확인 ○: 화물자동차 운수사업법 제7조제2항 '3개월 이내' — law.go.kr 현행 원문 확인(2026-10-21) · 교차 점검 반영</t>
@@ -15714,10 +15986,14 @@
       <c r="N195" s="3" t="n"/>
       <c r="O195" s="3" t="inlineStr">
         <is>
-          <t>draft</t>
-        </is>
-      </c>
-      <c r="P195" s="3" t="n"/>
+          <t>verified</t>
+        </is>
+      </c>
+      <c r="P195" s="3" t="inlineStr">
+        <is>
+          <t>개발자 / 2026-10-21</t>
+        </is>
+      </c>
       <c r="Q195" s="3" t="inlineStr">
         <is>
           <t>AI 3차 초안(2026-10-21) · 근거 확인 ○: 화물자동차 운수사업법 제16조제1항 — law.go.kr 현행 원문 확인(2026-10-21)</t>
@@ -15789,10 +16065,14 @@
       <c r="N196" s="3" t="n"/>
       <c r="O196" s="3" t="inlineStr">
         <is>
-          <t>draft</t>
-        </is>
-      </c>
-      <c r="P196" s="3" t="n"/>
+          <t>verified</t>
+        </is>
+      </c>
+      <c r="P196" s="3" t="inlineStr">
+        <is>
+          <t>개발자 / 2026-10-21</t>
+        </is>
+      </c>
       <c r="Q196" s="3" t="inlineStr">
         <is>
           <t>AI 3차 초안(2026-10-21) · 근거 확인 ○: 화물자동차 운수사업법 제17조제1항 '90일 이내' — law.go.kr 현행 원문 확인(2026-10-21) · 교차 점검 반영</t>
@@ -15864,10 +16144,14 @@
       <c r="N197" s="3" t="n"/>
       <c r="O197" s="3" t="inlineStr">
         <is>
-          <t>draft</t>
-        </is>
-      </c>
-      <c r="P197" s="3" t="n"/>
+          <t>verified</t>
+        </is>
+      </c>
+      <c r="P197" s="3" t="inlineStr">
+        <is>
+          <t>개발자 / 2026-10-21</t>
+        </is>
+      </c>
       <c r="Q197" s="3" t="inlineStr">
         <is>
           <t>AI 3차 초안(2026-10-21) · 근거 확인 ○: 화물자동차 운수사업법 제18조제1항·제3항 — law.go.kr 현행 원문 확인(2026-10-21)</t>
@@ -15939,10 +16223,14 @@
       <c r="N198" s="3" t="n"/>
       <c r="O198" s="3" t="inlineStr">
         <is>
-          <t>draft</t>
-        </is>
-      </c>
-      <c r="P198" s="3" t="n"/>
+          <t>verified</t>
+        </is>
+      </c>
+      <c r="P198" s="3" t="inlineStr">
+        <is>
+          <t>개발자 / 2026-10-21</t>
+        </is>
+      </c>
       <c r="Q198" s="3" t="inlineStr">
         <is>
           <t>AI 3차 초안(2026-10-21) · 근거 확인 ○: 화물자동차 운수사업법 제19조제1항 단서(제1호·제5호·제13호) — law.go.kr 현행 원문 확인(2026-10-21)</t>
@@ -16014,10 +16302,14 @@
       <c r="N199" s="3" t="n"/>
       <c r="O199" s="3" t="inlineStr">
         <is>
-          <t>draft</t>
-        </is>
-      </c>
-      <c r="P199" s="3" t="n"/>
+          <t>verified</t>
+        </is>
+      </c>
+      <c r="P199" s="3" t="inlineStr">
+        <is>
+          <t>개발자 / 2026-10-21</t>
+        </is>
+      </c>
       <c r="Q199" s="3" t="inlineStr">
         <is>
           <t>AI 3차 초안(2026-10-21) · 근거 확인 ○: 화물자동차 운수사업법 시행령 제5조의2제1항 '차령 13년' — law.go.kr 현행 원문 확인(2026-10-21) · 교차 점검 반영</t>
@@ -16089,10 +16381,14 @@
       <c r="N200" s="3" t="n"/>
       <c r="O200" s="3" t="inlineStr">
         <is>
-          <t>draft</t>
-        </is>
-      </c>
-      <c r="P200" s="3" t="n"/>
+          <t>verified</t>
+        </is>
+      </c>
+      <c r="P200" s="3" t="inlineStr">
+        <is>
+          <t>개발자 / 2026-10-21</t>
+        </is>
+      </c>
       <c r="Q200" s="3" t="inlineStr">
         <is>
           <t>AI 3차 초안(2026-10-21) · 근거 확인 ○: 화물자동차 운수사업법 제20조제1항 제1~4호 — law.go.kr 현행 원문 확인(2026-10-21)</t>
@@ -16164,10 +16460,14 @@
       <c r="N201" s="3" t="n"/>
       <c r="O201" s="3" t="inlineStr">
         <is>
-          <t>draft</t>
-        </is>
-      </c>
-      <c r="P201" s="3" t="n"/>
+          <t>verified</t>
+        </is>
+      </c>
+      <c r="P201" s="3" t="inlineStr">
+        <is>
+          <t>개발자 / 2026-10-21</t>
+        </is>
+      </c>
       <c r="Q201" s="3" t="inlineStr">
         <is>
           <t>AI 3차 초안(2026-10-21) · 근거 확인 ○: 화물자동차 운수사업법 제21조제1항 '2천만원 이하' — law.go.kr 현행 원문 확인(2026-10-21)</t>
@@ -16238,7 +16538,12 @@
       </c>
       <c r="O202" t="inlineStr">
         <is>
-          <t>draft</t>
+          <t>verified</t>
+        </is>
+      </c>
+      <c r="P202" t="inlineStr">
+        <is>
+          <t>개발자 / 2026-10-21</t>
         </is>
       </c>
       <c r="Q202" t="inlineStr">
@@ -16311,7 +16616,12 @@
       </c>
       <c r="O203" t="inlineStr">
         <is>
-          <t>draft</t>
+          <t>verified</t>
+        </is>
+      </c>
+      <c r="P203" t="inlineStr">
+        <is>
+          <t>개발자 / 2026-10-21</t>
         </is>
       </c>
       <c r="Q203" t="inlineStr">
@@ -16384,7 +16694,12 @@
       </c>
       <c r="O204" t="inlineStr">
         <is>
-          <t>draft</t>
+          <t>verified</t>
+        </is>
+      </c>
+      <c r="P204" t="inlineStr">
+        <is>
+          <t>개발자 / 2026-10-21</t>
         </is>
       </c>
       <c r="Q204" t="inlineStr">
@@ -16457,7 +16772,12 @@
       </c>
       <c r="O205" t="inlineStr">
         <is>
-          <t>draft</t>
+          <t>verified</t>
+        </is>
+      </c>
+      <c r="P205" t="inlineStr">
+        <is>
+          <t>개발자 / 2026-10-21</t>
         </is>
       </c>
       <c r="Q205" t="inlineStr">
@@ -16530,7 +16850,12 @@
       </c>
       <c r="O206" t="inlineStr">
         <is>
-          <t>draft</t>
+          <t>verified</t>
+        </is>
+      </c>
+      <c r="P206" t="inlineStr">
+        <is>
+          <t>개발자 / 2026-10-21</t>
         </is>
       </c>
       <c r="Q206" t="inlineStr">
@@ -16603,7 +16928,12 @@
       </c>
       <c r="O207" t="inlineStr">
         <is>
-          <t>draft</t>
+          <t>verified</t>
+        </is>
+      </c>
+      <c r="P207" t="inlineStr">
+        <is>
+          <t>개발자 / 2026-10-21</t>
         </is>
       </c>
       <c r="Q207" t="inlineStr">
@@ -16676,7 +17006,12 @@
       </c>
       <c r="O208" t="inlineStr">
         <is>
-          <t>draft</t>
+          <t>verified</t>
+        </is>
+      </c>
+      <c r="P208" t="inlineStr">
+        <is>
+          <t>개발자 / 2026-10-21</t>
         </is>
       </c>
       <c r="Q208" t="inlineStr">
@@ -16749,7 +17084,12 @@
       </c>
       <c r="O209" t="inlineStr">
         <is>
-          <t>draft</t>
+          <t>verified</t>
+        </is>
+      </c>
+      <c r="P209" t="inlineStr">
+        <is>
+          <t>개발자 / 2026-10-21</t>
         </is>
       </c>
       <c r="Q209" t="inlineStr">
@@ -16822,7 +17162,12 @@
       </c>
       <c r="O210" t="inlineStr">
         <is>
-          <t>draft</t>
+          <t>verified</t>
+        </is>
+      </c>
+      <c r="P210" t="inlineStr">
+        <is>
+          <t>개발자 / 2026-10-21</t>
         </is>
       </c>
       <c r="Q210" t="inlineStr">
@@ -16895,7 +17240,12 @@
       </c>
       <c r="O211" t="inlineStr">
         <is>
-          <t>draft</t>
+          <t>verified</t>
+        </is>
+      </c>
+      <c r="P211" t="inlineStr">
+        <is>
+          <t>개발자 / 2026-10-21</t>
         </is>
       </c>
       <c r="Q211" t="inlineStr">
@@ -16968,7 +17318,12 @@
       </c>
       <c r="O212" t="inlineStr">
         <is>
-          <t>draft</t>
+          <t>verified</t>
+        </is>
+      </c>
+      <c r="P212" t="inlineStr">
+        <is>
+          <t>개발자 / 2026-10-21</t>
         </is>
       </c>
       <c r="Q212" t="inlineStr">
@@ -17041,7 +17396,12 @@
       </c>
       <c r="O213" t="inlineStr">
         <is>
-          <t>draft</t>
+          <t>verified</t>
+        </is>
+      </c>
+      <c r="P213" t="inlineStr">
+        <is>
+          <t>개발자 / 2026-10-21</t>
         </is>
       </c>
       <c r="Q213" t="inlineStr">
@@ -17114,7 +17474,12 @@
       </c>
       <c r="O214" t="inlineStr">
         <is>
-          <t>draft</t>
+          <t>verified</t>
+        </is>
+      </c>
+      <c r="P214" t="inlineStr">
+        <is>
+          <t>개발자 / 2026-10-21</t>
         </is>
       </c>
       <c r="Q214" t="inlineStr">
@@ -17187,7 +17552,12 @@
       </c>
       <c r="O215" t="inlineStr">
         <is>
-          <t>draft</t>
+          <t>verified</t>
+        </is>
+      </c>
+      <c r="P215" t="inlineStr">
+        <is>
+          <t>개발자 / 2026-10-21</t>
         </is>
       </c>
       <c r="Q215" t="inlineStr">
@@ -17260,7 +17630,12 @@
       </c>
       <c r="O216" t="inlineStr">
         <is>
-          <t>draft</t>
+          <t>verified</t>
+        </is>
+      </c>
+      <c r="P216" t="inlineStr">
+        <is>
+          <t>개발자 / 2026-10-21</t>
         </is>
       </c>
       <c r="Q216" t="inlineStr">
@@ -17333,7 +17708,12 @@
       </c>
       <c r="O217" t="inlineStr">
         <is>
-          <t>draft</t>
+          <t>verified</t>
+        </is>
+      </c>
+      <c r="P217" t="inlineStr">
+        <is>
+          <t>개발자 / 2026-10-21</t>
         </is>
       </c>
       <c r="Q217" t="inlineStr">
@@ -17406,7 +17786,12 @@
       </c>
       <c r="O218" t="inlineStr">
         <is>
-          <t>draft</t>
+          <t>verified</t>
+        </is>
+      </c>
+      <c r="P218" t="inlineStr">
+        <is>
+          <t>개발자 / 2026-10-21</t>
         </is>
       </c>
       <c r="Q218" t="inlineStr">
@@ -17479,7 +17864,12 @@
       </c>
       <c r="O219" t="inlineStr">
         <is>
-          <t>draft</t>
+          <t>verified</t>
+        </is>
+      </c>
+      <c r="P219" t="inlineStr">
+        <is>
+          <t>개발자 / 2026-10-21</t>
         </is>
       </c>
       <c r="Q219" t="inlineStr">
@@ -17552,7 +17942,12 @@
       </c>
       <c r="O220" t="inlineStr">
         <is>
-          <t>draft</t>
+          <t>verified</t>
+        </is>
+      </c>
+      <c r="P220" t="inlineStr">
+        <is>
+          <t>개발자 / 2026-10-21</t>
         </is>
       </c>
       <c r="Q220" t="inlineStr">
@@ -17625,7 +18020,12 @@
       </c>
       <c r="O221" t="inlineStr">
         <is>
-          <t>draft</t>
+          <t>verified</t>
+        </is>
+      </c>
+      <c r="P221" t="inlineStr">
+        <is>
+          <t>개발자 / 2026-10-21</t>
         </is>
       </c>
       <c r="Q221" t="inlineStr">
@@ -17698,7 +18098,12 @@
       </c>
       <c r="O222" t="inlineStr">
         <is>
-          <t>draft</t>
+          <t>verified</t>
+        </is>
+      </c>
+      <c r="P222" t="inlineStr">
+        <is>
+          <t>개발자 / 2026-10-21</t>
         </is>
       </c>
       <c r="Q222" t="inlineStr">
@@ -17771,7 +18176,12 @@
       </c>
       <c r="O223" t="inlineStr">
         <is>
-          <t>draft</t>
+          <t>verified</t>
+        </is>
+      </c>
+      <c r="P223" t="inlineStr">
+        <is>
+          <t>개발자 / 2026-10-21</t>
         </is>
       </c>
       <c r="Q223" t="inlineStr">
@@ -17844,7 +18254,12 @@
       </c>
       <c r="O224" t="inlineStr">
         <is>
-          <t>draft</t>
+          <t>verified</t>
+        </is>
+      </c>
+      <c r="P224" t="inlineStr">
+        <is>
+          <t>개발자 / 2026-10-21</t>
         </is>
       </c>
       <c r="Q224" t="inlineStr">
@@ -17917,7 +18332,12 @@
       </c>
       <c r="O225" t="inlineStr">
         <is>
-          <t>draft</t>
+          <t>verified</t>
+        </is>
+      </c>
+      <c r="P225" t="inlineStr">
+        <is>
+          <t>개발자 / 2026-10-21</t>
         </is>
       </c>
       <c r="Q225" t="inlineStr">
@@ -17990,7 +18410,12 @@
       </c>
       <c r="O226" t="inlineStr">
         <is>
-          <t>draft</t>
+          <t>verified</t>
+        </is>
+      </c>
+      <c r="P226" t="inlineStr">
+        <is>
+          <t>개발자 / 2026-10-21</t>
         </is>
       </c>
       <c r="Q226" t="inlineStr">
@@ -18063,7 +18488,12 @@
       </c>
       <c r="O227" t="inlineStr">
         <is>
-          <t>draft</t>
+          <t>verified</t>
+        </is>
+      </c>
+      <c r="P227" t="inlineStr">
+        <is>
+          <t>개발자 / 2026-10-21</t>
         </is>
       </c>
       <c r="Q227" t="inlineStr">
@@ -18136,7 +18566,12 @@
       </c>
       <c r="O228" t="inlineStr">
         <is>
-          <t>draft</t>
+          <t>verified</t>
+        </is>
+      </c>
+      <c r="P228" t="inlineStr">
+        <is>
+          <t>개발자 / 2026-10-21</t>
         </is>
       </c>
       <c r="Q228" t="inlineStr">
@@ -18209,7 +18644,12 @@
       </c>
       <c r="O229" t="inlineStr">
         <is>
-          <t>draft</t>
+          <t>verified</t>
+        </is>
+      </c>
+      <c r="P229" t="inlineStr">
+        <is>
+          <t>개발자 / 2026-10-21</t>
         </is>
       </c>
       <c r="Q229" t="inlineStr">
@@ -18282,7 +18722,12 @@
       </c>
       <c r="O230" t="inlineStr">
         <is>
-          <t>draft</t>
+          <t>verified</t>
+        </is>
+      </c>
+      <c r="P230" t="inlineStr">
+        <is>
+          <t>개발자 / 2026-10-21</t>
         </is>
       </c>
       <c r="Q230" t="inlineStr">
@@ -18355,7 +18800,12 @@
       </c>
       <c r="O231" t="inlineStr">
         <is>
-          <t>draft</t>
+          <t>verified</t>
+        </is>
+      </c>
+      <c r="P231" t="inlineStr">
+        <is>
+          <t>개발자 / 2026-10-21</t>
         </is>
       </c>
       <c r="Q231" t="inlineStr">
@@ -18428,7 +18878,12 @@
       </c>
       <c r="O232" t="inlineStr">
         <is>
-          <t>draft</t>
+          <t>verified</t>
+        </is>
+      </c>
+      <c r="P232" t="inlineStr">
+        <is>
+          <t>개발자 / 2026-10-21</t>
         </is>
       </c>
       <c r="Q232" t="inlineStr">
@@ -18501,7 +18956,12 @@
       </c>
       <c r="O233" t="inlineStr">
         <is>
-          <t>draft</t>
+          <t>verified</t>
+        </is>
+      </c>
+      <c r="P233" t="inlineStr">
+        <is>
+          <t>개발자 / 2026-10-21</t>
         </is>
       </c>
       <c r="Q233" t="inlineStr">
@@ -18574,7 +19034,12 @@
       </c>
       <c r="O234" t="inlineStr">
         <is>
-          <t>draft</t>
+          <t>verified</t>
+        </is>
+      </c>
+      <c r="P234" t="inlineStr">
+        <is>
+          <t>개발자 / 2026-10-21</t>
         </is>
       </c>
       <c r="Q234" t="inlineStr">
@@ -18647,7 +19112,12 @@
       </c>
       <c r="O235" t="inlineStr">
         <is>
-          <t>draft</t>
+          <t>verified</t>
+        </is>
+      </c>
+      <c r="P235" t="inlineStr">
+        <is>
+          <t>개발자 / 2026-10-21</t>
         </is>
       </c>
       <c r="Q235" t="inlineStr">
@@ -18720,7 +19190,12 @@
       </c>
       <c r="O236" t="inlineStr">
         <is>
-          <t>draft</t>
+          <t>verified</t>
+        </is>
+      </c>
+      <c r="P236" t="inlineStr">
+        <is>
+          <t>개발자 / 2026-10-21</t>
         </is>
       </c>
       <c r="Q236" t="inlineStr">
@@ -18793,7 +19268,12 @@
       </c>
       <c r="O237" t="inlineStr">
         <is>
-          <t>draft</t>
+          <t>verified</t>
+        </is>
+      </c>
+      <c r="P237" t="inlineStr">
+        <is>
+          <t>개발자 / 2026-10-21</t>
         </is>
       </c>
       <c r="Q237" t="inlineStr">
@@ -18866,7 +19346,12 @@
       </c>
       <c r="O238" t="inlineStr">
         <is>
-          <t>draft</t>
+          <t>verified</t>
+        </is>
+      </c>
+      <c r="P238" t="inlineStr">
+        <is>
+          <t>개발자 / 2026-10-21</t>
         </is>
       </c>
       <c r="Q238" t="inlineStr">
@@ -18939,7 +19424,12 @@
       </c>
       <c r="O239" t="inlineStr">
         <is>
-          <t>draft</t>
+          <t>verified</t>
+        </is>
+      </c>
+      <c r="P239" t="inlineStr">
+        <is>
+          <t>개발자 / 2026-10-21</t>
         </is>
       </c>
       <c r="Q239" t="inlineStr">
@@ -19012,7 +19502,12 @@
       </c>
       <c r="O240" t="inlineStr">
         <is>
-          <t>draft</t>
+          <t>verified</t>
+        </is>
+      </c>
+      <c r="P240" t="inlineStr">
+        <is>
+          <t>개발자 / 2026-10-21</t>
         </is>
       </c>
       <c r="Q240" t="inlineStr">
@@ -19085,7 +19580,12 @@
       </c>
       <c r="O241" t="inlineStr">
         <is>
-          <t>draft</t>
+          <t>verified</t>
+        </is>
+      </c>
+      <c r="P241" t="inlineStr">
+        <is>
+          <t>개발자 / 2026-10-21</t>
         </is>
       </c>
       <c r="Q241" t="inlineStr">
@@ -19158,7 +19658,12 @@
       </c>
       <c r="O242" t="inlineStr">
         <is>
-          <t>draft</t>
+          <t>verified</t>
+        </is>
+      </c>
+      <c r="P242" t="inlineStr">
+        <is>
+          <t>개발자 / 2026-10-21</t>
         </is>
       </c>
       <c r="Q242" t="inlineStr">
@@ -19231,7 +19736,12 @@
       </c>
       <c r="O243" t="inlineStr">
         <is>
-          <t>draft</t>
+          <t>verified</t>
+        </is>
+      </c>
+      <c r="P243" t="inlineStr">
+        <is>
+          <t>개발자 / 2026-10-21</t>
         </is>
       </c>
       <c r="Q243" t="inlineStr">
@@ -19304,7 +19814,12 @@
       </c>
       <c r="O244" t="inlineStr">
         <is>
-          <t>draft</t>
+          <t>verified</t>
+        </is>
+      </c>
+      <c r="P244" t="inlineStr">
+        <is>
+          <t>개발자 / 2026-10-21</t>
         </is>
       </c>
       <c r="Q244" t="inlineStr">
@@ -19377,7 +19892,12 @@
       </c>
       <c r="O245" t="inlineStr">
         <is>
-          <t>draft</t>
+          <t>verified</t>
+        </is>
+      </c>
+      <c r="P245" t="inlineStr">
+        <is>
+          <t>개발자 / 2026-10-21</t>
         </is>
       </c>
       <c r="Q245" t="inlineStr">
@@ -19450,7 +19970,12 @@
       </c>
       <c r="O246" t="inlineStr">
         <is>
-          <t>draft</t>
+          <t>verified</t>
+        </is>
+      </c>
+      <c r="P246" t="inlineStr">
+        <is>
+          <t>개발자 / 2026-10-21</t>
         </is>
       </c>
       <c r="Q246" t="inlineStr">
@@ -19523,7 +20048,12 @@
       </c>
       <c r="O247" t="inlineStr">
         <is>
-          <t>draft</t>
+          <t>verified</t>
+        </is>
+      </c>
+      <c r="P247" t="inlineStr">
+        <is>
+          <t>개발자 / 2026-10-21</t>
         </is>
       </c>
       <c r="Q247" t="inlineStr">
@@ -19596,7 +20126,12 @@
       </c>
       <c r="O248" t="inlineStr">
         <is>
-          <t>draft</t>
+          <t>verified</t>
+        </is>
+      </c>
+      <c r="P248" t="inlineStr">
+        <is>
+          <t>개발자 / 2026-10-21</t>
         </is>
       </c>
       <c r="Q248" t="inlineStr">
@@ -19669,7 +20204,12 @@
       </c>
       <c r="O249" t="inlineStr">
         <is>
-          <t>draft</t>
+          <t>verified</t>
+        </is>
+      </c>
+      <c r="P249" t="inlineStr">
+        <is>
+          <t>개발자 / 2026-10-21</t>
         </is>
       </c>
       <c r="Q249" t="inlineStr">
@@ -19742,7 +20282,12 @@
       </c>
       <c r="O250" t="inlineStr">
         <is>
-          <t>draft</t>
+          <t>verified</t>
+        </is>
+      </c>
+      <c r="P250" t="inlineStr">
+        <is>
+          <t>개발자 / 2026-10-21</t>
         </is>
       </c>
       <c r="Q250" t="inlineStr">
@@ -19815,7 +20360,12 @@
       </c>
       <c r="O251" t="inlineStr">
         <is>
-          <t>draft</t>
+          <t>verified</t>
+        </is>
+      </c>
+      <c r="P251" t="inlineStr">
+        <is>
+          <t>개발자 / 2026-10-21</t>
         </is>
       </c>
       <c r="Q251" t="inlineStr">

--- a/data/raw/문제_LAW.xlsx
+++ b/data/raw/문제_LAW.xlsx
@@ -565,7 +565,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:Q251"/>
+  <dimension ref="A1:Q376"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="11" customWidth="1" min="1" max="1"/>
@@ -20371,6 +20371,9756 @@
       <c r="Q251" t="inlineStr">
         <is>
           <t>AI 3차 초안(2026-10-21) · 근거 확인 ○: 도로교통법 제49조 제1항 제8호: '운전자는 정당한 사유 없이 다음 각 목의 어느 하나에 해당하는 행위를 하여 다른 사람에게 피해를 주는 소음을 발생시키지 아니할 것 가. 자동차등을 급히 출발시키거나 속도를 급격히 높이는 행위 나. 자동차등의 원동기 동력을 차의 바퀴에 전달시키지 아니하고 원동기의 회전수를 증가시키는 행위 다. 반복적이거나 연속적으로 경음기를 울리는 행위' (rtl.txt 확인)</t>
+        </is>
+      </c>
+    </row>
+    <row r="252">
+      <c r="A252" t="inlineStr">
+        <is>
+          <t>LAW-0251</t>
+        </is>
+      </c>
+      <c r="B252" t="inlineStr">
+        <is>
+          <t>보행자가 보도에서 통행하는 원칙으로 옳은 것은?</t>
+        </is>
+      </c>
+      <c r="C252" t="inlineStr">
+        <is>
+          <t>좌측통행</t>
+        </is>
+      </c>
+      <c r="D252" t="inlineStr">
+        <is>
+          <t>우측통행</t>
+        </is>
+      </c>
+      <c r="E252" t="inlineStr">
+        <is>
+          <t>보도 중앙 통행</t>
+        </is>
+      </c>
+      <c r="F252" t="inlineStr">
+        <is>
+          <t>차도 쪽 가장자리 통행</t>
+        </is>
+      </c>
+      <c r="G252" t="n">
+        <v>2</v>
+      </c>
+      <c r="H252" t="inlineStr">
+        <is>
+          <t>보행자는 보도에서는 우측통행을 원칙으로 한다(도로교통법 제8조제4항).</t>
+        </is>
+      </c>
+      <c r="I252" t="inlineStr">
+        <is>
+          <t>차마가 도로 중앙의 오른쪽을 다니는 것과 같은 방향 원칙을 떠올려 보세요.</t>
+        </is>
+      </c>
+      <c r="J252" t="inlineStr">
+        <is>
+          <t>도로교통법 제8조제4항</t>
+        </is>
+      </c>
+      <c r="K252" t="inlineStr">
+        <is>
+          <t>2026-10-22</t>
+        </is>
+      </c>
+      <c r="L252" t="inlineStr">
+        <is>
+          <t>자체 작성</t>
+        </is>
+      </c>
+      <c r="M252" t="n">
+        <v>1</v>
+      </c>
+      <c r="O252" t="inlineStr">
+        <is>
+          <t>verified</t>
+        </is>
+      </c>
+      <c r="P252" t="inlineStr">
+        <is>
+          <t>1등 / 2026-10-22</t>
+        </is>
+      </c>
+      <c r="Q252" t="inlineStr">
+        <is>
+          <t>AI 4차 초안(2026-10-21) · 근거 확인 ○: 도로교통법 제8조제4항 '보행자는 보도에서는 우측통행을 원칙으로 한다' 원문 확인(2026.10.13 시행본)</t>
+        </is>
+      </c>
+    </row>
+    <row r="253">
+      <c r="A253" t="inlineStr">
+        <is>
+          <t>LAW-0252</t>
+        </is>
+      </c>
+      <c r="B253" t="inlineStr">
+        <is>
+          <t>도로교통법령상 보도 대신 차도로 통행할 수 있는 사람이나 행렬에 해당하지 않는 것은?</t>
+        </is>
+      </c>
+      <c r="C253" t="inlineStr">
+        <is>
+          <t>말·소 등 큰 동물을 몰고 가는 사람</t>
+        </is>
+      </c>
+      <c r="D253" t="inlineStr">
+        <is>
+          <t>휴대전화를 보며 걷는 일반 보행자</t>
+        </is>
+      </c>
+      <c r="E253" t="inlineStr">
+        <is>
+          <t>장의(葬儀) 행렬</t>
+        </is>
+      </c>
+      <c r="F253" t="inlineStr">
+        <is>
+          <t>도로에서 청소나 보수 작업을 하고 있는 사람</t>
+        </is>
+      </c>
+      <c r="G253" t="n">
+        <v>2</v>
+      </c>
+      <c r="H253" t="inlineStr">
+        <is>
+          <t>시행령 제7조는 큰 동물을 몰고 가는 사람, 통행에 지장을 주는 물건 운반자, 청소·보수 작업자, 군부대 행렬, 기·현수막 휴대 행렬, 장의 행렬을 차도 통행 대상으로 정한다. 일반 보행자는 보도로 통행해야 한다.</t>
+        </is>
+      </c>
+      <c r="I253" t="inlineStr">
+        <is>
+          <t>보도에 있으면 다른 보행자의 통행에 지장을 줄 만한 사람이나 무리인지 따져 보세요.</t>
+        </is>
+      </c>
+      <c r="J253" t="inlineStr">
+        <is>
+          <t>도로교통법 제9조제1항, 도로교통법 시행령 제7조</t>
+        </is>
+      </c>
+      <c r="K253" t="inlineStr">
+        <is>
+          <t>2026-10-22</t>
+        </is>
+      </c>
+      <c r="L253" t="inlineStr">
+        <is>
+          <t>자체 작성</t>
+        </is>
+      </c>
+      <c r="M253" t="n">
+        <v>2</v>
+      </c>
+      <c r="O253" t="inlineStr">
+        <is>
+          <t>verified</t>
+        </is>
+      </c>
+      <c r="P253" t="inlineStr">
+        <is>
+          <t>1등 / 2026-10-22</t>
+        </is>
+      </c>
+      <c r="Q253" t="inlineStr">
+        <is>
+          <t>AI 4차 초안(2026-10-21) · 근거 확인 ○: 도로교통법 시행령 제7조 각 호 원문 확인</t>
+        </is>
+      </c>
+    </row>
+    <row r="254">
+      <c r="A254" t="inlineStr">
+        <is>
+          <t>LAW-0253</t>
+        </is>
+      </c>
+      <c r="B254" t="inlineStr">
+        <is>
+          <t>도로교통법상 '영유아'의 나이 기준은?</t>
+        </is>
+      </c>
+      <c r="C254" t="inlineStr">
+        <is>
+          <t>6세 미만</t>
+        </is>
+      </c>
+      <c r="D254" t="inlineStr">
+        <is>
+          <t>5세 미만</t>
+        </is>
+      </c>
+      <c r="E254" t="inlineStr">
+        <is>
+          <t>8세 미만</t>
+        </is>
+      </c>
+      <c r="F254" t="inlineStr">
+        <is>
+          <t>13세 미만</t>
+        </is>
+      </c>
+      <c r="G254" t="n">
+        <v>1</v>
+      </c>
+      <c r="H254" t="inlineStr">
+        <is>
+          <t>도로교통법 제11조제1항은 영유아를 6세 미만인 사람으로 정하고, 보호자는 교통이 빈번한 도로에서 영유아가 혼자 보행하게 해서는 안 된다.</t>
+        </is>
+      </c>
+      <c r="I254" t="inlineStr">
+        <is>
+          <t>어린이(13세 미만)보다 훨씬 어린, 대체로 초등학교에 들어가기 전 나이대입니다.</t>
+        </is>
+      </c>
+      <c r="J254" t="inlineStr">
+        <is>
+          <t>도로교통법 제11조제1항</t>
+        </is>
+      </c>
+      <c r="K254" t="inlineStr">
+        <is>
+          <t>2026-10-22</t>
+        </is>
+      </c>
+      <c r="L254" t="inlineStr">
+        <is>
+          <t>자체 작성</t>
+        </is>
+      </c>
+      <c r="M254" t="n">
+        <v>1</v>
+      </c>
+      <c r="O254" t="inlineStr">
+        <is>
+          <t>verified</t>
+        </is>
+      </c>
+      <c r="P254" t="inlineStr">
+        <is>
+          <t>1등 / 2026-10-22</t>
+        </is>
+      </c>
+      <c r="Q254" t="inlineStr">
+        <is>
+          <t>AI 4차 초안(2026-10-21) · 근거 확인 ○: 도로교통법 제11조제1항 '영유아(6세 미만인 사람을 말한다)' 원문 확인</t>
+        </is>
+      </c>
+    </row>
+    <row r="255">
+      <c r="A255" t="inlineStr">
+        <is>
+          <t>LAW-0254</t>
+        </is>
+      </c>
+      <c r="B255" t="inlineStr">
+        <is>
+          <t>도로교통법령상 고령운전자 표지에 대한 설명으로 옳은 것은?</t>
+        </is>
+      </c>
+      <c r="C255" t="inlineStr">
+        <is>
+          <t>65세 이상 운전자는 다른 운전자가 알아볼 수 있도록 표지를 차에 붙이고 운전할 수 있다</t>
+        </is>
+      </c>
+      <c r="D255" t="inlineStr">
+        <is>
+          <t>75세 이상 운전자는 반드시 표지를 붙여야 하며 붙이지 않으면 범칙금이 부과된다</t>
+        </is>
+      </c>
+      <c r="E255" t="inlineStr">
+        <is>
+          <t>표지를 붙이려면 관할 경찰서장의 허가를 받아야 한다</t>
+        </is>
+      </c>
+      <c r="F255" t="inlineStr">
+        <is>
+          <t>표지는 사업용 화물자동차에는 붙일 수 없다</t>
+        </is>
+      </c>
+      <c r="G255" t="n">
+        <v>1</v>
+      </c>
+      <c r="H255" t="inlineStr">
+        <is>
+          <t>국가나 지방자치단체는 고령운전자 표지를 제작·배부할 수 있고, 고령운전자는 이를 차에 부착하고 운전할 수 있다(의무가 아님). 시행규칙은 그 대상을 운전면허를 받은 65세 이상인 사람으로 정한다.</t>
+        </is>
+      </c>
+      <c r="I255" t="inlineStr">
+        <is>
+          <t>법 조문의 끝맺음이 '하여야 한다'인지 '할 수 있다'인지에 주목해 보세요.</t>
+        </is>
+      </c>
+      <c r="J255" t="inlineStr">
+        <is>
+          <t>도로교통법 제7조의2, 도로교통법 시행규칙 제10조의2</t>
+        </is>
+      </c>
+      <c r="K255" t="inlineStr">
+        <is>
+          <t>2026-10-22</t>
+        </is>
+      </c>
+      <c r="L255" t="inlineStr">
+        <is>
+          <t>자체 작성</t>
+        </is>
+      </c>
+      <c r="M255" t="n">
+        <v>2</v>
+      </c>
+      <c r="O255" t="inlineStr">
+        <is>
+          <t>verified</t>
+        </is>
+      </c>
+      <c r="P255" t="inlineStr">
+        <is>
+          <t>1등 / 2026-10-22</t>
+        </is>
+      </c>
+      <c r="Q255" t="inlineStr">
+        <is>
+          <t>AI 4차 초안(2026-10-21) · 근거 확인 ○: 도로교통법 제7조의2제2항('부착하고 운전할 수 있다'), 시행규칙 제10조의2제1항(65세 이상) 원문 확인</t>
+        </is>
+      </c>
+    </row>
+    <row r="256">
+      <c r="A256" t="inlineStr">
+        <is>
+          <t>LAW-0255</t>
+        </is>
+      </c>
+      <c r="B256" t="inlineStr">
+        <is>
+          <t>안전표지로 진로 변경이 특별히 금지된 곳에서도 진로를 변경할 수 있는 경우는?</t>
+        </is>
+      </c>
+      <c r="C256" t="inlineStr">
+        <is>
+          <t>앞차가 제한속도보다 느리게 가는 경우</t>
+        </is>
+      </c>
+      <c r="D256" t="inlineStr">
+        <is>
+          <t>나가야 할 출구를 지나칠 것 같은 경우</t>
+        </is>
+      </c>
+      <c r="E256" t="inlineStr">
+        <is>
+          <t>도로의 파손이나 도로공사 등으로 장애물이 있는 경우</t>
+        </is>
+      </c>
+      <c r="F256" t="inlineStr">
+        <is>
+          <t>방향지시등을 30미터 전부터 켠 경우</t>
+        </is>
+      </c>
+      <c r="G256" t="n">
+        <v>3</v>
+      </c>
+      <c r="H256" t="inlineStr">
+        <is>
+          <t>진로 변경 금지 장소에서는 진로를 바꿀 수 없으나, 도로 파손이나 도로공사 등으로 장애물이 있는 경우에는 예외이다(제14조제5항 단서).</t>
+        </is>
+      </c>
+      <c r="I256" t="inlineStr">
+        <is>
+          <t>운전자의 편의가 아니라 '그 차로로 계속 갈 수 없는 물리적 사정'을 찾아보세요.</t>
+        </is>
+      </c>
+      <c r="J256" t="inlineStr">
+        <is>
+          <t>도로교통법 제14조제5항</t>
+        </is>
+      </c>
+      <c r="K256" t="inlineStr">
+        <is>
+          <t>2026-10-22</t>
+        </is>
+      </c>
+      <c r="L256" t="inlineStr">
+        <is>
+          <t>자체 작성</t>
+        </is>
+      </c>
+      <c r="M256" t="n">
+        <v>1</v>
+      </c>
+      <c r="O256" t="inlineStr">
+        <is>
+          <t>verified</t>
+        </is>
+      </c>
+      <c r="P256" t="inlineStr">
+        <is>
+          <t>1등 / 2026-10-22</t>
+        </is>
+      </c>
+      <c r="Q256" t="inlineStr">
+        <is>
+          <t>AI 4차 초안(2026-10-21) · 근거 확인 ○: 도로교통법 제14조제5항 원문 확인</t>
+        </is>
+      </c>
+    </row>
+    <row r="257">
+      <c r="A257" t="inlineStr">
+        <is>
+          <t>LAW-0256</t>
+        </is>
+      </c>
+      <c r="B257" t="inlineStr">
+        <is>
+          <t>차의 너비가 차로의 너비보다 넓은 차가 출발지 관할 경찰서장의 통행 허가를 받을 때, 그 차가 「도로법」상 운행허가 대상이라면 어떻게 처리되는가?</t>
+        </is>
+      </c>
+      <c r="C257" t="inlineStr">
+        <is>
+          <t>경찰서장 허가와 별도로 도로관리청의 운행허가를 반드시 다시 받아야 한다</t>
+        </is>
+      </c>
+      <c r="D257" t="inlineStr">
+        <is>
+          <t>경찰서장이 도로관리청과 미리 협의하여 허가하면 도로법상 운행허가를 받은 것으로 본다</t>
+        </is>
+      </c>
+      <c r="E257" t="inlineStr">
+        <is>
+          <t>도로법 운행허가 대상 차는 경찰서장이 허가할 수 없다</t>
+        </is>
+      </c>
+      <c r="F257" t="inlineStr">
+        <is>
+          <t>도착지 관할 시·도지사의 승인으로 두 허가를 대신한다</t>
+        </is>
+      </c>
+      <c r="G257" t="n">
+        <v>2</v>
+      </c>
+      <c r="H257" t="inlineStr">
+        <is>
+          <t>차로폭을 넘는 차의 통행허가 시 도로법상 운행허가 대상이면 경찰서장이 도로관리청과 미리 협의해야 하고, 협의를 거쳐 허가받은 차는 도로법상 운행허가를 받은 것으로 본다(제14조제3항·제4항).</t>
+        </is>
+      </c>
+      <c r="I257" t="inlineStr">
+        <is>
+          <t>두 기관이 같은 차를 두 번 심사하지 않도록 한 '협의 후 의제' 장치입니다.</t>
+        </is>
+      </c>
+      <c r="J257" t="inlineStr">
+        <is>
+          <t>도로교통법 제14조제3항·제4항</t>
+        </is>
+      </c>
+      <c r="K257" t="inlineStr">
+        <is>
+          <t>2026-10-22</t>
+        </is>
+      </c>
+      <c r="L257" t="inlineStr">
+        <is>
+          <t>자체 작성</t>
+        </is>
+      </c>
+      <c r="M257" t="n">
+        <v>3</v>
+      </c>
+      <c r="O257" t="inlineStr">
+        <is>
+          <t>verified</t>
+        </is>
+      </c>
+      <c r="P257" t="inlineStr">
+        <is>
+          <t>1등 / 2026-10-22</t>
+        </is>
+      </c>
+      <c r="Q257" t="inlineStr">
+        <is>
+          <t>AI 4차 초안(2026-10-21) · 근거 확인 ○: 도로교통법 제14조제3항(출발지 관할 경찰서장 허가)·제4항(협의 및 운행허가 의제) 원문 확인</t>
+        </is>
+      </c>
+    </row>
+    <row r="258">
+      <c r="A258" t="inlineStr">
+        <is>
+          <t>LAW-0257</t>
+        </is>
+      </c>
+      <c r="B258" t="inlineStr">
+        <is>
+          <t>통행 구분이 설치되지 않은 도로에서 뒤따라오는 차보다 느린 속도로 가려는 차(긴급자동차 제외)의 운전자가 해야 할 일은?</t>
+        </is>
+      </c>
+      <c r="C258" t="inlineStr">
+        <is>
+          <t>비상점멸등을 켜고 같은 속도로 계속 주행한다</t>
+        </is>
+      </c>
+      <c r="D258" t="inlineStr">
+        <is>
+          <t>도로 중앙선 쪽으로 붙어 뒤차가 오른쪽으로 지나가게 한다</t>
+        </is>
+      </c>
+      <c r="E258" t="inlineStr">
+        <is>
+          <t>도로의 우측 가장자리로 피하여 진로를 양보한다</t>
+        </is>
+      </c>
+      <c r="F258" t="inlineStr">
+        <is>
+          <t>경음기를 울려 뒤차에 속도를 줄이라고 알린다</t>
+        </is>
+      </c>
+      <c r="G258" t="n">
+        <v>3</v>
+      </c>
+      <c r="H258" t="inlineStr">
+        <is>
+          <t>모든 차(긴급자동차 제외)의 운전자는 뒤에서 따라오는 차보다 느린 속도로 가려는 경우 도로의 우측 가장자리로 피하여 진로를 양보해야 한다.</t>
+        </is>
+      </c>
+      <c r="I258" t="inlineStr">
+        <is>
+          <t>앞지르기는 앞차의 왼쪽으로 한다는 원칙과 함께 생각하면, 느린 차가 비켜 줄 방향이 보입니다.</t>
+        </is>
+      </c>
+      <c r="J258" t="inlineStr">
+        <is>
+          <t>도로교통법 제20조제1항</t>
+        </is>
+      </c>
+      <c r="K258" t="inlineStr">
+        <is>
+          <t>2026-10-22</t>
+        </is>
+      </c>
+      <c r="L258" t="inlineStr">
+        <is>
+          <t>자체 작성</t>
+        </is>
+      </c>
+      <c r="M258" t="n">
+        <v>1</v>
+      </c>
+      <c r="O258" t="inlineStr">
+        <is>
+          <t>verified</t>
+        </is>
+      </c>
+      <c r="P258" t="inlineStr">
+        <is>
+          <t>1등 / 2026-10-22</t>
+        </is>
+      </c>
+      <c r="Q258" t="inlineStr">
+        <is>
+          <t>AI 4차 초안(2026-10-21) · 근거 확인 ○: 도로교통법 제20조제1항 원문 확인</t>
+        </is>
+      </c>
+    </row>
+    <row r="259">
+      <c r="A259" t="inlineStr">
+        <is>
+          <t>LAW-0258</t>
+        </is>
+      </c>
+      <c r="B259" t="inlineStr">
+        <is>
+          <t>비탈진 곳이 아닌 좁은 도로에서 짐을 실은 화물자동차와 동승자도 없고 짐도 싣지 않은 화물자동차가 마주보고 진행할 때 진로를 양보해야 하는 차는?</t>
+        </is>
+      </c>
+      <c r="C259" t="inlineStr">
+        <is>
+          <t>물건을 실은 자동차</t>
+        </is>
+      </c>
+      <c r="D259" t="inlineStr">
+        <is>
+          <t>차체가 더 큰 자동차</t>
+        </is>
+      </c>
+      <c r="E259" t="inlineStr">
+        <is>
+          <t>동승자가 없고 물건을 싣지 않은 자동차</t>
+        </is>
+      </c>
+      <c r="F259" t="inlineStr">
+        <is>
+          <t>먼저 좁은 도로에 들어온 자동차</t>
+        </is>
+      </c>
+      <c r="G259" t="n">
+        <v>3</v>
+      </c>
+      <c r="H259" t="inlineStr">
+        <is>
+          <t>비탈진 좁은 도로 외의 좁은 도로에서는 사람을 태웠거나 물건을 실은 차와 빈 차가 마주칠 때 빈 차가 우측 가장자리로 피하여 양보한다(제20조제2항제2호).</t>
+        </is>
+      </c>
+      <c r="I259" t="inlineStr">
+        <is>
+          <t>움직이기 더 쉽고, 양보해도 손해(승객·화물 위험)가 적은 쪽이 어느 쪽인지 생각해 보세요.</t>
+        </is>
+      </c>
+      <c r="J259" t="inlineStr">
+        <is>
+          <t>도로교통법 제20조제2항제2호</t>
+        </is>
+      </c>
+      <c r="K259" t="inlineStr">
+        <is>
+          <t>2026-10-22</t>
+        </is>
+      </c>
+      <c r="L259" t="inlineStr">
+        <is>
+          <t>자체 작성</t>
+        </is>
+      </c>
+      <c r="M259" t="n">
+        <v>2</v>
+      </c>
+      <c r="O259" t="inlineStr">
+        <is>
+          <t>verified</t>
+        </is>
+      </c>
+      <c r="P259" t="inlineStr">
+        <is>
+          <t>1등 / 2026-10-22</t>
+        </is>
+      </c>
+      <c r="Q259" t="inlineStr">
+        <is>
+          <t>AI 4차 초안(2026-10-21) · 근거 확인 ○: 도로교통법 제20조제2항제2호 원문 확인</t>
+        </is>
+      </c>
+    </row>
+    <row r="260">
+      <c r="A260" t="inlineStr">
+        <is>
+          <t>LAW-0259</t>
+        </is>
+      </c>
+      <c r="B260" t="inlineStr">
+        <is>
+          <t>앞차의 우측으로 앞지르기를 할 수 있는 경우로 도로교통법에 규정된 것은?</t>
+        </is>
+      </c>
+      <c r="C260" t="inlineStr">
+        <is>
+          <t>자전거등의 운전자가 서행하거나 정지한 다른 차를 앞지르는 경우</t>
+        </is>
+      </c>
+      <c r="D260" t="inlineStr">
+        <is>
+          <t>고속도로 1차로에서 앞차가 너무 느린 경우</t>
+        </is>
+      </c>
+      <c r="E260" t="inlineStr">
+        <is>
+          <t>편도 2차로 일반도로에서 앞차가 제한속도보다 느린 경우</t>
+        </is>
+      </c>
+      <c r="F260" t="inlineStr">
+        <is>
+          <t>밤에 앞차가 상향등을 켜고 주행하는 경우</t>
+        </is>
+      </c>
+      <c r="G260" t="n">
+        <v>1</v>
+      </c>
+      <c r="H260" t="inlineStr">
+        <is>
+          <t>모든 차는 앞차의 좌측으로 앞질러야 하지만, 자전거등은 서행하거나 정지한 차를 우측으로 앞지를 수 있다. 이때 승하차하는 사람의 안전에 유의해야 한다.</t>
+        </is>
+      </c>
+      <c r="I260" t="inlineStr">
+        <is>
+          <t>도로 오른쪽 가장자리를 주로 다니는 차마에게만 인정되는 예외입니다.</t>
+        </is>
+      </c>
+      <c r="J260" t="inlineStr">
+        <is>
+          <t>도로교통법 제21조제1항·제2항</t>
+        </is>
+      </c>
+      <c r="K260" t="inlineStr">
+        <is>
+          <t>2026-10-22</t>
+        </is>
+      </c>
+      <c r="L260" t="inlineStr">
+        <is>
+          <t>자체 작성</t>
+        </is>
+      </c>
+      <c r="M260" t="n">
+        <v>2</v>
+      </c>
+      <c r="O260" t="inlineStr">
+        <is>
+          <t>verified</t>
+        </is>
+      </c>
+      <c r="P260" t="inlineStr">
+        <is>
+          <t>1등 / 2026-10-22</t>
+        </is>
+      </c>
+      <c r="Q260" t="inlineStr">
+        <is>
+          <t>AI 4차 초안(2026-10-21) · 근거 확인 ○: 도로교통법 제21조제2항 원문 확인</t>
+        </is>
+      </c>
+    </row>
+    <row r="261">
+      <c r="A261" t="inlineStr">
+        <is>
+          <t>LAW-0260</t>
+        </is>
+      </c>
+      <c r="B261" t="inlineStr">
+        <is>
+          <t>모든 차의 운전자가 운전하는 차를 갑자기 정지시키거나 속도를 줄이는 급제동을 할 수 있는 경우는?</t>
+        </is>
+      </c>
+      <c r="C261" t="inlineStr">
+        <is>
+          <t>뒤차가 너무 가까이 따라와 경고하려는 경우</t>
+        </is>
+      </c>
+      <c r="D261" t="inlineStr">
+        <is>
+          <t>앞지르기를 당한 뒤 항의하려는 경우</t>
+        </is>
+      </c>
+      <c r="E261" t="inlineStr">
+        <is>
+          <t>위험방지를 위한 경우와 그 밖의 부득이한 경우</t>
+        </is>
+      </c>
+      <c r="F261" t="inlineStr">
+        <is>
+          <t>길을 잘못 들어 주변을 살피려는 경우</t>
+        </is>
+      </c>
+      <c r="G261" t="n">
+        <v>3</v>
+      </c>
+      <c r="H261" t="inlineStr">
+        <is>
+          <t>운전자는 위험방지를 위한 경우와 그 밖의 부득이한 경우가 아니면 급제동을 해서는 안 된다(제19조제4항).</t>
+        </is>
+      </c>
+      <c r="I261" t="inlineStr">
+        <is>
+          <t>급제동은 뒤차 추돌을 부르는 행동이라, 그보다 더 큰 위험을 피할 때만 허용됩니다.</t>
+        </is>
+      </c>
+      <c r="J261" t="inlineStr">
+        <is>
+          <t>도로교통법 제19조제4항</t>
+        </is>
+      </c>
+      <c r="K261" t="inlineStr">
+        <is>
+          <t>2026-10-22</t>
+        </is>
+      </c>
+      <c r="L261" t="inlineStr">
+        <is>
+          <t>자체 작성</t>
+        </is>
+      </c>
+      <c r="M261" t="n">
+        <v>1</v>
+      </c>
+      <c r="O261" t="inlineStr">
+        <is>
+          <t>verified</t>
+        </is>
+      </c>
+      <c r="P261" t="inlineStr">
+        <is>
+          <t>1등 / 2026-10-22</t>
+        </is>
+      </c>
+      <c r="Q261" t="inlineStr">
+        <is>
+          <t>AI 4차 초안(2026-10-21) · 근거 확인 ○: 도로교통법 제19조제4항 원문 확인</t>
+        </is>
+      </c>
+    </row>
+    <row r="262">
+      <c r="A262" t="inlineStr">
+        <is>
+          <t>LAW-0261</t>
+        </is>
+      </c>
+      <c r="B262" t="inlineStr">
+        <is>
+          <t>보행자가 횡단보도가 설치되지 않은 도로를 횡단하고 있을 때 운전자가 해야 할 일은?</t>
+        </is>
+      </c>
+      <c r="C262" t="inlineStr">
+        <is>
+          <t>안전거리를 두고 일시정지하여 보행자가 안전하게 횡단하도록 한다</t>
+        </is>
+      </c>
+      <c r="D262" t="inlineStr">
+        <is>
+          <t>횡단보도가 아니므로 경음기를 울리고 계속 진행한다</t>
+        </is>
+      </c>
+      <c r="E262" t="inlineStr">
+        <is>
+          <t>보행자 뒤쪽으로 돌아서 속도를 줄이지 않고 지나간다</t>
+        </is>
+      </c>
+      <c r="F262" t="inlineStr">
+        <is>
+          <t>보행자가 다 건널 때까지 상향등을 켜 경고한다</t>
+        </is>
+      </c>
+      <c r="G262" t="n">
+        <v>1</v>
+      </c>
+      <c r="H262" t="inlineStr">
+        <is>
+          <t>보행자가 횡단보도가 없는 도로를 횡단하고 있을 때에도 운전자는 안전거리를 두고 일시정지하여 보행자가 안전하게 횡단할 수 있도록 해야 한다(제27조제5항).</t>
+        </is>
+      </c>
+      <c r="I262" t="inlineStr">
+        <is>
+          <t>횡단보도 밖이라도 보행자를 보호하는 원칙은 같습니다. 바퀴를 어떻게 해야 할지 생각해 보세요.</t>
+        </is>
+      </c>
+      <c r="J262" t="inlineStr">
+        <is>
+          <t>도로교통법 제27조제5항</t>
+        </is>
+      </c>
+      <c r="K262" t="inlineStr">
+        <is>
+          <t>2026-10-22</t>
+        </is>
+      </c>
+      <c r="L262" t="inlineStr">
+        <is>
+          <t>자체 작성</t>
+        </is>
+      </c>
+      <c r="M262" t="n">
+        <v>1</v>
+      </c>
+      <c r="O262" t="inlineStr">
+        <is>
+          <t>verified</t>
+        </is>
+      </c>
+      <c r="P262" t="inlineStr">
+        <is>
+          <t>1등 / 2026-10-22</t>
+        </is>
+      </c>
+      <c r="Q262" t="inlineStr">
+        <is>
+          <t>AI 4차 초안(2026-10-21) · 근거 확인 ○: 도로교통법 제27조제5항 원문 확인</t>
+        </is>
+      </c>
+    </row>
+    <row r="263">
+      <c r="A263" t="inlineStr">
+        <is>
+          <t>LAW-0262</t>
+        </is>
+      </c>
+      <c r="B263" t="inlineStr">
+        <is>
+          <t>경찰서장이나 시장등이 주차위반 차를 견인·보관하고 반환 조치나 공고를 하였는데도 차의 사용자나 운전자가 반환을 요구하지 않을 때, 그 차를 매각하거나 폐차할 수 있는 기준은?</t>
+        </is>
+      </c>
+      <c r="C263" t="inlineStr">
+        <is>
+          <t>견인한 날부터 7일 이내에 반환을 요구하지 않은 때</t>
+        </is>
+      </c>
+      <c r="D263" t="inlineStr">
+        <is>
+          <t>조치 또는 공고를 한 날부터 1개월 이내에 반환을 요구하지 않은 때</t>
+        </is>
+      </c>
+      <c r="E263" t="inlineStr">
+        <is>
+          <t>조치 또는 공고를 한 날부터 6개월 이내에 반환을 요구하지 않은 때</t>
+        </is>
+      </c>
+      <c r="F263" t="inlineStr">
+        <is>
+          <t>견인한 날부터 1년이 지난 때</t>
+        </is>
+      </c>
+      <c r="G263" t="n">
+        <v>2</v>
+      </c>
+      <c r="H263" t="inlineStr">
+        <is>
+          <t>반환 조치나 공고를 한 날부터 1개월 이내에 반환을 요구하지 않으면 대통령령에 따라 매각하거나 폐차할 수 있고, 이동·보관·매각 등 비용은 차의 사용자가 부담한다(제35조제5항·제6항).</t>
+        </is>
+      </c>
+      <c r="I263" t="inlineStr">
+        <is>
+          <t>보관 비용이 계속 쌓이므로 기간을 길게 두지 않습니다. 기산점이 견인한 날인지, 조치·공고한 날인지도 확인하세요.</t>
+        </is>
+      </c>
+      <c r="J263" t="inlineStr">
+        <is>
+          <t>도로교통법 제35조제5항</t>
+        </is>
+      </c>
+      <c r="K263" t="inlineStr">
+        <is>
+          <t>2026-10-22</t>
+        </is>
+      </c>
+      <c r="L263" t="inlineStr">
+        <is>
+          <t>자체 작성</t>
+        </is>
+      </c>
+      <c r="M263" t="n">
+        <v>3</v>
+      </c>
+      <c r="O263" t="inlineStr">
+        <is>
+          <t>verified</t>
+        </is>
+      </c>
+      <c r="P263" t="inlineStr">
+        <is>
+          <t>1등 / 2026-10-22</t>
+        </is>
+      </c>
+      <c r="Q263" t="inlineStr">
+        <is>
+          <t>AI 4차 초안(2026-10-21) · 근거 확인 ○: 도로교통법 제35조제5항 '조치 또는 공고를 한 날부터 1개월 이내' 원문 확인 · 교차 점검 반영</t>
+        </is>
+      </c>
+    </row>
+    <row r="264">
+      <c r="A264" t="inlineStr">
+        <is>
+          <t>LAW-0263</t>
+        </is>
+      </c>
+      <c r="B264" t="inlineStr">
+        <is>
+          <t>차도와 보도의 구별이 없는 도로에서 정차할 때 지켜야 할 방법으로 옳은 것은?</t>
+        </is>
+      </c>
+      <c r="C264" t="inlineStr">
+        <is>
+          <t>도로의 왼쪽 가장자리에 바짝 붙여 정차한다</t>
+        </is>
+      </c>
+      <c r="D264" t="inlineStr">
+        <is>
+          <t>도로의 오른쪽 가장자리로부터 중앙으로 2미터 이상 떨어져 정차한다</t>
+        </is>
+      </c>
+      <c r="E264" t="inlineStr">
+        <is>
+          <t>도로의 오른쪽 가장자리로부터 중앙으로 50센티미터 이상의 거리를 두어야 한다</t>
+        </is>
+      </c>
+      <c r="F264" t="inlineStr">
+        <is>
+          <t>도로 중앙선에 붙여 정차한다</t>
+        </is>
+      </c>
+      <c r="G264" t="n">
+        <v>3</v>
+      </c>
+      <c r="H264" t="inlineStr">
+        <is>
+          <t>모든 차는 도로에서 정차할 때 차도의 오른쪽 가장자리에 정차해야 하며, 차도와 보도의 구별이 없는 도로에서는 오른쪽 가장자리로부터 중앙으로 50센티미터 이상 거리를 두어야 한다(시행령 제11조제1항제1호).</t>
+        </is>
+      </c>
+      <c r="I264" t="inlineStr">
+        <is>
+          <t>보행자가 길 가장자리로 지나갈 수 있을 만큼의 좁은 틈을 남기는 기준입니다.</t>
+        </is>
+      </c>
+      <c r="J264" t="inlineStr">
+        <is>
+          <t>도로교통법 제34조, 도로교통법 시행령 제11조제1항제1호</t>
+        </is>
+      </c>
+      <c r="K264" t="inlineStr">
+        <is>
+          <t>2026-10-22</t>
+        </is>
+      </c>
+      <c r="L264" t="inlineStr">
+        <is>
+          <t>자체 작성</t>
+        </is>
+      </c>
+      <c r="M264" t="n">
+        <v>3</v>
+      </c>
+      <c r="O264" t="inlineStr">
+        <is>
+          <t>verified</t>
+        </is>
+      </c>
+      <c r="P264" t="inlineStr">
+        <is>
+          <t>1등 / 2026-10-22</t>
+        </is>
+      </c>
+      <c r="Q264" t="inlineStr">
+        <is>
+          <t>AI 4차 초안(2026-10-21) · 근거 확인 ○: 도로교통법 시행령 제11조제1항제1호 '50센티미터 이상의 거리' 원문 확인</t>
+        </is>
+      </c>
+    </row>
+    <row r="265">
+      <c r="A265" t="inlineStr">
+        <is>
+          <t>LAW-0264</t>
+        </is>
+      </c>
+      <c r="B265" t="inlineStr">
+        <is>
+          <t>도로교통법상 등화를 켜야 하는 '밤'의 뜻으로 옳은 것은?</t>
+        </is>
+      </c>
+      <c r="C265" t="inlineStr">
+        <is>
+          <t>오후 6시부터 다음 날 오전 6시까지</t>
+        </is>
+      </c>
+      <c r="D265" t="inlineStr">
+        <is>
+          <t>오후 8시부터 다음 날 오전 5시까지</t>
+        </is>
+      </c>
+      <c r="E265" t="inlineStr">
+        <is>
+          <t>가로등이 켜져 있는 시간</t>
+        </is>
+      </c>
+      <c r="F265" t="inlineStr">
+        <is>
+          <t>해가 진 후부터 해가 뜨기 전까지</t>
+        </is>
+      </c>
+      <c r="G265" t="n">
+        <v>4</v>
+      </c>
+      <c r="H265" t="inlineStr">
+        <is>
+          <t>도로교통법 제37조제1항제1호는 밤을 '해가 진 후부터 해가 뜨기 전까지'로 정한다. 시계 시각이 아니라 일몰·일출이 기준이다.</t>
+        </is>
+      </c>
+      <c r="I265" t="inlineStr">
+        <is>
+          <t>계절에 따라 길이가 달라지는 기준입니다. 고정된 시각이 아닙니다.</t>
+        </is>
+      </c>
+      <c r="J265" t="inlineStr">
+        <is>
+          <t>도로교통법 제37조제1항제1호</t>
+        </is>
+      </c>
+      <c r="K265" t="inlineStr">
+        <is>
+          <t>2026-10-22</t>
+        </is>
+      </c>
+      <c r="L265" t="inlineStr">
+        <is>
+          <t>자체 작성</t>
+        </is>
+      </c>
+      <c r="M265" t="n">
+        <v>1</v>
+      </c>
+      <c r="O265" t="inlineStr">
+        <is>
+          <t>verified</t>
+        </is>
+      </c>
+      <c r="P265" t="inlineStr">
+        <is>
+          <t>1등 / 2026-10-22</t>
+        </is>
+      </c>
+      <c r="Q265" t="inlineStr">
+        <is>
+          <t>AI 4차 초안(2026-10-21) · 근거 확인 ○: 도로교통법 제37조제1항제1호 괄호 정의 원문 확인</t>
+        </is>
+      </c>
+    </row>
+    <row r="266">
+      <c r="A266" t="inlineStr">
+        <is>
+          <t>LAW-0265</t>
+        </is>
+      </c>
+      <c r="B266" t="inlineStr">
+        <is>
+          <t>밤에 마주 오는 차와 서로 마주보고 진행할 때 운전자의 등화 조작 방법으로 옳은 것은?</t>
+        </is>
+      </c>
+      <c r="C266" t="inlineStr">
+        <is>
+          <t>상대 차가 잘 보도록 전조등을 위로 향하게 한다</t>
+        </is>
+      </c>
+      <c r="D266" t="inlineStr">
+        <is>
+          <t>전조등을 끄고 미등만 켠 채 계속 주행한다</t>
+        </is>
+      </c>
+      <c r="E266" t="inlineStr">
+        <is>
+          <t>전조등을 깜빡여 상대 차에게 먼저 지나가라고 신호한다</t>
+        </is>
+      </c>
+      <c r="F266" t="inlineStr">
+        <is>
+          <t>전조등의 밝기를 줄이거나 불빛의 방향을 아래로 향하게 하거나 잠시 전조등을 끈다</t>
+        </is>
+      </c>
+      <c r="G266" t="n">
+        <v>4</v>
+      </c>
+      <c r="H266" t="inlineStr">
+        <is>
+          <t>밤에 서로 마주보고 진행할 때는 전조등의 밝기를 줄이거나 불빛 방향을 아래로 향하게 하거나 잠시 전조등을 꺼야 한다(시행령 제20조제1항제1호).</t>
+        </is>
+      </c>
+      <c r="I266" t="inlineStr">
+        <is>
+          <t>상대 운전자의 눈부심을 줄이는 방향으로 조작해야 합니다.</t>
+        </is>
+      </c>
+      <c r="J266" t="inlineStr">
+        <is>
+          <t>도로교통법 제37조제2항, 도로교통법 시행령 제20조제1항제1호</t>
+        </is>
+      </c>
+      <c r="K266" t="inlineStr">
+        <is>
+          <t>2026-10-22</t>
+        </is>
+      </c>
+      <c r="L266" t="inlineStr">
+        <is>
+          <t>자체 작성</t>
+        </is>
+      </c>
+      <c r="M266" t="n">
+        <v>1</v>
+      </c>
+      <c r="O266" t="inlineStr">
+        <is>
+          <t>verified</t>
+        </is>
+      </c>
+      <c r="P266" t="inlineStr">
+        <is>
+          <t>1등 / 2026-10-22</t>
+        </is>
+      </c>
+      <c r="Q266" t="inlineStr">
+        <is>
+          <t>AI 4차 초안(2026-10-21) · 근거 확인 ○: 도로교통법 시행령 제20조제1항제1호 원문 확인</t>
+        </is>
+      </c>
+    </row>
+    <row r="267">
+      <c r="A267" t="inlineStr">
+        <is>
+          <t>LAW-0266</t>
+        </is>
+      </c>
+      <c r="B267" t="inlineStr">
+        <is>
+          <t>도로교통법상 운전자가 해서는 안 되는 행위로 규정된 것은?</t>
+        </is>
+      </c>
+      <c r="C267" t="inlineStr">
+        <is>
+          <t>영유아나 동물을 안고 운전 장치를 조작하는 행위</t>
+        </is>
+      </c>
+      <c r="D267" t="inlineStr">
+        <is>
+          <t>정차한 상태에서 지도를 확인하는 행위</t>
+        </is>
+      </c>
+      <c r="E267" t="inlineStr">
+        <is>
+          <t>운전 전에 좌석과 후사경 위치를 조절하는 행위</t>
+        </is>
+      </c>
+      <c r="F267" t="inlineStr">
+        <is>
+          <t>운전 중 라디오를 듣는 행위</t>
+        </is>
+      </c>
+      <c r="G267" t="n">
+        <v>1</v>
+      </c>
+      <c r="H267" t="inlineStr">
+        <is>
+          <t>운전자는 영유아나 동물을 안고 운전 장치를 조작하거나 운전석 주위에 물건을 싣는 등 안전에 지장을 줄 우려가 있는 상태로 운전해서는 안 된다(제39조제5항).</t>
+        </is>
+      </c>
+      <c r="I267" t="inlineStr">
+        <is>
+          <t>두 손과 시야가 운전에만 쓰이지 못하게 만드는 상태를 찾아보세요.</t>
+        </is>
+      </c>
+      <c r="J267" t="inlineStr">
+        <is>
+          <t>도로교통법 제39조제5항</t>
+        </is>
+      </c>
+      <c r="K267" t="inlineStr">
+        <is>
+          <t>2026-10-22</t>
+        </is>
+      </c>
+      <c r="L267" t="inlineStr">
+        <is>
+          <t>자체 작성</t>
+        </is>
+      </c>
+      <c r="M267" t="n">
+        <v>1</v>
+      </c>
+      <c r="O267" t="inlineStr">
+        <is>
+          <t>verified</t>
+        </is>
+      </c>
+      <c r="P267" t="inlineStr">
+        <is>
+          <t>1등 / 2026-10-22</t>
+        </is>
+      </c>
+      <c r="Q267" t="inlineStr">
+        <is>
+          <t>AI 4차 초안(2026-10-21) · 근거 확인 ○: 도로교통법 제39조제5항 원문 확인</t>
+        </is>
+      </c>
+    </row>
+    <row r="268">
+      <c r="A268" t="inlineStr">
+        <is>
+          <t>LAW-0267</t>
+        </is>
+      </c>
+      <c r="B268" t="inlineStr">
+        <is>
+          <t>정비 상태가 매우 불량하여 위험 발생 우려가 있는 차에 대해 시·도경찰청장이 정비기간을 정하여 그 차의 사용을 정지시킬 수 있는 범위는?</t>
+        </is>
+      </c>
+      <c r="C268" t="inlineStr">
+        <is>
+          <t>3일의 범위</t>
+        </is>
+      </c>
+      <c r="D268" t="inlineStr">
+        <is>
+          <t>30일의 범위</t>
+        </is>
+      </c>
+      <c r="E268" t="inlineStr">
+        <is>
+          <t>3개월의 범위</t>
+        </is>
+      </c>
+      <c r="F268" t="inlineStr">
+        <is>
+          <t>10일의 범위</t>
+        </is>
+      </c>
+      <c r="G268" t="n">
+        <v>4</v>
+      </c>
+      <c r="H268" t="inlineStr">
+        <is>
+          <t>시·도경찰청장은 정비 상태가 매우 불량한 차의 자동차등록증을 보관하고 운전의 일시정지를 명할 수 있으며, 필요하면 10일의 범위에서 정비기간을 정해 사용을 정지시킬 수 있다(제41조제3항).</t>
+        </is>
+      </c>
+      <c r="I268" t="inlineStr">
+        <is>
+          <t>정비를 마칠 수 있을 만큼은 주되 오래 묶어 두지는 않는, 한 달보다 훨씬 짧은 기간입니다.</t>
+        </is>
+      </c>
+      <c r="J268" t="inlineStr">
+        <is>
+          <t>도로교통법 제41조제3항</t>
+        </is>
+      </c>
+      <c r="K268" t="inlineStr">
+        <is>
+          <t>2026-10-22</t>
+        </is>
+      </c>
+      <c r="L268" t="inlineStr">
+        <is>
+          <t>자체 작성</t>
+        </is>
+      </c>
+      <c r="M268" t="n">
+        <v>2</v>
+      </c>
+      <c r="O268" t="inlineStr">
+        <is>
+          <t>verified</t>
+        </is>
+      </c>
+      <c r="P268" t="inlineStr">
+        <is>
+          <t>1등 / 2026-10-22</t>
+        </is>
+      </c>
+      <c r="Q268" t="inlineStr">
+        <is>
+          <t>AI 4차 초안(2026-10-21) · 근거 확인 ○: 도로교통법 제41조제3항 '10일의 범위에서 정비기간을 정하여' 원문 확인</t>
+        </is>
+      </c>
+    </row>
+    <row r="269">
+      <c r="A269" t="inlineStr">
+        <is>
+          <t>LAW-0268</t>
+        </is>
+      </c>
+      <c r="B269" t="inlineStr">
+        <is>
+          <t>약물의 영향으로 정상적으로 운전하지 못할 우려가 있다고 인정할 상당한 이유가 있을 때 경찰공무원이 실시할 수 있는 측정 방법으로 법령에 규정된 것은?</t>
+        </is>
+      </c>
+      <c r="C269" t="inlineStr">
+        <is>
+          <t>운전자 동의 없이 현장에서 혈액을 강제로 채취하는 검사</t>
+        </is>
+      </c>
+      <c r="D269" t="inlineStr">
+        <is>
+          <t>직선보행·한 발 서기 등 상태 평가나 타액 등을 채취하는 간이시약검사</t>
+        </is>
+      </c>
+      <c r="E269" t="inlineStr">
+        <is>
+          <t>운전자의 진술서만 받는 방법</t>
+        </is>
+      </c>
+      <c r="F269" t="inlineStr">
+        <is>
+          <t>차량 블랙박스 영상만 확인하는 방법</t>
+        </is>
+      </c>
+      <c r="G269" t="n">
+        <v>2</v>
+      </c>
+      <c r="H269" t="inlineStr">
+        <is>
+          <t>경찰공무원은 보행·서기 상태 평가와 타액 간이시약검사 등으로 약물 복용 여부를 측정할 수 있고, 운전자는 이에 응해야 한다. 결과에 불복하면 운전자 동의를 받아 혈액 채취 등으로 다시 측정한다.</t>
+        </is>
+      </c>
+      <c r="I269" t="inlineStr">
+        <is>
+          <t>음주의 호흡측정처럼 현장에서 바로 할 수 있는 간단한 방법을 떠올려 보세요. 혈액은 '동의'가 붙는 재측정 단계입니다.</t>
+        </is>
+      </c>
+      <c r="J269" t="inlineStr">
+        <is>
+          <t>도로교통법 제45조제2항·제3항, 도로교통법 시행규칙 제28조의2</t>
+        </is>
+      </c>
+      <c r="K269" t="inlineStr">
+        <is>
+          <t>2026-10-22</t>
+        </is>
+      </c>
+      <c r="L269" t="inlineStr">
+        <is>
+          <t>자체 작성</t>
+        </is>
+      </c>
+      <c r="M269" t="n">
+        <v>2</v>
+      </c>
+      <c r="O269" t="inlineStr">
+        <is>
+          <t>verified</t>
+        </is>
+      </c>
+      <c r="P269" t="inlineStr">
+        <is>
+          <t>1등 / 2026-10-22</t>
+        </is>
+      </c>
+      <c r="Q269" t="inlineStr">
+        <is>
+          <t>AI 4차 초안(2026-10-21) · 근거 확인 ○: 도로교통법 제45조제2항·제3항, 시행규칙 제28조의2제1항 원문 확인</t>
+        </is>
+      </c>
+    </row>
+    <row r="270">
+      <c r="A270" t="inlineStr">
+        <is>
+          <t>LAW-0269</t>
+        </is>
+      </c>
+      <c r="B270" t="inlineStr">
+        <is>
+          <t>도로교통법상 공동 위험행위의 성립 요건으로 옳은 것은?</t>
+        </is>
+      </c>
+      <c r="C270" t="inlineStr">
+        <is>
+          <t>1명이 1대의 자동차로 여러 차례 차로를 바꾸며 위협하는 것</t>
+        </is>
+      </c>
+      <c r="D270" t="inlineStr">
+        <is>
+          <t>고속도로에서 3대 이상이 일정 간격으로 함께 주행하는 것</t>
+        </is>
+      </c>
+      <c r="E270" t="inlineStr">
+        <is>
+          <t>도로에서 2명 이상이 공동으로 2대 이상의 자동차등을 정당한 사유 없이 줄지어 통행하면서 위해나 교통상의 위험을 발생하게 하는 것</t>
+        </is>
+      </c>
+      <c r="F270" t="inlineStr">
+        <is>
+          <t>동승자가 운전자에게 과속을 권유하는 것</t>
+        </is>
+      </c>
+      <c r="G270" t="n">
+        <v>3</v>
+      </c>
+      <c r="H270" t="inlineStr">
+        <is>
+          <t>공동 위험행위는 2명 이상이 공동으로 2대 이상의 자동차등을 앞뒤 또는 좌우로 줄지어 통행하며 위해나 위험을 발생시키는 행위이다. 동승자도 이를 주도해서는 안 된다.</t>
+        </is>
+      </c>
+      <c r="I270" t="inlineStr">
+        <is>
+          <t>'공동'이라는 말에서 사람 수와 차 대수가 각각 최소 얼마인지 생각해 보세요. 혼자 하는 위협 운전은 다른 이름입니다.</t>
+        </is>
+      </c>
+      <c r="J270" t="inlineStr">
+        <is>
+          <t>도로교통법 제46조</t>
+        </is>
+      </c>
+      <c r="K270" t="inlineStr">
+        <is>
+          <t>2026-10-22</t>
+        </is>
+      </c>
+      <c r="L270" t="inlineStr">
+        <is>
+          <t>자체 작성</t>
+        </is>
+      </c>
+      <c r="M270" t="n">
+        <v>2</v>
+      </c>
+      <c r="O270" t="inlineStr">
+        <is>
+          <t>verified</t>
+        </is>
+      </c>
+      <c r="P270" t="inlineStr">
+        <is>
+          <t>1등 / 2026-10-22</t>
+        </is>
+      </c>
+      <c r="Q270" t="inlineStr">
+        <is>
+          <t>AI 4차 초안(2026-10-21) · 근거 확인 ○: 도로교통법 제46조제1항·제2항 원문 확인</t>
+        </is>
+      </c>
+    </row>
+    <row r="271">
+      <c r="A271" t="inlineStr">
+        <is>
+          <t>LAW-0270</t>
+        </is>
+      </c>
+      <c r="B271" t="inlineStr">
+        <is>
+          <t>모든 운전자의 준수사항으로 옳은 것은?</t>
+        </is>
+      </c>
+      <c r="C271" t="inlineStr">
+        <is>
+          <t>차를 떠날 때 시동을 켠 채 잠시 자리를 비우는 것은 허용된다</t>
+        </is>
+      </c>
+      <c r="D271" t="inlineStr">
+        <is>
+          <t>승객이 차 안에서 춤추는 등 소란을 피워도 운전자는 운행을 계속할 수 있다</t>
+        </is>
+      </c>
+      <c r="E271" t="inlineStr">
+        <is>
+          <t>문을 열 때 안전 확인은 동승자 몫이므로 운전자는 하지 않아도 된다</t>
+        </is>
+      </c>
+      <c r="F271" t="inlineStr">
+        <is>
+          <t>도로에 자동차를 세워둔 채 시비·다툼 등을 하여 다른 차마의 통행을 방해하지 않는다</t>
+        </is>
+      </c>
+      <c r="G271" t="n">
+        <v>4</v>
+      </c>
+      <c r="H271" t="inlineStr">
+        <is>
+          <t>운전자는 도로에 차를 세워둔 채 시비·다툼으로 통행을 방해해서는 안 되고, 차를 떠날 때 필요한 조치를 해야 하며, 승객의 소란행위를 내버려둔 채 운행하거나 안전 확인 없이 문을 열어서는 안 된다(제49조제1항).</t>
+        </is>
+      </c>
+      <c r="I271" t="inlineStr">
+        <is>
+          <t>다른 보기들은 모두 '사고 예방 책임'을 남에게 미루거나 소홀히 하는 내용입니다.</t>
+        </is>
+      </c>
+      <c r="J271" t="inlineStr">
+        <is>
+          <t>도로교통법 제49조제1항제5호~제9호</t>
+        </is>
+      </c>
+      <c r="K271" t="inlineStr">
+        <is>
+          <t>2026-10-22</t>
+        </is>
+      </c>
+      <c r="L271" t="inlineStr">
+        <is>
+          <t>자체 작성</t>
+        </is>
+      </c>
+      <c r="M271" t="n">
+        <v>1</v>
+      </c>
+      <c r="O271" t="inlineStr">
+        <is>
+          <t>verified</t>
+        </is>
+      </c>
+      <c r="P271" t="inlineStr">
+        <is>
+          <t>1등 / 2026-10-22</t>
+        </is>
+      </c>
+      <c r="Q271" t="inlineStr">
+        <is>
+          <t>AI 4차 초안(2026-10-21) · 근거 확인 ○: 도로교통법 제49조제1항제5호·제6호·제7호·제9호 원문 확인</t>
+        </is>
+      </c>
+    </row>
+    <row r="272">
+      <c r="A272" t="inlineStr">
+        <is>
+          <t>LAW-0271</t>
+        </is>
+      </c>
+      <c r="B272" t="inlineStr">
+        <is>
+          <t>운행기록계를 설치해야 하는 화물자동차 운전자의 금지행위로 도로교통법에 규정된 것은?</t>
+        </is>
+      </c>
+      <c r="C272" t="inlineStr">
+        <is>
+          <t>운행을 마친 뒤 운행기록을 확인하는 행위</t>
+        </is>
+      </c>
+      <c r="D272" t="inlineStr">
+        <is>
+          <t>운행 전에 운행기록계 작동 상태를 점검하는 행위</t>
+        </is>
+      </c>
+      <c r="E272" t="inlineStr">
+        <is>
+          <t>운행기록계를 정비업체에서 정기 점검받는 행위</t>
+        </is>
+      </c>
+      <c r="F272" t="inlineStr">
+        <is>
+          <t>고장 등으로 사용할 수 없는 운행기록계가 설치된 자동차를 운전하는 행위</t>
+        </is>
+      </c>
+      <c r="G272" t="n">
+        <v>4</v>
+      </c>
+      <c r="H272" t="inlineStr">
+        <is>
+          <t>운행기록계 설치 대상 자동차의 운전자는 운행기록계가 없거나 고장 등으로 사용할 수 없는 상태로 운전하거나, 운행기록계를 원래 목적대로 사용하지 않고 운전해서는 안 된다(제50조제5항).</t>
+        </is>
+      </c>
+      <c r="I272" t="inlineStr">
+        <is>
+          <t>기록이 제대로 남지 않게 되는 상황을 고르세요.</t>
+        </is>
+      </c>
+      <c r="J272" t="inlineStr">
+        <is>
+          <t>도로교통법 제50조제5항, 도로교통법 시행규칙 제33조</t>
+        </is>
+      </c>
+      <c r="K272" t="inlineStr">
+        <is>
+          <t>2026-10-22</t>
+        </is>
+      </c>
+      <c r="L272" t="inlineStr">
+        <is>
+          <t>자체 작성</t>
+        </is>
+      </c>
+      <c r="M272" t="n">
+        <v>2</v>
+      </c>
+      <c r="O272" t="inlineStr">
+        <is>
+          <t>verified</t>
+        </is>
+      </c>
+      <c r="P272" t="inlineStr">
+        <is>
+          <t>1등 / 2026-10-22</t>
+        </is>
+      </c>
+      <c r="Q272" t="inlineStr">
+        <is>
+          <t>AI 4차 초안(2026-10-21) · 근거 확인 ○: 도로교통법 제50조제5항제1호·제2호, 시행규칙 제33조 원문 확인</t>
+        </is>
+      </c>
+    </row>
+    <row r="273">
+      <c r="A273" t="inlineStr">
+        <is>
+          <t>LAW-0272</t>
+        </is>
+      </c>
+      <c r="B273" t="inlineStr">
+        <is>
+          <t>도로교통법 제50조제5항의 운전자 금지행위 중 '승차를 거부하는 행위' 금지가 적용되는 운전자는?</t>
+        </is>
+      </c>
+      <c r="C273" t="inlineStr">
+        <is>
+          <t>모든 사업용 화물자동차의 운전자</t>
+        </is>
+      </c>
+      <c r="D273" t="inlineStr">
+        <is>
+          <t>용달화물자동차의 운전자</t>
+        </is>
+      </c>
+      <c r="E273" t="inlineStr">
+        <is>
+          <t>자가용 승합자동차의 운전자</t>
+        </is>
+      </c>
+      <c r="F273" t="inlineStr">
+        <is>
+          <t>사업용 승합자동차와 노면전차의 운전자</t>
+        </is>
+      </c>
+      <c r="G273" t="n">
+        <v>4</v>
+      </c>
+      <c r="H273" t="inlineStr">
+        <is>
+          <t>제50조제5항은 운행기록계 관련 금지행위와 승차거부 금지를 정하면서, 승차거부(제3호)는 사업용 승합자동차와 노면전차의 운전자에 한정한다고 단서로 규정한다.</t>
+        </is>
+      </c>
+      <c r="I273" t="inlineStr">
+        <is>
+          <t>승차를 거부할 '승객'을 태우는 차, 그중에서도 여럿을 태우는 사업용 차를 생각해 보세요.</t>
+        </is>
+      </c>
+      <c r="J273" t="inlineStr">
+        <is>
+          <t>도로교통법 제50조제5항 단서</t>
+        </is>
+      </c>
+      <c r="K273" t="inlineStr">
+        <is>
+          <t>2026-10-22</t>
+        </is>
+      </c>
+      <c r="L273" t="inlineStr">
+        <is>
+          <t>자체 작성</t>
+        </is>
+      </c>
+      <c r="M273" t="n">
+        <v>3</v>
+      </c>
+      <c r="O273" t="inlineStr">
+        <is>
+          <t>verified</t>
+        </is>
+      </c>
+      <c r="P273" t="inlineStr">
+        <is>
+          <t>1등 / 2026-10-22</t>
+        </is>
+      </c>
+      <c r="Q273" t="inlineStr">
+        <is>
+          <t>AI 4차 초안(2026-10-21) · 근거 확인 ○: 도로교통법 제50조제5항 단서 '제3호는 사업용 승합자동차와 노면전차의 운전자에 한정한다' 원문 확인</t>
+        </is>
+      </c>
+    </row>
+    <row r="274">
+      <c r="A274" t="inlineStr">
+        <is>
+          <t>LAW-0273</t>
+        </is>
+      </c>
+      <c r="B274" t="inlineStr">
+        <is>
+          <t>도로교통법령상 좌석안전띠를 매지 않아도 되는 경우로 규정된 것은?</t>
+        </is>
+      </c>
+      <c r="C274" t="inlineStr">
+        <is>
+          <t>자동차를 후진시키기 위하여 운전하는 때</t>
+        </is>
+      </c>
+      <c r="D274" t="inlineStr">
+        <is>
+          <t>시내에서 짧은 거리를 운전하는 때</t>
+        </is>
+      </c>
+      <c r="E274" t="inlineStr">
+        <is>
+          <t>고속도로가 아닌 일반도로를 운전하는 때</t>
+        </is>
+      </c>
+      <c r="F274" t="inlineStr">
+        <is>
+          <t>운전 경력이 10년 이상인 운전자가 운전하는 때</t>
+        </is>
+      </c>
+      <c r="G274" t="n">
+        <v>1</v>
+      </c>
+      <c r="H274" t="inlineStr">
+        <is>
+          <t>시행규칙 제31조는 후진을 위해 운전하는 때, 부상·질병·임신 등으로 착용이 적당하지 않은 때, 긴급자동차가 본래 용도로 운행 중인 때 등을 착용 예외로 정한다. 거리·도로 종류·경력은 예외 사유가 아니다.</t>
+        </is>
+      </c>
+      <c r="I274" t="inlineStr">
+        <is>
+          <t>거리·도로 종류·운전 경력은 예외 사유가 아닙니다. 안전띠를 매면 필요한 동작을 하기 어려운 경우를 생각해 보세요.</t>
+        </is>
+      </c>
+      <c r="J274" t="inlineStr">
+        <is>
+          <t>도로교통법 제50조제1항, 도로교통법 시행규칙 제31조제2호</t>
+        </is>
+      </c>
+      <c r="K274" t="inlineStr">
+        <is>
+          <t>2026-10-22</t>
+        </is>
+      </c>
+      <c r="L274" t="inlineStr">
+        <is>
+          <t>자체 작성</t>
+        </is>
+      </c>
+      <c r="M274" t="n">
+        <v>1</v>
+      </c>
+      <c r="O274" t="inlineStr">
+        <is>
+          <t>verified</t>
+        </is>
+      </c>
+      <c r="P274" t="inlineStr">
+        <is>
+          <t>1등 / 2026-10-22</t>
+        </is>
+      </c>
+      <c r="Q274" t="inlineStr">
+        <is>
+          <t>AI 4차 초안(2026-10-21) · 근거 확인 ○: 도로교통법 시행규칙 제31조제2호 원문 확인 · 교차 점검 반영</t>
+        </is>
+      </c>
+    </row>
+    <row r="275">
+      <c r="A275" t="inlineStr">
+        <is>
+          <t>LAW-0274</t>
+        </is>
+      </c>
+      <c r="B275" t="inlineStr">
+        <is>
+          <t>중앙선이 설치되지 않은 도로나 편도 1차로인 도로에서 어린이통학버스가 정차하여 승하차 표시 점멸등을 작동 중일 때 반대방향에서 오는 차의 운전자가 해야 할 일은?</t>
+        </is>
+      </c>
+      <c r="C275" t="inlineStr">
+        <is>
+          <t>어린이통학버스에 이르기 전에 일시정지하여 안전을 확인한 후 서행한다</t>
+        </is>
+      </c>
+      <c r="D275" t="inlineStr">
+        <is>
+          <t>반대방향이므로 속도를 유지하며 지나간다</t>
+        </is>
+      </c>
+      <c r="E275" t="inlineStr">
+        <is>
+          <t>경음기를 울려 어린이에게 차가 온다는 것을 알리고 지나간다</t>
+        </is>
+      </c>
+      <c r="F275" t="inlineStr">
+        <is>
+          <t>통학버스를 앞질러 신속히 지나간다</t>
+        </is>
+      </c>
+      <c r="G275" t="n">
+        <v>1</v>
+      </c>
+      <c r="H275" t="inlineStr">
+        <is>
+          <t>중앙선이 없는 도로와 편도 1차로 도로에서는 반대방향에서 진행하는 차의 운전자도 어린이통학버스에 이르기 전에 일시정지하여 안전을 확인한 후 서행해야 한다(제51조제2항).</t>
+        </is>
+      </c>
+      <c r="I275" t="inlineStr">
+        <is>
+          <t>길이 좁아 어린이가 버스 앞뒤로 나와 반대편 차로까지 건널 수 있다는 점을 생각해 보세요.</t>
+        </is>
+      </c>
+      <c r="J275" t="inlineStr">
+        <is>
+          <t>도로교통법 제51조제2항</t>
+        </is>
+      </c>
+      <c r="K275" t="inlineStr">
+        <is>
+          <t>2026-10-22</t>
+        </is>
+      </c>
+      <c r="L275" t="inlineStr">
+        <is>
+          <t>자체 작성</t>
+        </is>
+      </c>
+      <c r="M275" t="n">
+        <v>2</v>
+      </c>
+      <c r="O275" t="inlineStr">
+        <is>
+          <t>verified</t>
+        </is>
+      </c>
+      <c r="P275" t="inlineStr">
+        <is>
+          <t>1등 / 2026-10-22</t>
+        </is>
+      </c>
+      <c r="Q275" t="inlineStr">
+        <is>
+          <t>AI 4차 초안(2026-10-21) · 근거 확인 ○: 도로교통법 제51조제2항 원문 확인</t>
+        </is>
+      </c>
+    </row>
+    <row r="276">
+      <c r="A276" t="inlineStr">
+        <is>
+          <t>LAW-0275</t>
+        </is>
+      </c>
+      <c r="B276" t="inlineStr">
+        <is>
+          <t>어린이통학버스를 계속 운영·운전하는 사람과 동승보호자가 받아야 하는 정기 안전교육의 주기는?</t>
+        </is>
+      </c>
+      <c r="C276" t="inlineStr">
+        <is>
+          <t>2년마다</t>
+        </is>
+      </c>
+      <c r="D276" t="inlineStr">
+        <is>
+          <t>매년</t>
+        </is>
+      </c>
+      <c r="E276" t="inlineStr">
+        <is>
+          <t>3년마다</t>
+        </is>
+      </c>
+      <c r="F276" t="inlineStr">
+        <is>
+          <t>5년마다</t>
+        </is>
+      </c>
+      <c r="G276" t="n">
+        <v>1</v>
+      </c>
+      <c r="H276" t="inlineStr">
+        <is>
+          <t>어린이통학버스 정기 안전교육은 계속 운영·운전하는 사람과 동승한 보호자를 대상으로 2년마다 실시한다(제53조의3제2항제2호). 교육은 3시간 이상이다(시행령 제31조의2제3항).</t>
+        </is>
+      </c>
+      <c r="I276" t="inlineStr">
+        <is>
+          <t>운전적성 정밀검사나 면허 갱신보다 훨씬 짧고, 해마다보다는 긴 주기입니다.</t>
+        </is>
+      </c>
+      <c r="J276" t="inlineStr">
+        <is>
+          <t>도로교통법 제53조의3제2항제2호</t>
+        </is>
+      </c>
+      <c r="K276" t="inlineStr">
+        <is>
+          <t>2026-10-22</t>
+        </is>
+      </c>
+      <c r="L276" t="inlineStr">
+        <is>
+          <t>자체 작성</t>
+        </is>
+      </c>
+      <c r="M276" t="n">
+        <v>2</v>
+      </c>
+      <c r="O276" t="inlineStr">
+        <is>
+          <t>verified</t>
+        </is>
+      </c>
+      <c r="P276" t="inlineStr">
+        <is>
+          <t>1등 / 2026-10-22</t>
+        </is>
+      </c>
+      <c r="Q276" t="inlineStr">
+        <is>
+          <t>AI 4차 초안(2026-10-21) · 근거 확인 ○: 도로교통법 제53조의3제2항제2호 '2년마다 정기적으로' 원문 확인</t>
+        </is>
+      </c>
+    </row>
+    <row r="277">
+      <c r="A277" t="inlineStr">
+        <is>
+          <t>LAW-0276</t>
+        </is>
+      </c>
+      <c r="B277" t="inlineStr">
+        <is>
+          <t>어린이통학버스 운전자가 운행을 마친 후 해야 할 일로 옳은 것은?</t>
+        </is>
+      </c>
+      <c r="C277" t="inlineStr">
+        <is>
+          <t>동승보호자가 있으면 운전자는 확인하지 않아도 된다</t>
+        </is>
+      </c>
+      <c r="D277" t="inlineStr">
+        <is>
+          <t>어린이 하차확인장치를 작동하여 어린이나 영유아가 모두 내렸는지 확인한다</t>
+        </is>
+      </c>
+      <c r="E277" t="inlineStr">
+        <is>
+          <t>차고지에 도착하면 즉시 시동을 끄고 차를 떠난다</t>
+        </is>
+      </c>
+      <c r="F277" t="inlineStr">
+        <is>
+          <t>다음 날 첫 운행 전에만 차 안을 확인한다</t>
+        </is>
+      </c>
+      <c r="G277" t="n">
+        <v>2</v>
+      </c>
+      <c r="H277" t="inlineStr">
+        <is>
+          <t>어린이통학버스 운전자는 운행을 마친 후 어린이나 영유아가 모두 하차했는지 확인해야 하며, 이때 어린이 하차확인장치를 작동해야 한다(제53조제4항·제5항).</t>
+        </is>
+      </c>
+      <c r="I277" t="inlineStr">
+        <is>
+          <t>차 안에 아이가 혼자 남는 사고를 막으려는 규정입니다. 확인 책임을 누가 지는지 생각해 보세요.</t>
+        </is>
+      </c>
+      <c r="J277" t="inlineStr">
+        <is>
+          <t>도로교통법 제53조제4항·제5항</t>
+        </is>
+      </c>
+      <c r="K277" t="inlineStr">
+        <is>
+          <t>2026-10-22</t>
+        </is>
+      </c>
+      <c r="L277" t="inlineStr">
+        <is>
+          <t>자체 작성</t>
+        </is>
+      </c>
+      <c r="M277" t="n">
+        <v>1</v>
+      </c>
+      <c r="O277" t="inlineStr">
+        <is>
+          <t>verified</t>
+        </is>
+      </c>
+      <c r="P277" t="inlineStr">
+        <is>
+          <t>1등 / 2026-10-22</t>
+        </is>
+      </c>
+      <c r="Q277" t="inlineStr">
+        <is>
+          <t>AI 4차 초안(2026-10-21) · 근거 확인 ○: 도로교통법 제53조제4항·제5항 원문 확인 · 교차 점검 반영</t>
+        </is>
+      </c>
+    </row>
+    <row r="278">
+      <c r="A278" t="inlineStr">
+        <is>
+          <t>LAW-0277</t>
+        </is>
+      </c>
+      <c r="B278" t="inlineStr">
+        <is>
+          <t>교통사고가 났을 때 운전자등이 경찰관서에 신고하지 않아도 되는 경우는?</t>
+        </is>
+      </c>
+      <c r="C278" t="inlineStr">
+        <is>
+          <t>피해자가 경상이고 서로 연락처를 교환한 경우</t>
+        </is>
+      </c>
+      <c r="D278" t="inlineStr">
+        <is>
+          <t>사고 장소가 고속도로가 아닌 일반도로인 경우</t>
+        </is>
+      </c>
+      <c r="E278" t="inlineStr">
+        <is>
+          <t>차만 손괴된 것이 분명하고 도로에서의 위험방지와 원활한 소통을 위한 조치를 한 경우</t>
+        </is>
+      </c>
+      <c r="F278" t="inlineStr">
+        <is>
+          <t>가해 차량이 종합보험에 가입되어 있는 경우</t>
+        </is>
+      </c>
+      <c r="G278" t="n">
+        <v>3</v>
+      </c>
+      <c r="H278" t="inlineStr">
+        <is>
+          <t>운전자등은 사고 장소, 사상자 수 등을 경찰에 지체 없이 신고해야 하지만, 차만 손괴된 것이 분명하고 위험방지·소통에 필요한 조치를 한 경우에는 신고하지 않아도 된다(제54조제2항 단서).</t>
+        </is>
+      </c>
+      <c r="I278" t="inlineStr">
+        <is>
+          <t>합의나 보험 가입 여부, 도로의 종류는 신고 의무와 관계가 없습니다. 피해의 종류와 현장 조치를 함께 보세요.</t>
+        </is>
+      </c>
+      <c r="J278" t="inlineStr">
+        <is>
+          <t>도로교통법 제54조제2항</t>
+        </is>
+      </c>
+      <c r="K278" t="inlineStr">
+        <is>
+          <t>2026-10-22</t>
+        </is>
+      </c>
+      <c r="L278" t="inlineStr">
+        <is>
+          <t>자체 작성</t>
+        </is>
+      </c>
+      <c r="M278" t="n">
+        <v>2</v>
+      </c>
+      <c r="O278" t="inlineStr">
+        <is>
+          <t>verified</t>
+        </is>
+      </c>
+      <c r="P278" t="inlineStr">
+        <is>
+          <t>1등 / 2026-10-22</t>
+        </is>
+      </c>
+      <c r="Q278" t="inlineStr">
+        <is>
+          <t>AI 4차 초안(2026-10-21) · 근거 확인 ○: 도로교통법 제54조제2항 단서 원문 확인 · 교차 점검 반영</t>
+        </is>
+      </c>
+    </row>
+    <row r="279">
+      <c r="A279" t="inlineStr">
+        <is>
+          <t>LAW-0278</t>
+        </is>
+      </c>
+      <c r="B279" t="inlineStr">
+        <is>
+          <t>운전자를 고용하고 있는 사람 등 '고용주등'의 의무로 옳은 것은?</t>
+        </is>
+      </c>
+      <c r="C279" t="inlineStr">
+        <is>
+          <t>운전자의 법규 위반은 운전자 개인의 문제이므로 고용주등은 감독할 의무가 없다</t>
+        </is>
+      </c>
+      <c r="D279" t="inlineStr">
+        <is>
+          <t>화물이 급한 경우에는 무면허 운전자에게도 운전을 지시할 수 있다</t>
+        </is>
+      </c>
+      <c r="E279" t="inlineStr">
+        <is>
+          <t>술에 취한 상태 등 운전해서는 안 되는 운전자가 운전하는 것을 알고도 말리지 않거나 운전하도록 시켜서는 안 된다</t>
+        </is>
+      </c>
+      <c r="F279" t="inlineStr">
+        <is>
+          <t>운전자가 과로 상태라도 계약된 운행이면 운전을 시켜야 한다</t>
+        </is>
+      </c>
+      <c r="G279" t="n">
+        <v>3</v>
+      </c>
+      <c r="H279" t="inlineStr">
+        <is>
+          <t>고용주등은 운전자에게 법령을 지키도록 항상 주의시키고 감독해야 하며, 무면허·음주·과로 등으로 운전해서는 안 되는 운전자가 운전하는 것을 알고도 말리지 않거나 운전하도록 시켜서는 안 된다(제56조).</t>
+        </is>
+      </c>
+      <c r="I279" t="inlineStr">
+        <is>
+          <t>도로교통법 제43조(무면허)부터 제45조(과로 등)까지가 무엇을 금지하는지 떠올려 보세요.</t>
+        </is>
+      </c>
+      <c r="J279" t="inlineStr">
+        <is>
+          <t>도로교통법 제56조</t>
+        </is>
+      </c>
+      <c r="K279" t="inlineStr">
+        <is>
+          <t>2026-10-22</t>
+        </is>
+      </c>
+      <c r="L279" t="inlineStr">
+        <is>
+          <t>자체 작성</t>
+        </is>
+      </c>
+      <c r="M279" t="n">
+        <v>1</v>
+      </c>
+      <c r="O279" t="inlineStr">
+        <is>
+          <t>verified</t>
+        </is>
+      </c>
+      <c r="P279" t="inlineStr">
+        <is>
+          <t>1등 / 2026-10-22</t>
+        </is>
+      </c>
+      <c r="Q279" t="inlineStr">
+        <is>
+          <t>AI 4차 초안(2026-10-21) · 근거 확인 ○: 도로교통법 제56조제1항·제2항 원문 확인</t>
+        </is>
+      </c>
+    </row>
+    <row r="280">
+      <c r="A280" t="inlineStr">
+        <is>
+          <t>LAW-0279</t>
+        </is>
+      </c>
+      <c r="B280" t="inlineStr">
+        <is>
+          <t>고속도로등에서 고장으로 운행할 수 없게 된 자동차의 고장자동차 표지(안전삼각대 등)를 설치하는 위치로 옳은 것은?</t>
+        </is>
+      </c>
+      <c r="C280" t="inlineStr">
+        <is>
+          <t>고장 난 자동차의 바로 앞쪽 범퍼 위</t>
+        </is>
+      </c>
+      <c r="D280" t="inlineStr">
+        <is>
+          <t>중앙분리대 위</t>
+        </is>
+      </c>
+      <c r="E280" t="inlineStr">
+        <is>
+          <t>그 자동차의 후방에서 접근하는 자동차의 운전자가 확인할 수 있는 위치</t>
+        </is>
+      </c>
+      <c r="F280" t="inlineStr">
+        <is>
+          <t>고장 난 자동차의 적재함 안</t>
+        </is>
+      </c>
+      <c r="G280" t="n">
+        <v>3</v>
+      </c>
+      <c r="H280" t="inlineStr">
+        <is>
+          <t>고장자동차의 표지는 후방에서 접근하는 자동차의 운전자가 확인할 수 있는 위치에 설치해야 한다(시행규칙 제40조제3항). 또한 표지는 항상 비치하고, 고장 시 차를 도로의 우측 가장자리에 정지시켜야 한다(법 제67조제2항).</t>
+        </is>
+      </c>
+      <c r="I280" t="inlineStr">
+        <is>
+          <t>고속도로 2차 사고는 대부분 뒤에서 달려오는 차와 부딪히는 사고입니다.</t>
+        </is>
+      </c>
+      <c r="J280" t="inlineStr">
+        <is>
+          <t>도로교통법 제66조·제67조제2항, 도로교통법 시행규칙 제40조제3항</t>
+        </is>
+      </c>
+      <c r="K280" t="inlineStr">
+        <is>
+          <t>2026-10-22</t>
+        </is>
+      </c>
+      <c r="L280" t="inlineStr">
+        <is>
+          <t>자체 작성</t>
+        </is>
+      </c>
+      <c r="M280" t="n">
+        <v>2</v>
+      </c>
+      <c r="O280" t="inlineStr">
+        <is>
+          <t>verified</t>
+        </is>
+      </c>
+      <c r="P280" t="inlineStr">
+        <is>
+          <t>1등 / 2026-10-22</t>
+        </is>
+      </c>
+      <c r="Q280" t="inlineStr">
+        <is>
+          <t>AI 4차 초안(2026-10-21) · 근거 확인 ○: 도로교통법 시행규칙 제40조제3항, 법 제67조제2항 원문 확인</t>
+        </is>
+      </c>
+    </row>
+    <row r="281">
+      <c r="A281" t="inlineStr">
+        <is>
+          <t>LAW-0280</t>
+        </is>
+      </c>
+      <c r="B281" t="inlineStr">
+        <is>
+          <t>도로교통법상 누구든지 해서는 안 되는 도로에서의 금지행위에 해당하는 것은?</t>
+        </is>
+      </c>
+      <c r="C281" t="inlineStr">
+        <is>
+          <t>도로를 통행하고 있는 차마에서 밖으로 물건을 던지는 행위</t>
+        </is>
+      </c>
+      <c r="D281" t="inlineStr">
+        <is>
+          <t>신호에 따라 횡단보도를 건너는 행위</t>
+        </is>
+      </c>
+      <c r="E281" t="inlineStr">
+        <is>
+          <t>정차한 차에서 안전을 확인한 후 내리는 행위</t>
+        </is>
+      </c>
+      <c r="F281" t="inlineStr">
+        <is>
+          <t>보도에서 우측으로 걸어가는 행위</t>
+        </is>
+      </c>
+      <c r="G281" t="n">
+        <v>1</v>
+      </c>
+      <c r="H281" t="inlineStr">
+        <is>
+          <t>도로를 통행하는 차마에서 밖으로 물건을 던지는 행위, 도로에 교통에 방해될 물건을 내버려두는 행위 등은 누구에게나 금지된다(제68조).</t>
+        </is>
+      </c>
+      <c r="I281" t="inlineStr">
+        <is>
+          <t>다른 사람이나 차를 다치게 할 수 있는 행동을 고르세요.</t>
+        </is>
+      </c>
+      <c r="J281" t="inlineStr">
+        <is>
+          <t>도로교통법 제68조제3항제5호</t>
+        </is>
+      </c>
+      <c r="K281" t="inlineStr">
+        <is>
+          <t>2026-10-22</t>
+        </is>
+      </c>
+      <c r="L281" t="inlineStr">
+        <is>
+          <t>자체 작성</t>
+        </is>
+      </c>
+      <c r="M281" t="n">
+        <v>1</v>
+      </c>
+      <c r="O281" t="inlineStr">
+        <is>
+          <t>verified</t>
+        </is>
+      </c>
+      <c r="P281" t="inlineStr">
+        <is>
+          <t>1등 / 2026-10-22</t>
+        </is>
+      </c>
+      <c r="Q281" t="inlineStr">
+        <is>
+          <t>AI 4차 초안(2026-10-21) · 근거 확인 ○: 도로교통법 제68조제3항제5호 원문 확인</t>
+        </is>
+      </c>
+    </row>
+    <row r="282">
+      <c r="A282" t="inlineStr">
+        <is>
+          <t>LAW-0281</t>
+        </is>
+      </c>
+      <c r="B282" t="inlineStr">
+        <is>
+          <t>다음 중 특별교통안전 '의무교육'이 아니라 신청하면 받을 수 있는 '권장교육' 대상자는?</t>
+        </is>
+      </c>
+      <c r="C282" t="inlineStr">
+        <is>
+          <t>운전면허 취소처분을 받고 다시 면허를 받으려는 사람</t>
+        </is>
+      </c>
+      <c r="D282" t="inlineStr">
+        <is>
+          <t>운전면허효력 정지처분을 받은 초보운전자로서 정지기간이 끝나지 않은 사람</t>
+        </is>
+      </c>
+      <c r="E282" t="inlineStr">
+        <is>
+          <t>어린이 보호구역에서 어린이를 다치게 하는 사고로 벌점을 받은 날부터 1년 이내인 사람</t>
+        </is>
+      </c>
+      <c r="F282" t="inlineStr">
+        <is>
+          <t>운전면허를 받은 사람 중 교육을 받으려는 날에 65세 이상인 사람</t>
+        </is>
+      </c>
+      <c r="G282" t="n">
+        <v>4</v>
+      </c>
+      <c r="H282" t="inlineStr">
+        <is>
+          <t>65세 이상 운전자는 시·도경찰청장에게 신청하여 특별교통안전 권장교육을 받을 수 있다(제73조제3항제4호). 나머지는 모두 의무교육 대상이다(제73조제2항).</t>
+        </is>
+      </c>
+      <c r="I282" t="inlineStr">
+        <is>
+          <t>다른 보기들은 모두 처분이나 사고 등 '잘못'이 계기가 된 사람입니다.</t>
+        </is>
+      </c>
+      <c r="J282" t="inlineStr">
+        <is>
+          <t>도로교통법 제73조제2항·제3항</t>
+        </is>
+      </c>
+      <c r="K282" t="inlineStr">
+        <is>
+          <t>2026-10-22</t>
+        </is>
+      </c>
+      <c r="L282" t="inlineStr">
+        <is>
+          <t>자체 작성</t>
+        </is>
+      </c>
+      <c r="M282" t="n">
+        <v>3</v>
+      </c>
+      <c r="O282" t="inlineStr">
+        <is>
+          <t>verified</t>
+        </is>
+      </c>
+      <c r="P282" t="inlineStr">
+        <is>
+          <t>1등 / 2026-10-22</t>
+        </is>
+      </c>
+      <c r="Q282" t="inlineStr">
+        <is>
+          <t>AI 4차 초안(2026-10-21) · 근거 확인 ○: 도로교통법 제73조제2항제1호·제4호·제5호, 제3항제4호 원문 확인</t>
+        </is>
+      </c>
+    </row>
+    <row r="283">
+      <c r="A283" t="inlineStr">
+        <is>
+          <t>LAW-0282</t>
+        </is>
+      </c>
+      <c r="B283" t="inlineStr">
+        <is>
+          <t>운전면허증 갱신일에 75세 이상인 사람에 대한 설명으로 옳은 것은?</t>
+        </is>
+      </c>
+      <c r="C283" t="inlineStr">
+        <is>
+          <t>운전면허증 갱신기간 이내에 노화와 안전운전 등에 관한 교통안전교육을 받아야 한다</t>
+        </is>
+      </c>
+      <c r="D283" t="inlineStr">
+        <is>
+          <t>교통안전교육 없이 적성검사만 받으면 갱신할 수 있다</t>
+        </is>
+      </c>
+      <c r="E283" t="inlineStr">
+        <is>
+          <t>75세가 되면 운전면허가 자동으로 취소된다</t>
+        </is>
+      </c>
+      <c r="F283" t="inlineStr">
+        <is>
+          <t>교통안전교육은 원하는 사람만 받는 권장교육이다</t>
+        </is>
+      </c>
+      <c r="G283" t="n">
+        <v>1</v>
+      </c>
+      <c r="H283" t="inlineStr">
+        <is>
+          <t>갱신일에 75세 이상인 사람은 갱신기간 이내에 노화와 안전운전, 약물과 운전, 인지능력별 대처, 교통법령 이해 등의 교통안전교육을 받아야 하며, 받지 않으면 운전면허증을 갱신받을 수 없다(제73조제5항, 제87조제3항).</t>
+        </is>
+      </c>
+      <c r="I283" t="inlineStr">
+        <is>
+          <t>이 교육을 받지 않으면 면허증 갱신 자체가 막힌다는 점을 생각해 보세요.</t>
+        </is>
+      </c>
+      <c r="J283" t="inlineStr">
+        <is>
+          <t>도로교통법 제73조제5항, 제87조제3항제1호</t>
+        </is>
+      </c>
+      <c r="K283" t="inlineStr">
+        <is>
+          <t>2026-10-22</t>
+        </is>
+      </c>
+      <c r="L283" t="inlineStr">
+        <is>
+          <t>자체 작성</t>
+        </is>
+      </c>
+      <c r="M283" t="n">
+        <v>2</v>
+      </c>
+      <c r="O283" t="inlineStr">
+        <is>
+          <t>verified</t>
+        </is>
+      </c>
+      <c r="P283" t="inlineStr">
+        <is>
+          <t>1등 / 2026-10-22</t>
+        </is>
+      </c>
+      <c r="Q283" t="inlineStr">
+        <is>
+          <t>AI 4차 초안(2026-10-21) · 근거 확인 ○: 도로교통법 제73조제5항, 제87조제3항제1호 원문 확인</t>
+        </is>
+      </c>
+    </row>
+    <row r="284">
+      <c r="A284" t="inlineStr">
+        <is>
+          <t>LAW-0283</t>
+        </is>
+      </c>
+      <c r="B284" t="inlineStr">
+        <is>
+          <t>듣지 못하는 사람이 받을 수 없는 운전면허는?</t>
+        </is>
+      </c>
+      <c r="C284" t="inlineStr">
+        <is>
+          <t>제2종 보통면허</t>
+        </is>
+      </c>
+      <c r="D284" t="inlineStr">
+        <is>
+          <t>제1종 보통면허</t>
+        </is>
+      </c>
+      <c r="E284" t="inlineStr">
+        <is>
+          <t>제2종 원동기장치자전거면허</t>
+        </is>
+      </c>
+      <c r="F284" t="inlineStr">
+        <is>
+          <t>제1종 대형면허와 제1종 특수면허</t>
+        </is>
+      </c>
+      <c r="G284" t="n">
+        <v>4</v>
+      </c>
+      <c r="H284" t="inlineStr">
+        <is>
+          <t>듣지 못하는 사람은 제1종 운전면허 중 대형면허·특수면허만 받을 수 없다(제82조제1항제3호). 제1종·제2종 보통면허는 받을 수 있다.</t>
+        </is>
+      </c>
+      <c r="I284" t="inlineStr">
+        <is>
+          <t>보통면허는 듣지 못하는 사람도 받을 수 있습니다. 제한은 일부 제1종 면허에만 있습니다.</t>
+        </is>
+      </c>
+      <c r="J284" t="inlineStr">
+        <is>
+          <t>도로교통법 제82조제1항제3호</t>
+        </is>
+      </c>
+      <c r="K284" t="inlineStr">
+        <is>
+          <t>2026-10-22</t>
+        </is>
+      </c>
+      <c r="L284" t="inlineStr">
+        <is>
+          <t>자체 작성</t>
+        </is>
+      </c>
+      <c r="M284" t="n">
+        <v>2</v>
+      </c>
+      <c r="O284" t="inlineStr">
+        <is>
+          <t>verified</t>
+        </is>
+      </c>
+      <c r="P284" t="inlineStr">
+        <is>
+          <t>1등 / 2026-10-22</t>
+        </is>
+      </c>
+      <c r="Q284" t="inlineStr">
+        <is>
+          <t>AI 4차 초안(2026-10-21) · 근거 확인 ○: 도로교통법 제82조제1항제3호 괄호 원문 확인 · 교차 점검 반영</t>
+        </is>
+      </c>
+    </row>
+    <row r="285">
+      <c r="A285" t="inlineStr">
+        <is>
+          <t>LAW-0284</t>
+        </is>
+      </c>
+      <c r="B285" t="inlineStr">
+        <is>
+          <t>운전면허(원동기장치자전거면허 제외)를 받을 수 없는 나이 기준은?</t>
+        </is>
+      </c>
+      <c r="C285" t="inlineStr">
+        <is>
+          <t>16세 미만</t>
+        </is>
+      </c>
+      <c r="D285" t="inlineStr">
+        <is>
+          <t>17세 미만</t>
+        </is>
+      </c>
+      <c r="E285" t="inlineStr">
+        <is>
+          <t>18세 미만</t>
+        </is>
+      </c>
+      <c r="F285" t="inlineStr">
+        <is>
+          <t>20세 미만</t>
+        </is>
+      </c>
+      <c r="G285" t="n">
+        <v>3</v>
+      </c>
+      <c r="H285" t="inlineStr">
+        <is>
+          <t>18세 미만인 사람은 운전면허를 받을 수 없다. 원동기장치자전거면허는 16세 미만이 결격이며, 제1종 대형·특수면허는 19세 미만이거나 운전경험 1년 미만이면 받을 수 없다(제82조제1항).</t>
+        </is>
+      </c>
+      <c r="I285" t="inlineStr">
+        <is>
+          <t>원동기장치자전거면허보다 높은 나이이고, 제1종 대형·특수면허 나이 기준보다는 낮습니다.</t>
+        </is>
+      </c>
+      <c r="J285" t="inlineStr">
+        <is>
+          <t>도로교통법 제82조제1항제1호</t>
+        </is>
+      </c>
+      <c r="K285" t="inlineStr">
+        <is>
+          <t>2026-10-22</t>
+        </is>
+      </c>
+      <c r="L285" t="inlineStr">
+        <is>
+          <t>자체 작성</t>
+        </is>
+      </c>
+      <c r="M285" t="n">
+        <v>1</v>
+      </c>
+      <c r="O285" t="inlineStr">
+        <is>
+          <t>verified</t>
+        </is>
+      </c>
+      <c r="P285" t="inlineStr">
+        <is>
+          <t>1등 / 2026-10-22</t>
+        </is>
+      </c>
+      <c r="Q285" t="inlineStr">
+        <is>
+          <t>AI 4차 초안(2026-10-21) · 근거 확인 ○: 도로교통법 제82조제1항제1호 원문 확인 · 교차 점검 반영</t>
+        </is>
+      </c>
+    </row>
+    <row r="286">
+      <c r="A286" t="inlineStr">
+        <is>
+          <t>LAW-0285</t>
+        </is>
+      </c>
+      <c r="B286" t="inlineStr">
+        <is>
+          <t>술에 취한 상태에서 운전하다가 사람을 사망에 이르게 하여 운전면허가 취소된 사람이 다시 운전면허를 받을 수 없는 기간은? (취소된 날부터)</t>
+        </is>
+      </c>
+      <c r="C286" t="inlineStr">
+        <is>
+          <t>1년</t>
+        </is>
+      </c>
+      <c r="D286" t="inlineStr">
+        <is>
+          <t>5년</t>
+        </is>
+      </c>
+      <c r="E286" t="inlineStr">
+        <is>
+          <t>2년</t>
+        </is>
+      </c>
+      <c r="F286" t="inlineStr">
+        <is>
+          <t>3년</t>
+        </is>
+      </c>
+      <c r="G286" t="n">
+        <v>2</v>
+      </c>
+      <c r="H286" t="inlineStr">
+        <is>
+          <t>술에 취한 상태 등에서 운전하다가 사람을 사망에 이르게 한 경우 운전면허가 취소된 날부터 5년간 운전면허를 받을 수 없다(제82조제2항제3호나목).</t>
+        </is>
+      </c>
+      <c r="I286" t="inlineStr">
+        <is>
+          <t>음주운전으로 교통사고만 낸 경우(2년)보다 결과가 훨씬 무거운 경우입니다.</t>
+        </is>
+      </c>
+      <c r="J286" t="inlineStr">
+        <is>
+          <t>도로교통법 제82조제2항제3호나목</t>
+        </is>
+      </c>
+      <c r="K286" t="inlineStr">
+        <is>
+          <t>2026-10-22</t>
+        </is>
+      </c>
+      <c r="L286" t="inlineStr">
+        <is>
+          <t>자체 작성</t>
+        </is>
+      </c>
+      <c r="M286" t="n">
+        <v>2</v>
+      </c>
+      <c r="O286" t="inlineStr">
+        <is>
+          <t>verified</t>
+        </is>
+      </c>
+      <c r="P286" t="inlineStr">
+        <is>
+          <t>1등 / 2026-10-22</t>
+        </is>
+      </c>
+      <c r="Q286" t="inlineStr">
+        <is>
+          <t>AI 4차 초안(2026-10-21) · 근거 확인 ○: 도로교통법 제82조제2항제3호나목 원문 확인 · 교차 점검 반영</t>
+        </is>
+      </c>
+    </row>
+    <row r="287">
+      <c r="A287" t="inlineStr">
+        <is>
+          <t>LAW-0286</t>
+        </is>
+      </c>
+      <c r="B287" t="inlineStr">
+        <is>
+          <t>다른 사람의 자동차를 훔친 사람이 무면허로 그 자동차를 운전한 경우 운전면허를 받을 수 없는 기간은?</t>
+        </is>
+      </c>
+      <c r="C287" t="inlineStr">
+        <is>
+          <t>위반한 날부터 1년</t>
+        </is>
+      </c>
+      <c r="D287" t="inlineStr">
+        <is>
+          <t>위반한 날부터 2년</t>
+        </is>
+      </c>
+      <c r="E287" t="inlineStr">
+        <is>
+          <t>위반한 날부터 3년</t>
+        </is>
+      </c>
+      <c r="F287" t="inlineStr">
+        <is>
+          <t>위반한 날부터 5년</t>
+        </is>
+      </c>
+      <c r="G287" t="n">
+        <v>3</v>
+      </c>
+      <c r="H287" t="inlineStr">
+        <is>
+          <t>자동차등을 이용하여 범죄행위를 하거나 다른 사람의 자동차등을 훔치거나 빼앗은 사람이 무면허로 그 자동차등을 운전한 경우 위반한 날부터 3년간 면허를 받을 수 없다(제82조제2항제5호).</t>
+        </is>
+      </c>
+      <c r="I287" t="inlineStr">
+        <is>
+          <t>일반 무면허(1년)보다 무겁고, 음주 사망사고(5년)보다는 가벼운 중간 단계입니다.</t>
+        </is>
+      </c>
+      <c r="J287" t="inlineStr">
+        <is>
+          <t>도로교통법 제82조제2항제5호</t>
+        </is>
+      </c>
+      <c r="K287" t="inlineStr">
+        <is>
+          <t>2026-10-22</t>
+        </is>
+      </c>
+      <c r="L287" t="inlineStr">
+        <is>
+          <t>자체 작성</t>
+        </is>
+      </c>
+      <c r="M287" t="n">
+        <v>3</v>
+      </c>
+      <c r="O287" t="inlineStr">
+        <is>
+          <t>verified</t>
+        </is>
+      </c>
+      <c r="P287" t="inlineStr">
+        <is>
+          <t>1등 / 2026-10-22</t>
+        </is>
+      </c>
+      <c r="Q287" t="inlineStr">
+        <is>
+          <t>AI 4차 초안(2026-10-21) · 근거 확인 ○: 도로교통법 제82조제2항제5호 후단 원문 확인</t>
+        </is>
+      </c>
+    </row>
+    <row r="288">
+      <c r="A288" t="inlineStr">
+        <is>
+          <t>LAW-0287</t>
+        </is>
+      </c>
+      <c r="B288" t="inlineStr">
+        <is>
+          <t>운전면허 결격기간 중이라도 운전면허를 받을 수 있는 경우는?</t>
+        </is>
+      </c>
+      <c r="C288" t="inlineStr">
+        <is>
+          <t>해당 위반 사유로 벌금형이 확정된 경우</t>
+        </is>
+      </c>
+      <c r="D288" t="inlineStr">
+        <is>
+          <t>해당 위반 사유로 선고유예의 판결이 확정된 경우</t>
+        </is>
+      </c>
+      <c r="E288" t="inlineStr">
+        <is>
+          <t>해당 위반 사유로 징역형의 집행유예가 선고된 경우</t>
+        </is>
+      </c>
+      <c r="F288" t="inlineStr">
+        <is>
+          <t>결격기간의 절반이 지난 경우</t>
+        </is>
+      </c>
+      <c r="G288" t="n">
+        <v>2</v>
+      </c>
+      <c r="H288" t="inlineStr">
+        <is>
+          <t>결격 사유로 벌금 미만의 형이 확정되거나 선고유예 판결이 확정된 경우, 또는 기소유예나 소년법상 보호처분 결정이 있는 경우에는 결격기간 내라도 운전면허를 받을 수 있다(제82조제2항 단서).</t>
+        </is>
+      </c>
+      <c r="I288" t="inlineStr">
+        <is>
+          <t>형사처벌이 아주 가볍거나 사실상 처벌하지 않기로 한 경우에만 인정되는 예외입니다.</t>
+        </is>
+      </c>
+      <c r="J288" t="inlineStr">
+        <is>
+          <t>도로교통법 제82조제2항 단서</t>
+        </is>
+      </c>
+      <c r="K288" t="inlineStr">
+        <is>
+          <t>2026-10-22</t>
+        </is>
+      </c>
+      <c r="L288" t="inlineStr">
+        <is>
+          <t>자체 작성</t>
+        </is>
+      </c>
+      <c r="M288" t="n">
+        <v>3</v>
+      </c>
+      <c r="O288" t="inlineStr">
+        <is>
+          <t>verified</t>
+        </is>
+      </c>
+      <c r="P288" t="inlineStr">
+        <is>
+          <t>1등 / 2026-10-22</t>
+        </is>
+      </c>
+      <c r="Q288" t="inlineStr">
+        <is>
+          <t>AI 4차 초안(2026-10-21) · 근거 확인 ○: 도로교통법 제82조제2항 단서 원문 확인</t>
+        </is>
+      </c>
+    </row>
+    <row r="289">
+      <c r="A289" t="inlineStr">
+        <is>
+          <t>LAW-0288</t>
+        </is>
+      </c>
+      <c r="B289" t="inlineStr">
+        <is>
+          <t>운전면허 취소처분을 받은 사람이 결격기간이 끝난 뒤 운전면허를 다시 받기 위한 요건으로 옳은 것은?</t>
+        </is>
+      </c>
+      <c r="C289" t="inlineStr">
+        <is>
+          <t>결격기간이 끝나면 별도 교육 없이 바로 응시할 수 있다</t>
+        </is>
+      </c>
+      <c r="D289" t="inlineStr">
+        <is>
+          <t>운전적성 정밀검사만 받으면 된다</t>
+        </is>
+      </c>
+      <c r="E289" t="inlineStr">
+        <is>
+          <t>한국교통안전공단의 운전자격 교육을 받아야 한다</t>
+        </is>
+      </c>
+      <c r="F289" t="inlineStr">
+        <is>
+          <t>취소처분 이후 특별교통안전 의무교육을 받아야 한다</t>
+        </is>
+      </c>
+      <c r="G289" t="n">
+        <v>4</v>
+      </c>
+      <c r="H289" t="inlineStr">
+        <is>
+          <t>운전면허 취소처분을 받은 사람은 결격기간이 끝났더라도 그 취소처분 이후 특별교통안전 의무교육을 받지 않으면 운전면허를 받을 수 없다(제82조제3항).</t>
+        </is>
+      </c>
+      <c r="I289" t="inlineStr">
+        <is>
+          <t>기간이 지나는 것만으로 충분하지 않고, 한국도로교통공단이 실시하는 특별한 교육이 따로 필요합니다.</t>
+        </is>
+      </c>
+      <c r="J289" t="inlineStr">
+        <is>
+          <t>도로교통법 제82조제3항</t>
+        </is>
+      </c>
+      <c r="K289" t="inlineStr">
+        <is>
+          <t>2026-10-22</t>
+        </is>
+      </c>
+      <c r="L289" t="inlineStr">
+        <is>
+          <t>자체 작성</t>
+        </is>
+      </c>
+      <c r="M289" t="n">
+        <v>2</v>
+      </c>
+      <c r="O289" t="inlineStr">
+        <is>
+          <t>verified</t>
+        </is>
+      </c>
+      <c r="P289" t="inlineStr">
+        <is>
+          <t>1등 / 2026-10-22</t>
+        </is>
+      </c>
+      <c r="Q289" t="inlineStr">
+        <is>
+          <t>AI 4차 초안(2026-10-21) · 근거 확인 ○: 도로교통법 제82조제3항, 시행령 제38조제3항 원문 확인</t>
+        </is>
+      </c>
+    </row>
+    <row r="290">
+      <c r="A290" t="inlineStr">
+        <is>
+          <t>LAW-0289</t>
+        </is>
+      </c>
+      <c r="B290" t="inlineStr">
+        <is>
+          <t>운전면허의 효력이 발생하는 시점은?</t>
+        </is>
+      </c>
+      <c r="C290" t="inlineStr">
+        <is>
+          <t>본인 또는 대리인이 운전면허증을 발급받은 때</t>
+        </is>
+      </c>
+      <c r="D290" t="inlineStr">
+        <is>
+          <t>운전면허시험에 합격한 때</t>
+        </is>
+      </c>
+      <c r="E290" t="inlineStr">
+        <is>
+          <t>합격자 발표 다음 날</t>
+        </is>
+      </c>
+      <c r="F290" t="inlineStr">
+        <is>
+          <t>응시원서를 접수한 때</t>
+        </is>
+      </c>
+      <c r="G290" t="n">
+        <v>1</v>
+      </c>
+      <c r="H290" t="inlineStr">
+        <is>
+          <t>운전면허의 효력은 본인 또는 대리인이 운전면허증을 발급받은 때부터 발생한다(제85조제5항). 합격만 하고 면허증을 받기 전에 운전하면 무면허가 된다.</t>
+        </is>
+      </c>
+      <c r="I290" t="inlineStr">
+        <is>
+          <t>시험 합격과 실제로 손에 쥐는 것 사이에 시간 차가 있다는 점에 주의하세요.</t>
+        </is>
+      </c>
+      <c r="J290" t="inlineStr">
+        <is>
+          <t>도로교통법 제85조제5항</t>
+        </is>
+      </c>
+      <c r="K290" t="inlineStr">
+        <is>
+          <t>2026-10-22</t>
+        </is>
+      </c>
+      <c r="L290" t="inlineStr">
+        <is>
+          <t>자체 작성</t>
+        </is>
+      </c>
+      <c r="M290" t="n">
+        <v>1</v>
+      </c>
+      <c r="O290" t="inlineStr">
+        <is>
+          <t>verified</t>
+        </is>
+      </c>
+      <c r="P290" t="inlineStr">
+        <is>
+          <t>1등 / 2026-10-22</t>
+        </is>
+      </c>
+      <c r="Q290" t="inlineStr">
+        <is>
+          <t>AI 4차 초안(2026-10-21) · 근거 확인 ○: 도로교통법 제85조제5항 원문 확인</t>
+        </is>
+      </c>
+    </row>
+    <row r="291">
+      <c r="A291" t="inlineStr">
+        <is>
+          <t>LAW-0290</t>
+        </is>
+      </c>
+      <c r="B291" t="inlineStr">
+        <is>
+          <t>제2종 운전면허를 받은 사람 중 정기 적성검사를 받아야 하는 사람은?</t>
+        </is>
+      </c>
+      <c r="C291" t="inlineStr">
+        <is>
+          <t>갱신기간에 60세 이상인 사람</t>
+        </is>
+      </c>
+      <c r="D291" t="inlineStr">
+        <is>
+          <t>운전면허증 갱신기간에 70세 이상인 사람</t>
+        </is>
+      </c>
+      <c r="E291" t="inlineStr">
+        <is>
+          <t>갱신기간에 65세 이상인 사람</t>
+        </is>
+      </c>
+      <c r="F291" t="inlineStr">
+        <is>
+          <t>갱신기간에 80세 이상인 사람</t>
+        </is>
+      </c>
+      <c r="G291" t="n">
+        <v>2</v>
+      </c>
+      <c r="H291" t="inlineStr">
+        <is>
+          <t>정기 적성검사는 제1종 운전면허를 받은 사람과, 제2종 운전면허를 받은 사람 중 갱신기간에 70세 이상인 사람이 받는다(제87조제2항).</t>
+        </is>
+      </c>
+      <c r="I291" t="inlineStr">
+        <is>
+          <t>제1종은 모두 받지만 제2종은 일정 나이 이상만 받습니다. 고령 기준 가운데 어느 값이 쓰였는지 떠올려 보세요.</t>
+        </is>
+      </c>
+      <c r="J291" t="inlineStr">
+        <is>
+          <t>도로교통법 제87조제2항제2호</t>
+        </is>
+      </c>
+      <c r="K291" t="inlineStr">
+        <is>
+          <t>2026-10-22</t>
+        </is>
+      </c>
+      <c r="L291" t="inlineStr">
+        <is>
+          <t>자체 작성</t>
+        </is>
+      </c>
+      <c r="M291" t="n">
+        <v>2</v>
+      </c>
+      <c r="O291" t="inlineStr">
+        <is>
+          <t>verified</t>
+        </is>
+      </c>
+      <c r="P291" t="inlineStr">
+        <is>
+          <t>1등 / 2026-10-22</t>
+        </is>
+      </c>
+      <c r="Q291" t="inlineStr">
+        <is>
+          <t>AI 4차 초안(2026-10-21) · 근거 확인 ○: 도로교통법 제87조제2항제2호 원문 확인 · 교차 점검 반영</t>
+        </is>
+      </c>
+    </row>
+    <row r="292">
+      <c r="A292" t="inlineStr">
+        <is>
+          <t>LAW-0291</t>
+        </is>
+      </c>
+      <c r="B292" t="inlineStr">
+        <is>
+          <t>운전면허증 재발급·갱신 등을 신청한 사람에게 발급하는 임시운전증명서의 유효기간 원칙은? (취소·정지처분 대상자 제외)</t>
+        </is>
+      </c>
+      <c r="C292" t="inlineStr">
+        <is>
+          <t>7일 이내</t>
+        </is>
+      </c>
+      <c r="D292" t="inlineStr">
+        <is>
+          <t>30일 이내</t>
+        </is>
+      </c>
+      <c r="E292" t="inlineStr">
+        <is>
+          <t>60일 이내</t>
+        </is>
+      </c>
+      <c r="F292" t="inlineStr">
+        <is>
+          <t>20일 이내</t>
+        </is>
+      </c>
+      <c r="G292" t="n">
+        <v>4</v>
+      </c>
+      <c r="H292" t="inlineStr">
+        <is>
+          <t>임시운전증명서의 유효기간은 20일 이내로 하되, 운전면허 취소·정지처분 대상자는 40일 이내로 할 수 있고, 경찰서장이 필요하면 1회에 한해 20일 범위에서 연장할 수 있다(시행규칙 제88조제2항). 유효기간 중에는 운전면허증과 같은 효력이 있다.</t>
+        </is>
+      </c>
+      <c r="I292" t="inlineStr">
+        <is>
+          <t>처분 대상자에게 주는 기간의 절반이며, 한 달보다 짧습니다.</t>
+        </is>
+      </c>
+      <c r="J292" t="inlineStr">
+        <is>
+          <t>도로교통법 제91조, 도로교통법 시행규칙 제88조제2항</t>
+        </is>
+      </c>
+      <c r="K292" t="inlineStr">
+        <is>
+          <t>2026-10-22</t>
+        </is>
+      </c>
+      <c r="L292" t="inlineStr">
+        <is>
+          <t>자체 작성</t>
+        </is>
+      </c>
+      <c r="M292" t="n">
+        <v>2</v>
+      </c>
+      <c r="O292" t="inlineStr">
+        <is>
+          <t>verified</t>
+        </is>
+      </c>
+      <c r="P292" t="inlineStr">
+        <is>
+          <t>1등 / 2026-10-22</t>
+        </is>
+      </c>
+      <c r="Q292" t="inlineStr">
+        <is>
+          <t>AI 4차 초안(2026-10-21) · 근거 확인 ○: 도로교통법 시행규칙 제88조제2항 '20일 이내…40일 이내' 원문 확인</t>
+        </is>
+      </c>
+    </row>
+    <row r="293">
+      <c r="A293" t="inlineStr">
+        <is>
+          <t>LAW-0292</t>
+        </is>
+      </c>
+      <c r="B293" t="inlineStr">
+        <is>
+          <t>최고속도보다 시속 100킬로미터를 초과한 속도로 몇 회 이상 자동차등을 운전한 경우가 운전면허 취소·정지 사유로 규정되어 있는가?</t>
+        </is>
+      </c>
+      <c r="C293" t="inlineStr">
+        <is>
+          <t>2회 이상</t>
+        </is>
+      </c>
+      <c r="D293" t="inlineStr">
+        <is>
+          <t>5회 이상</t>
+        </is>
+      </c>
+      <c r="E293" t="inlineStr">
+        <is>
+          <t>1회 이상</t>
+        </is>
+      </c>
+      <c r="F293" t="inlineStr">
+        <is>
+          <t>3회 이상</t>
+        </is>
+      </c>
+      <c r="G293" t="n">
+        <v>4</v>
+      </c>
+      <c r="H293" t="inlineStr">
+        <is>
+          <t>도로교통법 제93조제1항제5호의3은 최고속도보다 시속 100킬로미터를 초과한 속도로 3회 이상 운전한 경우를 운전면허 취소·정지 사유로 정한다.</t>
+        </is>
+      </c>
+      <c r="I293" t="inlineStr">
+        <is>
+          <t>1회 초과속도 벌점이 크지만, 이 조항은 그런 극단적 과속을 '여러 번 되풀이'한 경우를 따로 묶어 둔 것입니다.</t>
+        </is>
+      </c>
+      <c r="J293" t="inlineStr">
+        <is>
+          <t>도로교통법 제93조제1항제5호의3</t>
+        </is>
+      </c>
+      <c r="K293" t="inlineStr">
+        <is>
+          <t>2026-10-22</t>
+        </is>
+      </c>
+      <c r="L293" t="inlineStr">
+        <is>
+          <t>자체 작성</t>
+        </is>
+      </c>
+      <c r="M293" t="n">
+        <v>2</v>
+      </c>
+      <c r="O293" t="inlineStr">
+        <is>
+          <t>verified</t>
+        </is>
+      </c>
+      <c r="P293" t="inlineStr">
+        <is>
+          <t>1등 / 2026-10-22</t>
+        </is>
+      </c>
+      <c r="Q293" t="inlineStr">
+        <is>
+          <t>AI 4차 초안(2026-10-21) · 근거 확인 ○: 도로교통법 제93조제1항제5호의3 원문 확인</t>
+        </is>
+      </c>
+    </row>
+    <row r="294">
+      <c r="A294" t="inlineStr">
+        <is>
+          <t>LAW-0293</t>
+        </is>
+      </c>
+      <c r="B294" t="inlineStr">
+        <is>
+          <t>「자동차관리법」에 따라 등록되지 않았거나 임시운행허가를 받지 않은 자동차(이륜자동차 제외)를 운전한 경우의 운전면허 처분은?</t>
+        </is>
+      </c>
+      <c r="C294" t="inlineStr">
+        <is>
+          <t>벌점 10점을 부과한다</t>
+        </is>
+      </c>
+      <c r="D294" t="inlineStr">
+        <is>
+          <t>운전면허 효력을 30일 정지한다</t>
+        </is>
+      </c>
+      <c r="E294" t="inlineStr">
+        <is>
+          <t>처분 없이 과태료만 부과한다</t>
+        </is>
+      </c>
+      <c r="F294" t="inlineStr">
+        <is>
+          <t>운전면허를 취소해야 한다</t>
+        </is>
+      </c>
+      <c r="G294" t="n">
+        <v>4</v>
+      </c>
+      <c r="H294" t="inlineStr">
+        <is>
+          <t>제93조제1항제16호의 미등록·무허가 자동차 운전은 같은 항 단서에 따라 운전면허를 반드시 취소해야 하는 사유이다.</t>
+        </is>
+      </c>
+      <c r="I294" t="inlineStr">
+        <is>
+          <t>제93조 단서에서 '취소하여야 하고'에 묶인 호 번호 목록을 떠올려 보세요.</t>
+        </is>
+      </c>
+      <c r="J294" t="inlineStr">
+        <is>
+          <t>도로교통법 제93조제1항제16호</t>
+        </is>
+      </c>
+      <c r="K294" t="inlineStr">
+        <is>
+          <t>2026-10-22</t>
+        </is>
+      </c>
+      <c r="L294" t="inlineStr">
+        <is>
+          <t>자체 작성</t>
+        </is>
+      </c>
+      <c r="M294" t="n">
+        <v>2</v>
+      </c>
+      <c r="O294" t="inlineStr">
+        <is>
+          <t>verified</t>
+        </is>
+      </c>
+      <c r="P294" t="inlineStr">
+        <is>
+          <t>1등 / 2026-10-22</t>
+        </is>
+      </c>
+      <c r="Q294" t="inlineStr">
+        <is>
+          <t>AI 4차 초안(2026-10-21) · 근거 확인 ○: 도로교통법 제93조제1항 단서 및 제16호 원문 확인</t>
+        </is>
+      </c>
+    </row>
+    <row r="295">
+      <c r="A295" t="inlineStr">
+        <is>
+          <t>LAW-0294</t>
+        </is>
+      </c>
+      <c r="B295" t="inlineStr">
+        <is>
+          <t>연습운전면허를 받은 사람이 교통사고를 일으켰어도 연습운전면허가 취소되지 않는 경우는?</t>
+        </is>
+      </c>
+      <c r="C295" t="inlineStr">
+        <is>
+          <t>주행연습 중 사람을 다치게 했으나 경상인 경우</t>
+        </is>
+      </c>
+      <c r="D295" t="inlineStr">
+        <is>
+          <t>동승 지도자 없이 혼자 연습하다 사고를 낸 경우</t>
+        </is>
+      </c>
+      <c r="E295" t="inlineStr">
+        <is>
+          <t>사업용 화물자동차를 운전하다 사고를 낸 경우</t>
+        </is>
+      </c>
+      <c r="F295" t="inlineStr">
+        <is>
+          <t>교통사고를 일으켰으나 물적 피해만 발생한 경우</t>
+        </is>
+      </c>
+      <c r="G295" t="n">
+        <v>4</v>
+      </c>
+      <c r="H295" t="inlineStr">
+        <is>
+          <t>연습운전면허는 사고나 법규 위반 시 취소가 원칙이지만, 강사·시험관 지시에 따른 운전 중 사고, 도로가 아닌 곳의 사고, 물적 피해만 발생한 사고는 예외이다(시행령 제59조).</t>
+        </is>
+      </c>
+      <c r="I295" t="inlineStr">
+        <is>
+          <t>예외 사유는 본인 책임이 없거나 피해가 가벼운 경우입니다. 사람이 다친 경우는 해당하지 않습니다.</t>
+        </is>
+      </c>
+      <c r="J295" t="inlineStr">
+        <is>
+          <t>도로교통법 제93조제3항, 도로교통법 시행령 제59조</t>
+        </is>
+      </c>
+      <c r="K295" t="inlineStr">
+        <is>
+          <t>2026-10-22</t>
+        </is>
+      </c>
+      <c r="L295" t="inlineStr">
+        <is>
+          <t>자체 작성</t>
+        </is>
+      </c>
+      <c r="M295" t="n">
+        <v>2</v>
+      </c>
+      <c r="O295" t="inlineStr">
+        <is>
+          <t>verified</t>
+        </is>
+      </c>
+      <c r="P295" t="inlineStr">
+        <is>
+          <t>1등 / 2026-10-22</t>
+        </is>
+      </c>
+      <c r="Q295" t="inlineStr">
+        <is>
+          <t>AI 4차 초안(2026-10-21) · 근거 확인 ○: 도로교통법 시행령 제59조제1호~제3호 원문 확인</t>
+        </is>
+      </c>
+    </row>
+    <row r="296">
+      <c r="A296" t="inlineStr">
+        <is>
+          <t>LAW-0295</t>
+        </is>
+      </c>
+      <c r="B296" t="inlineStr">
+        <is>
+          <t>운전면허 취소처분이나 정지처분을 받은 사람이 운전면허증을 반납해야 하는 기간은?</t>
+        </is>
+      </c>
+      <c r="C296" t="inlineStr">
+        <is>
+          <t>사유가 발생한 날부터 3일 이내</t>
+        </is>
+      </c>
+      <c r="D296" t="inlineStr">
+        <is>
+          <t>사유가 발생한 날부터 7일 이내</t>
+        </is>
+      </c>
+      <c r="E296" t="inlineStr">
+        <is>
+          <t>사유가 발생한 날부터 15일 이내</t>
+        </is>
+      </c>
+      <c r="F296" t="inlineStr">
+        <is>
+          <t>사유가 발생한 날부터 30일 이내</t>
+        </is>
+      </c>
+      <c r="G296" t="n">
+        <v>2</v>
+      </c>
+      <c r="H296" t="inlineStr">
+        <is>
+          <t>운전면허 취소·정지처분을 받은 경우 등에는 사유가 발생한 날부터 7일 이내에 주소지 관할 시·도경찰청장에게 운전면허증을 반납해야 한다. 정지처분으로 반납받은 면허증은 정지기간이 끝나면 즉시 돌려준다(제95조).</t>
+        </is>
+      </c>
+      <c r="I296" t="inlineStr">
+        <is>
+          <t>처분을 받은 뒤 오래 미루지 말라는 취지로, 다른 처분 관련 기한(이의신청 60일 등)보다 훨씬 짧습니다.</t>
+        </is>
+      </c>
+      <c r="J296" t="inlineStr">
+        <is>
+          <t>도로교통법 제95조제1항</t>
+        </is>
+      </c>
+      <c r="K296" t="inlineStr">
+        <is>
+          <t>2026-10-22</t>
+        </is>
+      </c>
+      <c r="L296" t="inlineStr">
+        <is>
+          <t>자체 작성</t>
+        </is>
+      </c>
+      <c r="M296" t="n">
+        <v>2</v>
+      </c>
+      <c r="O296" t="inlineStr">
+        <is>
+          <t>verified</t>
+        </is>
+      </c>
+      <c r="P296" t="inlineStr">
+        <is>
+          <t>1등 / 2026-10-22</t>
+        </is>
+      </c>
+      <c r="Q296" t="inlineStr">
+        <is>
+          <t>AI 4차 초안(2026-10-21) · 근거 확인 ○: 도로교통법 제95조제1항 '7일 이내' 원문 확인</t>
+        </is>
+      </c>
+    </row>
+    <row r="297">
+      <c r="A297" t="inlineStr">
+        <is>
+          <t>LAW-0296</t>
+        </is>
+      </c>
+      <c r="B297" t="inlineStr">
+        <is>
+          <t>외국에서 발급받은 국제운전면허증으로 국내에서 운전하는 사람에 대한 설명으로 옳은 것은?</t>
+        </is>
+      </c>
+      <c r="C297" t="inlineStr">
+        <is>
+          <t>입국한 날부터 3년 동안 운전할 수 있다</t>
+        </is>
+      </c>
+      <c r="D297" t="inlineStr">
+        <is>
+          <t>국제운전면허증에 기재되지 않은 차종도 운전할 수 있다</t>
+        </is>
+      </c>
+      <c r="E297" t="inlineStr">
+        <is>
+          <t>대여사업용 자동차를 빌려 운전하는 것도 금지된다</t>
+        </is>
+      </c>
+      <c r="F297" t="inlineStr">
+        <is>
+          <t>「화물자동차 운수사업법」에 따른 사업용 화물자동차는 운전할 수 없다</t>
+        </is>
+      </c>
+      <c r="G297" t="n">
+        <v>4</v>
+      </c>
+      <c r="H297" t="inlineStr">
+        <is>
+          <t>국제운전면허증 소지자는 입국한 날부터 1년 동안 기재된 차종만 운전할 수 있고, 여객·화물 사업용 자동차는 운전할 수 없다. 다만 대여사업용 자동차를 임차하여 운전하는 것은 허용된다(제96조).</t>
+        </is>
+      </c>
+      <c r="I297" t="inlineStr">
+        <is>
+          <t>외국 면허로 국내에서 '영업'을 하는 것까지 허용되는지 생각해 보세요.</t>
+        </is>
+      </c>
+      <c r="J297" t="inlineStr">
+        <is>
+          <t>도로교통법 제96조제1항·제2항</t>
+        </is>
+      </c>
+      <c r="K297" t="inlineStr">
+        <is>
+          <t>2026-10-22</t>
+        </is>
+      </c>
+      <c r="L297" t="inlineStr">
+        <is>
+          <t>자체 작성</t>
+        </is>
+      </c>
+      <c r="M297" t="n">
+        <v>2</v>
+      </c>
+      <c r="O297" t="inlineStr">
+        <is>
+          <t>verified</t>
+        </is>
+      </c>
+      <c r="P297" t="inlineStr">
+        <is>
+          <t>1등 / 2026-10-22</t>
+        </is>
+      </c>
+      <c r="Q297" t="inlineStr">
+        <is>
+          <t>AI 4차 초안(2026-10-21) · 근거 확인 ○: 도로교통법 제96조제1항(입국한 날부터 1년, 기재 차종 한정)·제2항(사업용 운전 금지, 대여사업용 예외) 원문 확인</t>
+        </is>
+      </c>
+    </row>
+    <row r="298">
+      <c r="A298" t="inlineStr">
+        <is>
+          <t>LAW-0297</t>
+        </is>
+      </c>
+      <c r="B298" t="inlineStr">
+        <is>
+          <t>국내 운전면허를 근거로 발급받은 국제운전면허증(국외 운전용)의 효력에 대한 설명으로 옳은 것은?</t>
+        </is>
+      </c>
+      <c r="C298" t="inlineStr">
+        <is>
+          <t>국내 운전면허가 취소되어도 유효기간까지는 효력이 유지된다</t>
+        </is>
+      </c>
+      <c r="D298" t="inlineStr">
+        <is>
+          <t>국내 운전면허의 효력이 정지되면 그 정지기간 동안 효력이 정지된다</t>
+        </is>
+      </c>
+      <c r="E298" t="inlineStr">
+        <is>
+          <t>유효기간은 발급받은 날부터 3년이다</t>
+        </is>
+      </c>
+      <c r="F298" t="inlineStr">
+        <is>
+          <t>원동기장치자전거면허만 가진 사람도 발급받을 수 있다</t>
+        </is>
+      </c>
+      <c r="G298" t="n">
+        <v>2</v>
+      </c>
+      <c r="H298" t="inlineStr">
+        <is>
+          <t>국외 운전용 국제운전면허증의 유효기간은 발급받은 날부터 1년이며, 국내면허가 취소되면 효력을 잃고 정지되면 그 기간 동안 정지된다(제98조). 원동기장치자전거면허·연습면허 소지자는 발급 대상이 아니다(시행규칙 제98조).</t>
+        </is>
+      </c>
+      <c r="I298" t="inlineStr">
+        <is>
+          <t>국제운전면허증은 국내 면허에 '딸린' 증명서라는 점을 생각해 보세요.</t>
+        </is>
+      </c>
+      <c r="J298" t="inlineStr">
+        <is>
+          <t>도로교통법 제98조제2항~제4항, 도로교통법 시행규칙 제98조제1항</t>
+        </is>
+      </c>
+      <c r="K298" t="inlineStr">
+        <is>
+          <t>2026-10-22</t>
+        </is>
+      </c>
+      <c r="L298" t="inlineStr">
+        <is>
+          <t>자체 작성</t>
+        </is>
+      </c>
+      <c r="M298" t="n">
+        <v>3</v>
+      </c>
+      <c r="O298" t="inlineStr">
+        <is>
+          <t>verified</t>
+        </is>
+      </c>
+      <c r="P298" t="inlineStr">
+        <is>
+          <t>1등 / 2026-10-22</t>
+        </is>
+      </c>
+      <c r="Q298" t="inlineStr">
+        <is>
+          <t>AI 4차 초안(2026-10-21) · 근거 확인 ○: 도로교통법 제98조제2항·제3항·제4항, 시행규칙 제98조제1항 괄호 원문 확인</t>
+        </is>
+      </c>
+    </row>
+    <row r="299">
+      <c r="A299" t="inlineStr">
+        <is>
+          <t>LAW-0298</t>
+        </is>
+      </c>
+      <c r="B299" t="inlineStr">
+        <is>
+          <t>범칙행위를 한 사람 중 '범칙자'에 해당하지 않아 범칙금 통고처분 대상이 되지 않는 사람은?</t>
+        </is>
+      </c>
+      <c r="C299" t="inlineStr">
+        <is>
+          <t>신호위반을 처음 한 화물자동차 운전자</t>
+        </is>
+      </c>
+      <c r="D299" t="inlineStr">
+        <is>
+          <t>범칙행위 당시 운전면허증등을 제시하지 못하거나 신원·면허 확인 질문에 응하지 않은 운전자</t>
+        </is>
+      </c>
+      <c r="E299" t="inlineStr">
+        <is>
+          <t>운전면허증을 제시하고 경찰관의 질문에 성실히 답한 운전자</t>
+        </is>
+      </c>
+      <c r="F299" t="inlineStr">
+        <is>
+          <t>범칙행위로 교통사고를 냈으나 종합보험 가입 등으로 처벌을 받지 않게 된 운전자</t>
+        </is>
+      </c>
+      <c r="G299" t="n">
+        <v>2</v>
+      </c>
+      <c r="H299" t="inlineStr">
+        <is>
+          <t>운전면허증등을 제시하지 못하거나 신원 확인 질문에 응하지 않은 운전자, 범칙행위로 교통사고를 일으킨 사람은 범칙자에서 제외된다. 다만 교특법 특례로 처벌받지 않게 된 사람은 다시 범칙자에 포함된다(제162조제2항).</t>
+        </is>
+      </c>
+      <c r="I299" t="inlineStr">
+        <is>
+          <t>현장에서 '누구인지, 면허가 있는지'를 확인할 수 없는 사람에게 간이 절차를 적용할 수 있을지 생각해 보세요.</t>
+        </is>
+      </c>
+      <c r="J299" t="inlineStr">
+        <is>
+          <t>도로교통법 제162조제2항</t>
+        </is>
+      </c>
+      <c r="K299" t="inlineStr">
+        <is>
+          <t>2026-10-22</t>
+        </is>
+      </c>
+      <c r="L299" t="inlineStr">
+        <is>
+          <t>자체 작성</t>
+        </is>
+      </c>
+      <c r="M299" t="n">
+        <v>3</v>
+      </c>
+      <c r="O299" t="inlineStr">
+        <is>
+          <t>verified</t>
+        </is>
+      </c>
+      <c r="P299" t="inlineStr">
+        <is>
+          <t>1등 / 2026-10-22</t>
+        </is>
+      </c>
+      <c r="Q299" t="inlineStr">
+        <is>
+          <t>AI 4차 초안(2026-10-21) · 근거 확인 ○: 도로교통법 제162조제2항제1호·제2호 및 단서 원문 확인</t>
+        </is>
+      </c>
+    </row>
+    <row r="300">
+      <c r="A300" t="inlineStr">
+        <is>
+          <t>LAW-0299</t>
+        </is>
+      </c>
+      <c r="B300" t="inlineStr">
+        <is>
+          <t>경찰서장이 범칙금 납부통고를 하지 않고 즉결심판을 청구해야 하는 사람은?</t>
+        </is>
+      </c>
+      <c r="C300" t="inlineStr">
+        <is>
+          <t>범칙금을 처음 통고받는 사람</t>
+        </is>
+      </c>
+      <c r="D300" t="inlineStr">
+        <is>
+          <t>주소가 확실한 사람</t>
+        </is>
+      </c>
+      <c r="E300" t="inlineStr">
+        <is>
+          <t>범칙금 납부통고서를 받은 사람</t>
+        </is>
+      </c>
+      <c r="F300" t="inlineStr">
+        <is>
+          <t>달아날 우려가 있는 사람</t>
+        </is>
+      </c>
+      <c r="G300" t="n">
+        <v>4</v>
+      </c>
+      <c r="H300" t="inlineStr">
+        <is>
+          <t>성명이나 주소가 확실하지 않은 사람, 달아날 우려가 있는 사람, 범칙금 납부통고서 받기를 거부한 사람에게는 통고처분을 하지 않으며, 이들에 대해서는 지체 없이 즉결심판을 청구해야 한다(제163조제1항, 제165조제1항).</t>
+        </is>
+      </c>
+      <c r="I300" t="inlineStr">
+        <is>
+          <t>통고처분은 나중에 스스로 돈을 내도록 믿고 보내는 절차입니다. 그 믿음이 성립하지 않는 사람을 고르세요.</t>
+        </is>
+      </c>
+      <c r="J300" t="inlineStr">
+        <is>
+          <t>도로교통법 제163조제1항, 제165조제1항</t>
+        </is>
+      </c>
+      <c r="K300" t="inlineStr">
+        <is>
+          <t>2026-10-22</t>
+        </is>
+      </c>
+      <c r="L300" t="inlineStr">
+        <is>
+          <t>자체 작성</t>
+        </is>
+      </c>
+      <c r="M300" t="n">
+        <v>2</v>
+      </c>
+      <c r="O300" t="inlineStr">
+        <is>
+          <t>verified</t>
+        </is>
+      </c>
+      <c r="P300" t="inlineStr">
+        <is>
+          <t>1등 / 2026-10-22</t>
+        </is>
+      </c>
+      <c r="Q300" t="inlineStr">
+        <is>
+          <t>AI 4차 초안(2026-10-21) · 근거 확인 ○: 도로교통법 제163조제1항제1호~제3호, 제165조제1항제1호 원문 확인</t>
+        </is>
+      </c>
+    </row>
+    <row r="301">
+      <c r="A301" t="inlineStr">
+        <is>
+          <t>LAW-0300</t>
+        </is>
+      </c>
+      <c r="B301" t="inlineStr">
+        <is>
+          <t>교통사고처리 특례법에서 말하는 '차'에 포함되는 것은?</t>
+        </is>
+      </c>
+      <c r="C301" t="inlineStr">
+        <is>
+          <t>철도차량</t>
+        </is>
+      </c>
+      <c r="D301" t="inlineStr">
+        <is>
+          <t>선박</t>
+        </is>
+      </c>
+      <c r="E301" t="inlineStr">
+        <is>
+          <t>「건설기계관리법」에 따른 건설기계</t>
+        </is>
+      </c>
+      <c r="F301" t="inlineStr">
+        <is>
+          <t>항공기</t>
+        </is>
+      </c>
+      <c r="G301" t="n">
+        <v>3</v>
+      </c>
+      <c r="H301" t="inlineStr">
+        <is>
+          <t>교통사고처리 특례법의 '차'는 도로교통법상 차와 건설기계관리법에 따른 건설기계를 말한다(제2조제1호). 따라서 굴착기 등 건설기계 사고에도 특례가 적용될 수 있다.</t>
+        </is>
+      </c>
+      <c r="I301" t="inlineStr">
+        <is>
+          <t>도로 위를 달리는 장비 가운데 도로교통법의 '자동차'와 별도 법으로 관리되는 것을 떠올려 보세요.</t>
+        </is>
+      </c>
+      <c r="J301" t="inlineStr">
+        <is>
+          <t>교통사고처리 특례법 제2조제1호</t>
+        </is>
+      </c>
+      <c r="K301" t="inlineStr">
+        <is>
+          <t>2026-10-22</t>
+        </is>
+      </c>
+      <c r="L301" t="inlineStr">
+        <is>
+          <t>자체 작성</t>
+        </is>
+      </c>
+      <c r="M301" t="n">
+        <v>2</v>
+      </c>
+      <c r="O301" t="inlineStr">
+        <is>
+          <t>verified</t>
+        </is>
+      </c>
+      <c r="P301" t="inlineStr">
+        <is>
+          <t>1등 / 2026-10-22</t>
+        </is>
+      </c>
+      <c r="Q301" t="inlineStr">
+        <is>
+          <t>AI 4차 초안(2026-10-21) · 근거 확인 ○: 교통사고처리 특례법 제2조제1호 원문 확인(2025.6.4 시행본)</t>
+        </is>
+      </c>
+    </row>
+    <row r="302">
+      <c r="A302" t="inlineStr">
+        <is>
+          <t>LAW-0301</t>
+        </is>
+      </c>
+      <c r="B302" t="inlineStr">
+        <is>
+          <t>교통사고처리 특례법상 12대 중과실 중 '무면허운전'에 대한 설명으로 옳은 것은?</t>
+        </is>
+      </c>
+      <c r="C302" t="inlineStr">
+        <is>
+          <t>면허 정지 중 운전은 무면허가 아니므로 특례가 적용된다</t>
+        </is>
+      </c>
+      <c r="D302" t="inlineStr">
+        <is>
+          <t>운전면허 효력이 정지 중인 때 운전한 경우도 운전면허를 받지 않은 것으로 본다</t>
+        </is>
+      </c>
+      <c r="E302" t="inlineStr">
+        <is>
+          <t>국제운전면허증으로 운전하는 것은 언제나 무면허로 본다</t>
+        </is>
+      </c>
+      <c r="F302" t="inlineStr">
+        <is>
+          <t>건설기계조종사면허 없이 건설기계를 운전한 경우는 포함되지 않는다</t>
+        </is>
+      </c>
+      <c r="G302" t="n">
+        <v>2</v>
+      </c>
+      <c r="H302" t="inlineStr">
+        <is>
+          <t>제3조제2항제7호는 운전면허·건설기계조종사면허 없이 또는 국제운전면허증 없이 운전한 경우를 정하며, 면허 효력이 정지 중이거나 운전 금지 중인 때에도 면허를 받지 않은 것으로 본다.</t>
+        </is>
+      </c>
+      <c r="I302" t="inlineStr">
+        <is>
+          <t>면허증을 갖고 있더라도 '운전할 수 있는 상태'인지가 기준입니다.</t>
+        </is>
+      </c>
+      <c r="J302" t="inlineStr">
+        <is>
+          <t>교통사고처리 특례법 제3조제2항제7호</t>
+        </is>
+      </c>
+      <c r="K302" t="inlineStr">
+        <is>
+          <t>2026-10-22</t>
+        </is>
+      </c>
+      <c r="L302" t="inlineStr">
+        <is>
+          <t>자체 작성</t>
+        </is>
+      </c>
+      <c r="M302" t="n">
+        <v>3</v>
+      </c>
+      <c r="O302" t="inlineStr">
+        <is>
+          <t>verified</t>
+        </is>
+      </c>
+      <c r="P302" t="inlineStr">
+        <is>
+          <t>1등 / 2026-10-22</t>
+        </is>
+      </c>
+      <c r="Q302" t="inlineStr">
+        <is>
+          <t>AI 4차 초안(2026-10-21) · 근거 확인 ○: 교통사고처리 특례법 제3조제2항제7호 후단 원문 확인</t>
+        </is>
+      </c>
+    </row>
+    <row r="303">
+      <c r="A303" t="inlineStr">
+        <is>
+          <t>LAW-0302</t>
+        </is>
+      </c>
+      <c r="B303" t="inlineStr">
+        <is>
+          <t>자동차 교통사고로 피해자를 상해에 이르게 한 운전자가 구호 등 필요한 조치를 하지 않고 도주한 경우 특정범죄 가중처벌 등에 관한 법률상 처벌 기준은?</t>
+        </is>
+      </c>
+      <c r="C303" t="inlineStr">
+        <is>
+          <t>1년 이상의 유기징역 또는 500만원 이상 3천만원 이하의 벌금</t>
+        </is>
+      </c>
+      <c r="D303" t="inlineStr">
+        <is>
+          <t>5년 이하의 금고 또는 2천만원 이하의 벌금</t>
+        </is>
+      </c>
+      <c r="E303" t="inlineStr">
+        <is>
+          <t>3년 이상의 유기징역</t>
+        </is>
+      </c>
+      <c r="F303" t="inlineStr">
+        <is>
+          <t>무기 또는 5년 이상의 징역</t>
+        </is>
+      </c>
+      <c r="G303" t="n">
+        <v>1</v>
+      </c>
+      <c r="H303" t="inlineStr">
+        <is>
+          <t>도주 치상은 1년 이상의 유기징역 또는 500만원 이상 3천만원 이하의 벌금에 처한다(제5조의3제1항제2호). 피해자를 사고 장소에서 옮겨 유기하고 도주한 경우에는 3년 이상의 유기징역으로 더 무겁다.</t>
+        </is>
+      </c>
+      <c r="I303" t="inlineStr">
+        <is>
+          <t>사망 도주보다는 가볍지만, 교통사고처리 특례법의 기본 처벌(5년 이하 금고)보다는 무겁게 정해져 있습니다.</t>
+        </is>
+      </c>
+      <c r="J303" t="inlineStr">
+        <is>
+          <t>특정범죄 가중처벌 등에 관한 법률 제5조의3제1항제2호</t>
+        </is>
+      </c>
+      <c r="K303" t="inlineStr">
+        <is>
+          <t>2026-10-22</t>
+        </is>
+      </c>
+      <c r="L303" t="inlineStr">
+        <is>
+          <t>자체 작성</t>
+        </is>
+      </c>
+      <c r="M303" t="n">
+        <v>3</v>
+      </c>
+      <c r="O303" t="inlineStr">
+        <is>
+          <t>verified</t>
+        </is>
+      </c>
+      <c r="P303" t="inlineStr">
+        <is>
+          <t>1등 / 2026-10-22</t>
+        </is>
+      </c>
+      <c r="Q303" t="inlineStr">
+        <is>
+          <t>AI 4차 초안(2026-10-21) · 근거 확인 ○: 특정범죄 가중처벌 등에 관한 법률 제5조의3제1항제2호 원문 확인(2025.7.2 시행본) · 교차 점검 반영</t>
+        </is>
+      </c>
+    </row>
+    <row r="304">
+      <c r="A304" t="inlineStr">
+        <is>
+          <t>LAW-0303</t>
+        </is>
+      </c>
+      <c r="B304" t="inlineStr">
+        <is>
+          <t>자동차 교통사고로 피해자를 사망에 이르게 하고 도주하거나 도주 후 피해자가 사망한 경우의 처벌 기준은? (피해자를 옮겨 유기한 경우 제외)</t>
+        </is>
+      </c>
+      <c r="C304" t="inlineStr">
+        <is>
+          <t>무기 또는 5년 이상의 징역</t>
+        </is>
+      </c>
+      <c r="D304" t="inlineStr">
+        <is>
+          <t>사형, 무기 또는 5년 이상의 징역</t>
+        </is>
+      </c>
+      <c r="E304" t="inlineStr">
+        <is>
+          <t>1년 이상의 유기징역</t>
+        </is>
+      </c>
+      <c r="F304" t="inlineStr">
+        <is>
+          <t>무기 또는 3년 이상의 징역</t>
+        </is>
+      </c>
+      <c r="G304" t="n">
+        <v>1</v>
+      </c>
+      <c r="H304" t="inlineStr">
+        <is>
+          <t>사망 도주는 무기 또는 5년 이상의 징역에 처한다(제5조의3제1항제1호). 피해자를 사고 장소에서 옮겨 유기하고 도주하여 사망한 경우에는 사형까지 가능하다(제2항제1호).</t>
+        </is>
+      </c>
+      <c r="I304" t="inlineStr">
+        <is>
+          <t>유기 도주일 때만 가장 무거운 형벌이 추가된다는 점을 구분하세요.</t>
+        </is>
+      </c>
+      <c r="J304" t="inlineStr">
+        <is>
+          <t>특정범죄 가중처벌 등에 관한 법률 제5조의3제1항제1호</t>
+        </is>
+      </c>
+      <c r="K304" t="inlineStr">
+        <is>
+          <t>2026-10-22</t>
+        </is>
+      </c>
+      <c r="L304" t="inlineStr">
+        <is>
+          <t>자체 작성</t>
+        </is>
+      </c>
+      <c r="M304" t="n">
+        <v>2</v>
+      </c>
+      <c r="O304" t="inlineStr">
+        <is>
+          <t>verified</t>
+        </is>
+      </c>
+      <c r="P304" t="inlineStr">
+        <is>
+          <t>1등 / 2026-10-22</t>
+        </is>
+      </c>
+      <c r="Q304" t="inlineStr">
+        <is>
+          <t>AI 4차 초안(2026-10-21) · 근거 확인 ○: 특정범죄 가중처벌 등에 관한 법률 제5조의3제1항제1호·제2항제1호 원문 확인</t>
+        </is>
+      </c>
+    </row>
+    <row r="305">
+      <c r="A305" t="inlineStr">
+        <is>
+          <t>LAW-0304</t>
+        </is>
+      </c>
+      <c r="B305" t="inlineStr">
+        <is>
+          <t>사고운전자가 피해자를 사고 장소에서 옮겨 유기하고 도주하여 피해자가 상해를 입은 경우의 처벌 기준은?</t>
+        </is>
+      </c>
+      <c r="C305" t="inlineStr">
+        <is>
+          <t>1년 이상의 유기징역 또는 500만원 이상 3천만원 이하의 벌금</t>
+        </is>
+      </c>
+      <c r="D305" t="inlineStr">
+        <is>
+          <t>5년 이하의 금고</t>
+        </is>
+      </c>
+      <c r="E305" t="inlineStr">
+        <is>
+          <t>3년 이상의 유기징역</t>
+        </is>
+      </c>
+      <c r="F305" t="inlineStr">
+        <is>
+          <t>2년 이하의 징역 또는 500만원 이하의 벌금</t>
+        </is>
+      </c>
+      <c r="G305" t="n">
+        <v>3</v>
+      </c>
+      <c r="H305" t="inlineStr">
+        <is>
+          <t>피해자를 사고 장소로부터 옮겨 유기하고 도주하여 상해에 이르게 한 경우 3년 이상의 유기징역에 처하며, 벌금형은 없다(제5조의3제2항제2호).</t>
+        </is>
+      </c>
+      <c r="I305" t="inlineStr">
+        <is>
+          <t>피해자를 옮겨 버린 행위가 더해지면 단순 도주 치상보다 무거워집니다.</t>
+        </is>
+      </c>
+      <c r="J305" t="inlineStr">
+        <is>
+          <t>특정범죄 가중처벌 등에 관한 법률 제5조의3제2항제2호</t>
+        </is>
+      </c>
+      <c r="K305" t="inlineStr">
+        <is>
+          <t>2026-10-22</t>
+        </is>
+      </c>
+      <c r="L305" t="inlineStr">
+        <is>
+          <t>자체 작성</t>
+        </is>
+      </c>
+      <c r="M305" t="n">
+        <v>3</v>
+      </c>
+      <c r="O305" t="inlineStr">
+        <is>
+          <t>verified</t>
+        </is>
+      </c>
+      <c r="P305" t="inlineStr">
+        <is>
+          <t>1등 / 2026-10-22</t>
+        </is>
+      </c>
+      <c r="Q305" t="inlineStr">
+        <is>
+          <t>AI 4차 초안(2026-10-21) · 근거 확인 ○: 특정범죄 가중처벌 등에 관한 법률 제5조의3제2항제2호 원문 확인 · 교차 점검 반영</t>
+        </is>
+      </c>
+    </row>
+    <row r="306">
+      <c r="A306" t="inlineStr">
+        <is>
+          <t>LAW-0305</t>
+        </is>
+      </c>
+      <c r="B306" t="inlineStr">
+        <is>
+          <t>음주 또는 약물의 영향으로 정상적인 운전이 곤란한 상태에서 자동차등을 운전하여 사람을 사망에 이르게 한 사람의 처벌 기준은?</t>
+        </is>
+      </c>
+      <c r="C306" t="inlineStr">
+        <is>
+          <t>5년 이하의 금고 또는 2천만원 이하의 벌금</t>
+        </is>
+      </c>
+      <c r="D306" t="inlineStr">
+        <is>
+          <t>무기 또는 3년 이상의 징역</t>
+        </is>
+      </c>
+      <c r="E306" t="inlineStr">
+        <is>
+          <t>1년 이상 15년 이하의 징역</t>
+        </is>
+      </c>
+      <c r="F306" t="inlineStr">
+        <is>
+          <t>무기 또는 5년 이상의 징역</t>
+        </is>
+      </c>
+      <c r="G306" t="n">
+        <v>2</v>
+      </c>
+      <c r="H306" t="inlineStr">
+        <is>
+          <t>위험운전 치사는 무기 또는 3년 이상의 징역에 처한다. 상해에 이르게 한 경우는 1년 이상 15년 이하의 징역 또는 1천만원 이상 3천만원 이하의 벌금이다(제5조의11제1항).</t>
+        </is>
+      </c>
+      <c r="I306" t="inlineStr">
+        <is>
+          <t>어린이 보호구역 어린이 사망사고의 처벌 기준과 같은 수준입니다.</t>
+        </is>
+      </c>
+      <c r="J306" t="inlineStr">
+        <is>
+          <t>특정범죄 가중처벌 등에 관한 법률 제5조의11제1항</t>
+        </is>
+      </c>
+      <c r="K306" t="inlineStr">
+        <is>
+          <t>2026-10-22</t>
+        </is>
+      </c>
+      <c r="L306" t="inlineStr">
+        <is>
+          <t>자체 작성</t>
+        </is>
+      </c>
+      <c r="M306" t="n">
+        <v>2</v>
+      </c>
+      <c r="O306" t="inlineStr">
+        <is>
+          <t>verified</t>
+        </is>
+      </c>
+      <c r="P306" t="inlineStr">
+        <is>
+          <t>1등 / 2026-10-22</t>
+        </is>
+      </c>
+      <c r="Q306" t="inlineStr">
+        <is>
+          <t>AI 4차 초안(2026-10-21) · 근거 확인 ○: 특정범죄 가중처벌 등에 관한 법률 제5조의11제1항 원문 확인</t>
+        </is>
+      </c>
+    </row>
+    <row r="307">
+      <c r="A307" t="inlineStr">
+        <is>
+          <t>LAW-0306</t>
+        </is>
+      </c>
+      <c r="B307" t="inlineStr">
+        <is>
+          <t>특정범죄 가중처벌 등에 관한 법률상 어린이 보호구역 치사상 가중처벌에서 '어린이'의 기준은?</t>
+        </is>
+      </c>
+      <c r="C307" t="inlineStr">
+        <is>
+          <t>13세 미만인 사람</t>
+        </is>
+      </c>
+      <c r="D307" t="inlineStr">
+        <is>
+          <t>6세 미만인 사람</t>
+        </is>
+      </c>
+      <c r="E307" t="inlineStr">
+        <is>
+          <t>10세 미만인 사람</t>
+        </is>
+      </c>
+      <c r="F307" t="inlineStr">
+        <is>
+          <t>15세 미만인 사람</t>
+        </is>
+      </c>
+      <c r="G307" t="n">
+        <v>1</v>
+      </c>
+      <c r="H307" t="inlineStr">
+        <is>
+          <t>특가법 제5조의13은 어린이를 13세 미만인 사람으로 정한다. 도로교통법의 어린이 기준과 같으며, 영유아(6세 미만)와는 다르다.</t>
+        </is>
+      </c>
+      <c r="I307" t="inlineStr">
+        <is>
+          <t>도로교통법이 정한 '어린이' 나이 기준을 그대로 따릅니다. 영유아 기준과 헷갈리지 마세요.</t>
+        </is>
+      </c>
+      <c r="J307" t="inlineStr">
+        <is>
+          <t>특정범죄 가중처벌 등에 관한 법률 제5조의13</t>
+        </is>
+      </c>
+      <c r="K307" t="inlineStr">
+        <is>
+          <t>2026-10-22</t>
+        </is>
+      </c>
+      <c r="L307" t="inlineStr">
+        <is>
+          <t>자체 작성</t>
+        </is>
+      </c>
+      <c r="M307" t="n">
+        <v>1</v>
+      </c>
+      <c r="O307" t="inlineStr">
+        <is>
+          <t>verified</t>
+        </is>
+      </c>
+      <c r="P307" t="inlineStr">
+        <is>
+          <t>1등 / 2026-10-22</t>
+        </is>
+      </c>
+      <c r="Q307" t="inlineStr">
+        <is>
+          <t>AI 4차 초안(2026-10-21) · 근거 확인 ○: 특정범죄 가중처벌 등에 관한 법률 제5조의13 '어린이(13세 미만인 사람을 말한다)' 원문 확인 · 교차 점검 반영</t>
+        </is>
+      </c>
+    </row>
+    <row r="308">
+      <c r="A308" t="inlineStr">
+        <is>
+          <t>LAW-0307</t>
+        </is>
+      </c>
+      <c r="B308" t="inlineStr">
+        <is>
+          <t>견인자동차가 아닌 자동차로 총중량 2천킬로그램 미만인 자동차를 그 3배 이상의 총중량을 가진 자동차로 견인하여 일반도로를 통행할 때의 속도는?</t>
+        </is>
+      </c>
+      <c r="C308" t="inlineStr">
+        <is>
+          <t>매시 25킬로미터 이내</t>
+        </is>
+      </c>
+      <c r="D308" t="inlineStr">
+        <is>
+          <t>매시 30킬로미터 이내</t>
+        </is>
+      </c>
+      <c r="E308" t="inlineStr">
+        <is>
+          <t>매시 40킬로미터 이내</t>
+        </is>
+      </c>
+      <c r="F308" t="inlineStr">
+        <is>
+          <t>매시 50킬로미터 이내</t>
+        </is>
+      </c>
+      <c r="G308" t="n">
+        <v>2</v>
+      </c>
+      <c r="H308" t="inlineStr">
+        <is>
+          <t>견인자동차가 아닌 차로 다른 차를 견인하여 고속도로 외 도로를 통행할 때, 총중량 2천kg 미만 차를 그 3배 이상 총중량의 차로 견인하면 매시 30km 이내, 그 밖의 경우와 이륜자동차가 견인하는 경우는 매시 25km 이내이다(시행규칙 제20조).</t>
+        </is>
+      </c>
+      <c r="I308" t="inlineStr">
+        <is>
+          <t>끄는 차가 충분히 무거워 더 안정적인 경우이므로, 일반 견인 기준보다 조금 높습니다.</t>
+        </is>
+      </c>
+      <c r="J308" t="inlineStr">
+        <is>
+          <t>도로교통법 시행규칙 제20조제1호</t>
+        </is>
+      </c>
+      <c r="K308" t="inlineStr">
+        <is>
+          <t>2026-10-22</t>
+        </is>
+      </c>
+      <c r="L308" t="inlineStr">
+        <is>
+          <t>자체 작성</t>
+        </is>
+      </c>
+      <c r="M308" t="n">
+        <v>2</v>
+      </c>
+      <c r="O308" t="inlineStr">
+        <is>
+          <t>verified</t>
+        </is>
+      </c>
+      <c r="P308" t="inlineStr">
+        <is>
+          <t>1등 / 2026-10-22</t>
+        </is>
+      </c>
+      <c r="Q308" t="inlineStr">
+        <is>
+          <t>AI 4차 초안(2026-10-21) · 근거 확인 ○: 도로교통법 시행규칙 제20조제1호·제2호 원문 확인</t>
+        </is>
+      </c>
+    </row>
+    <row r="309">
+      <c r="A309" t="inlineStr">
+        <is>
+          <t>LAW-0308</t>
+        </is>
+      </c>
+      <c r="B309" t="inlineStr">
+        <is>
+          <t>자전거등이 자전거횡단도를 통행하고 있을 때 차마의 운전자가 해야 할 일은?</t>
+        </is>
+      </c>
+      <c r="C309" t="inlineStr">
+        <is>
+          <t>경음기를 울려 자전거를 먼저 비키게 한다</t>
+        </is>
+      </c>
+      <c r="D309" t="inlineStr">
+        <is>
+          <t>자전거 뒤쪽으로 돌아 속도를 유지하며 지나간다</t>
+        </is>
+      </c>
+      <c r="E309" t="inlineStr">
+        <is>
+          <t>자전거횡단도 앞(정지선이 있으면 정지선)에서 일시정지한다</t>
+        </is>
+      </c>
+      <c r="F309" t="inlineStr">
+        <is>
+          <t>상향등을 켜 자전거 운전자에게 경고한다</t>
+        </is>
+      </c>
+      <c r="G309" t="n">
+        <v>3</v>
+      </c>
+      <c r="H309" t="inlineStr">
+        <is>
+          <t>차마의 운전자는 자전거등이 자전거횡단도를 통행하고 있을 때 횡단을 방해하거나 위험하게 하지 않도록 자전거횡단도 앞(정지선이 있는 곳은 정지선)에서 일시정지해야 한다(제15조의2제3항).</t>
+        </is>
+      </c>
+      <c r="I309" t="inlineStr">
+        <is>
+          <t>횡단보도의 보행자 보호 규정과 같은 방식이 자전거에도 적용됩니다.</t>
+        </is>
+      </c>
+      <c r="J309" t="inlineStr">
+        <is>
+          <t>도로교통법 제15조의2제3항</t>
+        </is>
+      </c>
+      <c r="K309" t="inlineStr">
+        <is>
+          <t>2026-10-22</t>
+        </is>
+      </c>
+      <c r="L309" t="inlineStr">
+        <is>
+          <t>자체 작성</t>
+        </is>
+      </c>
+      <c r="M309" t="n">
+        <v>1</v>
+      </c>
+      <c r="O309" t="inlineStr">
+        <is>
+          <t>verified</t>
+        </is>
+      </c>
+      <c r="P309" t="inlineStr">
+        <is>
+          <t>1등 / 2026-10-22</t>
+        </is>
+      </c>
+      <c r="Q309" t="inlineStr">
+        <is>
+          <t>AI 4차 초안(2026-10-21) · 근거 확인 ○: 도로교통법 제15조의2제3항 원문 확인</t>
+        </is>
+      </c>
+    </row>
+    <row r="310">
+      <c r="A310" t="inlineStr">
+        <is>
+          <t>LAW-0309</t>
+        </is>
+      </c>
+      <c r="B310" t="inlineStr">
+        <is>
+          <t>운송사업자는 허가받은 날부터 일정 기간마다 차고지·차량 대수 등 허가기준에 관한 사항을 신고해야 한다. 시행령에서 정한 그 기간은?</t>
+        </is>
+      </c>
+      <c r="C310" t="inlineStr">
+        <is>
+          <t>1년</t>
+        </is>
+      </c>
+      <c r="D310" t="inlineStr">
+        <is>
+          <t>5년</t>
+        </is>
+      </c>
+      <c r="E310" t="inlineStr">
+        <is>
+          <t>3년</t>
+        </is>
+      </c>
+      <c r="F310" t="inlineStr">
+        <is>
+          <t>2년</t>
+        </is>
+      </c>
+      <c r="G310" t="n">
+        <v>2</v>
+      </c>
+      <c r="H310" t="inlineStr">
+        <is>
+          <t>법 제3조제9항은 허가받은 날부터 5년의 범위에서 대통령령으로 정하는 기간마다 신고하도록 하고, 시행령 제3조제3항은 그 기간을 5년으로 정하였다.</t>
+        </is>
+      </c>
+      <c r="I310" t="inlineStr">
+        <is>
+          <t>매년 받으면 행정 부담이 크므로, 법률이 허용한 범위 중 가장 긴 주기를 그대로 택했다.</t>
+        </is>
+      </c>
+      <c r="J310" t="inlineStr">
+        <is>
+          <t>화물자동차 운수사업법 제3조제9항, 같은 법 시행령 제3조제3항</t>
+        </is>
+      </c>
+      <c r="K310" t="inlineStr">
+        <is>
+          <t>2026-10-22</t>
+        </is>
+      </c>
+      <c r="L310" t="inlineStr">
+        <is>
+          <t>자체 작성</t>
+        </is>
+      </c>
+      <c r="M310" t="n">
+        <v>2</v>
+      </c>
+      <c r="O310" t="inlineStr">
+        <is>
+          <t>verified</t>
+        </is>
+      </c>
+      <c r="P310" t="inlineStr">
+        <is>
+          <t>1등 / 2026-10-22</t>
+        </is>
+      </c>
+      <c r="Q310" t="inlineStr">
+        <is>
+          <t>AI 4차 초안(2026-10-21) · 근거 확인 ○: 법 제3조제9항 '5년의 범위에서 대통령령으로 정하는 기간마다', 영 제3조제3항 '대통령령으로 정하는 기간이란 5년을 말한다' 확인. 국가법령정보센터 원문(법 2026.7.1., 영 2026.6.3., 규칙 2026.6.30. 시행)</t>
+        </is>
+      </c>
+    </row>
+    <row r="311">
+      <c r="A311" t="inlineStr">
+        <is>
+          <t>LAW-0310</t>
+        </is>
+      </c>
+      <c r="B311" t="inlineStr">
+        <is>
+          <t>운송사업자가 감차 조치 명령을 받은 경우, 그 후 일정 기간 동안은 증차를 수반하는 허가사항 변경을 할 수 없다. 그 기간은?</t>
+        </is>
+      </c>
+      <c r="C311" t="inlineStr">
+        <is>
+          <t>감차 조치 명령을 받은 후 6개월</t>
+        </is>
+      </c>
+      <c r="D311" t="inlineStr">
+        <is>
+          <t>감차 조치 명령을 받은 후 1년</t>
+        </is>
+      </c>
+      <c r="E311" t="inlineStr">
+        <is>
+          <t>감차 조치 명령을 받은 후 3년</t>
+        </is>
+      </c>
+      <c r="F311" t="inlineStr">
+        <is>
+          <t>감차 조치 명령을 받은 후 3개월</t>
+        </is>
+      </c>
+      <c r="G311" t="n">
+        <v>2</v>
+      </c>
+      <c r="H311" t="inlineStr">
+        <is>
+          <t>법 제3조제8항제2호에 따라 감차 조치 명령을 받은 후 1년이 지나지 않은 운송사업자는 증차를 수반하는 변경을 할 수 없다. 개선명령을 이행하지 않은 경우도 증차가 제한된다.</t>
+        </is>
+      </c>
+      <c r="I311" t="inlineStr">
+        <is>
+          <t>차를 줄이라는 처분을 받자마자 다시 늘리는 것을 막기 위한 제한입니다.</t>
+        </is>
+      </c>
+      <c r="J311" t="inlineStr">
+        <is>
+          <t>화물자동차 운수사업법 제3조제8항</t>
+        </is>
+      </c>
+      <c r="K311" t="inlineStr">
+        <is>
+          <t>2026-10-22</t>
+        </is>
+      </c>
+      <c r="L311" t="inlineStr">
+        <is>
+          <t>자체 작성</t>
+        </is>
+      </c>
+      <c r="M311" t="n">
+        <v>2</v>
+      </c>
+      <c r="O311" t="inlineStr">
+        <is>
+          <t>verified</t>
+        </is>
+      </c>
+      <c r="P311" t="inlineStr">
+        <is>
+          <t>1등 / 2026-10-22</t>
+        </is>
+      </c>
+      <c r="Q311" t="inlineStr">
+        <is>
+          <t>AI 4차 초안(2026-10-21) · 근거 확인 ○: 법 제3조제8항 '2. 제19조제1항에 따른 감차 조치 명령을 받은 후 1년이 지나지 아니한 경우' 확인. 국가법령정보센터 원문(법 2026.7.1., 영 2026.6.3., 규칙 2026.6.30. 시행) · 교차 점검 반영</t>
+        </is>
+      </c>
+    </row>
+    <row r="312">
+      <c r="A312" t="inlineStr">
+        <is>
+          <t>LAW-0311</t>
+        </is>
+      </c>
+      <c r="B312" t="inlineStr">
+        <is>
+          <t>운송사업자가 상호 변경 등 경미한 허가사항 변경신고를 한 경우, 국토교통부장관은 신고를 받은 날부터 며칠 이내에 신고수리 여부를 통지해야 하는가?</t>
+        </is>
+      </c>
+      <c r="C312" t="inlineStr">
+        <is>
+          <t>3일 이내</t>
+        </is>
+      </c>
+      <c r="D312" t="inlineStr">
+        <is>
+          <t>14일 이내</t>
+        </is>
+      </c>
+      <c r="E312" t="inlineStr">
+        <is>
+          <t>7일 이내</t>
+        </is>
+      </c>
+      <c r="F312" t="inlineStr">
+        <is>
+          <t>5일 이내</t>
+        </is>
+      </c>
+      <c r="G312" t="n">
+        <v>1</v>
+      </c>
+      <c r="H312" t="inlineStr">
+        <is>
+          <t>법 제3조제4항에 따라 변경신고를 받은 날부터 3일 이내에 수리 여부를 통지해야 하며, 기간 내 통지하지 않으면 기간이 끝난 다음 날 수리된 것으로 본다.</t>
+        </is>
+      </c>
+      <c r="I312" t="inlineStr">
+        <is>
+          <t>상호·대표자 변경처럼 서류만 확인하면 되는 간단한 신고라 처리 기간이 매우 짧다. 운임·요금 신고(14일)와 헷갈리지 말자.</t>
+        </is>
+      </c>
+      <c r="J312" t="inlineStr">
+        <is>
+          <t>화물자동차 운수사업법 제3조제4항·제5항</t>
+        </is>
+      </c>
+      <c r="K312" t="inlineStr">
+        <is>
+          <t>2026-10-22</t>
+        </is>
+      </c>
+      <c r="L312" t="inlineStr">
+        <is>
+          <t>자체 작성</t>
+        </is>
+      </c>
+      <c r="M312" t="n">
+        <v>2</v>
+      </c>
+      <c r="O312" t="inlineStr">
+        <is>
+          <t>verified</t>
+        </is>
+      </c>
+      <c r="P312" t="inlineStr">
+        <is>
+          <t>1등 / 2026-10-22</t>
+        </is>
+      </c>
+      <c r="Q312" t="inlineStr">
+        <is>
+          <t>AI 4차 초안(2026-10-21) · 근거 확인 ○: 법 제3조제4항 '변경신고를 받은 날부터 3일 이내에 신고수리 여부를 신고인에게 통지' 확인. 국가법령정보센터 원문(법 2026.7.1., 영 2026.6.3., 규칙 2026.6.30. 시행)</t>
+        </is>
+      </c>
+    </row>
+    <row r="313">
+      <c r="A313" t="inlineStr">
+        <is>
+          <t>LAW-0312</t>
+        </is>
+      </c>
+      <c r="B313" t="inlineStr">
+        <is>
+          <t>주사무소 외의 장소에서 상주하여 영업하려면 영업소 설치 허가를 받아야 한다. 이 허가 의무가 적용되지 않는 사업자는?</t>
+        </is>
+      </c>
+      <c r="C313" t="inlineStr">
+        <is>
+          <t>개인화물자동차 운송사업자</t>
+        </is>
+      </c>
+      <c r="D313" t="inlineStr">
+        <is>
+          <t>일반화물자동차 운송사업자</t>
+        </is>
+      </c>
+      <c r="E313" t="inlineStr">
+        <is>
+          <t>화물자동차 운송주선사업자</t>
+        </is>
+      </c>
+      <c r="F313" t="inlineStr">
+        <is>
+          <t>화물자동차 운송가맹사업자</t>
+        </is>
+      </c>
+      <c r="G313" t="n">
+        <v>1</v>
+      </c>
+      <c r="H313" t="inlineStr">
+        <is>
+          <t>법 제3조제11항 단서에 따라 개인 운송사업자는 영업소 설치 허가 대상에서 제외된다. 운송주선사업자(제24조제8항)와 운송가맹사업자(제29조제5항)는 허가를 받아야 한다.</t>
+        </is>
+      </c>
+      <c r="I313" t="inlineStr">
+        <is>
+          <t>차 한 대로 본인이 직접 운전하는 사업자에게 '다른 곳의 영업소'라는 개념이 맞는지 생각해 보자.</t>
+        </is>
+      </c>
+      <c r="J313" t="inlineStr">
+        <is>
+          <t>화물자동차 운수사업법 제3조제11항, 제24조제8항, 제29조제5항</t>
+        </is>
+      </c>
+      <c r="K313" t="inlineStr">
+        <is>
+          <t>2026-10-22</t>
+        </is>
+      </c>
+      <c r="L313" t="inlineStr">
+        <is>
+          <t>자체 작성</t>
+        </is>
+      </c>
+      <c r="M313" t="n">
+        <v>2</v>
+      </c>
+      <c r="O313" t="inlineStr">
+        <is>
+          <t>verified</t>
+        </is>
+      </c>
+      <c r="P313" t="inlineStr">
+        <is>
+          <t>1등 / 2026-10-22</t>
+        </is>
+      </c>
+      <c r="Q313" t="inlineStr">
+        <is>
+          <t>AI 4차 초안(2026-10-21) · 근거 확인 ○: 법 제3조제11항 '다만, 개인 운송사업자의 경우에는 그러하지 아니하다' 확인. 국가법령정보센터 원문(법 2026.7.1., 영 2026.6.3., 규칙 2026.6.30. 시행)</t>
+        </is>
+      </c>
+    </row>
+    <row r="314">
+      <c r="A314" t="inlineStr">
+        <is>
+          <t>LAW-0313</t>
+        </is>
+      </c>
+      <c r="B314" t="inlineStr">
+        <is>
+          <t>운송사업자의 허가취소 등으로 위·수탁계약이 해지된 위·수탁차주였던 사람이 3개월 내에 허가를 신청하면 기간을 한정한 임시허가를 받을 수 있다. 임시허가의 기간은?</t>
+        </is>
+      </c>
+      <c r="C314" t="inlineStr">
+        <is>
+          <t>1년 이내</t>
+        </is>
+      </c>
+      <c r="D314" t="inlineStr">
+        <is>
+          <t>6개월 이내</t>
+        </is>
+      </c>
+      <c r="E314" t="inlineStr">
+        <is>
+          <t>3개월 이내</t>
+        </is>
+      </c>
+      <c r="F314" t="inlineStr">
+        <is>
+          <t>2년 이내</t>
+        </is>
+      </c>
+      <c r="G314" t="n">
+        <v>2</v>
+      </c>
+      <c r="H314" t="inlineStr">
+        <is>
+          <t>법 제3조제12항에 따라 6개월 이내로 기간을 한정하여 임시허가를 할 수 있다. 그 기간 안에 다른 운송사업자와 위·수탁계약을 맺지 못하면 만료 후 3개월 내에 정식 허가를 신청할 수 있다.</t>
+        </is>
+      </c>
+      <c r="I314" t="inlineStr">
+        <is>
+          <t>새 운송사업자를 찾을 때까지 생계를 잇도록 기간을 한정해 주는 허가입니다. 신청 기한(3개월)과 헷갈리지 마세요.</t>
+        </is>
+      </c>
+      <c r="J314" t="inlineStr">
+        <is>
+          <t>화물자동차 운수사업법 제3조제12항·제13항</t>
+        </is>
+      </c>
+      <c r="K314" t="inlineStr">
+        <is>
+          <t>2026-10-22</t>
+        </is>
+      </c>
+      <c r="L314" t="inlineStr">
+        <is>
+          <t>자체 작성</t>
+        </is>
+      </c>
+      <c r="M314" t="n">
+        <v>3</v>
+      </c>
+      <c r="O314" t="inlineStr">
+        <is>
+          <t>verified</t>
+        </is>
+      </c>
+      <c r="P314" t="inlineStr">
+        <is>
+          <t>1등 / 2026-10-22</t>
+        </is>
+      </c>
+      <c r="Q314" t="inlineStr">
+        <is>
+          <t>AI 4차 초안(2026-10-21) · 근거 확인 ○: 법 제3조제12항 '3개월 내에 허가를 신청하는 경우 6개월 이내로 기간을 한정하여 허가(임시허가)' 확인. 국가법령정보센터 원문(법 2026.7.1., 영 2026.6.3., 규칙 2026.6.30. 시행) · 교차 점검 반영</t>
+        </is>
+      </c>
+    </row>
+    <row r="315">
+      <c r="A315" t="inlineStr">
+        <is>
+          <t>LAW-0314</t>
+        </is>
+      </c>
+      <c r="B315" t="inlineStr">
+        <is>
+          <t>운송사업을 상속받은 상속인에게 결격사유가 있더라도, 피상속인의 사망일부터 일정 기간 안에 사업을 다른 사람에게 양도하면 그 기간의 허가는 상속인에 대한 허가로 본다. 그 기간은?</t>
+        </is>
+      </c>
+      <c r="C315" t="inlineStr">
+        <is>
+          <t>1년 이내</t>
+        </is>
+      </c>
+      <c r="D315" t="inlineStr">
+        <is>
+          <t>3개월 이내</t>
+        </is>
+      </c>
+      <c r="E315" t="inlineStr">
+        <is>
+          <t>6개월 이내</t>
+        </is>
+      </c>
+      <c r="F315" t="inlineStr">
+        <is>
+          <t>1개월 이내</t>
+        </is>
+      </c>
+      <c r="G315" t="n">
+        <v>2</v>
+      </c>
+      <c r="H315" t="inlineStr">
+        <is>
+          <t>법 제17조제6항 단서에 따라 상속인이 사망일부터 3개월 이내에 양도하면 사망일부터 양도일까지의 허가는 상속인에 대한 허가로 본다.</t>
+        </is>
+      </c>
+      <c r="I315" t="inlineStr">
+        <is>
+          <t>결격사유가 있는 상속인이 사업을 정리할 수 있도록 짧은 유예 기간을 줍니다.</t>
+        </is>
+      </c>
+      <c r="J315" t="inlineStr">
+        <is>
+          <t>화물자동차 운수사업법 제17조제6항</t>
+        </is>
+      </c>
+      <c r="K315" t="inlineStr">
+        <is>
+          <t>2026-10-22</t>
+        </is>
+      </c>
+      <c r="L315" t="inlineStr">
+        <is>
+          <t>자체 작성</t>
+        </is>
+      </c>
+      <c r="M315" t="n">
+        <v>3</v>
+      </c>
+      <c r="O315" t="inlineStr">
+        <is>
+          <t>verified</t>
+        </is>
+      </c>
+      <c r="P315" t="inlineStr">
+        <is>
+          <t>1등 / 2026-10-22</t>
+        </is>
+      </c>
+      <c r="Q315" t="inlineStr">
+        <is>
+          <t>AI 4차 초안(2026-10-21) · 근거 확인 ○: 법 제17조제6항 '상속인이 피상속인의 사망일부터 3개월 이내에 그 화물자동차 운송사업을 다른 사람에게 양도하면' 확인. 국가법령정보센터 원문(법 2026.7.1., 영 2026.6.3., 규칙 2026.6.30. 시행) · 교차 점검 반영</t>
+        </is>
+      </c>
+    </row>
+    <row r="316">
+      <c r="A316" t="inlineStr">
+        <is>
+          <t>LAW-0315</t>
+        </is>
+      </c>
+      <c r="B316" t="inlineStr">
+        <is>
+          <t>일반화물자동차 운송사업 허가를 받은 자가 그 사업을 양도하려면 원칙적으로 허가받은 날부터 얼마가 지나야 하는가? (우수물류기업에 양도하는 경우 등 예외 제외)</t>
+        </is>
+      </c>
+      <c r="C316" t="inlineStr">
+        <is>
+          <t>1년</t>
+        </is>
+      </c>
+      <c r="D316" t="inlineStr">
+        <is>
+          <t>6개월</t>
+        </is>
+      </c>
+      <c r="E316" t="inlineStr">
+        <is>
+          <t>2년</t>
+        </is>
+      </c>
+      <c r="F316" t="inlineStr">
+        <is>
+          <t>5년</t>
+        </is>
+      </c>
+      <c r="G316" t="n">
+        <v>3</v>
+      </c>
+      <c r="H316" t="inlineStr">
+        <is>
+          <t>시행규칙 제23조제5항에 따라 허가받은 날(양수한 자는 양도·양수 신고일)부터 2년이 지나야 양도할 수 있다. 집화등 외의 개인화물자동차 운송사업자는 6개월이다.</t>
+        </is>
+      </c>
+      <c r="I316" t="inlineStr">
+        <is>
+          <t>허가를 받자마자 되파는 '허가 장사'를 막기 위한 기간이다. 개인 운송사업자에게는 더 짧은 기간이 따로 있다.</t>
+        </is>
+      </c>
+      <c r="J316" t="inlineStr">
+        <is>
+          <t>화물자동차 운수사업법 시행규칙 제23조제5항</t>
+        </is>
+      </c>
+      <c r="K316" t="inlineStr">
+        <is>
+          <t>2026-10-22</t>
+        </is>
+      </c>
+      <c r="L316" t="inlineStr">
+        <is>
+          <t>자체 작성</t>
+        </is>
+      </c>
+      <c r="M316" t="n">
+        <v>2</v>
+      </c>
+      <c r="O316" t="inlineStr">
+        <is>
+          <t>verified</t>
+        </is>
+      </c>
+      <c r="P316" t="inlineStr">
+        <is>
+          <t>1등 / 2026-10-22</t>
+        </is>
+      </c>
+      <c r="Q316" t="inlineStr">
+        <is>
+          <t>AI 4차 초안(2026-10-21) · 근거 확인 ○: 규칙 제23조제5항 '화물자동차 운송사업을 양도하려면 ... 2년의 기간이 지나야 한다. 다만 ... 개인화물자동차 운송사업자는 6개월' 확인. 국가법령정보센터 원문(법 2026.7.1., 영 2026.6.3., 규칙 2026.6.30. 시행)</t>
+        </is>
+      </c>
+    </row>
+    <row r="317">
+      <c r="A317" t="inlineStr">
+        <is>
+          <t>LAW-0316</t>
+        </is>
+      </c>
+      <c r="B317" t="inlineStr">
+        <is>
+          <t>법인인 운송사업자의 임원 중 결격사유에 해당하는 사람이 있으면 허가취소 사유가 된다. 이때 허가를 취소하지 않는 경우는?</t>
+        </is>
+      </c>
+      <c r="C317" t="inlineStr">
+        <is>
+          <t>1년 이내에 그 임원을 바꾸어 임명한 경우</t>
+        </is>
+      </c>
+      <c r="D317" t="inlineStr">
+        <is>
+          <t>결격사유가 있는 임원이 1명뿐인 경우</t>
+        </is>
+      </c>
+      <c r="E317" t="inlineStr">
+        <is>
+          <t>3개월 이내에 그 임원을 바꾸어 임명한 경우</t>
+        </is>
+      </c>
+      <c r="F317" t="inlineStr">
+        <is>
+          <t>결격사유가 있는 사람이 대표자가 아닌 임원인 경우</t>
+        </is>
+      </c>
+      <c r="G317" t="n">
+        <v>3</v>
+      </c>
+      <c r="H317" t="inlineStr">
+        <is>
+          <t>법 제19조제1항제5호 단서에 따라 법인의 임원 중 결격사유자가 있는 경우 3개월 이내에 그 임원을 개임하면 허가를 취소하지 않는다.</t>
+        </is>
+      </c>
+      <c r="I317" t="inlineStr">
+        <is>
+          <t>결격 임원을 바꿀 짧은 유예 기간이 주어집니다. 1년처럼 길지는 않습니다.</t>
+        </is>
+      </c>
+      <c r="J317" t="inlineStr">
+        <is>
+          <t>화물자동차 운수사업법 제19조제1항제5호</t>
+        </is>
+      </c>
+      <c r="K317" t="inlineStr">
+        <is>
+          <t>2026-10-22</t>
+        </is>
+      </c>
+      <c r="L317" t="inlineStr">
+        <is>
+          <t>자체 작성</t>
+        </is>
+      </c>
+      <c r="M317" t="n">
+        <v>2</v>
+      </c>
+      <c r="O317" t="inlineStr">
+        <is>
+          <t>verified</t>
+        </is>
+      </c>
+      <c r="P317" t="inlineStr">
+        <is>
+          <t>1등 / 2026-10-22</t>
+        </is>
+      </c>
+      <c r="Q317" t="inlineStr">
+        <is>
+          <t>AI 4차 초안(2026-10-21) · 근거 확인 ○: 법 제19조제1항제5호 '3개월 이내에 그 임원을 개임(改任)하면 허가를 취소하지 아니한다' 확인. 국가법령정보센터 원문(법 2026.7.1., 영 2026.6.3., 규칙 2026.6.30. 시행) · 교차 점검 반영</t>
+        </is>
+      </c>
+    </row>
+    <row r="318">
+      <c r="A318" t="inlineStr">
+        <is>
+          <t>LAW-0317</t>
+        </is>
+      </c>
+      <c r="B318" t="inlineStr">
+        <is>
+          <t>허가를 받은 후 6개월간의 운송실적이 기준에 미달하면 허가취소 등의 사유가 된다. 시행규칙이 정한 이 기준은 연간 시장평균운송매출액의 얼마 이상인가?</t>
+        </is>
+      </c>
+      <c r="C318" t="inlineStr">
+        <is>
+          <t>100분의 5 이상</t>
+        </is>
+      </c>
+      <c r="D318" t="inlineStr">
+        <is>
+          <t>100분의 10 이상</t>
+        </is>
+      </c>
+      <c r="E318" t="inlineStr">
+        <is>
+          <t>100분의 50 이상</t>
+        </is>
+      </c>
+      <c r="F318" t="inlineStr">
+        <is>
+          <t>100분의 20 이상</t>
+        </is>
+      </c>
+      <c r="G318" t="n">
+        <v>1</v>
+      </c>
+      <c r="H318" t="inlineStr">
+        <is>
+          <t>시행규칙 제28조의2에 따라 국토교통부장관이 매년 고시하는 연간 시장평균운송매출액의 100분의 5 이상에 해당하는 운송매출액이 기준이다.</t>
+        </is>
+      </c>
+      <c r="I318" t="inlineStr">
+        <is>
+          <t>실제 영업을 하는지만 가려내는 아주 낮은 문턱이다. 직접운송 비율(100분의 50)과 혼동하지 말자.</t>
+        </is>
+      </c>
+      <c r="J318" t="inlineStr">
+        <is>
+          <t>화물자동차 운수사업법 제19조제1항제1호의2, 같은 법 시행규칙 제28조의2</t>
+        </is>
+      </c>
+      <c r="K318" t="inlineStr">
+        <is>
+          <t>2026-10-22</t>
+        </is>
+      </c>
+      <c r="L318" t="inlineStr">
+        <is>
+          <t>자체 작성</t>
+        </is>
+      </c>
+      <c r="M318" t="n">
+        <v>3</v>
+      </c>
+      <c r="O318" t="inlineStr">
+        <is>
+          <t>verified</t>
+        </is>
+      </c>
+      <c r="P318" t="inlineStr">
+        <is>
+          <t>1등 / 2026-10-22</t>
+        </is>
+      </c>
+      <c r="Q318" t="inlineStr">
+        <is>
+          <t>AI 4차 초안(2026-10-21) · 근거 확인 ○: 규칙 제28조의2 '연간 시장평균운송매출액 ... 의 100분의 5 이상에 해당하는 운송매출액' 확인. 국가법령정보센터 원문(법 2026.7.1., 영 2026.6.3., 규칙 2026.6.30. 시행)</t>
+        </is>
+      </c>
+    </row>
+    <row r="319">
+      <c r="A319" t="inlineStr">
+        <is>
+          <t>LAW-0318</t>
+        </is>
+      </c>
+      <c r="B319" t="inlineStr">
+        <is>
+          <t>화물자동차 운수사업법령상 허가취소 등의 사유가 되는 '중대한 교통사고'에 해당하지 않는 것은? (사상자가 발생한 경우)</t>
+        </is>
+      </c>
+      <c r="C319" t="inlineStr">
+        <is>
+          <t>신호위반 등 교통사고처리 특례법 제3조제2항 단서 사유로 일어난 사고</t>
+        </is>
+      </c>
+      <c r="D319" t="inlineStr">
+        <is>
+          <t>화물자동차의 정비불량으로 일어난 사고</t>
+        </is>
+      </c>
+      <c r="E319" t="inlineStr">
+        <is>
+          <t>운수종사자에게 귀책사유가 없는 화물자동차의 추락 사고</t>
+        </is>
+      </c>
+      <c r="F319" t="inlineStr">
+        <is>
+          <t>운수종사자의 과실로 화물자동차가 전복된 사고</t>
+        </is>
+      </c>
+      <c r="G319" t="n">
+        <v>3</v>
+      </c>
+      <c r="H319" t="inlineStr">
+        <is>
+          <t>시행령 제6조제1항에 따라 특례법 단서 사유, 정비불량, 전복·추락(운수종사자에게 귀책사유가 있는 경우만)으로 사상자가 발생한 경우가 중대한 교통사고이다.</t>
+        </is>
+      </c>
+      <c r="I319" t="inlineStr">
+        <is>
+          <t>전복·추락은 운전하는 사람의 잘못이 있을 때만 '중대한 사고'로 따진다.</t>
+        </is>
+      </c>
+      <c r="J319" t="inlineStr">
+        <is>
+          <t>화물자동차 운수사업법 제19조제2항, 같은 법 시행령 제6조제1항</t>
+        </is>
+      </c>
+      <c r="K319" t="inlineStr">
+        <is>
+          <t>2026-10-22</t>
+        </is>
+      </c>
+      <c r="L319" t="inlineStr">
+        <is>
+          <t>자체 작성</t>
+        </is>
+      </c>
+      <c r="M319" t="n">
+        <v>2</v>
+      </c>
+      <c r="O319" t="inlineStr">
+        <is>
+          <t>verified</t>
+        </is>
+      </c>
+      <c r="P319" t="inlineStr">
+        <is>
+          <t>1등 / 2026-10-22</t>
+        </is>
+      </c>
+      <c r="Q319" t="inlineStr">
+        <is>
+          <t>AI 4차 초안(2026-10-21) · 근거 확인 ○: 영 제6조제1항 '3. 화물자동차의 전복 또는 추락. 다만, 운수종사자에게 귀책사유가 있는 경우만 해당' 확인. 국가법령정보센터 원문(법 2026.7.1., 영 2026.6.3., 규칙 2026.6.30. 시행)</t>
+        </is>
+      </c>
+    </row>
+    <row r="320">
+      <c r="A320" t="inlineStr">
+        <is>
+          <t>LAW-0319</t>
+        </is>
+      </c>
+      <c r="B320" t="inlineStr">
+        <is>
+          <t>사업정지처분을 갈음하는 과징금 납부통지를 받은 운송사업자는 납부통지일부터 며칠 이내에 과징금을 내야 하는가?</t>
+        </is>
+      </c>
+      <c r="C320" t="inlineStr">
+        <is>
+          <t>30일 이내</t>
+        </is>
+      </c>
+      <c r="D320" t="inlineStr">
+        <is>
+          <t>60일 이내</t>
+        </is>
+      </c>
+      <c r="E320" t="inlineStr">
+        <is>
+          <t>15일 이내</t>
+        </is>
+      </c>
+      <c r="F320" t="inlineStr">
+        <is>
+          <t>7일 이내</t>
+        </is>
+      </c>
+      <c r="G320" t="n">
+        <v>1</v>
+      </c>
+      <c r="H320" t="inlineStr">
+        <is>
+          <t>시행령 제8조제2항에 따라 통지를 받은 자는 수납기관(은행·우체국)에 납부통지일부터 30일 이내에 과징금을 내야 한다.</t>
+        </is>
+      </c>
+      <c r="I320" t="inlineStr">
+        <is>
+          <t>과징금은 은행·우체국 등 수납기관에 냅니다. 범칙금(10일)보다는 넉넉한 기간입니다.</t>
+        </is>
+      </c>
+      <c r="J320" t="inlineStr">
+        <is>
+          <t>화물자동차 운수사업법 제21조, 같은 법 시행령 제8조제2항</t>
+        </is>
+      </c>
+      <c r="K320" t="inlineStr">
+        <is>
+          <t>2026-10-22</t>
+        </is>
+      </c>
+      <c r="L320" t="inlineStr">
+        <is>
+          <t>자체 작성</t>
+        </is>
+      </c>
+      <c r="M320" t="n">
+        <v>2</v>
+      </c>
+      <c r="O320" t="inlineStr">
+        <is>
+          <t>verified</t>
+        </is>
+      </c>
+      <c r="P320" t="inlineStr">
+        <is>
+          <t>1등 / 2026-10-22</t>
+        </is>
+      </c>
+      <c r="Q320" t="inlineStr">
+        <is>
+          <t>AI 4차 초안(2026-10-21) · 근거 확인 ○: 영 제8조제2항 '납부통지일부터 30일 이내에 과징금을 내야 한다' 확인. 국가법령정보센터 원문(법 2026.7.1., 영 2026.6.3., 규칙 2026.6.30. 시행) · 교차 점검 반영</t>
+        </is>
+      </c>
+    </row>
+    <row r="321">
+      <c r="A321" t="inlineStr">
+        <is>
+          <t>LAW-0320</t>
+        </is>
+      </c>
+      <c r="B321" t="inlineStr">
+        <is>
+          <t>국토교통부장관이 운송사업자에게 명할 수 있는 개선명령 사항이 아닌 것은?</t>
+        </is>
+      </c>
+      <c r="C321" t="inlineStr">
+        <is>
+          <t>적재물배상보험등의 가입</t>
+        </is>
+      </c>
+      <c r="D321" t="inlineStr">
+        <is>
+          <t>운임 및 요금의 인하</t>
+        </is>
+      </c>
+      <c r="E321" t="inlineStr">
+        <is>
+          <t>운송약관의 변경</t>
+        </is>
+      </c>
+      <c r="F321" t="inlineStr">
+        <is>
+          <t>화물자동차의 구조변경 및 운송시설의 개선</t>
+        </is>
+      </c>
+      <c r="G321" t="n">
+        <v>2</v>
+      </c>
+      <c r="H321" t="inlineStr">
+        <is>
+          <t>법 제13조의 개선명령 사항은 운송약관 변경, 구조변경·운송시설 개선, 안전운송 조치, 보험 가입, 위·수탁차량 번호판·대폐차 조치 등이며 운임 인하는 없다.</t>
+        </is>
+      </c>
+      <c r="I321" t="inlineStr">
+        <is>
+          <t>개선명령은 안전·운송질서·화주 편의를 위한 것이다. 사업자의 가격 결정에 직접 손대는 내용인지 따져 보자.</t>
+        </is>
+      </c>
+      <c r="J321" t="inlineStr">
+        <is>
+          <t>화물자동차 운수사업법 제13조</t>
+        </is>
+      </c>
+      <c r="K321" t="inlineStr">
+        <is>
+          <t>2026-10-22</t>
+        </is>
+      </c>
+      <c r="L321" t="inlineStr">
+        <is>
+          <t>자체 작성</t>
+        </is>
+      </c>
+      <c r="M321" t="n">
+        <v>1</v>
+      </c>
+      <c r="O321" t="inlineStr">
+        <is>
+          <t>verified</t>
+        </is>
+      </c>
+      <c r="P321" t="inlineStr">
+        <is>
+          <t>1등 / 2026-10-22</t>
+        </is>
+      </c>
+      <c r="Q321" t="inlineStr">
+        <is>
+          <t>AI 4차 초안(2026-10-21) · 근거 확인 ○: 법 제13조 각 호(운송약관의 변경, 구조변경 및 운송시설의 개선, 안전운송 조치, 적재물배상보험등 가입 등) 확인. 국가법령정보센터 원문(법 2026.7.1., 영 2026.6.3., 규칙 2026.6.30. 시행)</t>
+        </is>
+      </c>
+    </row>
+    <row r="322">
+      <c r="A322" t="inlineStr">
+        <is>
+          <t>LAW-0321</t>
+        </is>
+      </c>
+      <c r="B322" t="inlineStr">
+        <is>
+          <t>휴업기간이 끝나 반납했던 자동차등록번호판을 되돌려 받은 운송사업자가 해야 할 일은?</t>
+        </is>
+      </c>
+      <c r="C322" t="inlineStr">
+        <is>
+          <t>번호판을 달기 전에 한국교통안전공단의 임시검사를 받는다</t>
+        </is>
+      </c>
+      <c r="D322" t="inlineStr">
+        <is>
+          <t>번호판을 달고 관할 경찰서장의 확인을 받는다</t>
+        </is>
+      </c>
+      <c r="E322" t="inlineStr">
+        <is>
+          <t>번호판을 달고 협회에 신고만 하면 된다</t>
+        </is>
+      </c>
+      <c r="F322" t="inlineStr">
+        <is>
+          <t>번호판을 해당 화물자동차에 달고 시·도지사의 봉인을 받는다</t>
+        </is>
+      </c>
+      <c r="G322" t="n">
+        <v>4</v>
+      </c>
+      <c r="H322" t="inlineStr">
+        <is>
+          <t>법 제20조제3항에 따라 등록번호판을 되돌려 받은 운송사업자는 이를 해당 화물자동차에 달고 시·도지사의 봉인을 받아야 한다.</t>
+        </is>
+      </c>
+      <c r="I322" t="inlineStr">
+        <is>
+          <t>번호판이 떼어지지 않도록 고정하는 절차는 자동차 등록 사무를 맡은 기관이 한다.</t>
+        </is>
+      </c>
+      <c r="J322" t="inlineStr">
+        <is>
+          <t>화물자동차 운수사업법 제20조제3항</t>
+        </is>
+      </c>
+      <c r="K322" t="inlineStr">
+        <is>
+          <t>2026-10-22</t>
+        </is>
+      </c>
+      <c r="L322" t="inlineStr">
+        <is>
+          <t>자체 작성</t>
+        </is>
+      </c>
+      <c r="M322" t="n">
+        <v>2</v>
+      </c>
+      <c r="O322" t="inlineStr">
+        <is>
+          <t>verified</t>
+        </is>
+      </c>
+      <c r="P322" t="inlineStr">
+        <is>
+          <t>1등 / 2026-10-22</t>
+        </is>
+      </c>
+      <c r="Q322" t="inlineStr">
+        <is>
+          <t>AI 4차 초안(2026-10-21) · 근거 확인 ○: 법 제20조제3항 '자동차등록번호판을 되돌려 받은 운송사업자는 이를 해당 화물자동차에 달고 시ㆍ도지사의 봉인을 받아야' 확인. 국가법령정보센터 원문(법 2026.7.1., 영 2026.6.3., 규칙 2026.6.30. 시행)</t>
+        </is>
+      </c>
+    </row>
+    <row r="323">
+      <c r="A323" t="inlineStr">
+        <is>
+          <t>LAW-0322</t>
+        </is>
+      </c>
+      <c r="B323" t="inlineStr">
+        <is>
+          <t>관할관청이 화물운송 종사자격의 효력정지 처분을 할 때 처분기준 일수를 조정할 수 있는 범위로 옳은 것은?</t>
+        </is>
+      </c>
+      <c r="C323" t="inlineStr">
+        <is>
+          <t>2배까지 늘리는 것만 가능하다</t>
+        </is>
+      </c>
+      <c r="D323" t="inlineStr">
+        <is>
+          <t>3분의 1 범위에서 줄이는 것만 가능하다</t>
+        </is>
+      </c>
+      <c r="E323" t="inlineStr">
+        <is>
+          <t>처분기준 일수는 어떤 경우에도 조정할 수 없다</t>
+        </is>
+      </c>
+      <c r="F323" t="inlineStr">
+        <is>
+          <t>2분의 1 범위에서 줄이거나 늘릴 수 있되, 늘리는 것은 최근 1년 내 같은 위반을 2회 이상 한 경우만 가능하다</t>
+        </is>
+      </c>
+      <c r="G323" t="n">
+        <v>4</v>
+      </c>
+      <c r="H323" t="inlineStr">
+        <is>
+          <t>시행규칙 제33조의2제2항에 따라 동기·횟수 등을 고려해 처분기준 일수의 2분의 1 범위에서 줄이거나 늘릴 수 있고, 늘리는 경우는 최근 1년 이내 같은 위반을 2회 이상 한 경우로 한정된다.</t>
+        </is>
+      </c>
+      <c r="I323" t="inlineStr">
+        <is>
+          <t>처분 일수를 조정할 때 위반 동기와 횟수를 고려합니다. 무겁게 할 때는 조건이 더 까다롭습니다.</t>
+        </is>
+      </c>
+      <c r="J323" t="inlineStr">
+        <is>
+          <t>화물자동차 운수사업법 시행규칙 제33조의2제2항</t>
+        </is>
+      </c>
+      <c r="K323" t="inlineStr">
+        <is>
+          <t>2026-10-22</t>
+        </is>
+      </c>
+      <c r="L323" t="inlineStr">
+        <is>
+          <t>자체 작성</t>
+        </is>
+      </c>
+      <c r="M323" t="n">
+        <v>3</v>
+      </c>
+      <c r="O323" t="inlineStr">
+        <is>
+          <t>verified</t>
+        </is>
+      </c>
+      <c r="P323" t="inlineStr">
+        <is>
+          <t>1등 / 2026-10-22</t>
+        </is>
+      </c>
+      <c r="Q323" t="inlineStr">
+        <is>
+          <t>AI 4차 초안(2026-10-21) · 근거 확인 ○: 규칙 제33조의2제2항 '처분기준 일수의 2분의 1의 범위에서 줄이거나 늘릴 수 있다. 다만, 늘리는 경우에는 ... 최근 1년 이내에 같은 위반행위를 2회 이상 한 경우만' 확인. 국가법령정보센터 원문(법 2026.7.1., 영 2026.6.3., 규칙 2026.6.30. 시행) · 교차 점검 반영</t>
+        </is>
+      </c>
+    </row>
+    <row r="324">
+      <c r="A324" t="inlineStr">
+        <is>
+          <t>LAW-0323</t>
+        </is>
+      </c>
+      <c r="B324" t="inlineStr">
+        <is>
+          <t>화물자동차 운송주선사업자가 허가사항 변경신고서를 제출하는 곳은?</t>
+        </is>
+      </c>
+      <c r="C324" t="inlineStr">
+        <is>
+          <t>협회</t>
+        </is>
+      </c>
+      <c r="D324" t="inlineStr">
+        <is>
+          <t>한국교통연구원</t>
+        </is>
+      </c>
+      <c r="E324" t="inlineStr">
+        <is>
+          <t>한국교통안전공단</t>
+        </is>
+      </c>
+      <c r="F324" t="inlineStr">
+        <is>
+          <t>관할 경찰서</t>
+        </is>
+      </c>
+      <c r="G324" t="n">
+        <v>1</v>
+      </c>
+      <c r="H324" t="inlineStr">
+        <is>
+          <t>시행규칙 제36조제1항에 따라 변경신고서는 협회에 제출하며(시행령 제15조제2항의 권한 위탁), 협회는 그 사실을 관할관청에 보고한다.</t>
+        </is>
+      </c>
+      <c r="I324" t="inlineStr">
+        <is>
+          <t>국토교통부장관의 권한 중 일부가 위탁되어 있습니다. 위탁받은 곳은 접수 후 관할관청에 보고합니다.</t>
+        </is>
+      </c>
+      <c r="J324" t="inlineStr">
+        <is>
+          <t>화물자동차 운수사업법 제24조제2항, 같은 법 시행령 제15조제2항, 시행규칙 제36조</t>
+        </is>
+      </c>
+      <c r="K324" t="inlineStr">
+        <is>
+          <t>2026-10-22</t>
+        </is>
+      </c>
+      <c r="L324" t="inlineStr">
+        <is>
+          <t>자체 작성</t>
+        </is>
+      </c>
+      <c r="M324" t="n">
+        <v>2</v>
+      </c>
+      <c r="O324" t="inlineStr">
+        <is>
+          <t>verified</t>
+        </is>
+      </c>
+      <c r="P324" t="inlineStr">
+        <is>
+          <t>1등 / 2026-10-22</t>
+        </is>
+      </c>
+      <c r="Q324" t="inlineStr">
+        <is>
+          <t>AI 4차 초안(2026-10-21) · 근거 확인 ○: 규칙 제36조제1항 '허가사항 변경신고서를 협회에 제출', 영 제15조제2항 '허가사항 변경신고에 관한 권한을 협회에 위탁' 확인. 국가법령정보센터 원문(법 2026.7.1., 영 2026.6.3., 규칙 2026.6.30. 시행) · 교차 점검 반영</t>
+        </is>
+      </c>
+    </row>
+    <row r="325">
+      <c r="A325" t="inlineStr">
+        <is>
+          <t>LAW-0324</t>
+        </is>
+      </c>
+      <c r="B325" t="inlineStr">
+        <is>
+          <t>시행규칙에서 정한 화물자동차 운송주선사업자의 준수사항으로 옳은 것은?</t>
+        </is>
+      </c>
+      <c r="C325" t="inlineStr">
+        <is>
+          <t>적재물배상보험등은 영업을 시작한 뒤 1년 안에만 가입하면 된다</t>
+        </is>
+      </c>
+      <c r="D325" t="inlineStr">
+        <is>
+          <t>이사화물을 주선할 때 견적서·계약서는 운송이 끝난 뒤에 발급한다</t>
+        </is>
+      </c>
+      <c r="E325" t="inlineStr">
+        <is>
+          <t>허가증에 적힌 상호 외에 다른 상호도 자유롭게 사용할 수 있다</t>
+        </is>
+      </c>
+      <c r="F325" t="inlineStr">
+        <is>
+          <t>자가용 화물자동차의 소유자나 사용자에게 화물운송을 주선하지 않는다</t>
+        </is>
+      </c>
+      <c r="G325" t="n">
+        <v>4</v>
+      </c>
+      <c r="H325" t="inlineStr">
+        <is>
+          <t>시행규칙 제38조의3제2항에 따라 자가용 화물자동차 소유자·사용자에게 주선하지 않을 것, 허가증의 상호만 사용할 것, 보험에 가입한 상태로 영업할 것, 이사화물은 운송 시작 전에 견적서 등을 발급할 것을 지켜야 한다.</t>
+        </is>
+      </c>
+      <c r="I325" t="inlineStr">
+        <is>
+          <t>자가용 화물차의 유상운송은 원칙적으로 금지되어 있다는 점과 연결해 보자.</t>
+        </is>
+      </c>
+      <c r="J325" t="inlineStr">
+        <is>
+          <t>화물자동차 운수사업법 제26조제7항, 같은 법 시행규칙 제38조의3제2항</t>
+        </is>
+      </c>
+      <c r="K325" t="inlineStr">
+        <is>
+          <t>2026-10-22</t>
+        </is>
+      </c>
+      <c r="L325" t="inlineStr">
+        <is>
+          <t>자체 작성</t>
+        </is>
+      </c>
+      <c r="M325" t="n">
+        <v>2</v>
+      </c>
+      <c r="O325" t="inlineStr">
+        <is>
+          <t>verified</t>
+        </is>
+      </c>
+      <c r="P325" t="inlineStr">
+        <is>
+          <t>1등 / 2026-10-22</t>
+        </is>
+      </c>
+      <c r="Q325" t="inlineStr">
+        <is>
+          <t>AI 4차 초안(2026-10-21) · 근거 확인 ○: 규칙 제38조의3제2항 '3. 자가용 화물자동차의 소유자 또는 사용자에게 화물운송을 주선하지 아니할 것', '4. 허가증에 기재된 상호만 사용할 것' 등 확인. 국가법령정보센터 원문(법 2026.7.1., 영 2026.6.3., 규칙 2026.6.30. 시행)</t>
+        </is>
+      </c>
+    </row>
+    <row r="326">
+      <c r="A326" t="inlineStr">
+        <is>
+          <t>LAW-0325</t>
+        </is>
+      </c>
+      <c r="B326" t="inlineStr">
+        <is>
+          <t>국토교통부장관이 화물자동차 운송가맹사업의 허가 신청을 받은 경우, 신청을 받은 날부터 며칠 이내에 허가 여부를 통지해야 하는가?</t>
+        </is>
+      </c>
+      <c r="C326" t="inlineStr">
+        <is>
+          <t>60일 이내</t>
+        </is>
+      </c>
+      <c r="D326" t="inlineStr">
+        <is>
+          <t>20일 이내</t>
+        </is>
+      </c>
+      <c r="E326" t="inlineStr">
+        <is>
+          <t>5일 이내</t>
+        </is>
+      </c>
+      <c r="F326" t="inlineStr">
+        <is>
+          <t>3일 이내</t>
+        </is>
+      </c>
+      <c r="G326" t="n">
+        <v>2</v>
+      </c>
+      <c r="H326" t="inlineStr">
+        <is>
+          <t>법 제29조제6항에 따라 허가·변경허가 신청이나 변경신고를 받은 날부터 20일 이내에 허가 또는 신고수리 여부를 통지해야 하며, 통지가 없으면 기간이 끝난 다음 날 허가한 것으로 본다.</t>
+        </is>
+      </c>
+      <c r="I326" t="inlineStr">
+        <is>
+          <t>가맹점 구성·화물정보망 등 살필 것이 많아 간단한 변경신고보다 처리 기간이 길다.</t>
+        </is>
+      </c>
+      <c r="J326" t="inlineStr">
+        <is>
+          <t>화물자동차 운수사업법 제29조제6항·제7항</t>
+        </is>
+      </c>
+      <c r="K326" t="inlineStr">
+        <is>
+          <t>2026-10-22</t>
+        </is>
+      </c>
+      <c r="L326" t="inlineStr">
+        <is>
+          <t>자체 작성</t>
+        </is>
+      </c>
+      <c r="M326" t="n">
+        <v>3</v>
+      </c>
+      <c r="O326" t="inlineStr">
+        <is>
+          <t>verified</t>
+        </is>
+      </c>
+      <c r="P326" t="inlineStr">
+        <is>
+          <t>1등 / 2026-10-22</t>
+        </is>
+      </c>
+      <c r="Q326" t="inlineStr">
+        <is>
+          <t>AI 4차 초안(2026-10-21) · 근거 확인 ○: 법 제29조제6항 '신청을 받거나 변경신고를 받은 날부터 20일 이내에 허가 또는 신고수리 여부를 신청인에게 통지' 확인. 국가법령정보센터 원문(법 2026.7.1., 영 2026.6.3., 규칙 2026.6.30. 시행)</t>
+        </is>
+      </c>
+    </row>
+    <row r="327">
+      <c r="A327" t="inlineStr">
+        <is>
+          <t>LAW-0326</t>
+        </is>
+      </c>
+      <c r="B327" t="inlineStr">
+        <is>
+          <t>운송주선사업자인 운송가맹점이 성실히 이행해야 하는 역할은?</t>
+        </is>
+      </c>
+      <c r="C327" t="inlineStr">
+        <is>
+          <t>화물정보망의 설치·운영</t>
+        </is>
+      </c>
+      <c r="D327" t="inlineStr">
+        <is>
+          <t>직접운송물량과 가맹점 운송물량의 공정한 배정</t>
+        </is>
+      </c>
+      <c r="E327" t="inlineStr">
+        <is>
+          <t>운송가맹사업자에 대한 운송화물의 확보·공급</t>
+        </is>
+      </c>
+      <c r="F327" t="inlineStr">
+        <is>
+          <t>화물의 원활한 운송을 위한 차량 위치의 통지</t>
+        </is>
+      </c>
+      <c r="G327" t="n">
+        <v>3</v>
+      </c>
+      <c r="H327" t="inlineStr">
+        <is>
+          <t>법 제30조제2항제3호에 따라 운송주선사업자인 가맹점은 운송화물의 확보·공급을 맡는다. 차량 위치 통지는 운송사업자·위수탁차주인 가맹점, 정보망 운영과 물량 배정은 운송가맹사업자의 역할이다.</t>
+        </is>
+      </c>
+      <c r="I327" t="inlineStr">
+        <is>
+          <t>차를 갖지 않고 화물을 모아 주는 일을 하는 사업자가 가맹 구조에서 무엇을 보탤지 생각해 보자.</t>
+        </is>
+      </c>
+      <c r="J327" t="inlineStr">
+        <is>
+          <t>화물자동차 운수사업법 제30조</t>
+        </is>
+      </c>
+      <c r="K327" t="inlineStr">
+        <is>
+          <t>2026-10-22</t>
+        </is>
+      </c>
+      <c r="L327" t="inlineStr">
+        <is>
+          <t>자체 작성</t>
+        </is>
+      </c>
+      <c r="M327" t="n">
+        <v>3</v>
+      </c>
+      <c r="O327" t="inlineStr">
+        <is>
+          <t>verified</t>
+        </is>
+      </c>
+      <c r="P327" t="inlineStr">
+        <is>
+          <t>1등 / 2026-10-22</t>
+        </is>
+      </c>
+      <c r="Q327" t="inlineStr">
+        <is>
+          <t>AI 4차 초안(2026-10-21) · 근거 확인 ○: 법 제30조제2항 '3. 운송가맹사업자에 대한 운송화물의 확보ㆍ공급(운송주선사업자인 운송가맹점만 해당)' 확인. 국가법령정보센터 원문(법 2026.7.1., 영 2026.6.3., 규칙 2026.6.30. 시행)</t>
+        </is>
+      </c>
+    </row>
+    <row r="328">
+      <c r="A328" t="inlineStr">
+        <is>
+          <t>LAW-0327</t>
+        </is>
+      </c>
+      <c r="B328" t="inlineStr">
+        <is>
+          <t>보험회사등은 적재물배상보험 등의 계약 종료 사실을 의무가입자에게 언제 알려야 하는가?</t>
+        </is>
+      </c>
+      <c r="C328" t="inlineStr">
+        <is>
+          <t>계약 종료일 당일에 알린다</t>
+        </is>
+      </c>
+      <c r="D328" t="inlineStr">
+        <is>
+          <t>계약이 끝난 뒤 30일 이내에 알린다</t>
+        </is>
+      </c>
+      <c r="E328" t="inlineStr">
+        <is>
+          <t>계약 종료일 7일 전에 한 번 알린다</t>
+        </is>
+      </c>
+      <c r="F328" t="inlineStr">
+        <is>
+          <t>계약 종료일 30일 전과 10일 전에 각각 알린다</t>
+        </is>
+      </c>
+      <c r="G328" t="n">
+        <v>4</v>
+      </c>
+      <c r="H328" t="inlineStr">
+        <is>
+          <t>법 제38조제1항(30일 전까지)과 시행규칙 제41조의15제1항에 따라 종료일 30일 전과 10일 전에 각각 통지하고, 미가입 시 500만원 이하 과태료가 부과된다는 안내를 포함해야 한다.</t>
+        </is>
+      </c>
+      <c r="I328" t="inlineStr">
+        <is>
+          <t>보험 공백이 생기지 않도록 종료일보다 앞서 알려야 합니다. 법률이 정한 '30일 전까지'를 시행규칙이 더 구체화했습니다.</t>
+        </is>
+      </c>
+      <c r="J328" t="inlineStr">
+        <is>
+          <t>화물자동차 운수사업법 제38조제1항, 같은 법 시행규칙 제41조의15</t>
+        </is>
+      </c>
+      <c r="K328" t="inlineStr">
+        <is>
+          <t>2026-10-22</t>
+        </is>
+      </c>
+      <c r="L328" t="inlineStr">
+        <is>
+          <t>자체 작성</t>
+        </is>
+      </c>
+      <c r="M328" t="n">
+        <v>2</v>
+      </c>
+      <c r="O328" t="inlineStr">
+        <is>
+          <t>verified</t>
+        </is>
+      </c>
+      <c r="P328" t="inlineStr">
+        <is>
+          <t>1등 / 2026-10-22</t>
+        </is>
+      </c>
+      <c r="Q328" t="inlineStr">
+        <is>
+          <t>AI 4차 초안(2026-10-21) · 근거 확인 ○: 규칙 제41조의15제1항 '계약 종료일 30일 전과 10일 전에 각각 통지' 확인. 국가법령정보센터 원문(법 2026.7.1., 영 2026.6.3., 규칙 2026.6.30. 시행) · 교차 점검 반영</t>
+        </is>
+      </c>
+    </row>
+    <row r="329">
+      <c r="A329" t="inlineStr">
+        <is>
+          <t>LAW-0328</t>
+        </is>
+      </c>
+      <c r="B329" t="inlineStr">
+        <is>
+          <t>적재물배상보험등의 가입 방법(가입 단위)에 대한 설명으로 옳은 것은?</t>
+        </is>
+      </c>
+      <c r="C329" t="inlineStr">
+        <is>
+          <t>운송사업자는 보유 대수와 관계없이 사업자별로 1건만 가입한다</t>
+        </is>
+      </c>
+      <c r="D329" t="inlineStr">
+        <is>
+          <t>운송주선사업자는 주선하는 화물 1건마다 따로 가입한다</t>
+        </is>
+      </c>
+      <c r="E329" t="inlineStr">
+        <is>
+          <t>운송가맹사업자는 차량 소유 여부와 관계없이 화물자동차별로만 가입한다</t>
+        </is>
+      </c>
+      <c r="F329" t="inlineStr">
+        <is>
+          <t>운송주선사업자는 각 사업자별로 가입한다</t>
+        </is>
+      </c>
+      <c r="G329" t="n">
+        <v>4</v>
+      </c>
+      <c r="H329" t="inlineStr">
+        <is>
+          <t>시행령 제9조의7에 따라 운송사업자는 각 화물자동차별, 운송주선사업자는 각 사업자별, 운송가맹사업자는 차량을 직접 소유하면 화물자동차별 및 사업자별, 그 외는 사업자별로 가입한다.</t>
+        </is>
+      </c>
+      <c r="I329" t="inlineStr">
+        <is>
+          <t>차를 갖지 않는 사업자는 '차량별'로 가입할 수가 없다는 점에서 출발하자.</t>
+        </is>
+      </c>
+      <c r="J329" t="inlineStr">
+        <is>
+          <t>화물자동차 운수사업법 제35조, 같은 법 시행령 제9조의7</t>
+        </is>
+      </c>
+      <c r="K329" t="inlineStr">
+        <is>
+          <t>2026-10-22</t>
+        </is>
+      </c>
+      <c r="L329" t="inlineStr">
+        <is>
+          <t>자체 작성</t>
+        </is>
+      </c>
+      <c r="M329" t="n">
+        <v>3</v>
+      </c>
+      <c r="O329" t="inlineStr">
+        <is>
+          <t>verified</t>
+        </is>
+      </c>
+      <c r="P329" t="inlineStr">
+        <is>
+          <t>1등 / 2026-10-22</t>
+        </is>
+      </c>
+      <c r="Q329" t="inlineStr">
+        <is>
+          <t>AI 4차 초안(2026-10-21) · 근거 확인 ○: 영 제9조의7 '1. 운송사업자: 각 화물자동차별로 가입 2. 운송주선사업자: 각 사업자별로 가입 3. 운송가맹사업자 ...' 확인. 국가법령정보센터 원문(법 2026.7.1., 영 2026.6.3., 규칙 2026.6.30. 시행)</t>
+        </is>
+      </c>
+    </row>
+    <row r="330">
+      <c r="A330" t="inlineStr">
+        <is>
+          <t>LAW-0329</t>
+        </is>
+      </c>
+      <c r="B330" t="inlineStr">
+        <is>
+          <t>적재물사고를 일으킬 개연성이 높아 여러 보험회사가 공동으로 책임보험계약을 체결할 수 있는 경우에 해당하는 것은?</t>
+        </is>
+      </c>
+      <c r="C330" t="inlineStr">
+        <is>
+          <t>운전자가 과거 2년 동안 속도위반을 1회 한 경우</t>
+        </is>
+      </c>
+      <c r="D330" t="inlineStr">
+        <is>
+          <t>운전자가 과거 1년 동안 주차위반을 3회 한 경우</t>
+        </is>
+      </c>
+      <c r="E330" t="inlineStr">
+        <is>
+          <t>운송사업자가 새로 운송사업 허가를 받은 경우</t>
+        </is>
+      </c>
+      <c r="F330" t="inlineStr">
+        <is>
+          <t>운전자가 과거 2년 동안 술에 취한 상태에서의 운전금지를 2회 이상 위반한 경력이 있는 경우</t>
+        </is>
+      </c>
+      <c r="G330" t="n">
+        <v>4</v>
+      </c>
+      <c r="H330" t="inlineStr">
+        <is>
+          <t>시행규칙 제41조의14에 따라 운전자가 과거 2년 동안 무면허운전, 음주운전, 사고발생 시 조치의무를 2회 이상 위반한 경력이 있는 경우 등에 공동 계약을 체결할 수 있다.</t>
+        </is>
+      </c>
+      <c r="I330" t="inlineStr">
+        <is>
+          <t>보험회사 한 곳이 감당하기 어려운 '위험한 운전 경력'이 무엇인지 떠올려 보자.</t>
+        </is>
+      </c>
+      <c r="J330" t="inlineStr">
+        <is>
+          <t>화물자동차 운수사업법 제36조제2항, 같은 법 시행규칙 제41조의14</t>
+        </is>
+      </c>
+      <c r="K330" t="inlineStr">
+        <is>
+          <t>2026-10-22</t>
+        </is>
+      </c>
+      <c r="L330" t="inlineStr">
+        <is>
+          <t>자체 작성</t>
+        </is>
+      </c>
+      <c r="M330" t="n">
+        <v>2</v>
+      </c>
+      <c r="O330" t="inlineStr">
+        <is>
+          <t>verified</t>
+        </is>
+      </c>
+      <c r="P330" t="inlineStr">
+        <is>
+          <t>1등 / 2026-10-22</t>
+        </is>
+      </c>
+      <c r="Q330" t="inlineStr">
+        <is>
+          <t>AI 4차 초안(2026-10-21) · 근거 확인 ○: 규칙 제41조의14 '과거 2년 동안 ... 무면허운전, 음주운전 금지, 사고발생 시 조치의무를 2회 이상 위반한 경력' 확인. 국가법령정보센터 원문(법 2026.7.1., 영 2026.6.3., 규칙 2026.6.30. 시행)</t>
+        </is>
+      </c>
+    </row>
+    <row r="331">
+      <c r="A331" t="inlineStr">
+        <is>
+          <t>LAW-0330</t>
+        </is>
+      </c>
+      <c r="B331" t="inlineStr">
+        <is>
+          <t>운송사업자가 위·수탁계약을 해지하려는 경우의 원칙적인 절차로 옳은 것은?</t>
+        </is>
+      </c>
+      <c r="C331" t="inlineStr">
+        <is>
+          <t>2개월 이상의 유예기간을 두고 위반 사실과 해지 사실을 서면으로 2회 이상 통지한다</t>
+        </is>
+      </c>
+      <c r="D331" t="inlineStr">
+        <is>
+          <t>유예기간 없이 문자메시지로 1회 통지한다</t>
+        </is>
+      </c>
+      <c r="E331" t="inlineStr">
+        <is>
+          <t>1개월의 유예기간을 두고 구두로 1회 통지한다</t>
+        </is>
+      </c>
+      <c r="F331" t="inlineStr">
+        <is>
+          <t>15일의 유예기간을 두고 서면으로 1회 통지한다</t>
+        </is>
+      </c>
+      <c r="G331" t="n">
+        <v>1</v>
+      </c>
+      <c r="H331" t="inlineStr">
+        <is>
+          <t>법 제40조의3제1항에 따라 2개월 이상의 유예기간을 두고 위반 사실을 밝히고 시정하지 않으면 해지한다는 사실을 서면으로 2회 이상 통지해야 하며, 이 절차를 거치지 않은 해지는 효력이 없다.</t>
+        </is>
+      </c>
+      <c r="I331" t="inlineStr">
+        <is>
+          <t>위·수탁차주에게 위반을 고칠 기회를 주는 절차입니다. 이 절차를 거치지 않은 해지는 효력이 없습니다.</t>
+        </is>
+      </c>
+      <c r="J331" t="inlineStr">
+        <is>
+          <t>화물자동차 운수사업법 제40조의3제1항·제2항</t>
+        </is>
+      </c>
+      <c r="K331" t="inlineStr">
+        <is>
+          <t>2026-10-22</t>
+        </is>
+      </c>
+      <c r="L331" t="inlineStr">
+        <is>
+          <t>자체 작성</t>
+        </is>
+      </c>
+      <c r="M331" t="n">
+        <v>1</v>
+      </c>
+      <c r="O331" t="inlineStr">
+        <is>
+          <t>verified</t>
+        </is>
+      </c>
+      <c r="P331" t="inlineStr">
+        <is>
+          <t>1등 / 2026-10-22</t>
+        </is>
+      </c>
+      <c r="Q331" t="inlineStr">
+        <is>
+          <t>AI 4차 초안(2026-10-21) · 근거 확인 ○: 법 제40조의3제1항 '2개월 이상의 유예기간을 두고 ... 서면으로 2회 이상 통지' 확인. 국가법령정보센터 원문(법 2026.7.1., 영 2026.6.3., 규칙 2026.6.30. 시행) · 교차 점검 반영</t>
+        </is>
+      </c>
+    </row>
+    <row r="332">
+      <c r="A332" t="inlineStr">
+        <is>
+          <t>LAW-0331</t>
+        </is>
+      </c>
+      <c r="B332" t="inlineStr">
+        <is>
+          <t>위·수탁차주가 업무상 질병 등 부득이한 사유로 위·수탁계약상 지위를 양도하겠다고 운송사업자에게 서면 통지했다. 운송사업자가 통지일부터 일정 기간 안에 거절하지 않으면 동의한 것으로 본다. 그 기간은?</t>
+        </is>
+      </c>
+      <c r="C332" t="inlineStr">
+        <is>
+          <t>7일 이내</t>
+        </is>
+      </c>
+      <c r="D332" t="inlineStr">
+        <is>
+          <t>3개월 이내</t>
+        </is>
+      </c>
+      <c r="E332" t="inlineStr">
+        <is>
+          <t>1개월 이내</t>
+        </is>
+      </c>
+      <c r="F332" t="inlineStr">
+        <is>
+          <t>15일 이내</t>
+        </is>
+      </c>
+      <c r="G332" t="n">
+        <v>3</v>
+      </c>
+      <c r="H332" t="inlineStr">
+        <is>
+          <t>법 제40조의4제4항에 따라 통지가 있은 날부터 1개월 이내에 운송사업자가 동의를 거절하지 않으면 양도에 동의한 것으로 본다.</t>
+        </is>
+      </c>
+      <c r="I332" t="inlineStr">
+        <is>
+          <t>운송사업자가 답을 미루기만 하는 것을 막기 위해, 기간 안에 거절하지 않으면 동의한 것으로 봅니다.</t>
+        </is>
+      </c>
+      <c r="J332" t="inlineStr">
+        <is>
+          <t>화물자동차 운수사업법 제40조의4제3항·제4항</t>
+        </is>
+      </c>
+      <c r="K332" t="inlineStr">
+        <is>
+          <t>2026-10-22</t>
+        </is>
+      </c>
+      <c r="L332" t="inlineStr">
+        <is>
+          <t>자체 작성</t>
+        </is>
+      </c>
+      <c r="M332" t="n">
+        <v>2</v>
+      </c>
+      <c r="O332" t="inlineStr">
+        <is>
+          <t>verified</t>
+        </is>
+      </c>
+      <c r="P332" t="inlineStr">
+        <is>
+          <t>1등 / 2026-10-22</t>
+        </is>
+      </c>
+      <c r="Q332" t="inlineStr">
+        <is>
+          <t>AI 4차 초안(2026-10-21) · 근거 확인 ○: 법 제40조의4제4항 '통지가 있은 날부터 1개월 이내에 운송사업자가 양도에 대한 동의를 거절하지 아니하는 경우에는 ... 동의한 것으로 본다' 확인. 국가법령정보센터 원문(법 2026.7.1., 영 2026.6.3., 규칙 2026.6.30. 시행) · 교차 점검 반영</t>
+        </is>
+      </c>
+    </row>
+    <row r="333">
+      <c r="A333" t="inlineStr">
+        <is>
+          <t>LAW-0332</t>
+        </is>
+      </c>
+      <c r="B333" t="inlineStr">
+        <is>
+          <t>화물자동차 운수사업법상 압류할 수 없는 것은?</t>
+        </is>
+      </c>
+      <c r="C333" t="inlineStr">
+        <is>
+          <t>유가보조금으로 지급된 금품과 이를 받을 권리</t>
+        </is>
+      </c>
+      <c r="D333" t="inlineStr">
+        <is>
+          <t>운송사업자 명의의 일반 예금</t>
+        </is>
+      </c>
+      <c r="E333" t="inlineStr">
+        <is>
+          <t>운송사업자가 소유한 사무실 건물</t>
+        </is>
+      </c>
+      <c r="F333" t="inlineStr">
+        <is>
+          <t>운송주선사업자가 받은 주선 수수료</t>
+        </is>
+      </c>
+      <c r="G333" t="n">
+        <v>1</v>
+      </c>
+      <c r="H333" t="inlineStr">
+        <is>
+          <t>법 제58조에 따라 위·수탁계약으로 현물출자된 차량과 제43조제2항·제3항에 따라 지급된 보조금(유가보조금 등) 및 이를 받을 권리는 압류하지 못한다.</t>
+        </is>
+      </c>
+      <c r="I333" t="inlineStr">
+        <is>
+          <t>화물차주의 생계 수단과 연료비 지원금은 빚 때문에 빼앗기지 않도록 보호한다.</t>
+        </is>
+      </c>
+      <c r="J333" t="inlineStr">
+        <is>
+          <t>화물자동차 운수사업법 제58조</t>
+        </is>
+      </c>
+      <c r="K333" t="inlineStr">
+        <is>
+          <t>2026-10-22</t>
+        </is>
+      </c>
+      <c r="L333" t="inlineStr">
+        <is>
+          <t>자체 작성</t>
+        </is>
+      </c>
+      <c r="M333" t="n">
+        <v>2</v>
+      </c>
+      <c r="O333" t="inlineStr">
+        <is>
+          <t>verified</t>
+        </is>
+      </c>
+      <c r="P333" t="inlineStr">
+        <is>
+          <t>1등 / 2026-10-22</t>
+        </is>
+      </c>
+      <c r="Q333" t="inlineStr">
+        <is>
+          <t>AI 4차 초안(2026-10-21) · 근거 확인 ○: 법 제58조 '현물출자된 차량 및 제43조제2항 또는 제3항에 따라 지급된 금품과 이를 받을 권리는 압류하지 못한다' 확인. 국가법령정보센터 원문(법 2026.7.1., 영 2026.6.3., 규칙 2026.6.30. 시행)</t>
+        </is>
+      </c>
+    </row>
+    <row r="334">
+      <c r="A334" t="inlineStr">
+        <is>
+          <t>LAW-0333</t>
+        </is>
+      </c>
+      <c r="B334" t="inlineStr">
+        <is>
+          <t>운송사업자등이 거짓이나 부정한 방법으로 유가보조금을 받아 처음 적발된 경우(1차 위반) 보조금 지급정지 기간은?</t>
+        </is>
+      </c>
+      <c r="C334" t="inlineStr">
+        <is>
+          <t>3개월</t>
+        </is>
+      </c>
+      <c r="D334" t="inlineStr">
+        <is>
+          <t>6개월</t>
+        </is>
+      </c>
+      <c r="E334" t="inlineStr">
+        <is>
+          <t>2년</t>
+        </is>
+      </c>
+      <c r="F334" t="inlineStr">
+        <is>
+          <t>1개월</t>
+        </is>
+      </c>
+      <c r="G334" t="n">
+        <v>2</v>
+      </c>
+      <c r="H334" t="inlineStr">
+        <is>
+          <t>시행령 제9조의16제1항에 따라 1차 위반은 6개월, 2차 위반은 1년의 보조금 지급정지를 한다. 법 제44조의2는 5년의 범위에서 정지하도록 정하고 있다.</t>
+        </is>
+      </c>
+      <c r="I334" t="inlineStr">
+        <is>
+          <t>2차 위반이 1년이니, 1차는 그보다 가볍다.</t>
+        </is>
+      </c>
+      <c r="J334" t="inlineStr">
+        <is>
+          <t>화물자동차 운수사업법 제44조의2제1항, 같은 법 시행령 제9조의16</t>
+        </is>
+      </c>
+      <c r="K334" t="inlineStr">
+        <is>
+          <t>2026-10-22</t>
+        </is>
+      </c>
+      <c r="L334" t="inlineStr">
+        <is>
+          <t>자체 작성</t>
+        </is>
+      </c>
+      <c r="M334" t="n">
+        <v>2</v>
+      </c>
+      <c r="O334" t="inlineStr">
+        <is>
+          <t>verified</t>
+        </is>
+      </c>
+      <c r="P334" t="inlineStr">
+        <is>
+          <t>1등 / 2026-10-22</t>
+        </is>
+      </c>
+      <c r="Q334" t="inlineStr">
+        <is>
+          <t>AI 4차 초안(2026-10-21) · 근거 확인 ○: 영 제9조의16제1항 '1. 1차 위반: 6개월의 보조금 지급정지 2. 2차 위반: 1년' 확인. 국가법령정보센터 원문(법 2026.7.1., 영 2026.6.3., 규칙 2026.6.30. 시행)</t>
+        </is>
+      </c>
+    </row>
+    <row r="335">
+      <c r="A335" t="inlineStr">
+        <is>
+          <t>LAW-0334</t>
+        </is>
+      </c>
+      <c r="B335" t="inlineStr">
+        <is>
+          <t>주유업자가 운송사업자의 유가보조금 부정수급 행위에 1회 가담·공모한 경우, 해당 사업소의 유류구매카드 거래기능 정지 기간은?</t>
+        </is>
+      </c>
+      <c r="C335" t="inlineStr">
+        <is>
+          <t>10년</t>
+        </is>
+      </c>
+      <c r="D335" t="inlineStr">
+        <is>
+          <t>6개월</t>
+        </is>
+      </c>
+      <c r="E335" t="inlineStr">
+        <is>
+          <t>3년</t>
+        </is>
+      </c>
+      <c r="F335" t="inlineStr">
+        <is>
+          <t>1년</t>
+        </is>
+      </c>
+      <c r="G335" t="n">
+        <v>3</v>
+      </c>
+      <c r="H335" t="inlineStr">
+        <is>
+          <t>시행령 제9조의17제1항에 따라 1회 가담·공모하면 거래기능 정지 3년, 2회 이상이면 5년이다.</t>
+        </is>
+      </c>
+      <c r="I335" t="inlineStr">
+        <is>
+          <t>부정수급에 가담한 주유소는 운송사업자의 1차 지급정지보다 훨씬 무겁게 다룬다. 2회 이상이면 법률상 상한까지 간다.</t>
+        </is>
+      </c>
+      <c r="J335" t="inlineStr">
+        <is>
+          <t>화물자동차 운수사업법 제44조의2제2항, 같은 법 시행령 제9조의17</t>
+        </is>
+      </c>
+      <c r="K335" t="inlineStr">
+        <is>
+          <t>2026-10-22</t>
+        </is>
+      </c>
+      <c r="L335" t="inlineStr">
+        <is>
+          <t>자체 작성</t>
+        </is>
+      </c>
+      <c r="M335" t="n">
+        <v>3</v>
+      </c>
+      <c r="O335" t="inlineStr">
+        <is>
+          <t>verified</t>
+        </is>
+      </c>
+      <c r="P335" t="inlineStr">
+        <is>
+          <t>1등 / 2026-10-22</t>
+        </is>
+      </c>
+      <c r="Q335" t="inlineStr">
+        <is>
+          <t>AI 4차 초안(2026-10-21) · 근거 확인 ○: 영 제9조의17제1항 '1. 1회 가담ㆍ공모한 경우: 유류구매카드의 거래기능 정지 3년 2. 2회 이상 ... 5년' 확인. 국가법령정보센터 원문(법 2026.7.1., 영 2026.6.3., 규칙 2026.6.30. 시행)</t>
+        </is>
+      </c>
+    </row>
+    <row r="336">
+      <c r="A336" t="inlineStr">
+        <is>
+          <t>LAW-0335</t>
+        </is>
+      </c>
+      <c r="B336" t="inlineStr">
+        <is>
+          <t>시행령에서 정한 유가보조금 지급 요건으로 옳은 것은?</t>
+        </is>
+      </c>
+      <c r="C336" t="inlineStr">
+        <is>
+          <t>차량 연료와 다른 종류의 유류라도 영수증이 있으면 된다</t>
+        </is>
+      </c>
+      <c r="D336" t="inlineStr">
+        <is>
+          <t>사업자등록을 하지 않았더라도 실제로 운행하면 된다</t>
+        </is>
+      </c>
+      <c r="E336" t="inlineStr">
+        <is>
+          <t>주유소 등의 고정된 설비에서 해당 화물자동차에 직접 주유받을 것</t>
+        </is>
+      </c>
+      <c r="F336" t="inlineStr">
+        <is>
+          <t>화물운송 종사자격이 없는 사람이 운행해도 된다</t>
+        </is>
+      </c>
+      <c r="G336" t="n">
+        <v>3</v>
+      </c>
+      <c r="H336" t="inlineStr">
+        <is>
+          <t>시행령 제9조의14제1항에 따라 사업자등록을 하고 실제 사업을 하는 자가 구매한 유류일 것, 종사자격 요건을 갖춘 자가 운행할 것, 고정된 설비에서 직접 주유받을 것, 차량 연료와 일치하는 유류일 것 등을 모두 갖추어야 한다.</t>
+        </is>
+      </c>
+      <c r="I336" t="inlineStr">
+        <is>
+          <t>통에 담아 옮겨 넣는 방식이라면 실제로 그 차에 썼는지 확인하기 어렵다.</t>
+        </is>
+      </c>
+      <c r="J336" t="inlineStr">
+        <is>
+          <t>화물자동차 운수사업법 제43조제2항, 같은 법 시행령 제9조의14제1항</t>
+        </is>
+      </c>
+      <c r="K336" t="inlineStr">
+        <is>
+          <t>2026-10-22</t>
+        </is>
+      </c>
+      <c r="L336" t="inlineStr">
+        <is>
+          <t>자체 작성</t>
+        </is>
+      </c>
+      <c r="M336" t="n">
+        <v>1</v>
+      </c>
+      <c r="O336" t="inlineStr">
+        <is>
+          <t>verified</t>
+        </is>
+      </c>
+      <c r="P336" t="inlineStr">
+        <is>
+          <t>1등 / 2026-10-22</t>
+        </is>
+      </c>
+      <c r="Q336" t="inlineStr">
+        <is>
+          <t>AI 4차 초안(2026-10-21) · 근거 확인 ○: 영 제9조의14제1항 '4. 주유소ㆍ충전소ㆍ자가주유시설 또는 자가충전시설의 고정된 설비에서 유류를 직접 주유 또는 충전받을 것' 등 확인. 국가법령정보센터 원문(법 2026.7.1., 영 2026.6.3., 규칙 2026.6.30. 시행)</t>
+        </is>
+      </c>
+    </row>
+    <row r="337">
+      <c r="A337" t="inlineStr">
+        <is>
+          <t>LAW-0336</t>
+        </is>
+      </c>
+      <c r="B337" t="inlineStr">
+        <is>
+          <t>공영차고지를 설치한 자가 공영차고지를 임대(운영 위탁 포함)할 수 있는 상대가 아닌 것은?</t>
+        </is>
+      </c>
+      <c r="C337" t="inlineStr">
+        <is>
+          <t>운송사업자로 구성된 협동조합</t>
+        </is>
+      </c>
+      <c r="D337" t="inlineStr">
+        <is>
+          <t>운송가맹사업자</t>
+        </is>
+      </c>
+      <c r="E337" t="inlineStr">
+        <is>
+          <t>운송주선사업자</t>
+        </is>
+      </c>
+      <c r="F337" t="inlineStr">
+        <is>
+          <t>사업자단체</t>
+        </is>
+      </c>
+      <c r="G337" t="n">
+        <v>3</v>
+      </c>
+      <c r="H337" t="inlineStr">
+        <is>
+          <t>법 제45조제1항에 따라 공영차고지는 사업자단체, 운송사업자, 운송가맹사업자, 운송사업자로 구성된 협동조합에 임대할 수 있다. 차고지가 필요 없는 운송주선사업자는 포함되지 않는다.</t>
+        </is>
+      </c>
+      <c r="I337" t="inlineStr">
+        <is>
+          <t>차고지는 화물차를 세워 두는 곳이다. 차량을 직접 운용하지 않는 사업자가 누구인지 찾자.</t>
+        </is>
+      </c>
+      <c r="J337" t="inlineStr">
+        <is>
+          <t>화물자동차 운수사업법 제45조제1항</t>
+        </is>
+      </c>
+      <c r="K337" t="inlineStr">
+        <is>
+          <t>2026-10-22</t>
+        </is>
+      </c>
+      <c r="L337" t="inlineStr">
+        <is>
+          <t>자체 작성</t>
+        </is>
+      </c>
+      <c r="M337" t="n">
+        <v>1</v>
+      </c>
+      <c r="O337" t="inlineStr">
+        <is>
+          <t>verified</t>
+        </is>
+      </c>
+      <c r="P337" t="inlineStr">
+        <is>
+          <t>1등 / 2026-10-22</t>
+        </is>
+      </c>
+      <c r="Q337" t="inlineStr">
+        <is>
+          <t>AI 4차 초안(2026-10-21) · 근거 확인 ○: 법 제45조제1항 '1. 사업자단체 2. 운송사업자 3. 운송가맹사업자 4. 운송사업자로 구성된 협동조합' 확인. 국가법령정보센터 원문(법 2026.7.1., 영 2026.6.3., 규칙 2026.6.30. 시행)</t>
+        </is>
+      </c>
+    </row>
+    <row r="338">
+      <c r="A338" t="inlineStr">
+        <is>
+          <t>LAW-0337</t>
+        </is>
+      </c>
+      <c r="B338" t="inlineStr">
+        <is>
+          <t>자가용 화물자동차로 화물자동차 운송사업을 경영한 경우, 시·도지사가 그 자동차의 사용을 제한하거나 금지할 수 있는 기간은?</t>
+        </is>
+      </c>
+      <c r="C338" t="inlineStr">
+        <is>
+          <t>6개월 이내</t>
+        </is>
+      </c>
+      <c r="D338" t="inlineStr">
+        <is>
+          <t>2년 이내</t>
+        </is>
+      </c>
+      <c r="E338" t="inlineStr">
+        <is>
+          <t>1개월 이내</t>
+        </is>
+      </c>
+      <c r="F338" t="inlineStr">
+        <is>
+          <t>3개월 이내</t>
+        </is>
+      </c>
+      <c r="G338" t="n">
+        <v>1</v>
+      </c>
+      <c r="H338" t="inlineStr">
+        <is>
+          <t>법 제56조의2제1항에 따라 시·도지사는 6개월 이내의 기간을 정하여 사용을 제한하거나 금지할 수 있고, 금지한 경우 등록증·번호판 반납 규정을 준용한다.</t>
+        </is>
+      </c>
+      <c r="I338" t="inlineStr">
+        <is>
+          <t>운송사업자에 대한 사업정지 처분의 최대 기간과 같은 길이다.</t>
+        </is>
+      </c>
+      <c r="J338" t="inlineStr">
+        <is>
+          <t>화물자동차 운수사업법 제56조의2</t>
+        </is>
+      </c>
+      <c r="K338" t="inlineStr">
+        <is>
+          <t>2026-10-22</t>
+        </is>
+      </c>
+      <c r="L338" t="inlineStr">
+        <is>
+          <t>자체 작성</t>
+        </is>
+      </c>
+      <c r="M338" t="n">
+        <v>2</v>
+      </c>
+      <c r="O338" t="inlineStr">
+        <is>
+          <t>verified</t>
+        </is>
+      </c>
+      <c r="P338" t="inlineStr">
+        <is>
+          <t>1등 / 2026-10-22</t>
+        </is>
+      </c>
+      <c r="Q338" t="inlineStr">
+        <is>
+          <t>AI 4차 초안(2026-10-21) · 근거 확인 ○: 법 제56조의2제1항 '6개월 이내의 기간을 정하여 그 자동차의 사용을 제한하거나 금지할 수 있다' 확인. 국가법령정보센터 원문(법 2026.7.1., 영 2026.6.3., 규칙 2026.6.30. 시행)</t>
+        </is>
+      </c>
+    </row>
+    <row r="339">
+      <c r="A339" t="inlineStr">
+        <is>
+          <t>LAW-0338</t>
+        </is>
+      </c>
+      <c r="B339" t="inlineStr">
+        <is>
+          <t>영농조합법인이 소유한 자가용 화물자동차에 대해 시·도지사가 유상운송을 허가하는 경우, 그 허가기간은?</t>
+        </is>
+      </c>
+      <c r="C339" t="inlineStr">
+        <is>
+          <t>1년 이내</t>
+        </is>
+      </c>
+      <c r="D339" t="inlineStr">
+        <is>
+          <t>5년 이내</t>
+        </is>
+      </c>
+      <c r="E339" t="inlineStr">
+        <is>
+          <t>2년 이내</t>
+        </is>
+      </c>
+      <c r="F339" t="inlineStr">
+        <is>
+          <t>3년 이내</t>
+        </is>
+      </c>
+      <c r="G339" t="n">
+        <v>4</v>
+      </c>
+      <c r="H339" t="inlineStr">
+        <is>
+          <t>시행규칙 제51조제2항에 따라 영농조합법인 자가용 화물자동차의 유상운송 허가기간은 3년 이내이며, 만료일 30일 전까지 연장을 신청할 수 있다.</t>
+        </is>
+      </c>
+      <c r="I339" t="inlineStr">
+        <is>
+          <t>한 번 허가로 몇 해 농사철을 이어 쓸 수 있도록 하되, 기간을 정해 다시 점검한다.</t>
+        </is>
+      </c>
+      <c r="J339" t="inlineStr">
+        <is>
+          <t>화물자동차 운수사업법 제56조, 같은 법 시행규칙 제49조·제51조</t>
+        </is>
+      </c>
+      <c r="K339" t="inlineStr">
+        <is>
+          <t>2026-10-22</t>
+        </is>
+      </c>
+      <c r="L339" t="inlineStr">
+        <is>
+          <t>자체 작성</t>
+        </is>
+      </c>
+      <c r="M339" t="n">
+        <v>3</v>
+      </c>
+      <c r="O339" t="inlineStr">
+        <is>
+          <t>verified</t>
+        </is>
+      </c>
+      <c r="P339" t="inlineStr">
+        <is>
+          <t>1등 / 2026-10-22</t>
+        </is>
+      </c>
+      <c r="Q339" t="inlineStr">
+        <is>
+          <t>AI 4차 초안(2026-10-21) · 근거 확인 ○: 규칙 제51조제2항 '영농조합법인이 소유하는 자가용 화물자동차에 대한 유상운송 허가기간은 3년 이내' 확인. 국가법령정보센터 원문(법 2026.7.1., 영 2026.6.3., 규칙 2026.6.30. 시행)</t>
+        </is>
+      </c>
+    </row>
+    <row r="340">
+      <c r="A340" t="inlineStr">
+        <is>
+          <t>LAW-0339</t>
+        </is>
+      </c>
+      <c r="B340" t="inlineStr">
+        <is>
+          <t>허가 없이 자가용 화물자동차를 유상으로 화물운송용으로 제공하거나 임대한 자에 대한 벌칙은?</t>
+        </is>
+      </c>
+      <c r="C340" t="inlineStr">
+        <is>
+          <t>2년 이하의 징역 또는 2천만원 이하의 벌금</t>
+        </is>
+      </c>
+      <c r="D340" t="inlineStr">
+        <is>
+          <t>500만원 이하의 과태료</t>
+        </is>
+      </c>
+      <c r="E340" t="inlineStr">
+        <is>
+          <t>1년 이하의 징역 또는 1천만원 이하의 벌금</t>
+        </is>
+      </c>
+      <c r="F340" t="inlineStr">
+        <is>
+          <t>3년 이하의 징역 또는 3천만원 이하의 벌금</t>
+        </is>
+      </c>
+      <c r="G340" t="n">
+        <v>1</v>
+      </c>
+      <c r="H340" t="inlineStr">
+        <is>
+          <t>법 제67조제7호에 따라 제56조를 위반한 자는 2년 이하의 징역 또는 2천만원 이하의 벌금에 처한다. 무허가 운송사업 경영과 같은 수준이다.</t>
+        </is>
+      </c>
+      <c r="I340" t="inlineStr">
+        <is>
+          <t>사실상 허가 없이 운송사업을 한 것과 같으므로, 무허가 영업과 같은 형벌을 받는다.</t>
+        </is>
+      </c>
+      <c r="J340" t="inlineStr">
+        <is>
+          <t>화물자동차 운수사업법 제56조, 제67조제7호</t>
+        </is>
+      </c>
+      <c r="K340" t="inlineStr">
+        <is>
+          <t>2026-10-22</t>
+        </is>
+      </c>
+      <c r="L340" t="inlineStr">
+        <is>
+          <t>자체 작성</t>
+        </is>
+      </c>
+      <c r="M340" t="n">
+        <v>2</v>
+      </c>
+      <c r="O340" t="inlineStr">
+        <is>
+          <t>verified</t>
+        </is>
+      </c>
+      <c r="P340" t="inlineStr">
+        <is>
+          <t>1등 / 2026-10-22</t>
+        </is>
+      </c>
+      <c r="Q340" t="inlineStr">
+        <is>
+          <t>AI 4차 초안(2026-10-21) · 근거 확인 ○: 법 제67조 '2년 이하의 징역 또는 2천만원 이하의 벌금 ... 7. 제56조를 위반하여 자가용 화물자동차를 유상으로 화물운송용으로 제공하거나 임대한 자' 확인. 국가법령정보센터 원문(법 2026.7.1., 영 2026.6.3., 규칙 2026.6.30. 시행)</t>
+        </is>
+      </c>
+    </row>
+    <row r="341">
+      <c r="A341" t="inlineStr">
+        <is>
+          <t>LAW-0340</t>
+        </is>
+      </c>
+      <c r="B341" t="inlineStr">
+        <is>
+          <t>운송사업의 신규등록·증차·대폐차에 충당되는 화물자동차의 차령 조건(차령 5년 이내)이 적용되지 않는 차량은?</t>
+        </is>
+      </c>
+      <c r="C341" t="inlineStr">
+        <is>
+          <t>밴형 화물자동차</t>
+        </is>
+      </c>
+      <c r="D341" t="inlineStr">
+        <is>
+          <t>위험물을 수송하는 탱크트레일러</t>
+        </is>
+      </c>
+      <c r="E341" t="inlineStr">
+        <is>
+          <t>일반형 화물자동차</t>
+        </is>
+      </c>
+      <c r="F341" t="inlineStr">
+        <is>
+          <t>덤프형 화물자동차</t>
+        </is>
+      </c>
+      <c r="G341" t="n">
+        <v>4</v>
+      </c>
+      <c r="H341" t="inlineStr">
+        <is>
+          <t>시행규칙 제52조의2제7호에 따라 덤프형 화물자동차, 피견인자동차(특수가연물·위험물 탱크트레일러 제외), 특수자동차는 차량충당조건을 적용하지 않는다.</t>
+        </is>
+      </c>
+      <c r="I341" t="inlineStr">
+        <is>
+          <t>공사 현장 등 특수한 용도로 쓰이는 차종이 예외다. 위험물 운반 차량은 안전을 위해 예외에서 다시 빠진다.</t>
+        </is>
+      </c>
+      <c r="J341" t="inlineStr">
+        <is>
+          <t>화물자동차 운수사업법 제57조, 같은 법 시행규칙 제52조의2</t>
+        </is>
+      </c>
+      <c r="K341" t="inlineStr">
+        <is>
+          <t>2026-10-22</t>
+        </is>
+      </c>
+      <c r="L341" t="inlineStr">
+        <is>
+          <t>자체 작성</t>
+        </is>
+      </c>
+      <c r="M341" t="n">
+        <v>2</v>
+      </c>
+      <c r="O341" t="inlineStr">
+        <is>
+          <t>verified</t>
+        </is>
+      </c>
+      <c r="P341" t="inlineStr">
+        <is>
+          <t>1등 / 2026-10-22</t>
+        </is>
+      </c>
+      <c r="Q341" t="inlineStr">
+        <is>
+          <t>AI 4차 초안(2026-10-21) · 근거 확인 ○: 규칙 제52조의2 '7. 덤프형 화물자동차, 피견인자동차(... 위험물을 수송하기 위한 탱크트레일러는 제외한다) 또는 특수자동차' 확인. 국가법령정보센터 원문(법 2026.7.1., 영 2026.6.3., 규칙 2026.6.30. 시행)</t>
+        </is>
+      </c>
+    </row>
+    <row r="342">
+      <c r="A342" t="inlineStr">
+        <is>
+          <t>LAW-0341</t>
+        </is>
+      </c>
+      <c r="B342" t="inlineStr">
+        <is>
+          <t>운송사업자가 대폐차 변경신고를 한 경우, 원칙적으로 언제까지 대폐차를 해야 하는가?</t>
+        </is>
+      </c>
+      <c r="C342" t="inlineStr">
+        <is>
+          <t>변경신고를 한 날부터 1년 이내</t>
+        </is>
+      </c>
+      <c r="D342" t="inlineStr">
+        <is>
+          <t>변경신고를 한 날부터 7일 이내</t>
+        </is>
+      </c>
+      <c r="E342" t="inlineStr">
+        <is>
+          <t>변경신고를 한 날부터 15일 이내</t>
+        </is>
+      </c>
+      <c r="F342" t="inlineStr">
+        <is>
+          <t>변경신고를 한 날부터 30일 이내</t>
+        </is>
+      </c>
+      <c r="G342" t="n">
+        <v>3</v>
+      </c>
+      <c r="H342" t="inlineStr">
+        <is>
+          <t>시행규칙 제52조의3제1항제2호에 따라 대폐차 변경신고를 한 날부터 15일 이내에 대폐차해야 하며, 고시한 부득이한 사유가 있으면 6개월 이내에 할 수 있다.</t>
+        </is>
+      </c>
+      <c r="I342" t="inlineStr">
+        <is>
+          <t>자동차 매매 후 이전등록 기간과 같은 길이다.</t>
+        </is>
+      </c>
+      <c r="J342" t="inlineStr">
+        <is>
+          <t>화물자동차 운수사업법 제57조제2항, 같은 법 시행규칙 제52조의3</t>
+        </is>
+      </c>
+      <c r="K342" t="inlineStr">
+        <is>
+          <t>2026-10-22</t>
+        </is>
+      </c>
+      <c r="L342" t="inlineStr">
+        <is>
+          <t>자체 작성</t>
+        </is>
+      </c>
+      <c r="M342" t="n">
+        <v>2</v>
+      </c>
+      <c r="O342" t="inlineStr">
+        <is>
+          <t>verified</t>
+        </is>
+      </c>
+      <c r="P342" t="inlineStr">
+        <is>
+          <t>1등 / 2026-10-22</t>
+        </is>
+      </c>
+      <c r="Q342" t="inlineStr">
+        <is>
+          <t>AI 4차 초안(2026-10-21) · 근거 확인 ○: 규칙 제52조의3제1항 '2. 기한: 대폐차 변경신고를 한 날부터 15일 이내에 대폐차할 것. 다만 ... 6개월 이내' 확인. 국가법령정보센터 원문(법 2026.7.1., 영 2026.6.3., 규칙 2026.6.30. 시행)</t>
+        </is>
+      </c>
+    </row>
+    <row r="343">
+      <c r="A343" t="inlineStr">
+        <is>
+          <t>LAW-0342</t>
+        </is>
+      </c>
+      <c r="B343" t="inlineStr">
+        <is>
+          <t>시·도지사가 신고포상금을 지급할 수 있는 신고·고발 대상에 해당하지 않는 것은?</t>
+        </is>
+      </c>
+      <c r="C343" t="inlineStr">
+        <is>
+          <t>거짓이나 부정한 방법으로 유가보조금을 받은 자</t>
+        </is>
+      </c>
+      <c r="D343" t="inlineStr">
+        <is>
+          <t>밤샘주차 장소를 위반한 운송사업자</t>
+        </is>
+      </c>
+      <c r="E343" t="inlineStr">
+        <is>
+          <t>적재화물 이탈방지를 위한 덮개·고정장치 조치를 하지 않은 운송사업자</t>
+        </is>
+      </c>
+      <c r="F343" t="inlineStr">
+        <is>
+          <t>자가용 화물자동차를 유상으로 화물운송용으로 제공한 자</t>
+        </is>
+      </c>
+      <c r="G343" t="n">
+        <v>2</v>
+      </c>
+      <c r="H343" t="inlineStr">
+        <is>
+          <t>법 제60조의2제1항의 포상금 대상은 자가용 유상운송, 고장·사고차량 관련 부정 금품 수수, 덮개·고정 미조치, 재위탁 금지 위반, 보조금 부정수급, 무허가 경영 등이며 밤샘주차 위반은 없다.</t>
+        </is>
+      </c>
+      <c r="I343" t="inlineStr">
+        <is>
+          <t>포상금은 시민 제보가 꼭 필요한 중대한 불법 행위에 걸려 있다.</t>
+        </is>
+      </c>
+      <c r="J343" t="inlineStr">
+        <is>
+          <t>화물자동차 운수사업법 제60조의2제1항</t>
+        </is>
+      </c>
+      <c r="K343" t="inlineStr">
+        <is>
+          <t>2026-10-22</t>
+        </is>
+      </c>
+      <c r="L343" t="inlineStr">
+        <is>
+          <t>자체 작성</t>
+        </is>
+      </c>
+      <c r="M343" t="n">
+        <v>1</v>
+      </c>
+      <c r="O343" t="inlineStr">
+        <is>
+          <t>verified</t>
+        </is>
+      </c>
+      <c r="P343" t="inlineStr">
+        <is>
+          <t>1등 / 2026-10-22</t>
+        </is>
+      </c>
+      <c r="Q343" t="inlineStr">
+        <is>
+          <t>AI 4차 초안(2026-10-21) · 근거 확인 ○: 법 제60조의2제1항 각 호(자가용 유상운송, 덮개ㆍ포장ㆍ고정장치 미조치, 보조금 부정수급 등) 확인. 밤샘주차는 열거되어 있지 않음. 국가법령정보센터 원문(법 2026.7.1., 영 2026.6.3., 규칙 2026.6.30. 시행)</t>
+        </is>
+      </c>
+    </row>
+    <row r="344">
+      <c r="A344" t="inlineStr">
+        <is>
+          <t>LAW-0343</t>
+        </is>
+      </c>
+      <c r="B344" t="inlineStr">
+        <is>
+          <t>화물운송서비스 평가의 기준으로 법률에 규정된 것이 아닌 것은?</t>
+        </is>
+      </c>
+      <c r="C344" t="inlineStr">
+        <is>
+          <t>화물운송서비스의 이용자 만족도</t>
+        </is>
+      </c>
+      <c r="D344" t="inlineStr">
+        <is>
+          <t>화물운송서비스의 신속성 및 정확성</t>
+        </is>
+      </c>
+      <c r="E344" t="inlineStr">
+        <is>
+          <t>운송사업자가 보유한 화물자동차의 대수</t>
+        </is>
+      </c>
+      <c r="F344" t="inlineStr">
+        <is>
+          <t>화물운송서비스의 안전성</t>
+        </is>
+      </c>
+      <c r="G344" t="n">
+        <v>3</v>
+      </c>
+      <c r="H344" t="inlineStr">
+        <is>
+          <t>법 제47조의6제2항에 따라 평가 기준은 이용자 만족도, 신속성 및 정확성, 안전성 등이며, 평가에는 이용자 설문조사가 포함되어야 한다.</t>
+        </is>
+      </c>
+      <c r="I344" t="inlineStr">
+        <is>
+          <t>'서비스'를 평가하는 것이지 회사의 규모를 평가하는 것이 아니다.</t>
+        </is>
+      </c>
+      <c r="J344" t="inlineStr">
+        <is>
+          <t>화물자동차 운수사업법 제47조의6제2항</t>
+        </is>
+      </c>
+      <c r="K344" t="inlineStr">
+        <is>
+          <t>2026-10-22</t>
+        </is>
+      </c>
+      <c r="L344" t="inlineStr">
+        <is>
+          <t>자체 작성</t>
+        </is>
+      </c>
+      <c r="M344" t="n">
+        <v>1</v>
+      </c>
+      <c r="O344" t="inlineStr">
+        <is>
+          <t>verified</t>
+        </is>
+      </c>
+      <c r="P344" t="inlineStr">
+        <is>
+          <t>1등 / 2026-10-22</t>
+        </is>
+      </c>
+      <c r="Q344" t="inlineStr">
+        <is>
+          <t>AI 4차 초안(2026-10-21) · 근거 확인 ○: 법 제47조의6제2항 '1. 이용자 만족도 2. 신속성 및 정확성 3. 안전성' 확인. 국가법령정보센터 원문(법 2026.7.1., 영 2026.6.3., 규칙 2026.6.30. 시행)</t>
+        </is>
+      </c>
+    </row>
+    <row r="345">
+      <c r="A345" t="inlineStr">
+        <is>
+          <t>LAW-0344</t>
+        </is>
+      </c>
+      <c r="B345" t="inlineStr">
+        <is>
+          <t>국토교통부장관이 적재물사고 손해배상에 관한 화주의 분쟁조정 업무를 위탁할 수 있는 기관은?</t>
+        </is>
+      </c>
+      <c r="C345" t="inlineStr">
+        <is>
+          <t>도로교통공단</t>
+        </is>
+      </c>
+      <c r="D345" t="inlineStr">
+        <is>
+          <t>한국교통안전공단</t>
+        </is>
+      </c>
+      <c r="E345" t="inlineStr">
+        <is>
+          <t>관할 지방법원</t>
+        </is>
+      </c>
+      <c r="F345" t="inlineStr">
+        <is>
+          <t>한국소비자원 또는 등록된 소비자단체</t>
+        </is>
+      </c>
+      <c r="G345" t="n">
+        <v>4</v>
+      </c>
+      <c r="H345" t="inlineStr">
+        <is>
+          <t>법 제7조제6항에 따라 분쟁조정 업무를 소비자기본법에 따른 한국소비자원 또는 등록한 소비자단체에 위탁할 수 있다.</t>
+        </is>
+      </c>
+      <c r="I345" t="inlineStr">
+        <is>
+          <t>화주는 운송서비스를 이용하는 '소비자'라는 관점에서 생각하자.</t>
+        </is>
+      </c>
+      <c r="J345" t="inlineStr">
+        <is>
+          <t>화물자동차 운수사업법 제7조제3항~제6항</t>
+        </is>
+      </c>
+      <c r="K345" t="inlineStr">
+        <is>
+          <t>2026-10-22</t>
+        </is>
+      </c>
+      <c r="L345" t="inlineStr">
+        <is>
+          <t>자체 작성</t>
+        </is>
+      </c>
+      <c r="M345" t="n">
+        <v>2</v>
+      </c>
+      <c r="O345" t="inlineStr">
+        <is>
+          <t>verified</t>
+        </is>
+      </c>
+      <c r="P345" t="inlineStr">
+        <is>
+          <t>1등 / 2026-10-22</t>
+        </is>
+      </c>
+      <c r="Q345" t="inlineStr">
+        <is>
+          <t>AI 4차 초안(2026-10-21) · 근거 확인 ○: 법 제7조제6항 '「소비자기본법」 제33조제1항에 따른 한국소비자원 또는 같은 법 제29조제1항에 따라 등록한 소비자단체에 위탁할 수 있다' 확인. 국가법령정보센터 원문(법 2026.7.1., 영 2026.6.3., 규칙 2026.6.30. 시행)</t>
+        </is>
+      </c>
+    </row>
+    <row r="346">
+      <c r="A346" t="inlineStr">
+        <is>
+          <t>LAW-0345</t>
+        </is>
+      </c>
+      <c r="B346" t="inlineStr">
+        <is>
+          <t>밴형 화물자동차로 화주와 화물을 함께 운송하는 운송사업자는 사업용 표시에 더해 '화물'이라는 문구를 표시해야 한다. 표시해야 하는 언어로 옳은 것은?</t>
+        </is>
+      </c>
+      <c r="C346" t="inlineStr">
+        <is>
+          <t>한국어, 영어, 중국어, 일본어</t>
+        </is>
+      </c>
+      <c r="D346" t="inlineStr">
+        <is>
+          <t>한국어, 영어</t>
+        </is>
+      </c>
+      <c r="E346" t="inlineStr">
+        <is>
+          <t>한국어만</t>
+        </is>
+      </c>
+      <c r="F346" t="inlineStr">
+        <is>
+          <t>한국어, 영어, 러시아어</t>
+        </is>
+      </c>
+      <c r="G346" t="n">
+        <v>1</v>
+      </c>
+      <c r="H346" t="inlineStr">
+        <is>
+          <t>시행규칙 제21조제8호다목에 따라 사업용 표시를 하고 추가로 '화물'을 한국어, 영어, 중국어 및 일본어로 표시해야 한다.</t>
+        </is>
+      </c>
+      <c r="I346" t="inlineStr">
+        <is>
+          <t>택시로 오인하지 않도록 '화물'이라는 문구를 여러 언어로 표시합니다.</t>
+        </is>
+      </c>
+      <c r="J346" t="inlineStr">
+        <is>
+          <t>화물자동차 운수사업법 제11조, 같은 법 시행규칙 제21조제8호</t>
+        </is>
+      </c>
+      <c r="K346" t="inlineStr">
+        <is>
+          <t>2026-10-22</t>
+        </is>
+      </c>
+      <c r="L346" t="inlineStr">
+        <is>
+          <t>자체 작성</t>
+        </is>
+      </c>
+      <c r="M346" t="n">
+        <v>1</v>
+      </c>
+      <c r="O346" t="inlineStr">
+        <is>
+          <t>verified</t>
+        </is>
+      </c>
+      <c r="P346" t="inlineStr">
+        <is>
+          <t>1등 / 2026-10-22</t>
+        </is>
+      </c>
+      <c r="Q346" t="inlineStr">
+        <is>
+          <t>AI 4차 초안(2026-10-21) · 근거 확인 ○: 규칙 제21조제8호다목 '추가로 “화물”을 한국어, 영어, 중국어 및 일본어로 표시할 것' 확인. 국가법령정보센터 원문(법 2026.7.1., 영 2026.6.3., 규칙 2026.6.30. 시행) · 교차 점검 반영</t>
+        </is>
+      </c>
+    </row>
+    <row r="347">
+      <c r="A347" t="inlineStr">
+        <is>
+          <t>LAW-0346</t>
+        </is>
+      </c>
+      <c r="B347" t="inlineStr">
+        <is>
+          <t>구난형 특수자동차로 고장·사고차량을 운송하는 운송사업자의 준수사항으로 옳은 것은?</t>
+        </is>
+      </c>
+      <c r="C347" t="inlineStr">
+        <is>
+          <t>경찰공무원이 차량 이동을 명해도 운전자의 동의가 없으면 옮길 수 없다</t>
+        </is>
+      </c>
+      <c r="D347" t="inlineStr">
+        <is>
+          <t>차량 소유자나 운전자에게 최종 목적지까지의 총 운임·요금에 대한 구난동의를 받은 뒤 운송을 시작한다</t>
+        </is>
+      </c>
+      <c r="E347" t="inlineStr">
+        <is>
+          <t>운임·요금은 목적지에 도착한 뒤에 알려 주면 된다</t>
+        </is>
+      </c>
+      <c r="F347" t="inlineStr">
+        <is>
+          <t>운전자가 원하지 않아도 사업자가 판단하면 구난할 수 있다</t>
+        </is>
+      </c>
+      <c r="G347" t="n">
+        <v>2</v>
+      </c>
+      <c r="H347" t="inlineStr">
+        <is>
+          <t>시행규칙 제21조제20호·제21호에 따라 소유자·운전자의 의사에 반하여 구난하지 않고, 총 운임·요금에 대한 구난동의를 받은 후 운송을 시작해야 한다. 다만 사망·중상이나 경찰의 이동 명령 등은 예외다.</t>
+        </is>
+      </c>
+      <c r="I347" t="inlineStr">
+        <is>
+          <t>견인 후 바가지 요금 분쟁을 막기 위해 '먼저 동의, 나중 운송'의 순서를 정했다.</t>
+        </is>
+      </c>
+      <c r="J347" t="inlineStr">
+        <is>
+          <t>화물자동차 운수사업법 제11조, 같은 법 시행규칙 제21조제20호·제21호</t>
+        </is>
+      </c>
+      <c r="K347" t="inlineStr">
+        <is>
+          <t>2026-10-22</t>
+        </is>
+      </c>
+      <c r="L347" t="inlineStr">
+        <is>
+          <t>자체 작성</t>
+        </is>
+      </c>
+      <c r="M347" t="n">
+        <v>1</v>
+      </c>
+      <c r="O347" t="inlineStr">
+        <is>
+          <t>verified</t>
+        </is>
+      </c>
+      <c r="P347" t="inlineStr">
+        <is>
+          <t>1등 / 2026-10-22</t>
+        </is>
+      </c>
+      <c r="Q347" t="inlineStr">
+        <is>
+          <t>AI 4차 초안(2026-10-21) · 근거 확인 ○: 규칙 제21조 '20. ... 의사에 반하여 구난을 지시하거나 구난하지 아니할 것 ... 나. 경찰공무원이 차량의 이동을 명한 경우' '21. ... 총 운임ㆍ요금에 대하여 ... 구난동의를 받은 후 운송을 시작' 확인. 국가법령정보센터 원문(법 2026.7.1., 영 2026.6.3., 규칙 2026.6.30. 시행)</t>
+        </is>
+      </c>
+    </row>
+    <row r="348">
+      <c r="A348" t="inlineStr">
+        <is>
+          <t>LAW-0347</t>
+        </is>
+      </c>
+      <c r="B348" t="inlineStr">
+        <is>
+          <t>자동차를 산 사람이 이전등록을 하지 않아 판 사람(양도자)이 대신 이전등록을 신청했다. 등록관청은 양수인에게 어떤 기간을 정해 이전등록을 신청하도록 최고해야 하는가?</t>
+        </is>
+      </c>
+      <c r="C348" t="inlineStr">
+        <is>
+          <t>30일 이상 60일 이내</t>
+        </is>
+      </c>
+      <c r="D348" t="inlineStr">
+        <is>
+          <t>3일 이상 5일 이내</t>
+        </is>
+      </c>
+      <c r="E348" t="inlineStr">
+        <is>
+          <t>최고 없이 즉시 등록원부를 정리한다</t>
+        </is>
+      </c>
+      <c r="F348" t="inlineStr">
+        <is>
+          <t>7일 이상 15일 이내</t>
+        </is>
+      </c>
+      <c r="G348" t="n">
+        <v>4</v>
+      </c>
+      <c r="H348" t="inlineStr">
+        <is>
+          <t>자동차등록령 제27조제2항에 따라 등록관청은 지체 없이 양수인에게 7일 이상 15일 이내의 기간을 정하여 이전등록을 신청할 것을 최고하고, 이의나 신청이 없으면 등록 절차를 마친다.</t>
+        </is>
+      </c>
+      <c r="I348" t="inlineStr">
+        <is>
+          <t>양수인에게 스스로 등록할 기회를 한 번 더 주는 절차입니다. 지나치게 길지도, 하루이틀처럼 짧지도 않습니다.</t>
+        </is>
+      </c>
+      <c r="J348" t="inlineStr">
+        <is>
+          <t>자동차관리법 제12조제4항·제5항, 자동차등록령 제27조</t>
+        </is>
+      </c>
+      <c r="K348" t="inlineStr">
+        <is>
+          <t>2026-10-22</t>
+        </is>
+      </c>
+      <c r="L348" t="inlineStr">
+        <is>
+          <t>자체 작성</t>
+        </is>
+      </c>
+      <c r="M348" t="n">
+        <v>3</v>
+      </c>
+      <c r="O348" t="inlineStr">
+        <is>
+          <t>verified</t>
+        </is>
+      </c>
+      <c r="P348" t="inlineStr">
+        <is>
+          <t>1등 / 2026-10-22</t>
+        </is>
+      </c>
+      <c r="Q348" t="inlineStr">
+        <is>
+          <t>AI 4차 초안(2026-10-21) · 근거 확인 ○: 자동차등록령 제27조제2항 '양수인에게 7일 이상 15일 이내의 기간을 정하여 이전등록을 신청할 것을 최고' 확인. 국가법령정보센터 원문(자동차관리법령·자동차등록령, 2026 시행본) · 교차 점검 반영</t>
+        </is>
+      </c>
+    </row>
+    <row r="349">
+      <c r="A349" t="inlineStr">
+        <is>
+          <t>LAW-0348</t>
+        </is>
+      </c>
+      <c r="B349" t="inlineStr">
+        <is>
+          <t>중고 화물자동차를 산 사람이 이전등록을 하지 않은 상태에서 이 차를 다른 사람에게 다시 팔려고 한다. 옳은 것은?</t>
+        </is>
+      </c>
+      <c r="C349" t="inlineStr">
+        <is>
+          <t>새로 사는 사람만 등록하면 중간 등록은 생략할 수 있다</t>
+        </is>
+      </c>
+      <c r="D349" t="inlineStr">
+        <is>
+          <t>최초 소유자 명의 그대로 넘겨도 된다</t>
+        </is>
+      </c>
+      <c r="E349" t="inlineStr">
+        <is>
+          <t>산 날부터 1년 안에 되팔면 이전등록을 하지 않아도 된다</t>
+        </is>
+      </c>
+      <c r="F349" t="inlineStr">
+        <is>
+          <t>다시 팔기 전에 먼저 자기 명의로 이전등록을 해야 한다</t>
+        </is>
+      </c>
+      <c r="G349" t="n">
+        <v>4</v>
+      </c>
+      <c r="H349" t="inlineStr">
+        <is>
+          <t>자동차관리법 제12조제3항에 따라 자동차를 양수한 자가 다시 제3자에게 양도하려면 양도 전에 자기 명의로 이전등록을 해야 한다.</t>
+        </is>
+      </c>
+      <c r="I349" t="inlineStr">
+        <is>
+          <t>소유권의 변동은 등록해야 효력이 생기므로, 소유자 기록이 끊기지 않아야 한다.</t>
+        </is>
+      </c>
+      <c r="J349" t="inlineStr">
+        <is>
+          <t>자동차관리법 제12조제3항</t>
+        </is>
+      </c>
+      <c r="K349" t="inlineStr">
+        <is>
+          <t>2026-10-22</t>
+        </is>
+      </c>
+      <c r="L349" t="inlineStr">
+        <is>
+          <t>자체 작성</t>
+        </is>
+      </c>
+      <c r="M349" t="n">
+        <v>1</v>
+      </c>
+      <c r="O349" t="inlineStr">
+        <is>
+          <t>verified</t>
+        </is>
+      </c>
+      <c r="P349" t="inlineStr">
+        <is>
+          <t>1등 / 2026-10-22</t>
+        </is>
+      </c>
+      <c r="Q349" t="inlineStr">
+        <is>
+          <t>AI 4차 초안(2026-10-21) · 근거 확인 ○: 자동차관리법 제12조제3항 '자동차를 양수한 자가 다시 제3자에게 양도하려는 경우에는 양도 전에 자기 명의로 ... 이전등록을 하여야 한다' 확인. 국가법령정보센터 원문(자동차관리법령·자동차등록령, 2026 시행본)</t>
+        </is>
+      </c>
+    </row>
+    <row r="350">
+      <c r="A350" t="inlineStr">
+        <is>
+          <t>LAW-0349</t>
+        </is>
+      </c>
+      <c r="B350" t="inlineStr">
+        <is>
+          <t>자동차관리법상 붙인 등록번호판을 뗄 수 있는 경우는?</t>
+        </is>
+      </c>
+      <c r="C350" t="inlineStr">
+        <is>
+          <t>번호판이 낡아 소유자가 임의로 떼고 운행하는 경우</t>
+        </is>
+      </c>
+      <c r="D350" t="inlineStr">
+        <is>
+          <t>주차단속을 피하기 위해 잠시 떼어 두는 경우</t>
+        </is>
+      </c>
+      <c r="E350" t="inlineStr">
+        <is>
+          <t>운전자가 세차를 하기 위해 스스로 떼는 경우</t>
+        </is>
+      </c>
+      <c r="F350" t="inlineStr">
+        <is>
+          <t>등록한 자동차정비업자가 정비를 위해 사업장 안에서 일시적으로 떼는 경우</t>
+        </is>
+      </c>
+      <c r="G350" t="n">
+        <v>4</v>
+      </c>
+      <c r="H350" t="inlineStr">
+        <is>
+          <t>자동차관리법 제10조제2항에 따라 등록번호판은 시·도지사의 허가, 정비업자의 사업장 내 일시 분리, 다른 법률의 특별한 규정이 있는 경우 외에는 뗄 수 없다.</t>
+        </is>
+      </c>
+      <c r="I350" t="inlineStr">
+        <is>
+          <t>번호판은 허가나 법률 근거 없이는 뗄 수 없습니다. 소유자 마음대로 떼는 경우는 모두 금지입니다.</t>
+        </is>
+      </c>
+      <c r="J350" t="inlineStr">
+        <is>
+          <t>자동차관리법 제10조제2항</t>
+        </is>
+      </c>
+      <c r="K350" t="inlineStr">
+        <is>
+          <t>2026-10-22</t>
+        </is>
+      </c>
+      <c r="L350" t="inlineStr">
+        <is>
+          <t>자체 작성</t>
+        </is>
+      </c>
+      <c r="M350" t="n">
+        <v>1</v>
+      </c>
+      <c r="O350" t="inlineStr">
+        <is>
+          <t>verified</t>
+        </is>
+      </c>
+      <c r="P350" t="inlineStr">
+        <is>
+          <t>1등 / 2026-10-22</t>
+        </is>
+      </c>
+      <c r="Q350" t="inlineStr">
+        <is>
+          <t>AI 4차 초안(2026-10-21) · 근거 확인 ○: 자동차관리법 제10조제2항 '2. 제53조에 따라 등록한 자동차정비업자가 정비를 위하여 사업장 내에서 ... 일시적으로 뗀 경우' 확인. 국가법령정보센터 원문(자동차관리법령·자동차등록령, 2026 시행본) · 교차 점검 반영</t>
+        </is>
+      </c>
+    </row>
+    <row r="351">
+      <c r="A351" t="inlineStr">
+        <is>
+          <t>LAW-0350</t>
+        </is>
+      </c>
+      <c r="B351" t="inlineStr">
+        <is>
+          <t>시·도지사가 직권으로 자동차 말소등록을 할 수 있는 경우는?</t>
+        </is>
+      </c>
+      <c r="C351" t="inlineStr">
+        <is>
+          <t>자동차세를 한 번 체납한 경우</t>
+        </is>
+      </c>
+      <c r="D351" t="inlineStr">
+        <is>
+          <t>의무보험 가입명령을 이행하지 않은 지 1년 이상 지난 경우</t>
+        </is>
+      </c>
+      <c r="E351" t="inlineStr">
+        <is>
+          <t>정기검사를 하루 늦게 받은 경우</t>
+        </is>
+      </c>
+      <c r="F351" t="inlineStr">
+        <is>
+          <t>소유자가 주소를 옮기고 변경등록을 늦게 한 경우</t>
+        </is>
+      </c>
+      <c r="G351" t="n">
+        <v>2</v>
+      </c>
+      <c r="H351" t="inlineStr">
+        <is>
+          <t>자동차관리법 제13조제3항에 따라 신청 의무자의 미신청, 차대 불일치, 운행정지 명령 위반 계속 운행, 부정 등록, 의무보험 가입명령 미이행 1년 이상 등의 경우 직권으로 말소등록할 수 있다.</t>
+        </is>
+      </c>
+      <c r="I351" t="inlineStr">
+        <is>
+          <t>사고가 나도 피해자를 보상할 수 없는 상태가 오래 계속된 차라면 도로에서 퇴출시킨다.</t>
+        </is>
+      </c>
+      <c r="J351" t="inlineStr">
+        <is>
+          <t>자동차관리법 제13조제3항제6호</t>
+        </is>
+      </c>
+      <c r="K351" t="inlineStr">
+        <is>
+          <t>2026-10-22</t>
+        </is>
+      </c>
+      <c r="L351" t="inlineStr">
+        <is>
+          <t>자체 작성</t>
+        </is>
+      </c>
+      <c r="M351" t="n">
+        <v>1</v>
+      </c>
+      <c r="O351" t="inlineStr">
+        <is>
+          <t>verified</t>
+        </is>
+      </c>
+      <c r="P351" t="inlineStr">
+        <is>
+          <t>1등 / 2026-10-22</t>
+        </is>
+      </c>
+      <c r="Q351" t="inlineStr">
+        <is>
+          <t>AI 4차 초안(2026-10-21) · 근거 확인 ○: 자동차관리법 제13조제3항 '6. 「자동차손해배상 보장법」 제6조제3항에 따른 의무보험 가입명령을 이행하지 아니한 지 1년 이상 경과한 경우' 확인. 국가법령정보센터 원문(자동차관리법령·자동차등록령, 2026 시행본)</t>
+        </is>
+      </c>
+    </row>
+    <row r="352">
+      <c r="A352" t="inlineStr">
+        <is>
+          <t>LAW-0351</t>
+        </is>
+      </c>
+      <c r="B352" t="inlineStr">
+        <is>
+          <t>시·도지사가 직권으로 말소등록을 하려는 경우, 원칙적으로 말소등록 예정일 얼마 전까지 소유자와 이해관계인에게 알려야 하는가?</t>
+        </is>
+      </c>
+      <c r="C352" t="inlineStr">
+        <is>
+          <t>7일 전까지</t>
+        </is>
+      </c>
+      <c r="D352" t="inlineStr">
+        <is>
+          <t>15일 전까지</t>
+        </is>
+      </c>
+      <c r="E352" t="inlineStr">
+        <is>
+          <t>3개월 전까지</t>
+        </is>
+      </c>
+      <c r="F352" t="inlineStr">
+        <is>
+          <t>1개월 전까지</t>
+        </is>
+      </c>
+      <c r="G352" t="n">
+        <v>4</v>
+      </c>
+      <c r="H352" t="inlineStr">
+        <is>
+          <t>자동차관리법 제13조제4항에 따라 사유와 말소등록 예정일을 명시하여 1개월 전까지 소유자 및 이해관계인에게 알려야 한다. 소유자 등이 동의한 경우 등은 예외다.</t>
+        </is>
+      </c>
+      <c r="I352" t="inlineStr">
+        <is>
+          <t>소유자와 이해관계인이 이의를 제기할 시간을 주려고 말소 예정일보다 미리 알리게 합니다.</t>
+        </is>
+      </c>
+      <c r="J352" t="inlineStr">
+        <is>
+          <t>자동차관리법 제13조제4항</t>
+        </is>
+      </c>
+      <c r="K352" t="inlineStr">
+        <is>
+          <t>2026-10-22</t>
+        </is>
+      </c>
+      <c r="L352" t="inlineStr">
+        <is>
+          <t>자체 작성</t>
+        </is>
+      </c>
+      <c r="M352" t="n">
+        <v>2</v>
+      </c>
+      <c r="O352" t="inlineStr">
+        <is>
+          <t>verified</t>
+        </is>
+      </c>
+      <c r="P352" t="inlineStr">
+        <is>
+          <t>1등 / 2026-10-22</t>
+        </is>
+      </c>
+      <c r="Q352" t="inlineStr">
+        <is>
+          <t>AI 4차 초안(2026-10-21) · 근거 확인 ○: 자동차관리법 제13조제4항 '말소등록 예정일을 명시하여 그 1개월 전까지 ... 알려야 한다' 확인. 국가법령정보센터 원문(자동차관리법령·자동차등록령, 2026 시행본) · 교차 점검 반영</t>
+        </is>
+      </c>
+    </row>
+    <row r="353">
+      <c r="A353" t="inlineStr">
+        <is>
+          <t>LAW-0352</t>
+        </is>
+      </c>
+      <c r="B353" t="inlineStr">
+        <is>
+          <t>정기검사(또는 종합검사)를 받지 않아 검사 명령을 받은 자동차 소유자가 명령을 이행하지 않은 지 일정 기간이 지나면 시장·군수·구청장은 운행정지를 명해야 한다. 그 기간은?</t>
+        </is>
+      </c>
+      <c r="C353" t="inlineStr">
+        <is>
+          <t>1개월 이상</t>
+        </is>
+      </c>
+      <c r="D353" t="inlineStr">
+        <is>
+          <t>1년 이상</t>
+        </is>
+      </c>
+      <c r="E353" t="inlineStr">
+        <is>
+          <t>6개월 이상</t>
+        </is>
+      </c>
+      <c r="F353" t="inlineStr">
+        <is>
+          <t>3개월 이상</t>
+        </is>
+      </c>
+      <c r="G353" t="n">
+        <v>2</v>
+      </c>
+      <c r="H353" t="inlineStr">
+        <is>
+          <t>자동차관리법 제37조제3항에 따라 검사 명령을 이행하지 않은 지 1년 이상 경과하면 해당 자동차의 운행정지를 명해야 하며, 이를 어기고 계속 운행하면 직권 말소 사유가 된다.</t>
+        </is>
+      </c>
+      <c r="I353" t="inlineStr">
+        <is>
+          <t>검사를 받으라는 명령을 오래 무시한 차에만 운행정지를 반드시 명하게 했습니다. 이 운행정지를 어기고 계속 운행하면 직권 말소 사유가 됩니다.</t>
+        </is>
+      </c>
+      <c r="J353" t="inlineStr">
+        <is>
+          <t>자동차관리법 제37조제1항제3호·제3항</t>
+        </is>
+      </c>
+      <c r="K353" t="inlineStr">
+        <is>
+          <t>2026-10-22</t>
+        </is>
+      </c>
+      <c r="L353" t="inlineStr">
+        <is>
+          <t>자체 작성</t>
+        </is>
+      </c>
+      <c r="M353" t="n">
+        <v>2</v>
+      </c>
+      <c r="O353" t="inlineStr">
+        <is>
+          <t>verified</t>
+        </is>
+      </c>
+      <c r="P353" t="inlineStr">
+        <is>
+          <t>1등 / 2026-10-22</t>
+        </is>
+      </c>
+      <c r="Q353" t="inlineStr">
+        <is>
+          <t>AI 4차 초안(2026-10-21) · 근거 확인 ○: 자동차관리법 제37조제3항 '검사 명령을 이행하지 아니한 지 1년 이상 경과한 경우에는 해당 자동차의 운행정지를 명하여야 한다' 확인. 국가법령정보센터 원문(자동차관리법령·자동차등록령, 2026 시행본) · 교차 점검 반영</t>
+        </is>
+      </c>
+    </row>
+    <row r="354">
+      <c r="A354" t="inlineStr">
+        <is>
+          <t>LAW-0353</t>
+        </is>
+      </c>
+      <c r="B354" t="inlineStr">
+        <is>
+          <t>천재지변이나 그 밖의 부득이한 사유로 자동차 정기검사를 받을 수 없는 경우에 대한 설명으로 옳은 것은?</t>
+        </is>
+      </c>
+      <c r="C354" t="inlineStr">
+        <is>
+          <t>검사 의무가 영구히 면제된다</t>
+        </is>
+      </c>
+      <c r="D354" t="inlineStr">
+        <is>
+          <t>국토교통부령에 따라 검사 기간을 연장받거나 검사를 유예받을 수 있다</t>
+        </is>
+      </c>
+      <c r="E354" t="inlineStr">
+        <is>
+          <t>말소등록을 한 뒤 다시 신규등록을 해야 한다</t>
+        </is>
+      </c>
+      <c r="F354" t="inlineStr">
+        <is>
+          <t>검사 유효기간이 자동으로 두 배로 늘어난다</t>
+        </is>
+      </c>
+      <c r="G354" t="n">
+        <v>2</v>
+      </c>
+      <c r="H354" t="inlineStr">
+        <is>
+          <t>자동차관리법 제43조제4항에 따라 국토교통부장관은 천재지변 등 부득이한 사유로 정기·튜닝·임시검사를 받을 수 없다고 인정되면 그 기간을 연장하거나 검사를 유예할 수 있다.</t>
+        </is>
+      </c>
+      <c r="I354" t="inlineStr">
+        <is>
+          <t>검사 자체를 없애는 것이 아니라, 사정이 풀릴 때까지 '미루어 주는' 제도다.</t>
+        </is>
+      </c>
+      <c r="J354" t="inlineStr">
+        <is>
+          <t>자동차관리법 제43조제4항</t>
+        </is>
+      </c>
+      <c r="K354" t="inlineStr">
+        <is>
+          <t>2026-10-22</t>
+        </is>
+      </c>
+      <c r="L354" t="inlineStr">
+        <is>
+          <t>자체 작성</t>
+        </is>
+      </c>
+      <c r="M354" t="n">
+        <v>1</v>
+      </c>
+      <c r="O354" t="inlineStr">
+        <is>
+          <t>verified</t>
+        </is>
+      </c>
+      <c r="P354" t="inlineStr">
+        <is>
+          <t>1등 / 2026-10-22</t>
+        </is>
+      </c>
+      <c r="Q354" t="inlineStr">
+        <is>
+          <t>AI 4차 초안(2026-10-21) · 근거 확인 ○: 자동차관리법 제43조제4항 '부득이한 사유로 ... 검사를 받을 수 없다고 인정될 때에는 ... 그 기간을 연장하거나 자동차검사를 유예할 수 있다' 확인. 국가법령정보센터 원문(자동차관리법령·자동차등록령, 2026 시행본)</t>
+        </is>
+      </c>
+    </row>
+    <row r="355">
+      <c r="A355" t="inlineStr">
+        <is>
+          <t>LAW-0354</t>
+        </is>
+      </c>
+      <c r="B355" t="inlineStr">
+        <is>
+          <t>정당한 사유 없이 자동차를 타인의 토지에 방치하면 강제 처리 대상이 된다. 분해·파손되지 않은 자동차의 경우 그 방치 기간 기준은?</t>
+        </is>
+      </c>
+      <c r="C355" t="inlineStr">
+        <is>
+          <t>1개월 이상</t>
+        </is>
+      </c>
+      <c r="D355" t="inlineStr">
+        <is>
+          <t>6개월 이상</t>
+        </is>
+      </c>
+      <c r="E355" t="inlineStr">
+        <is>
+          <t>15일 이상</t>
+        </is>
+      </c>
+      <c r="F355" t="inlineStr">
+        <is>
+          <t>2개월 이상</t>
+        </is>
+      </c>
+      <c r="G355" t="n">
+        <v>4</v>
+      </c>
+      <c r="H355" t="inlineStr">
+        <is>
+          <t>자동차관리법 시행령 제6조제1항에 따라 타인의 토지 방치 기준은 2개월(분해·파손되어 운행이 불가능한 경우에는 15일)이다.</t>
+        </is>
+      </c>
+      <c r="I355" t="inlineStr">
+        <is>
+          <t>부서져 움직일 수 없는 차는 더 짧은 기간(보름)으로 정했고, 멀쩡한 차는 그보다 넉넉하다.</t>
+        </is>
+      </c>
+      <c r="J355" t="inlineStr">
+        <is>
+          <t>자동차관리법 제26조제1항제3호, 같은 법 시행령 제6조제1항</t>
+        </is>
+      </c>
+      <c r="K355" t="inlineStr">
+        <is>
+          <t>2026-10-22</t>
+        </is>
+      </c>
+      <c r="L355" t="inlineStr">
+        <is>
+          <t>자체 작성</t>
+        </is>
+      </c>
+      <c r="M355" t="n">
+        <v>2</v>
+      </c>
+      <c r="O355" t="inlineStr">
+        <is>
+          <t>verified</t>
+        </is>
+      </c>
+      <c r="P355" t="inlineStr">
+        <is>
+          <t>1등 / 2026-10-22</t>
+        </is>
+      </c>
+      <c r="Q355" t="inlineStr">
+        <is>
+          <t>AI 4차 초안(2026-10-21) · 근거 확인 ○: 자동차관리법 시행령 제6조제1항 '대통령령으로 정하는 기간이란 2개월(자동차가 분해ㆍ파손되어 운행이 불가능한 경우에는 15일)' 확인. 국가법령정보센터 원문(자동차관리법령·자동차등록령, 2026 시행본)</t>
+        </is>
+      </c>
+    </row>
+    <row r="356">
+      <c r="A356" t="inlineStr">
+        <is>
+          <t>LAW-0355</t>
+        </is>
+      </c>
+      <c r="B356" t="inlineStr">
+        <is>
+          <t>도로법상 운행제한을 위반한 차량의 운전자에게 도로관리청이 명할 수 있는 조치가 아닌 것은?</t>
+        </is>
+      </c>
+      <c r="C356" t="inlineStr">
+        <is>
+          <t>차량의 운행중지</t>
+        </is>
+      </c>
+      <c r="D356" t="inlineStr">
+        <is>
+          <t>차량의 회차</t>
+        </is>
+      </c>
+      <c r="E356" t="inlineStr">
+        <is>
+          <t>차량의 몰수</t>
+        </is>
+      </c>
+      <c r="F356" t="inlineStr">
+        <is>
+          <t>적재물의 분리 운송</t>
+        </is>
+      </c>
+      <c r="G356" t="n">
+        <v>3</v>
+      </c>
+      <c r="H356" t="inlineStr">
+        <is>
+          <t>도로법 제80조에 따라 도로관리청은 운행제한 위반 차량의 운전자에게 회차, 적재물의 분리 운송, 운행중지를 명할 수 있다.</t>
+        </is>
+      </c>
+      <c r="I356" t="inlineStr">
+        <is>
+          <t>도로를 보호하기 위해 '돌려보내기, 나눠 싣기, 멈추기'를 시킬 수 있을 뿐, 재산을 빼앗는 처분은 없다.</t>
+        </is>
+      </c>
+      <c r="J356" t="inlineStr">
+        <is>
+          <t>도로법 제80조</t>
+        </is>
+      </c>
+      <c r="K356" t="inlineStr">
+        <is>
+          <t>2026-10-22</t>
+        </is>
+      </c>
+      <c r="L356" t="inlineStr">
+        <is>
+          <t>자체 작성</t>
+        </is>
+      </c>
+      <c r="M356" t="n">
+        <v>1</v>
+      </c>
+      <c r="O356" t="inlineStr">
+        <is>
+          <t>verified</t>
+        </is>
+      </c>
+      <c r="P356" t="inlineStr">
+        <is>
+          <t>1등 / 2026-10-22</t>
+        </is>
+      </c>
+      <c r="Q356" t="inlineStr">
+        <is>
+          <t>AI 4차 초안(2026-10-21) · 근거 확인 ○: 도로법 제80조 '1. 차량의 회차 2. 적재물의 분리 운송 3. 차량의 운행중지' 확인. 국가법령정보센터 원문(도로법·시행령, 2026.9.18. 시행)</t>
+        </is>
+      </c>
+    </row>
+    <row r="357">
+      <c r="A357" t="inlineStr">
+        <is>
+          <t>LAW-0356</t>
+        </is>
+      </c>
+      <c r="B357" t="inlineStr">
+        <is>
+          <t>도로법령상 고속국도 진입 요금소를 통과할 때 적재량 측정장비가 설치된 차로로 통행해야 하는 화물자동차는?</t>
+        </is>
+      </c>
+      <c r="C357" t="inlineStr">
+        <is>
+          <t>최대 적재량 1톤 이상인 화물자동차</t>
+        </is>
+      </c>
+      <c r="D357" t="inlineStr">
+        <is>
+          <t>최대 적재량 2.5톤 이상인 화물자동차</t>
+        </is>
+      </c>
+      <c r="E357" t="inlineStr">
+        <is>
+          <t>최대 적재량 4.5톤 이상인 화물자동차</t>
+        </is>
+      </c>
+      <c r="F357" t="inlineStr">
+        <is>
+          <t>총중량 40톤을 넘는 화물자동차만</t>
+        </is>
+      </c>
+      <c r="G357" t="n">
+        <v>3</v>
+      </c>
+      <c r="H357" t="inlineStr">
+        <is>
+          <t>도로법 시행령 제80조의2제1항에 따라 최대 적재량 4.5톤 이상인 화물자동차는 고속국도 진입 요금소에서 측정장비가 설치된 차로로 통행해야 한다.</t>
+        </is>
+      </c>
+      <c r="I357" t="inlineStr">
+        <is>
+          <t>소형·중형 화물차 모두가 대상은 아니며, 운행제한 기준(40톤)을 넘는 차만 측정하는 것도 아닙니다.</t>
+        </is>
+      </c>
+      <c r="J357" t="inlineStr">
+        <is>
+          <t>도로법 제78조제3항, 같은 법 시행령 제80조의2</t>
+        </is>
+      </c>
+      <c r="K357" t="inlineStr">
+        <is>
+          <t>2026-10-22</t>
+        </is>
+      </c>
+      <c r="L357" t="inlineStr">
+        <is>
+          <t>자체 작성</t>
+        </is>
+      </c>
+      <c r="M357" t="n">
+        <v>2</v>
+      </c>
+      <c r="O357" t="inlineStr">
+        <is>
+          <t>verified</t>
+        </is>
+      </c>
+      <c r="P357" t="inlineStr">
+        <is>
+          <t>1등 / 2026-10-22</t>
+        </is>
+      </c>
+      <c r="Q357" t="inlineStr">
+        <is>
+          <t>AI 4차 초안(2026-10-21) · 근거 확인 ○: 도로법 시행령 제80조의2제1항 '최대 적재량이 4.5톤 이상인 화물자동차의 운전자는 고속국도 진입 요금소를 통과할 때에는 적재량 측정장비가 설치된 차로로 통행' 확인. 국가법령정보센터 원문(도로법·시행령, 2026.9.18. 시행) · 교차 점검 반영</t>
+        </is>
+      </c>
+    </row>
+    <row r="358">
+      <c r="A358" t="inlineStr">
+        <is>
+          <t>LAW-0357</t>
+        </is>
+      </c>
+      <c r="B358" t="inlineStr">
+        <is>
+          <t>고속국도 진입 요금소의 적재량 측정장비 설치 차로를 통과할 때 지켜야 하는 속도는?</t>
+        </is>
+      </c>
+      <c r="C358" t="inlineStr">
+        <is>
+          <t>속도 제한 없이 완전히 정지했다가 출발</t>
+        </is>
+      </c>
+      <c r="D358" t="inlineStr">
+        <is>
+          <t>시속 10킬로미터 이하</t>
+        </is>
+      </c>
+      <c r="E358" t="inlineStr">
+        <is>
+          <t>시속 50킬로미터 이하</t>
+        </is>
+      </c>
+      <c r="F358" t="inlineStr">
+        <is>
+          <t>시속 30킬로미터 이하</t>
+        </is>
+      </c>
+      <c r="G358" t="n">
+        <v>2</v>
+      </c>
+      <c r="H358" t="inlineStr">
+        <is>
+          <t>도로법 시행령 제80조의2제1항 후단에 따라 측정 차로의 통행 속도는 시속 10킬로미터 이하여야 한다. 정해진 속도를 지키지 않거나 급가속·급감속하면 측정 방해 행위가 된다.</t>
+        </is>
+      </c>
+      <c r="I358" t="inlineStr">
+        <is>
+          <t>장비가 축마다 무게를 정확히 읽을 수 있도록 아주 천천히, 일정하게 지나가야 한다.</t>
+        </is>
+      </c>
+      <c r="J358" t="inlineStr">
+        <is>
+          <t>도로법 시행령 제80조의2제1항, 제80조</t>
+        </is>
+      </c>
+      <c r="K358" t="inlineStr">
+        <is>
+          <t>2026-10-22</t>
+        </is>
+      </c>
+      <c r="L358" t="inlineStr">
+        <is>
+          <t>자체 작성</t>
+        </is>
+      </c>
+      <c r="M358" t="n">
+        <v>1</v>
+      </c>
+      <c r="O358" t="inlineStr">
+        <is>
+          <t>verified</t>
+        </is>
+      </c>
+      <c r="P358" t="inlineStr">
+        <is>
+          <t>1등 / 2026-10-22</t>
+        </is>
+      </c>
+      <c r="Q358" t="inlineStr">
+        <is>
+          <t>AI 4차 초안(2026-10-21) · 근거 확인 ○: 도로법 시행령 제80조의2제1항 '이 경우 통행의 속도는 시속 10킬로미터 이하이어야 한다' 확인. 국가법령정보센터 원문(도로법·시행령, 2026.9.18. 시행)</t>
+        </is>
+      </c>
+    </row>
+    <row r="359">
+      <c r="A359" t="inlineStr">
+        <is>
+          <t>LAW-0358</t>
+        </is>
+      </c>
+      <c r="B359" t="inlineStr">
+        <is>
+          <t>도로법상 운행제한을 위반한 차량 운전자에게 과태료를 부과하지 않는 경우는?</t>
+        </is>
+      </c>
+      <c r="C359" t="inlineStr">
+        <is>
+          <t>운전자가 화주 등의 지시·요구로 위반한 사실을 신고하여 그 화주 등에게 과태료가 부과되는 경우</t>
+        </is>
+      </c>
+      <c r="D359" t="inlineStr">
+        <is>
+          <t>위반한 무게가 기준의 10% 이내인 경우</t>
+        </is>
+      </c>
+      <c r="E359" t="inlineStr">
+        <is>
+          <t>처음으로 위반한 경우</t>
+        </is>
+      </c>
+      <c r="F359" t="inlineStr">
+        <is>
+          <t>적재량 측정 후 스스로 회차한 경우</t>
+        </is>
+      </c>
+      <c r="G359" t="n">
+        <v>1</v>
+      </c>
+      <c r="H359" t="inlineStr">
+        <is>
+          <t>도로법 제117조제5항에 따라 운전자가 임차인의 관리 의무 위반이나 화주·운송사업자 등의 지시·요구 사실을 신고하여 그들에게 과태료가 부과되는 경우에는 운전자에게 과태료를 부과하지 않는다.</t>
+        </is>
+      </c>
+      <c r="I359" t="inlineStr">
+        <is>
+          <t>실제 책임이 있는 사람을 드러내도록 운전자의 신고를 장려하는 제도다.</t>
+        </is>
+      </c>
+      <c r="J359" t="inlineStr">
+        <is>
+          <t>도로법 제77조제3항, 제117조제1항·제5항</t>
+        </is>
+      </c>
+      <c r="K359" t="inlineStr">
+        <is>
+          <t>2026-10-22</t>
+        </is>
+      </c>
+      <c r="L359" t="inlineStr">
+        <is>
+          <t>자체 작성</t>
+        </is>
+      </c>
+      <c r="M359" t="n">
+        <v>1</v>
+      </c>
+      <c r="O359" t="inlineStr">
+        <is>
+          <t>verified</t>
+        </is>
+      </c>
+      <c r="P359" t="inlineStr">
+        <is>
+          <t>1등 / 2026-10-22</t>
+        </is>
+      </c>
+      <c r="Q359" t="inlineStr">
+        <is>
+          <t>AI 4차 초안(2026-10-21) · 근거 확인 ○: 도로법 제117조제5항 '2. 차량의 운전자가 화주 ... 등의 지시ㆍ요구 ... 에 따라 제77조제1항을 위반한 사실을 신고하여 ... 과태료를 부과하는 경우' 확인. 국가법령정보센터 원문(도로법·시행령, 2026.9.18. 시행)</t>
+        </is>
+      </c>
+    </row>
+    <row r="360">
+      <c r="A360" t="inlineStr">
+        <is>
+          <t>LAW-0359</t>
+        </is>
+      </c>
+      <c r="B360" t="inlineStr">
+        <is>
+          <t>운행제한 기준을 넘는 차량의 운행허가를 받으려는 자가 신청서에 원칙적으로 첨부해야 하는 서류는?</t>
+        </is>
+      </c>
+      <c r="C360" t="inlineStr">
+        <is>
+          <t>구조물 통과 하중 계산서</t>
+        </is>
+      </c>
+      <c r="D360" t="inlineStr">
+        <is>
+          <t>운전자의 운전경력증명서</t>
+        </is>
+      </c>
+      <c r="E360" t="inlineStr">
+        <is>
+          <t>자동차 정기검사 성적서</t>
+        </is>
+      </c>
+      <c r="F360" t="inlineStr">
+        <is>
+          <t>화주와 맺은 운송계약서</t>
+        </is>
+      </c>
+      <c r="G360" t="n">
+        <v>1</v>
+      </c>
+      <c r="H360" t="inlineStr">
+        <is>
+          <t>도로법 시행령 제79조제4항에 따라 운행 도로·구간·차량 제원·기간·목적·방법을 적은 신청서에 구조물 통과 하중 계산서를 첨부해야 한다. 초과 정도가 경미하면 생략할 수 있다.</t>
+        </is>
+      </c>
+      <c r="I360" t="inlineStr">
+        <is>
+          <t>다리·고가도로 같은 시설물이 그 차의 무게를 견딜 수 있는지 계산한 자료를 떠올리자.</t>
+        </is>
+      </c>
+      <c r="J360" t="inlineStr">
+        <is>
+          <t>도로법 제77조제1항 단서, 같은 법 시행령 제79조제4항</t>
+        </is>
+      </c>
+      <c r="K360" t="inlineStr">
+        <is>
+          <t>2026-10-22</t>
+        </is>
+      </c>
+      <c r="L360" t="inlineStr">
+        <is>
+          <t>자체 작성</t>
+        </is>
+      </c>
+      <c r="M360" t="n">
+        <v>2</v>
+      </c>
+      <c r="O360" t="inlineStr">
+        <is>
+          <t>verified</t>
+        </is>
+      </c>
+      <c r="P360" t="inlineStr">
+        <is>
+          <t>1등 / 2026-10-22</t>
+        </is>
+      </c>
+      <c r="Q360" t="inlineStr">
+        <is>
+          <t>AI 4차 초안(2026-10-21) · 근거 확인 ○: 도로법 시행령 제79조제4항 '제한차량 운행허가 신청서에 ... 적고, 구조물 통과 하중 계산서를 첨부하여 도로관리청에 제출' 확인. 국가법령정보센터 원문(도로법·시행령, 2026.9.18. 시행)</t>
+        </is>
+      </c>
+    </row>
+    <row r="361">
+      <c r="A361" t="inlineStr">
+        <is>
+          <t>LAW-0360</t>
+        </is>
+      </c>
+      <c r="B361" t="inlineStr">
+        <is>
+          <t>대기환경보전법상 운행차 배출가스 정밀검사를 받아야 하는 자동차는? (면제 대상 제외)</t>
+        </is>
+      </c>
+      <c r="C361" t="inlineStr">
+        <is>
+          <t>대기관리권역에 등록된 자동차</t>
+        </is>
+      </c>
+      <c r="D361" t="inlineStr">
+        <is>
+          <t>모든 지역에 등록된 이륜자동차</t>
+        </is>
+      </c>
+      <c r="E361" t="inlineStr">
+        <is>
+          <t>인구 10만명 이상인 모든 도시에 등록된 자동차</t>
+        </is>
+      </c>
+      <c r="F361" t="inlineStr">
+        <is>
+          <t>고속국도를 주로 운행하는 자동차</t>
+        </is>
+      </c>
+      <c r="G361" t="n">
+        <v>1</v>
+      </c>
+      <c r="H361" t="inlineStr">
+        <is>
+          <t>대기환경보전법 제63조제1항에 따라 대기관리권역 또는 인구 50만명 이상의 도시지역 중 대통령령으로 정하는 지역에 등록된 자동차의 소유자는 정밀검사를 받아야 한다.</t>
+        </is>
+      </c>
+      <c r="I361" t="inlineStr">
+        <is>
+          <t>대기오염이 심해 특별히 관리하는 '권역'이나 인구가 아주 많은 대도시가 기준이다.</t>
+        </is>
+      </c>
+      <c r="J361" t="inlineStr">
+        <is>
+          <t>대기환경보전법 제63조제1항</t>
+        </is>
+      </c>
+      <c r="K361" t="inlineStr">
+        <is>
+          <t>2026-10-22</t>
+        </is>
+      </c>
+      <c r="L361" t="inlineStr">
+        <is>
+          <t>자체 작성</t>
+        </is>
+      </c>
+      <c r="M361" t="n">
+        <v>1</v>
+      </c>
+      <c r="O361" t="inlineStr">
+        <is>
+          <t>verified</t>
+        </is>
+      </c>
+      <c r="P361" t="inlineStr">
+        <is>
+          <t>1등 / 2026-10-22</t>
+        </is>
+      </c>
+      <c r="Q361" t="inlineStr">
+        <is>
+          <t>AI 4차 초안(2026-10-21) · 근거 확인 ○: 대기환경보전법 제63조제1항 '1. 대기관리권역 2. 인구 50만명 이상의 도시지역 중 대통령령으로 정하는 지역' 확인. 국가법령정보센터 원문(대기환경보전법, 2026.9.18. 시행)</t>
+        </is>
+      </c>
+    </row>
+    <row r="362">
+      <c r="A362" t="inlineStr">
+        <is>
+          <t>LAW-0361</t>
+        </is>
+      </c>
+      <c r="B362" t="inlineStr">
+        <is>
+          <t>운행차 배출가스 정밀검사(관능·기능검사 제외)에서 2회 이상 부적합 판정을 받은 자동차 소유자가 해야 할 일은?</t>
+        </is>
+      </c>
+      <c r="C362" t="inlineStr">
+        <is>
+          <t>전문정비사업자에게 정비·점검을 받고 그 결과표를 종합검사대행자 등에게 제출한다</t>
+        </is>
+      </c>
+      <c r="D362" t="inlineStr">
+        <is>
+          <t>6개월 동안 운행을 멈춘 뒤 다시 검사를 받는다</t>
+        </is>
+      </c>
+      <c r="E362" t="inlineStr">
+        <is>
+          <t>시·도지사에게 검사 면제를 신청한다</t>
+        </is>
+      </c>
+      <c r="F362" t="inlineStr">
+        <is>
+          <t>자동차를 즉시 폐차해야 한다</t>
+        </is>
+      </c>
+      <c r="G362" t="n">
+        <v>1</v>
+      </c>
+      <c r="H362" t="inlineStr">
+        <is>
+          <t>대기환경보전법 제63조제4항에 따라 2회 이상 부적합 판정을 받으면 등록한 전문정비사업자에게 정비·점검을 받은 후 발급받은 결과표를 종합검사대행자 등에게 제출해야 한다. 위반하면 100만원 이하 과태료 대상이다.</t>
+        </is>
+      </c>
+      <c r="I362" t="inlineStr">
+        <is>
+          <t>같은 검사에서 계속 떨어진다면 원인을 고칠 전문가의 손을 거치게 한다.</t>
+        </is>
+      </c>
+      <c r="J362" t="inlineStr">
+        <is>
+          <t>대기환경보전법 제63조제4항</t>
+        </is>
+      </c>
+      <c r="K362" t="inlineStr">
+        <is>
+          <t>2026-10-22</t>
+        </is>
+      </c>
+      <c r="L362" t="inlineStr">
+        <is>
+          <t>자체 작성</t>
+        </is>
+      </c>
+      <c r="M362" t="n">
+        <v>1</v>
+      </c>
+      <c r="O362" t="inlineStr">
+        <is>
+          <t>verified</t>
+        </is>
+      </c>
+      <c r="P362" t="inlineStr">
+        <is>
+          <t>1등 / 2026-10-22</t>
+        </is>
+      </c>
+      <c r="Q362" t="inlineStr">
+        <is>
+          <t>AI 4차 초안(2026-10-21) · 근거 확인 ○: 대기환경보전법 제63조제4항 '2회 이상 부적합 판정을 받은 자동차의 소유자는 ... 전문정비사업자에게 정비ㆍ점검을 받은 후 ... 결과표를 ... 제출' 확인. 국가법령정보센터 원문(대기환경보전법, 2026.9.18. 시행)</t>
+        </is>
+      </c>
+    </row>
+    <row r="363">
+      <c r="A363" t="inlineStr">
+        <is>
+          <t>LAW-0362</t>
+        </is>
+      </c>
+      <c r="B363" t="inlineStr">
+        <is>
+          <t>대기환경보전법상 금지되는 행위는?</t>
+        </is>
+      </c>
+      <c r="C363" t="inlineStr">
+        <is>
+          <t>폐차하면서 배출가스 관련 부품을 해체하는 행위</t>
+        </is>
+      </c>
+      <c r="D363" t="inlineStr">
+        <is>
+          <t>인증받은 배출가스저감장치를 차량에 부착하는 행위</t>
+        </is>
+      </c>
+      <c r="E363" t="inlineStr">
+        <is>
+          <t>경유 화물차에 요소수를 넣지 않거나 적게 넣어 배출가스 저감 성능을 떨어뜨리는 행위</t>
+        </is>
+      </c>
+      <c r="F363" t="inlineStr">
+        <is>
+          <t>정비업소에서 점검·정비를 위해 배출가스 관련 부품을 잠시 떼어 내는 행위</t>
+        </is>
+      </c>
+      <c r="G363" t="n">
+        <v>3</v>
+      </c>
+      <c r="H363" t="inlineStr">
+        <is>
+          <t>대기환경보전법 제57조의2제1항에 따라 배출가스 관련 부품을 탈거·훼손·임의설정하거나 촉매제(요소수 등)를 사용하지 않거나 적게 사용해 성능을 떨어뜨리는 행위는 금지된다. 점검·정비·튜닝, 폐차 등은 예외다.</t>
+        </is>
+      </c>
+      <c r="I363" t="inlineStr">
+        <is>
+          <t>요소수는 질소산화물을 줄이는 '촉매제'다. 비용을 아끼려 빼먹으면 오염물질이 그대로 나온다.</t>
+        </is>
+      </c>
+      <c r="J363" t="inlineStr">
+        <is>
+          <t>대기환경보전법 제57조의2제1항</t>
+        </is>
+      </c>
+      <c r="K363" t="inlineStr">
+        <is>
+          <t>2026-10-22</t>
+        </is>
+      </c>
+      <c r="L363" t="inlineStr">
+        <is>
+          <t>자체 작성</t>
+        </is>
+      </c>
+      <c r="M363" t="n">
+        <v>1</v>
+      </c>
+      <c r="O363" t="inlineStr">
+        <is>
+          <t>verified</t>
+        </is>
+      </c>
+      <c r="P363" t="inlineStr">
+        <is>
+          <t>1등 / 2026-10-22</t>
+        </is>
+      </c>
+      <c r="Q363" t="inlineStr">
+        <is>
+          <t>AI 4차 초안(2026-10-21) · 근거 확인 ○: 대기환경보전법 제57조의2제1항 '배출가스 관련 부품을 탈거ㆍ훼손ㆍ해체ㆍ변경ㆍ임의설정 하거나 촉매제(요소수 등)를 사용하지 아니하거나 적게 사용하여 ...' 및 예외 각 호 확인. 국가법령정보센터 원문(대기환경보전법, 2026.9.18. 시행)</t>
+        </is>
+      </c>
+    </row>
+    <row r="364">
+      <c r="A364" t="inlineStr">
+        <is>
+          <t>LAW-0363</t>
+        </is>
+      </c>
+      <c r="B364" t="inlineStr">
+        <is>
+          <t>자동차의 배출가스 관련 부품을 임의로 탈거·훼손하여 그 성능을 떨어뜨린 자에 대한 대기환경보전법상 벌칙은?</t>
+        </is>
+      </c>
+      <c r="C364" t="inlineStr">
+        <is>
+          <t>300만원 이하의 벌금</t>
+        </is>
+      </c>
+      <c r="D364" t="inlineStr">
+        <is>
+          <t>1년 이하의 징역이나 1천만원 이하의 벌금</t>
+        </is>
+      </c>
+      <c r="E364" t="inlineStr">
+        <is>
+          <t>7년 이하의 징역이나 1억원 이하의 벌금</t>
+        </is>
+      </c>
+      <c r="F364" t="inlineStr">
+        <is>
+          <t>100만원 이하의 과태료</t>
+        </is>
+      </c>
+      <c r="G364" t="n">
+        <v>2</v>
+      </c>
+      <c r="H364" t="inlineStr">
+        <is>
+          <t>대기환경보전법 제91조제5호에 따라 제57조의2제1항을 위반한 자는 1년 이하의 징역이나 1천만원 이하의 벌금에 처한다.</t>
+        </is>
+      </c>
+      <c r="I364" t="inlineStr">
+        <is>
+          <t>과태료가 아니라 형벌(징역·벌금)이 정해진 행위다. 공장 무허가 배출 같은 가장 무거운 범죄 수준은 아니다.</t>
+        </is>
+      </c>
+      <c r="J364" t="inlineStr">
+        <is>
+          <t>대기환경보전법 제57조의2제1항, 제91조제5호</t>
+        </is>
+      </c>
+      <c r="K364" t="inlineStr">
+        <is>
+          <t>2026-10-22</t>
+        </is>
+      </c>
+      <c r="L364" t="inlineStr">
+        <is>
+          <t>자체 작성</t>
+        </is>
+      </c>
+      <c r="M364" t="n">
+        <v>2</v>
+      </c>
+      <c r="O364" t="inlineStr">
+        <is>
+          <t>verified</t>
+        </is>
+      </c>
+      <c r="P364" t="inlineStr">
+        <is>
+          <t>1등 / 2026-10-22</t>
+        </is>
+      </c>
+      <c r="Q364" t="inlineStr">
+        <is>
+          <t>AI 4차 초안(2026-10-21) · 근거 확인 ○: 대기환경보전법 제91조 '1년 이하의 징역이나 1천만원 이하의 벌금 ... 5. 제57조의2제1항을 위반하여 배출가스 관련 부품을 탈거ㆍ훼손 ...' 확인. 국가법령정보센터 원문(대기환경보전법, 2026.9.18. 시행)</t>
+        </is>
+      </c>
+    </row>
+    <row r="365">
+      <c r="A365" t="inlineStr">
+        <is>
+          <t>LAW-0364</t>
+        </is>
+      </c>
+      <c r="B365" t="inlineStr">
+        <is>
+          <t>도로나 주차장에서 실시하는 운행차 배출가스 수시점검에 따르지 않거나 기피·방해한 자에 대한 과태료의 법정 한도는?</t>
+        </is>
+      </c>
+      <c r="C365" t="inlineStr">
+        <is>
+          <t>200만원 이하</t>
+        </is>
+      </c>
+      <c r="D365" t="inlineStr">
+        <is>
+          <t>100만원 이하</t>
+        </is>
+      </c>
+      <c r="E365" t="inlineStr">
+        <is>
+          <t>1천만원 이하</t>
+        </is>
+      </c>
+      <c r="F365" t="inlineStr">
+        <is>
+          <t>50만원 이하</t>
+        </is>
+      </c>
+      <c r="G365" t="n">
+        <v>1</v>
+      </c>
+      <c r="H365" t="inlineStr">
+        <is>
+          <t>대기환경보전법 제94조제3항제11호에 따라 제61조제2항을 위반하여 점검에 따르지 않거나 기피·방해한 자에게는 200만원 이하의 과태료를 부과한다.</t>
+        </is>
+      </c>
+      <c r="I365" t="inlineStr">
+        <is>
+          <t>공회전 제한 위반 과태료 한도보다 한 단계 높다.</t>
+        </is>
+      </c>
+      <c r="J365" t="inlineStr">
+        <is>
+          <t>대기환경보전법 제61조제2항, 제94조제3항제11호</t>
+        </is>
+      </c>
+      <c r="K365" t="inlineStr">
+        <is>
+          <t>2026-10-22</t>
+        </is>
+      </c>
+      <c r="L365" t="inlineStr">
+        <is>
+          <t>자체 작성</t>
+        </is>
+      </c>
+      <c r="M365" t="n">
+        <v>2</v>
+      </c>
+      <c r="O365" t="inlineStr">
+        <is>
+          <t>verified</t>
+        </is>
+      </c>
+      <c r="P365" t="inlineStr">
+        <is>
+          <t>1등 / 2026-10-22</t>
+        </is>
+      </c>
+      <c r="Q365" t="inlineStr">
+        <is>
+          <t>AI 4차 초안(2026-10-21) · 근거 확인 ○: 대기환경보전법 제94조제3항 '200만원 이하의 과태료 ... 11. 제61조제2항을 위반하여 점검에 따르지 아니하거나 기피 또는 방해한 자' 확인. 국가법령정보센터 원문(대기환경보전법, 2026.9.18. 시행)</t>
+        </is>
+      </c>
+    </row>
+    <row r="366">
+      <c r="A366" t="inlineStr">
+        <is>
+          <t>LAW-0365</t>
+        </is>
+      </c>
+      <c r="B366" t="inlineStr">
+        <is>
+          <t>배출가스저감장치를 부착하는 등 저공해 조치를 하고 성능 유지 확인을 받은 자동차는 일정 기간 배출가스 정기검사와 정밀검사를 받지 않아도 된다. 그 기간은?</t>
+        </is>
+      </c>
+      <c r="C366" t="inlineStr">
+        <is>
+          <t>조치를 한 날부터 5년간</t>
+        </is>
+      </c>
+      <c r="D366" t="inlineStr">
+        <is>
+          <t>조치를 한 날부터 1년간</t>
+        </is>
+      </c>
+      <c r="E366" t="inlineStr">
+        <is>
+          <t>조치를 한 날부터 3년간</t>
+        </is>
+      </c>
+      <c r="F366" t="inlineStr">
+        <is>
+          <t>조치를 한 날부터 6개월간</t>
+        </is>
+      </c>
+      <c r="G366" t="n">
+        <v>3</v>
+      </c>
+      <c r="H366" t="inlineStr">
+        <is>
+          <t>대기환경보전법 제60조의2제3항에 따라 성능 유지 확인을 받은 자동차는 조치를 한 날부터 3년간 배출가스 정기검사와 정밀검사를 받지 않아도 된다.</t>
+        </is>
+      </c>
+      <c r="I366" t="inlineStr">
+        <is>
+          <t>새 장치를 단 직후에는 성능이 보장되므로 몇 해 동안 검사를 쉬게 해 준다.</t>
+        </is>
+      </c>
+      <c r="J366" t="inlineStr">
+        <is>
+          <t>대기환경보전법 제60조의2제1항·제3항</t>
+        </is>
+      </c>
+      <c r="K366" t="inlineStr">
+        <is>
+          <t>2026-10-22</t>
+        </is>
+      </c>
+      <c r="L366" t="inlineStr">
+        <is>
+          <t>자체 작성</t>
+        </is>
+      </c>
+      <c r="M366" t="n">
+        <v>1</v>
+      </c>
+      <c r="O366" t="inlineStr">
+        <is>
+          <t>verified</t>
+        </is>
+      </c>
+      <c r="P366" t="inlineStr">
+        <is>
+          <t>1등 / 2026-10-22</t>
+        </is>
+      </c>
+      <c r="Q366" t="inlineStr">
+        <is>
+          <t>AI 4차 초안(2026-10-21) · 근거 확인 ○: 대기환경보전법 제60조의2제3항 '조치를 한 날부터 3년간 제62조제1항에 따른 배출가스 정기검사 및 제63조제1항에 따른 배출가스 정밀검사를 받지 아니하여도 된다' 확인. 국가법령정보센터 원문(대기환경보전법, 2026.9.18. 시행)</t>
+        </is>
+      </c>
+    </row>
+    <row r="367">
+      <c r="A367" t="inlineStr">
+        <is>
+          <t>LAW-0366</t>
+        </is>
+      </c>
+      <c r="B367" t="inlineStr">
+        <is>
+          <t>길가의 건물이나 주차장 등에서 도로로 들어갈 때 차마의 운전자가 해야 할 일로 옳은 것은?</t>
+        </is>
+      </c>
+      <c r="C367" t="inlineStr">
+        <is>
+          <t>경음기를 울려 알린 뒤 빠르게 진입한다</t>
+        </is>
+      </c>
+      <c r="D367" t="inlineStr">
+        <is>
+          <t>일단 정지한 후 안전한지 확인하면서 서행한다</t>
+        </is>
+      </c>
+      <c r="E367" t="inlineStr">
+        <is>
+          <t>비상등을 켜고 멈추지 않고 진입한다</t>
+        </is>
+      </c>
+      <c r="F367" t="inlineStr">
+        <is>
+          <t>도로를 달리는 차가 양보해 줄 것으로 보고 그대로 진입한다</t>
+        </is>
+      </c>
+      <c r="G367" t="n">
+        <v>2</v>
+      </c>
+      <c r="H367" t="inlineStr">
+        <is>
+          <t>도로교통법 제18조제3항에 따라 길가의 건물이나 주차장 등에서 도로에 들어갈 때에는 일단 정지한 후 안전한지 확인하면서 서행해야 한다. 경음기·비상등으로 알리는 것만으로는 확인 의무를 대신할 수 없다.</t>
+        </is>
+      </c>
+      <c r="I367" t="inlineStr">
+        <is>
+          <t>건물이나 주차장에서 나오는 차는 도로 위의 차와 보행자에게 먼저 길을 내어 줘야 하는 입장입니다. 멈춤과 확인을 떠올리세요.</t>
+        </is>
+      </c>
+      <c r="J367" t="inlineStr">
+        <is>
+          <t>도로교통법 제18조제3항</t>
+        </is>
+      </c>
+      <c r="K367" t="inlineStr">
+        <is>
+          <t>2026-10-22</t>
+        </is>
+      </c>
+      <c r="L367" t="inlineStr">
+        <is>
+          <t>자체 작성</t>
+        </is>
+      </c>
+      <c r="M367" t="n">
+        <v>1</v>
+      </c>
+      <c r="O367" t="inlineStr">
+        <is>
+          <t>verified</t>
+        </is>
+      </c>
+      <c r="P367" t="inlineStr">
+        <is>
+          <t>1등 / 2026-10-22</t>
+        </is>
+      </c>
+      <c r="Q367" t="inlineStr">
+        <is>
+          <t>AI 4차 초안(2026-10-21) · 근거 확인 ○: 도로교통법 제18조③ "차마의 운전자는 길가의 건물이나 주차장 등에서 도로에 들어갈 때에는 일단 정지한 후에 안전한지 확인하면서 서행하여야 한다." (2026.10.13 시행 원문 확인)</t>
+        </is>
+      </c>
+    </row>
+    <row r="368">
+      <c r="A368" t="inlineStr">
+        <is>
+          <t>LAW-0367</t>
+        </is>
+      </c>
+      <c r="B368" t="inlineStr">
+        <is>
+          <t>도로교통법령상 자동차에 해서는 안 되는 도색이나 표지에 해당하는 것은?</t>
+        </is>
+      </c>
+      <c r="C368" t="inlineStr">
+        <is>
+          <t>회사 이름과 전화번호를 적재함 옆면에 표시한 것</t>
+        </is>
+      </c>
+      <c r="D368" t="inlineStr">
+        <is>
+          <t>화물자동차 뒷면에 최대적재량을 표시한 것</t>
+        </is>
+      </c>
+      <c r="E368" t="inlineStr">
+        <is>
+          <t>차체 전체를 하나의 밝은 색으로 칠한 것</t>
+        </is>
+      </c>
+      <c r="F368" t="inlineStr">
+        <is>
+          <t>욕설이나 음란한 행위를 묘사해 다른 사람에게 혐오감을 주는 그림</t>
+        </is>
+      </c>
+      <c r="G368" t="n">
+        <v>4</v>
+      </c>
+      <c r="H368" t="inlineStr">
+        <is>
+          <t>도로교통법 제42조와 시행령 제27조는 긴급자동차로 오인할 수 있는 색칠·표지와, 욕설·음란한 행위 묘사 등 다른 사람에게 혐오감을 주는 그림·기호·문자를 금지한다. 회사 이름·적재량 표시나 단색 도색은 이에 해당하지 않는다.</t>
+        </is>
+      </c>
+      <c r="I368" t="inlineStr">
+        <is>
+          <t>다른 운전자를 속이거나 불쾌하게 만드는 표시가 금지 대상입니다.</t>
+        </is>
+      </c>
+      <c r="J368" t="inlineStr">
+        <is>
+          <t>도로교통법 제42조, 도로교통법 시행령 제27조</t>
+        </is>
+      </c>
+      <c r="K368" t="inlineStr">
+        <is>
+          <t>2026-10-22</t>
+        </is>
+      </c>
+      <c r="L368" t="inlineStr">
+        <is>
+          <t>자체 작성</t>
+        </is>
+      </c>
+      <c r="M368" t="n">
+        <v>1</v>
+      </c>
+      <c r="O368" t="inlineStr">
+        <is>
+          <t>verified</t>
+        </is>
+      </c>
+      <c r="P368" t="inlineStr">
+        <is>
+          <t>1등 / 2026-10-22</t>
+        </is>
+      </c>
+      <c r="Q368" t="inlineStr">
+        <is>
+          <t>AI 4차 초안(2026-10-21) · 근거 확인 ○: 도로교통법 제42조① "…긴급자동차와 유사하거나 혐오감을 주는 도색이나 표지 등을 하거나…운전하여서는 아니 된다", 시행령 제27조 "1. 긴급자동차로 오인할 수 있는 색칠 또는 표지 2. 욕설을 표시하거나 음란한 행위를 묘사하는 등 다른 사람에게 혐오감을 주는 그림ㆍ기호 또는 문자" (원문 확인)</t>
+        </is>
+      </c>
+    </row>
+    <row r="369">
+      <c r="A369" t="inlineStr">
+        <is>
+          <t>LAW-0368</t>
+        </is>
+      </c>
+      <c r="B369" t="inlineStr">
+        <is>
+          <t>도로관리청 등의 명령에 따라 도로를 파거나 뚫는 공사를 하려는 공사시행자의 신고에 대한 설명으로 옳은 것은? (긴급히 시공할 필요가 있는 경우 제외)</t>
+        </is>
+      </c>
+      <c r="C369" t="inlineStr">
+        <is>
+          <t>공사시행 3일 전에 관할 경찰서장에게 신고한다</t>
+        </is>
+      </c>
+      <c r="D369" t="inlineStr">
+        <is>
+          <t>공사시행 7일 전에 관할 경찰서장에게 신고한다</t>
+        </is>
+      </c>
+      <c r="E369" t="inlineStr">
+        <is>
+          <t>공사시행 3일 전에 시·도지사에게 신고한다</t>
+        </is>
+      </c>
+      <c r="F369" t="inlineStr">
+        <is>
+          <t>공사를 시작한 후 지체 없이 국토교통부장관에게 신고한다</t>
+        </is>
+      </c>
+      <c r="G369" t="n">
+        <v>1</v>
+      </c>
+      <c r="H369" t="inlineStr">
+        <is>
+          <t>도로교통법 제69조제1항에 따라 공사시행자는 공사시행 3일 전에 일시·공사구간·공사기간·시행방법 등을 관할 경찰서장에게 신고해야 한다. 산사태나 수도관 파열처럼 긴급한 경우에만 안전조치 후 공사를 시작하고 지체 없이 신고할 수 있다.</t>
+        </is>
+      </c>
+      <c r="I369" t="inlineStr">
+        <is>
+          <t>공사로 생길 교통 혼잡에 대비해 현장의 교통 통제·단속을 맡는 기관이 미리 알아야 합니다.</t>
+        </is>
+      </c>
+      <c r="J369" t="inlineStr">
+        <is>
+          <t>도로교통법 제69조제1항</t>
+        </is>
+      </c>
+      <c r="K369" t="inlineStr">
+        <is>
+          <t>2026-10-22</t>
+        </is>
+      </c>
+      <c r="L369" t="inlineStr">
+        <is>
+          <t>자체 작성</t>
+        </is>
+      </c>
+      <c r="M369" t="n">
+        <v>3</v>
+      </c>
+      <c r="O369" t="inlineStr">
+        <is>
+          <t>verified</t>
+        </is>
+      </c>
+      <c r="P369" t="inlineStr">
+        <is>
+          <t>1등 / 2026-10-22</t>
+        </is>
+      </c>
+      <c r="Q369" t="inlineStr">
+        <is>
+          <t>AI 4차 초안(2026-10-21) · 근거 확인 ○: 도로교통법 제69조① "…공사시행자는 공사시행 3일 전에 그 일시, 공사구간, 공사기간 및 시행방법, 그 밖에 필요한 사항을 관할 경찰서장에게 신고하여야 한다. 다만, 산사태나 수도관 파열 등으로 긴급히 시공할 필요가 있는 경우에는…공사를 시작한 후에 지체 없이 신고하여야 한다." (원문 확인)</t>
+        </is>
+      </c>
+    </row>
+    <row r="370">
+      <c r="A370" t="inlineStr">
+        <is>
+          <t>LAW-0369</t>
+        </is>
+      </c>
+      <c r="B370" t="inlineStr">
+        <is>
+          <t>자동차를 운전할 때 운전면허증 대신 지니고 있어도 되는 증명서로 도로교통법에 규정된 것이 아닌 것은?</t>
+        </is>
+      </c>
+      <c r="C370" t="inlineStr">
+        <is>
+          <t>임시운전증명서</t>
+        </is>
+      </c>
+      <c r="D370" t="inlineStr">
+        <is>
+          <t>범칙금 납부통고서</t>
+        </is>
+      </c>
+      <c r="E370" t="inlineStr">
+        <is>
+          <t>자동차등록증</t>
+        </is>
+      </c>
+      <c r="F370" t="inlineStr">
+        <is>
+          <t>출석지시서</t>
+        </is>
+      </c>
+      <c r="G370" t="n">
+        <v>3</v>
+      </c>
+      <c r="H370" t="inlineStr">
+        <is>
+          <t>도로교통법 제92조제1항은 운전면허증등을 갈음하는 증명서로 임시운전증명서, 범칙금 납부통고서 또는 출석지시서, 출석고지서를 정하고 있다. 자동차등록증은 차에 관한 서류일 뿐 운전 자격을 증명하지 못한다.</t>
+        </is>
+      </c>
+      <c r="I370" t="inlineStr">
+        <is>
+          <t>자동차 자체에 관한 서류는 운전하는 사람의 자격을 증명하지 못합니다.</t>
+        </is>
+      </c>
+      <c r="J370" t="inlineStr">
+        <is>
+          <t>도로교통법 제92조제1항</t>
+        </is>
+      </c>
+      <c r="K370" t="inlineStr">
+        <is>
+          <t>2026-10-22</t>
+        </is>
+      </c>
+      <c r="L370" t="inlineStr">
+        <is>
+          <t>자체 작성</t>
+        </is>
+      </c>
+      <c r="M370" t="n">
+        <v>2</v>
+      </c>
+      <c r="O370" t="inlineStr">
+        <is>
+          <t>verified</t>
+        </is>
+      </c>
+      <c r="P370" t="inlineStr">
+        <is>
+          <t>1등 / 2026-10-22</t>
+        </is>
+      </c>
+      <c r="Q370" t="inlineStr">
+        <is>
+          <t>AI 4차 초안(2026-10-21) · 근거 확인 ○: 도로교통법 제92조①제2호 "운전면허증등을 갈음하는 다음 각 목의 증명서 가. 제91조에 따른 임시운전증명서 나. 제138조에 따른 범칙금 납부통고서 또는 출석지시서 다. 제143조제1항에 따른 출석고지서" (원문 확인)</t>
+        </is>
+      </c>
+    </row>
+    <row r="371">
+      <c r="A371" t="inlineStr">
+        <is>
+          <t>LAW-0370</t>
+        </is>
+      </c>
+      <c r="B371" t="inlineStr">
+        <is>
+          <t>도로교통법상 누구든지 교통단속을 회피할 목적으로 해서는 안 되는 행위로 규정된 것은?</t>
+        </is>
+      </c>
+      <c r="C371" t="inlineStr">
+        <is>
+          <t>내비게이션의 단속 카메라 위치 안내 기능을 켜 두는 행위</t>
+        </is>
+      </c>
+      <c r="D371" t="inlineStr">
+        <is>
+          <t>단속 구간에서 제한속도를 지켜 운전하는 행위</t>
+        </is>
+      </c>
+      <c r="E371" t="inlineStr">
+        <is>
+          <t>교통단속용 장비의 기능을 방해하는 장치를 차에 장착하는 행위</t>
+        </is>
+      </c>
+      <c r="F371" t="inlineStr">
+        <is>
+          <t>블랙박스를 설치해 운행 영상을 저장하는 행위</t>
+        </is>
+      </c>
+      <c r="G371" t="n">
+        <v>3</v>
+      </c>
+      <c r="H371" t="inlineStr">
+        <is>
+          <t>도로교통법 제46조의2는 교통단속을 회피할 목적으로 교통단속용 장비의 기능을 방해하는 장치를 제작·수입·판매 또는 장착하는 것을 금지한다. 단속 위치 안내나 블랙박스 설치는 이에 해당하지 않는다.</t>
+        </is>
+      </c>
+      <c r="I371" t="inlineStr">
+        <is>
+          <t>단속 위치를 '알려 주는' 것과 단속 장비 자체를 '무력화'하는 것은 다릅니다.</t>
+        </is>
+      </c>
+      <c r="J371" t="inlineStr">
+        <is>
+          <t>도로교통법 제46조의2</t>
+        </is>
+      </c>
+      <c r="K371" t="inlineStr">
+        <is>
+          <t>2026-10-22</t>
+        </is>
+      </c>
+      <c r="L371" t="inlineStr">
+        <is>
+          <t>자체 작성</t>
+        </is>
+      </c>
+      <c r="M371" t="n">
+        <v>2</v>
+      </c>
+      <c r="O371" t="inlineStr">
+        <is>
+          <t>verified</t>
+        </is>
+      </c>
+      <c r="P371" t="inlineStr">
+        <is>
+          <t>1등 / 2026-10-22</t>
+        </is>
+      </c>
+      <c r="Q371" t="inlineStr">
+        <is>
+          <t>AI 4차 초안(2026-10-21) · 근거 확인 ○: 도로교통법 제46조의2(교통단속용 장비의 기능방해 금지) "누구든지 교통단속을 회피할 목적으로 교통단속용 장비의 기능을 방해하는 장치를 제작ㆍ수입ㆍ판매 또는 장착하여서는 아니 된다." (원문 확인)</t>
+        </is>
+      </c>
+    </row>
+    <row r="372">
+      <c r="A372" t="inlineStr">
+        <is>
+          <t>LAW-0371</t>
+        </is>
+      </c>
+      <c r="B372" t="inlineStr">
+        <is>
+          <t>화물자동차 운수사업법상 운송사업자가 화물자동차 운전자를 채용할 때 기록·관리해야 하는 것으로 옳은 것은?</t>
+        </is>
+      </c>
+      <c r="C372" t="inlineStr">
+        <is>
+          <t>운전경력증명서 발급에 필요한 근무기간 등의 사항</t>
+        </is>
+      </c>
+      <c r="D372" t="inlineStr">
+        <is>
+          <t>운전자 가족의 직업과 재산 상태</t>
+        </is>
+      </c>
+      <c r="E372" t="inlineStr">
+        <is>
+          <t>운전자의 출신 학교와 학업 성적</t>
+        </is>
+      </c>
+      <c r="F372" t="inlineStr">
+        <is>
+          <t>운전자의 개인 신용카드 사용 내역</t>
+        </is>
+      </c>
+      <c r="G372" t="n">
+        <v>1</v>
+      </c>
+      <c r="H372" t="inlineStr">
+        <is>
+          <t>화물자동차 운수사업법 제10조제1항에 따라 운송사업자는 운전자를 채용할 때 근무기간 등 운전경력증명서 발급에 필요한 사항을 기록·관리해야 한다. 협회·연합회(사업자단체)는 이 기록·관리에 필요한 업무를 할 수 있다.</t>
+        </is>
+      </c>
+      <c r="I372" t="inlineStr">
+        <is>
+          <t>운전자가 나중에 다른 회사로 옮기거나 경력을 증명해야 할 때 '얼마나 일했는지'를 확인할 자료가 필요합니다.</t>
+        </is>
+      </c>
+      <c r="J372" t="inlineStr">
+        <is>
+          <t>화물자동차 운수사업법 제10조</t>
+        </is>
+      </c>
+      <c r="K372" t="inlineStr">
+        <is>
+          <t>2026-10-22</t>
+        </is>
+      </c>
+      <c r="L372" t="inlineStr">
+        <is>
+          <t>자체 작성</t>
+        </is>
+      </c>
+      <c r="M372" t="n">
+        <v>2</v>
+      </c>
+      <c r="O372" t="inlineStr">
+        <is>
+          <t>verified</t>
+        </is>
+      </c>
+      <c r="P372" t="inlineStr">
+        <is>
+          <t>1등 / 2026-10-22</t>
+        </is>
+      </c>
+      <c r="Q372" t="inlineStr">
+        <is>
+          <t>AI 4차 초안(2026-10-21) · 근거 확인 ○: 화물자동차 운수사업법 제10조① "운송사업자는 화물자동차의 운전자를 채용할 때에는 근무기간 등 운전경력증명서의 발급을 위하여 필요한 사항을 기록ㆍ관리하여야 한다." ② 사업자단체가 관련 업무 수행 가능 (2026.7.1 시행 원문 확인)</t>
+        </is>
+      </c>
+    </row>
+    <row r="373">
+      <c r="A373" t="inlineStr">
+        <is>
+          <t>LAW-0372</t>
+        </is>
+      </c>
+      <c r="B373" t="inlineStr">
+        <is>
+          <t>화물자동차 운수사업법상 운수사업자의 경영능력 향상을 위해 필요하다고 인정하면 경영을 담당하는 임원에게 경영자 연수교육을 실시할 수 있는 자는?</t>
+        </is>
+      </c>
+      <c r="C373" t="inlineStr">
+        <is>
+          <t>국토교통부장관</t>
+        </is>
+      </c>
+      <c r="D373" t="inlineStr">
+        <is>
+          <t>한국교통안전공단 이사장</t>
+        </is>
+      </c>
+      <c r="E373" t="inlineStr">
+        <is>
+          <t>시장·군수·구청장</t>
+        </is>
+      </c>
+      <c r="F373" t="inlineStr">
+        <is>
+          <t>시·도지사</t>
+        </is>
+      </c>
+      <c r="G373" t="n">
+        <v>4</v>
+      </c>
+      <c r="H373" t="inlineStr">
+        <is>
+          <t>화물자동차 운수사업법 제42조에 따라 시·도지사는 운수사업자의 경영능력 향상을 위해 필요하면 경영을 담당하는 임원(개인이면 운수사업자 본인)에게 경영자 연수교육을 실시할 수 있다.</t>
+        </is>
+      </c>
+      <c r="I373" t="inlineStr">
+        <is>
+          <t>중앙부처나 공단이 아니라 지방자치단체의 장이 실시 주체로 정해져 있습니다.</t>
+        </is>
+      </c>
+      <c r="J373" t="inlineStr">
+        <is>
+          <t>화물자동차 운수사업법 제42조</t>
+        </is>
+      </c>
+      <c r="K373" t="inlineStr">
+        <is>
+          <t>2026-10-22</t>
+        </is>
+      </c>
+      <c r="L373" t="inlineStr">
+        <is>
+          <t>자체 작성</t>
+        </is>
+      </c>
+      <c r="M373" t="n">
+        <v>3</v>
+      </c>
+      <c r="O373" t="inlineStr">
+        <is>
+          <t>verified</t>
+        </is>
+      </c>
+      <c r="P373" t="inlineStr">
+        <is>
+          <t>1등 / 2026-10-22</t>
+        </is>
+      </c>
+      <c r="Q373" t="inlineStr">
+        <is>
+          <t>AI 4차 초안(2026-10-21) · 근거 확인 ○: 화물자동차 운수사업법 제42조(경영자 연수교육) "시ㆍ도지사는 운수사업자의 경영능력 향상을 위하여 필요하다고 인정하면 경영을 담당하는 임원(개인인 경우에는 운수사업자를 말한다)에게 경영자 연수교육을 실시할 수 있다." (원문 확인)</t>
+        </is>
+      </c>
+    </row>
+    <row r="374">
+      <c r="A374" t="inlineStr">
+        <is>
+          <t>LAW-0373</t>
+        </is>
+      </c>
+      <c r="B374" t="inlineStr">
+        <is>
+          <t>화물자동차 운수사업법상 국가가 사업자단체나 운수사업자 등에게 재정적 지원을 할 수 있는 사업으로 규정된 것이 아닌 것은?</t>
+        </is>
+      </c>
+      <c r="C374" t="inlineStr">
+        <is>
+          <t>공동차고지 및 공영차고지 건설</t>
+        </is>
+      </c>
+      <c r="D374" t="inlineStr">
+        <is>
+          <t>운전자 개인의 주택 구입</t>
+        </is>
+      </c>
+      <c r="E374" t="inlineStr">
+        <is>
+          <t>낡은 차량의 대체</t>
+        </is>
+      </c>
+      <c r="F374" t="inlineStr">
+        <is>
+          <t>화물자동차 휴게소의 건설</t>
+        </is>
+      </c>
+      <c r="G374" t="n">
+        <v>2</v>
+      </c>
+      <c r="H374" t="inlineStr">
+        <is>
+          <t>화물자동차 운수사업법 제43조제1항은 공동차고지·공영차고지 건설, 운수사업의 정보화, 낡은 차량의 대체, 친환경 화물자동차 전환, 화물자동차 휴게소 건설, 서비스 향상을 위한 시설·장비 확충 등을 재정지원 대상으로 정한다. 운전자 개인의 주택 구입은 포함되지 않는다.</t>
+        </is>
+      </c>
+      <c r="I374" t="inlineStr">
+        <is>
+          <t>법이 지원하는 것은 운수사업 운영에 필요한 시설·차량·정보화 투자입니다.</t>
+        </is>
+      </c>
+      <c r="J374" t="inlineStr">
+        <is>
+          <t>화물자동차 운수사업법 제43조제1항</t>
+        </is>
+      </c>
+      <c r="K374" t="inlineStr">
+        <is>
+          <t>2026-10-22</t>
+        </is>
+      </c>
+      <c r="L374" t="inlineStr">
+        <is>
+          <t>자체 작성</t>
+        </is>
+      </c>
+      <c r="M374" t="n">
+        <v>2</v>
+      </c>
+      <c r="O374" t="inlineStr">
+        <is>
+          <t>verified</t>
+        </is>
+      </c>
+      <c r="P374" t="inlineStr">
+        <is>
+          <t>1등 / 2026-10-22</t>
+        </is>
+      </c>
+      <c r="Q374" t="inlineStr">
+        <is>
+          <t>AI 4차 초안(2026-10-21) · 근거 확인 ○: 화물자동차 운수사업법 제43조① "1. 공동차고지 및 공영차고지 건설 2. 화물자동차 운수사업의 정보화 3. 낡은 차량의 대체 4. 연료비가 절감되거나 환경친화적인 화물자동차 등으로의 전환… 5. 화물자동차 휴게소의 건설 6. …서비스 향상을 위한 시설ㆍ장비의 확충과 개선" (원문 확인)</t>
+        </is>
+      </c>
+    </row>
+    <row r="375">
+      <c r="A375" t="inlineStr">
+        <is>
+          <t>LAW-0374</t>
+        </is>
+      </c>
+      <c r="B375" t="inlineStr">
+        <is>
+          <t>도로법상 도로관리청 등이 구간을 정하여 도로의 통행을 금지하거나 제한할 수 있는 경우로 규정된 것이 아닌 것은?</t>
+        </is>
+      </c>
+      <c r="C375" t="inlineStr">
+        <is>
+          <t>출퇴근 시간대에 교통량이 평소보다 많아진 경우</t>
+        </is>
+      </c>
+      <c r="D375" t="inlineStr">
+        <is>
+          <t>도로에 관련된 공사로 부득이한 경우</t>
+        </is>
+      </c>
+      <c r="E375" t="inlineStr">
+        <is>
+          <t>도로가 파손되어 통행이 위험하다고 인정되는 경우</t>
+        </is>
+      </c>
+      <c r="F375" t="inlineStr">
+        <is>
+          <t>폭설·태풍 등 재해로 통행이 위험하거나 교통이 장시간 마비될 우려가 있는 경우</t>
+        </is>
+      </c>
+      <c r="G375" t="n">
+        <v>1</v>
+      </c>
+      <c r="H375" t="inlineStr">
+        <is>
+          <t>도로법 제76조제1항은 도로 관련 공사로 부득이한 경우, 도로 파손 등으로 통행이 위험한 경우, 천재지변 등 재해로 통행이 위험하거나 교통이 장시간 마비될 우려가 있는 경우에 통행을 금지·제한할 수 있게 한다. 단순한 교통량 증가는 사유가 아니다.</t>
+        </is>
+      </c>
+      <c r="I375" t="inlineStr">
+        <is>
+          <t>도로 자체의 공사·파손이나 재해처럼 통행이 '위험한' 사정이 기준입니다.</t>
+        </is>
+      </c>
+      <c r="J375" t="inlineStr">
+        <is>
+          <t>도로법 제76조제1항</t>
+        </is>
+      </c>
+      <c r="K375" t="inlineStr">
+        <is>
+          <t>2026-10-22</t>
+        </is>
+      </c>
+      <c r="L375" t="inlineStr">
+        <is>
+          <t>자체 작성</t>
+        </is>
+      </c>
+      <c r="M375" t="n">
+        <v>2</v>
+      </c>
+      <c r="O375" t="inlineStr">
+        <is>
+          <t>verified</t>
+        </is>
+      </c>
+      <c r="P375" t="inlineStr">
+        <is>
+          <t>1등 / 2026-10-22</t>
+        </is>
+      </c>
+      <c r="Q375" t="inlineStr">
+        <is>
+          <t>AI 4차 초안(2026-10-21) · 근거 확인 ○: 도로법 제76조①(2026.3.17 개정) "도로관리청, 한국도로공사 또는 민자도로 관리자는…1. 도로에 관련된 공사로 인하여 부득이한 경우 2. 도로가 파손되거나 그 밖의 사유로 통행이 위험하다고 인정되는 경우 3. 지진, 홍수, 폭설, 태풍 등 천재지변이나…교통이 장시간 마비될 우려가 있는 경우" (2026.9.18 시행 원문 확인)</t>
+        </is>
+      </c>
+    </row>
+    <row r="376">
+      <c r="A376" t="inlineStr">
+        <is>
+          <t>LAW-0375</t>
+        </is>
+      </c>
+      <c r="B376" t="inlineStr">
+        <is>
+          <t>도로법상 임차한 화물적재 차량이 차량 운행제한을 위반하여 운행되지 않도록 관리해야 하는 자로 규정된 것은?</t>
+        </is>
+      </c>
+      <c r="C376" t="inlineStr">
+        <is>
+          <t>차량을 빌려준 임대인(차량 소유자)</t>
+        </is>
+      </c>
+      <c r="D376" t="inlineStr">
+        <is>
+          <t>해당 도로를 관리하는 도로관리청</t>
+        </is>
+      </c>
+      <c r="E376" t="inlineStr">
+        <is>
+          <t>차량 임대차계약의 임차인으로서 차량의 화물적재를 사실상 관리하는 자</t>
+        </is>
+      </c>
+      <c r="F376" t="inlineStr">
+        <is>
+          <t>해당 차량을 마지막으로 정비한 자동차정비업자</t>
+        </is>
+      </c>
+      <c r="G376" t="n">
+        <v>3</v>
+      </c>
+      <c r="H376" t="inlineStr">
+        <is>
+          <t>도로법 제77조제2항에 따라 차량 임대차계약의 임차인으로서 화물적재를 사실상 관리하는 자는 임차한 차량이 운행제한을 위반하여 운행되지 않도록 관리해야 한다. 건설공사에 쓰이는 차량은 수급인·하수급인 또는 시공 참여자가 임차인에 해당한다.</t>
+        </is>
+      </c>
+      <c r="I376" t="inlineStr">
+        <is>
+          <t>서류상 차 주인보다, 차를 빌려 실제로 짐을 싣게 하는 쪽을 생각해 보세요.</t>
+        </is>
+      </c>
+      <c r="J376" t="inlineStr">
+        <is>
+          <t>도로법 제77조제2항</t>
+        </is>
+      </c>
+      <c r="K376" t="inlineStr">
+        <is>
+          <t>2026-10-22</t>
+        </is>
+      </c>
+      <c r="L376" t="inlineStr">
+        <is>
+          <t>자체 작성</t>
+        </is>
+      </c>
+      <c r="M376" t="n">
+        <v>3</v>
+      </c>
+      <c r="O376" t="inlineStr">
+        <is>
+          <t>verified</t>
+        </is>
+      </c>
+      <c r="P376" t="inlineStr">
+        <is>
+          <t>1등 / 2026-10-22</t>
+        </is>
+      </c>
+      <c r="Q376" t="inlineStr">
+        <is>
+          <t>AI 4차 초안(2026-10-21) · 근거 확인 ○: 도로법 제77조② "차량 임대차계약의 임차인(「건설산업기본법」에 따른 건설공사에 사용되는 차량의 경우 수급인ㆍ하수급인 또는 시공 참여자를 말한다…)으로서 차량의 화물적재를 사실상 관리하는 자는 임차한 화물적재 차량이 제1항에 따른 운행제한을 위반하여 운행되지 아니하도록 관리하여야 한다." (원문 확인)</t>
         </is>
       </c>
     </row>
